--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -1265,13 +1265,13 @@
         <v>131.15</v>
       </c>
       <c r="H5" s="2">
-        <v>149.51999999999998</v>
+        <v>149.38</v>
       </c>
       <c r="I5" s="2">
-        <v>171.4</v>
+        <v>171.12</v>
       </c>
       <c r="J5" s="2">
-        <v>197.52</v>
+        <v>197.08</v>
       </c>
     </row>
     <row r="6">
@@ -1333,13 +1333,13 @@
         <v>67.59</v>
       </c>
       <c r="H7" s="4">
-        <v>77.57</v>
+        <v>77.70999999999998</v>
       </c>
       <c r="I7" s="4">
-        <v>89.46000000000001</v>
+        <v>89.74000000000001</v>
       </c>
       <c r="J7" s="4">
-        <v>103.63999999999996</v>
+        <v>104.07999999999996</v>
       </c>
     </row>
     <row r="8">
@@ -1367,13 +1367,13 @@
         <v>34.009258327463016</v>
       </c>
       <c r="H8" s="2">
-        <v>34.158263243647895</v>
+        <v>34.21991280989916</v>
       </c>
       <c r="I8" s="2">
-        <v>34.29425745610673</v>
+        <v>34.40159472513992</v>
       </c>
       <c r="J8" s="2">
-        <v>34.41360074379067</v>
+        <v>34.559702483729566</v>
       </c>
     </row>
     <row r="9">
@@ -1392,19 +1392,19 @@
         <v>36.5</v>
       </c>
       <c r="E9" s="2">
-        <v>28.43</v>
+        <v>28.419999999999998</v>
       </c>
       <c r="F9" s="2">
-        <v>38.800000000000004</v>
+        <v>38.78</v>
       </c>
       <c r="G9" s="2">
-        <v>49.17</v>
+        <v>49.15</v>
       </c>
       <c r="H9" s="2">
-        <v>53.1</v>
+        <v>53.08</v>
       </c>
       <c r="I9" s="2">
-        <v>57.48</v>
+        <v>57.47</v>
       </c>
       <c r="J9" s="2">
         <v>62.43</v>
@@ -1698,22 +1698,22 @@
         <v>11.5</v>
       </c>
       <c r="E18" s="4">
-        <v>8.990000000000002</v>
+        <v>9.000000000000004</v>
       </c>
       <c r="F18" s="4">
-        <v>13.679999999999993</v>
+        <v>13.699999999999996</v>
       </c>
       <c r="G18" s="4">
-        <v>18.42</v>
+        <v>18.440000000000005</v>
       </c>
       <c r="H18" s="4">
-        <v>24.469999999999985</v>
+        <v>24.629999999999974</v>
       </c>
       <c r="I18" s="4">
-        <v>31.980000000000004</v>
+        <v>32.27</v>
       </c>
       <c r="J18" s="4">
-        <v>41.20999999999996</v>
+        <v>41.649999999999956</v>
       </c>
     </row>
     <row r="19">
@@ -1732,22 +1732,22 @@
         <v>7.666666666666666</v>
       </c>
       <c r="E19" s="2">
-        <v>7.969858156028371</v>
+        <v>7.978723404255322</v>
       </c>
       <c r="F19" s="2">
-        <v>8.785562905401061</v>
+        <v>8.79840729561364</v>
       </c>
       <c r="G19" s="2">
-        <v>9.26839086243333</v>
+        <v>9.278454261849655</v>
       </c>
       <c r="H19" s="2">
-        <v>10.77546347263199</v>
+        <v>10.84592011977629</v>
       </c>
       <c r="I19" s="2">
-        <v>12.259449513148816</v>
+        <v>12.370620256076057</v>
       </c>
       <c r="J19" s="2">
-        <v>13.683756142914053</v>
+        <v>13.829857882852956</v>
       </c>
     </row>
     <row r="20">
@@ -1766,22 +1766,22 @@
         <v>11.5</v>
       </c>
       <c r="E20" s="4">
-        <v>8.990000000000002</v>
+        <v>9.000000000000004</v>
       </c>
       <c r="F20" s="4">
-        <v>13.679999999999993</v>
+        <v>13.699999999999996</v>
       </c>
       <c r="G20" s="4">
-        <v>18.42</v>
+        <v>18.440000000000005</v>
       </c>
       <c r="H20" s="4">
-        <v>24.469999999999985</v>
+        <v>24.629999999999974</v>
       </c>
       <c r="I20" s="4">
-        <v>31.980000000000004</v>
+        <v>32.27</v>
       </c>
       <c r="J20" s="4">
-        <v>41.20999999999996</v>
+        <v>41.649999999999956</v>
       </c>
     </row>
   </sheetData>
@@ -2959,17 +2959,17 @@
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.84 % / 補助 65 % / 他 67.33 %</t>
+          <t xml:space="preserve">全社 65.78 % / 補助 65 % / 他 67.16 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.71 % / 補助 65 % / 他 67.16 %</t>
+          <t xml:space="preserve">全社 65.6 % / 補助 65 % / 他 66.83 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.59 % / 補助 65 % / 他 67 %</t>
+          <t xml:space="preserve">全社 65.44 % / 補助 65 % / 他 66.5 %</t>
         </is>
       </c>
     </row>
@@ -3021,17 +3021,17 @@
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.16 % / 補助 35 % / 他 32.67 %</t>
+          <t xml:space="preserve">全社 34.22 % / 補助 35 % / 他 32.84 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.29 % / 補助 35 % / 他 32.84 %</t>
+          <t xml:space="preserve">全社 34.4 % / 補助 35 % / 他 33.17 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.41 % / 補助 35 % / 他 33 %</t>
+          <t xml:space="preserve">全社 34.56 % / 補助 35 % / 他 33.5 %</t>
         </is>
       </c>
     </row>
@@ -3068,27 +3068,27 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.2 % / 補助 24.25 % / 他 25.73 %</t>
+          <t xml:space="preserve">全社 25.2 % / 補助 24.25 % / 他 25.71 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.92 % / 補助 24.25 % / 他 25.62 %</t>
+          <t xml:space="preserve">全社 24.91 % / 補助 24.25 % / 他 25.6 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.74 % / 補助 24.25 % / 他 25.49 %</t>
+          <t xml:space="preserve">全社 24.73 % / 補助 24.25 % / 他 25.46 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.38 % / 補助 22.25 % / 他 25.39 %</t>
+          <t xml:space="preserve">全社 23.37 % / 補助 22.25 % / 他 25.36 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.03 % / 補助 20.46 % / 他 25.28 %</t>
+          <t xml:space="preserve">全社 22.03 % / 補助 20.46 % / 他 25.27 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
@@ -3130,32 +3130,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.97 % / 補助 10.75 % / 他 6.44 %</t>
+          <t xml:space="preserve">全社 7.98 % / 補助 10.75 % / 他 6.46 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.79 % / 補助 10.75 % / 他 6.71 %</t>
+          <t xml:space="preserve">全社 8.8 % / 補助 10.75 % / 他 6.74 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.27 % / 補助 10.75 % / 他 7.01 %</t>
+          <t xml:space="preserve">全社 9.28 % / 補助 10.75 % / 他 7.04 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.78 % / 補助 12.75 % / 他 7.28 %</t>
+          <t xml:space="preserve">全社 10.85 % / 補助 12.75 % / 他 7.47 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.26 % / 補助 14.54 % / 他 7.56 %</t>
+          <t xml:space="preserve">全社 12.37 % / 補助 14.54 % / 他 7.9 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.68 % / 補助 16.13 % / 他 7.81 %</t>
+          <t xml:space="preserve">全社 13.83 % / 補助 16.13 % / 他 8.31 %</t>
         </is>
       </c>
     </row>
@@ -3192,32 +3192,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.22 % / 補助 16.18 % / 他 8.5 %</t>
+          <t xml:space="preserve">全社 11.23 % / 補助 16.18 % / 他 8.52 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.53 % / 補助 16.16 % / 他 8.69 %</t>
+          <t xml:space="preserve">全社 12.54 % / 補助 16.16 % / 他 8.72 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.29 % / 補助 16.17 % / 他 8.92 %</t>
+          <t xml:space="preserve">全社 13.3 % / 補助 16.17 % / 他 8.94 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.3 % / 補助 17.22 % / 他 9.11 %</t>
+          <t xml:space="preserve">全社 14.37 % / 補助 17.22 % / 他 9.31 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.33 % / 補助 18.24 % / 他 9.32 %</t>
+          <t xml:space="preserve">全社 15.44 % / 補助 18.24 % / 他 9.66 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 16.34 % / 補助 19.19 % / 他 9.51 %</t>
+          <t xml:space="preserve">全社 16.49 % / 補助 19.19 % / 他 10 %</t>
         </is>
       </c>
     </row>
@@ -3254,27 +3254,27 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.82 % / 補助 10 % / 他 11.28 %</t>
+          <t xml:space="preserve">全社 10.82 % / 補助 10 % / 他 11.26 %</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.55 % / 補助 10 % / 他 11.12 %</t>
+          <t xml:space="preserve">全社 10.53 % / 補助 10 % / 他 11.09 %</t>
         </is>
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.38 % / 補助 10 % / 他 10.96 %</t>
+          <t xml:space="preserve">全社 10.37 % / 補助 10 % / 他 10.93 %</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.08 % / 補助 9.67 % / 他 10.81 %</t>
+          <t xml:space="preserve">全社 10.07 % / 補助 9.67 % / 他 10.78 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.76 % / 補助 9.33 % / 他 10.65 %</t>
+          <t xml:space="preserve">全社 9.76 % / 補助 9.33 % / 他 10.64 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
@@ -3750,32 +3750,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.78 % / 補助 35.3 % / 他 59.3 %</t>
+          <t xml:space="preserve">全社 49.76 % / 補助 35.3 % / 他 59.26 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.9 % / 補助 35.35 % / 他 59.03 %</t>
+          <t xml:space="preserve">全社 45.87 % / 補助 35.35 % / 他 58.96 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 43.74 % / 補助 35.33 % / 他 58.61 %</t>
+          <t xml:space="preserve">全社 43.72 % / 補助 35.33 % / 他 58.54 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 40.62 % / 補助 32 % / 他 58.32 %</t>
+          <t xml:space="preserve">全社 40.5 % / 補助 32 % / 他 57.81 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 37.52 % / 補助 28.94 % / 他 57.99 %</t>
+          <t xml:space="preserve">全社 37.35 % / 補助 28.94 % / 他 57.11 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.57 % / 補助 26.21 % / 他 57.75 %</t>
+          <t xml:space="preserve">全社 34.37 % / 補助 26.21 % / 他 56.5 %</t>
         </is>
       </c>
     </row>
@@ -3951,17 +3951,17 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.096 億円/人 / 補助 0.155 億円/人 / 他 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.097 億円/人 / 補助 0.155 億円/人 / 他 0.045 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.123 億円/人 / 補助 0.205 億円/人 / 他 0.047 億円/人</t>
+          <t xml:space="preserve">全社 0.124 億円/人 / 補助 0.205 億円/人 / 他 0.049 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.154 億円/人 / 補助 0.265 億円/人 / 他 0.05 億円/人</t>
+          <t xml:space="preserve">全社 0.156 億円/人 / 補助 0.265 億円/人 / 他 0.053 億円/人</t>
         </is>
       </c>
     </row>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.168 億円/人 / 補助 0.254 億円/人 / 他 0.118 億円/人</t>
+          <t xml:space="preserve">全社 0.168 億円/人 / 補助 0.254 億円/人 / 他 0.119 億円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
@@ -4013,17 +4013,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.21 億円/人 / 補助 0.302 億円/人 / 他 0.129 億円/人</t>
+          <t xml:space="preserve">全社 0.211 億円/人 / 補助 0.302 億円/人 / 他 0.131 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.241 億円/人 / 補助 0.357 億円/人 / 他 0.135 億円/人</t>
+          <t xml:space="preserve">全社 0.242 億円/人 / 補助 0.357 億円/人 / 他 0.137 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.276 億円/人 / 補助 0.421 億円/人 / 他 0.141 億円/人</t>
+          <t xml:space="preserve">全社 0.278 億円/人 / 補助 0.421 億円/人 / 他 0.144 億円/人</t>
         </is>
       </c>
     </row>
@@ -4437,27 +4437,27 @@
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.35 倍 / 補助 2.99 倍 / 他 4.39 倍</t>
+          <t xml:space="preserve">全社 3.35 倍 / 補助 2.99 倍 / 他 4.4 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.3 倍 / 補助 2.98 倍 / 他 4.68 倍</t>
+          <t xml:space="preserve">全社 3.31 倍 / 補助 2.98 倍 / 他 4.69 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.06 倍 / 補助 3.85 倍 / 他 4.97 倍</t>
+          <t xml:space="preserve">全社 4.08 倍 / 補助 3.85 倍 / 他 5.08 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5 倍 / 補助 4.93 倍 / 他 5.29 倍</t>
+          <t xml:space="preserve">全社 5.03 倍 / 補助 4.93 倍 / 他 5.49 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.15 倍 / 補助 6.28 倍 / 他 5.61 倍</t>
+          <t xml:space="preserve">全社 6.21 倍 / 補助 6.28 倍 / 他 5.91 倍</t>
         </is>
       </c>
     </row>
@@ -4757,17 +4757,17 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2.33 pt</t>
+          <t xml:space="preserve">差 -2.16 pt</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2.16 pt</t>
+          <t xml:space="preserve">差 -1.83 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2 pt</t>
+          <t xml:space="preserve">差 -1.5 pt</t>
         </is>
       </c>
     </row>
@@ -4804,32 +4804,32 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.31 pt</t>
+          <t xml:space="preserve">差 4.29 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.04 pt</t>
+          <t xml:space="preserve">差 4.01 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.74 pt</t>
+          <t xml:space="preserve">差 3.71 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 5.47 pt</t>
+          <t xml:space="preserve">差 5.27 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.98 pt</t>
+          <t xml:space="preserve">差 6.64 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 8.32 pt</t>
+          <t xml:space="preserve">差 7.82 pt</t>
         </is>
       </c>
     </row>
@@ -4990,12 +4990,12 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 115.54 %</t>
+          <t xml:space="preserve">寄与率 116 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 91.68 %</t>
+          <t xml:space="preserve">寄与率 91.49 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
@@ -5005,17 +5005,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 92.73 %</t>
+          <t xml:space="preserve">寄与率 90.63 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 93.61 %</t>
+          <t xml:space="preserve">寄与率 92.02 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 94.8 %</t>
+          <t xml:space="preserve">寄与率 93.28 %</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5193,110 +5193,110 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">その他事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C10" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="D10" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 売上成長率</t>
+          <t xml:space="preserve">その他事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="C11" s="2">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="D11" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">その他事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B12" s="2">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2">
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>-15</v>
-      </c>
       <c r="D12" s="2">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 原価率改善ポイント</t>
+          <t xml:space="preserve">その他事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B13" s="2">
         <v>1</v>
       </c>
       <c r="C13" s="2">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="D13" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">その他事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>7.000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="C14" s="2">
-        <v>4.5</v>
+        <v>-15</v>
       </c>
       <c r="D14" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C15" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="D15" s="2">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">その他事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="D16" s="2">
         <v>20</v>
@@ -5305,30 +5305,30 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="2">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="D17" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">その他事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2">
-        <v>4</v>
+        <v>-15</v>
       </c>
       <c r="D18" s="2">
         <v>25</v>
@@ -5337,104 +5337,184 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>10.5</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C19" s="2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D19" s="2">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">その他事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
       </c>
       <c r="D20" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新規投資の耐用年数</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>10</v>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C21" s="2">
+        <v>-3</v>
+      </c>
+      <c r="D21" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業投資額</t>
+          <t xml:space="preserve">その他事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>45</v>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C22" s="2">
+        <v>-5</v>
+      </c>
+      <c r="D22" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">申請補助金額</t>
+          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">その他事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B24" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="C24" s="2">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B25" s="2">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新規投資の耐用年数</t>
+        </is>
+      </c>
+      <c r="B26" s="2">
+        <v>10</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業投資額</t>
+        </is>
+      </c>
+      <c r="B27" s="2">
+        <v>45</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申請補助金額</t>
+        </is>
+      </c>
+      <c r="B28" s="2">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">ローカルベンチマーク</t>
         </is>
       </c>
-      <c r="B24" s="2">
+      <c r="B29" s="2">
         <v>23</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C29" s="2">
         <v>0</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D29" s="2">
         <v>100</v>
       </c>
     </row>
@@ -5460,7 +5540,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjEsIm90aGVyU2FsZXNHcm93dGgiOjAuMDQsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAxLCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wNCwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDEsInByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJvdGhlclNnYVJhdGVFbmQiOjAuMTA1LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjQ1LCJzdWJzaWR5IjoxNSwibG9jYWxCZW5jaG1hcmsiOjIzfSwiZHJpdmVyUmFuZ2VzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOlstMC4wNSwwLjNdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjRdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbLTAuMTUsMC4yNV0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbLTAuMTUsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbLTAuMTUsMC4yNV0sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbLTAuMTUsMC4yNV0sInByb2plY3RQYXlHcm93dGgiOlswLjA0NSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlstMC4wMywwLjJdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6Wy0wLjA1LDAuMV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wNCwwLjI1XSwib3RoZXJTZ2FSYXRlRW5kIjpbMC4wNCwwLjI1XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLDAuMV0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MTUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MjguMSwibWF4Ijo1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjMuOSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAuMSwibWF4IjowLjIsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MzAsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIn0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNCwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMDksIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbLTAuMTUsMC4yNV0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbLTAuMTUsMC4yNV0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlstMC4xNSwwLjI1XSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlstMC4xNSwwLjI1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoxNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjcwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoyOC4xLCJtYXgiOjUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6My45LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MC4xLCJtYXgiOjAuMiwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnt9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIifQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <v>14.860490791493142</v>
+        <v>15.187557062867052</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
@@ -217,7 +217,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>102.41999999999996</v>
+        <v>105</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -269,7 +269,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>70.59038384911676</v>
+        <v>69.99078158951735</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -1195,13 +1195,13 @@
         <v>198.74</v>
       </c>
       <c r="H3" s="4">
-        <v>227.08999999999997</v>
+        <v>227.88</v>
       </c>
       <c r="I3" s="4">
-        <v>260.86</v>
+        <v>262.5</v>
       </c>
       <c r="J3" s="4">
-        <v>301.15999999999997</v>
+        <v>303.74</v>
       </c>
     </row>
     <row r="4">
@@ -1231,13 +1231,13 @@
         <v>27.63470554235441</v>
       </c>
       <c r="H4" s="2">
-        <v>14.26486867263761</v>
+        <v>14.66237294958237</v>
       </c>
       <c r="I4" s="2">
-        <v>14.870756087894677</v>
+        <v>15.192206424433907</v>
       </c>
       <c r="J4" s="2">
-        <v>15.4488997929924</v>
+        <v>15.710476190476186</v>
       </c>
     </row>
     <row r="5">
@@ -1265,13 +1265,13 @@
         <v>131.15</v>
       </c>
       <c r="H5" s="2">
-        <v>149.38</v>
+        <v>149.91</v>
       </c>
       <c r="I5" s="2">
-        <v>171.12</v>
+        <v>172.22</v>
       </c>
       <c r="J5" s="2">
-        <v>197.08</v>
+        <v>198.8</v>
       </c>
     </row>
     <row r="6">
@@ -1333,13 +1333,13 @@
         <v>67.59</v>
       </c>
       <c r="H7" s="4">
-        <v>77.70999999999998</v>
+        <v>77.97</v>
       </c>
       <c r="I7" s="4">
-        <v>89.74000000000001</v>
+        <v>90.28</v>
       </c>
       <c r="J7" s="4">
-        <v>104.07999999999996</v>
+        <v>104.94</v>
       </c>
     </row>
     <row r="8">
@@ -1367,13 +1367,13 @@
         <v>34.009258327463016</v>
       </c>
       <c r="H8" s="2">
-        <v>34.21991280989916</v>
+        <v>34.215376513954716</v>
       </c>
       <c r="I8" s="2">
-        <v>34.40159472513992</v>
+        <v>34.392380952380954</v>
       </c>
       <c r="J8" s="2">
-        <v>34.559702483729566</v>
+        <v>34.549285573187596</v>
       </c>
     </row>
     <row r="9">
@@ -1401,13 +1401,13 @@
         <v>49.15</v>
       </c>
       <c r="H9" s="2">
-        <v>53.08</v>
+        <v>53.13</v>
       </c>
       <c r="I9" s="2">
-        <v>57.47</v>
+        <v>57.56999999999999</v>
       </c>
       <c r="J9" s="2">
-        <v>62.43</v>
+        <v>62.57</v>
       </c>
     </row>
     <row r="10">
@@ -1435,13 +1435,13 @@
         <v>1.27</v>
       </c>
       <c r="H10" s="2">
-        <v>1.3399999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="I10" s="2">
-        <v>1.4</v>
+        <v>1.4100000000000001</v>
       </c>
       <c r="J10" s="2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="11">
@@ -1469,13 +1469,13 @@
         <v>1.27</v>
       </c>
       <c r="H11" s="2">
-        <v>1.3399999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="I11" s="2">
-        <v>1.4</v>
+        <v>1.4100000000000001</v>
       </c>
       <c r="J11" s="2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="12">
@@ -1537,13 +1537,13 @@
         <v>19.27</v>
       </c>
       <c r="H13" s="2">
-        <v>20.87</v>
+        <v>20.96</v>
       </c>
       <c r="I13" s="2">
-        <v>22.61</v>
+        <v>22.810000000000002</v>
       </c>
       <c r="J13" s="2">
-        <v>24.53</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="14">
@@ -1571,13 +1571,13 @@
         <v>19.27</v>
       </c>
       <c r="H14" s="2">
-        <v>20.87</v>
+        <v>20.96</v>
       </c>
       <c r="I14" s="2">
-        <v>22.61</v>
+        <v>22.810000000000002</v>
       </c>
       <c r="J14" s="2">
-        <v>24.53</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="15">
@@ -1707,13 +1707,13 @@
         <v>18.440000000000005</v>
       </c>
       <c r="H18" s="4">
-        <v>24.629999999999974</v>
+        <v>24.839999999999996</v>
       </c>
       <c r="I18" s="4">
-        <v>32.27</v>
+        <v>32.71000000000001</v>
       </c>
       <c r="J18" s="4">
-        <v>41.649999999999956</v>
+        <v>42.36999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1741,13 +1741,13 @@
         <v>9.278454261849655</v>
       </c>
       <c r="H19" s="2">
-        <v>10.84592011977629</v>
+        <v>10.900473933649288</v>
       </c>
       <c r="I19" s="2">
-        <v>12.370620256076057</v>
+        <v>12.460952380952383</v>
       </c>
       <c r="J19" s="2">
-        <v>13.829857882852956</v>
+        <v>13.949430433923746</v>
       </c>
     </row>
     <row r="20">
@@ -1775,13 +1775,13 @@
         <v>18.440000000000005</v>
       </c>
       <c r="H20" s="4">
-        <v>24.629999999999974</v>
+        <v>24.839999999999996</v>
       </c>
       <c r="I20" s="4">
-        <v>32.27</v>
+        <v>32.71000000000001</v>
       </c>
       <c r="J20" s="4">
-        <v>41.649999999999956</v>
+        <v>42.36999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2013,13 +2013,13 @@
         <v>60.38039649793701</v>
       </c>
       <c r="H5" s="2">
-        <v>63.93940728345589</v>
+        <v>63.717746182201154</v>
       </c>
       <c r="I5" s="2">
-        <v>67.35030284443762</v>
+        <v>66.9295238095238</v>
       </c>
       <c r="J5" s="2">
-        <v>70.59038384911676</v>
+        <v>69.99078158951735</v>
       </c>
     </row>
     <row r="6">
@@ -2897,17 +2897,17 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.26 % / 補助 21 % / 他 4 %</t>
+          <t xml:space="preserve">全社 14.66 % / 補助 21 % / 他 5 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.87 % / 補助 21 % / 他 4.01 %</t>
+          <t xml:space="preserve">全社 15.19 % / 補助 21 % / 他 5 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.45 % / 補助 21 % / 他 3.99 %</t>
+          <t xml:space="preserve">全社 15.71 % / 補助 21 % / 他 5 %</t>
         </is>
       </c>
     </row>
@@ -2964,12 +2964,12 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.6 % / 補助 65 % / 他 66.83 %</t>
+          <t xml:space="preserve">全社 65.61 % / 補助 65 % / 他 66.84 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.44 % / 補助 65 % / 他 66.5 %</t>
+          <t xml:space="preserve">全社 65.45 % / 補助 65 % / 他 66.51 %</t>
         </is>
       </c>
     </row>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.4 % / 補助 35 % / 他 33.17 %</t>
+          <t xml:space="preserve">全社 34.39 % / 補助 35 % / 他 33.16 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.56 % / 補助 35 % / 他 33.5 %</t>
+          <t xml:space="preserve">全社 34.55 % / 補助 35 % / 他 33.49 %</t>
         </is>
       </c>
     </row>
@@ -3083,17 +3083,17 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.37 % / 補助 22.25 % / 他 25.36 %</t>
+          <t xml:space="preserve">全社 23.31 % / 補助 22.25 % / 他 25.18 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.03 % / 補助 20.46 % / 他 25.27 %</t>
+          <t xml:space="preserve">全社 21.93 % / 補助 20.46 % / 他 24.9 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20.73 % / 補助 18.87 % / 他 25.19 %</t>
+          <t xml:space="preserve">全社 20.6 % / 補助 18.87 % / 他 24.63 %</t>
         </is>
       </c>
     </row>
@@ -3145,17 +3145,17 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.85 % / 補助 12.75 % / 他 7.47 %</t>
+          <t xml:space="preserve">全社 10.9 % / 補助 12.75 % / 他 7.66 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.37 % / 補助 14.54 % / 他 7.9 %</t>
+          <t xml:space="preserve">全社 12.46 % / 補助 14.54 % / 他 8.26 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.83 % / 補助 16.13 % / 他 8.31 %</t>
+          <t xml:space="preserve">全社 13.95 % / 補助 16.13 % / 他 8.86 %</t>
         </is>
       </c>
     </row>
@@ -3207,17 +3207,17 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.37 % / 補助 17.22 % / 他 9.31 %</t>
+          <t xml:space="preserve">全社 14.41 % / 補助 17.22 % / 他 9.47 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.44 % / 補助 18.24 % / 他 9.66 %</t>
+          <t xml:space="preserve">全社 15.51 % / 補助 18.24 % / 他 9.99 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 16.49 % / 補助 19.19 % / 他 10 %</t>
+          <t xml:space="preserve">全社 16.58 % / 補助 19.19 % / 他 10.51 %</t>
         </is>
       </c>
     </row>
@@ -3269,17 +3269,17 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.07 % / 補助 9.67 % / 他 10.78 %</t>
+          <t xml:space="preserve">全社 10.01 % / 補助 9.67 % / 他 10.62 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.76 % / 補助 9.33 % / 他 10.64 %</t>
+          <t xml:space="preserve">全社 9.66 % / 補助 9.33 % / 他 10.31 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.44 % / 補助 9 % / 他 10.5 %</t>
+          <t xml:space="preserve">全社 9.3 % / 補助 9 % / 他 10.01 %</t>
         </is>
       </c>
     </row>
@@ -3393,17 +3393,17 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.19 % / 補助 7.67 % / 他 11.89 %</t>
+          <t xml:space="preserve">全社 9.2 % / 補助 7.67 % / 他 11.89 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.67 % / 補助 7.05 % / 他 12.01 %</t>
+          <t xml:space="preserve">全社 8.69 % / 補助 7.05 % / 他 12.01 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.15 % / 補助 6.48 % / 他 12.14 %</t>
+          <t xml:space="preserve">全社 8.18 % / 補助 6.48 % / 他 12.13 %</t>
         </is>
       </c>
     </row>
@@ -3455,17 +3455,17 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.59 % / 補助 0.44 % / 他 0.85 %</t>
+          <t xml:space="preserve">全社 0.59 % / 補助 0.44 % / 他 0.86 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.54 % / 補助 0.38 % / 他 0.86 %</t>
+          <t xml:space="preserve">全社 0.54 % / 補助 0.38 % / 他 0.85 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.49 % / 補助 0.33 % / 他 0.86 %</t>
+          <t xml:space="preserve">全社 0.49 % / 補助 0.33 % / 他 0.84 %</t>
         </is>
       </c>
     </row>
@@ -3517,17 +3517,17 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.78 % / 補助 8.11 % / 他 12.75 %</t>
+          <t xml:space="preserve">全社 9.79 % / 補助 8.11 % / 他 12.75 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.2 % / 補助 7.43 % / 他 12.87 %</t>
+          <t xml:space="preserve">全社 9.23 % / 補助 7.43 % / 他 12.87 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.63 % / 補助 6.82 % / 他 13 %</t>
+          <t xml:space="preserve">全社 8.67 % / 補助 6.82 % / 他 12.98 %</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.087 億円/人 / 補助 0.1 億円/人 / 他 0.075 億円/人</t>
+          <t xml:space="preserve">全社 0.087 億円/人 / 補助 0.1 億円/人 / 他 0.076 億円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.092 億円/人 / 補助 0.107 億円/人 / 他 0.078 億円/人</t>
+          <t xml:space="preserve">全社 0.092 億円/人 / 補助 0.107 億円/人 / 他 0.079 億円/人</t>
         </is>
       </c>
     </row>
@@ -3641,17 +3641,17 @@
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.268 億円/人 / 補助 0.32 億円/人 / 他 0.233 億円/人</t>
+          <t xml:space="preserve">全社 0.27 億円/人 / 補助 0.32 億円/人 / 他 0.237 億円/人</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.28 億円/人 / 補助 0.335 億円/人 / 他 0.243 億円/人</t>
+          <t xml:space="preserve">全社 0.282 億円/人 / 補助 0.335 億円/人 / 他 0.247 億円/人</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.294 億円/人 / 補助 0.355 億円/人 / 他 0.253 億円/人</t>
+          <t xml:space="preserve">全社 0.296 億円/人 / 補助 0.355 億円/人 / 他 0.257 億円/人</t>
         </is>
       </c>
     </row>
@@ -3703,17 +3703,17 @@
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.78 % / 補助 7.02 % / 他 4.03 %</t>
+          <t xml:space="preserve">全社 5.96 % / 補助 7.02 % / 他 4.47 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.79 % / 補助 6.96 % / 他 3.99 %</t>
+          <t xml:space="preserve">全社 6 % / 補助 6.96 % / 他 4.54 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.92 % / 補助 7.02 % / 他 4.04 %</t>
+          <t xml:space="preserve">全社 6.05 % / 補助 7.02 % / 他 4.47 %</t>
         </is>
       </c>
     </row>
@@ -3765,17 +3765,17 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 40.5 % / 補助 32 % / 他 57.81 %</t>
+          <t xml:space="preserve">全社 40.45 % / 補助 32 % / 他 57.38 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 37.35 % / 補助 28.94 % / 他 57.11 %</t>
+          <t xml:space="preserve">全社 37.3 % / 補助 28.94 % / 他 56.3 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.37 % / 補助 26.21 % / 他 56.5 %</t>
+          <t xml:space="preserve">全社 34.32 % / 補助 26.21 % / 他 55.25 %</t>
         </is>
       </c>
     </row>
@@ -3889,17 +3889,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.891 億円/人 / 補助 1.214 億円/人 / 他 0.605 億円/人</t>
+          <t xml:space="preserve">全社 0.892 億円/人 / 補助 1.214 億円/人 / 他 0.608 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.999 億円/人 / 補助 1.413 億円/人 / 他 0.623 億円/人</t>
+          <t xml:space="preserve">全社 1 億円/人 / 補助 1.413 億円/人 / 他 0.629 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.126 億円/人 / 補助 1.643 億円/人 / 他 0.642 億円/人</t>
+          <t xml:space="preserve">全社 1.127 億円/人 / 補助 1.643 億円/人 / 他 0.651 億円/人</t>
         </is>
       </c>
     </row>
@@ -3951,17 +3951,17 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.097 億円/人 / 補助 0.155 億円/人 / 他 0.045 億円/人</t>
+          <t xml:space="preserve">全社 0.097 億円/人 / 補助 0.155 億円/人 / 他 0.047 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.124 億円/人 / 補助 0.205 億円/人 / 他 0.049 億円/人</t>
+          <t xml:space="preserve">全社 0.125 億円/人 / 補助 0.205 億円/人 / 他 0.052 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.156 億円/人 / 補助 0.265 億円/人 / 他 0.053 億円/人</t>
+          <t xml:space="preserve">全社 0.157 億円/人 / 補助 0.265 億円/人 / 他 0.058 億円/人</t>
         </is>
       </c>
     </row>
@@ -4013,17 +4013,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.211 億円/人 / 補助 0.302 億円/人 / 他 0.131 億円/人</t>
+          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.302 億円/人 / 他 0.132 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.242 億円/人 / 補助 0.357 億円/人 / 他 0.137 億円/人</t>
+          <t xml:space="preserve">全社 0.243 億円/人 / 補助 0.357 億円/人 / 他 0.141 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.278 億円/人 / 補助 0.421 億円/人 / 他 0.144 億円/人</t>
+          <t xml:space="preserve">全社 0.279 億円/人 / 補助 0.421 億円/人 / 他 0.15 億円/人</t>
         </is>
       </c>
     </row>
@@ -4075,17 +4075,17 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.39 % / 補助 4 % / 他 1 %</t>
+          <t xml:space="preserve">全社 2.66 % / 補助 4 % / 他 1.5 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.41 % / 補助 4 % / 他 1 %</t>
+          <t xml:space="preserve">全社 2.67 % / 補助 4 % / 他 1.5 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.43 % / 補助 4 % / 他 1 %</t>
+          <t xml:space="preserve">全社 2.69 % / 補助 4 % / 他 1.5 %</t>
         </is>
       </c>
     </row>
@@ -4137,17 +4137,17 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.88 pt / 補助 17 pt / 他 3 pt</t>
+          <t xml:space="preserve">全社 12.01 pt / 補助 17 pt / 他 3.5 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.47 pt / 補助 17 pt / 他 3.01 pt</t>
+          <t xml:space="preserve">全社 12.52 pt / 補助 17 pt / 他 3.49 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.02 pt / 補助 17 pt / 他 2.99 pt</t>
+          <t xml:space="preserve">全社 13.02 pt / 補助 17 pt / 他 3.5 pt</t>
         </is>
       </c>
     </row>
@@ -4261,17 +4261,17 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.52 % / 補助 4.48 % / 他 1.83 %</t>
+          <t xml:space="preserve">全社 3.51 % / 補助 4.48 % / 他 1.81 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.07 % / 補助 3.7 % / 他 1.76 %</t>
+          <t xml:space="preserve">全社 3.05 % / 補助 3.7 % / 他 1.73 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.66 % / 補助 3.06 % / 他 1.69 %</t>
+          <t xml:space="preserve">全社 2.63 % / 補助 3.06 % / 他 1.65 %</t>
         </is>
       </c>
     </row>
@@ -4447,17 +4447,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.08 倍 / 補助 3.85 倍 / 他 5.08 倍</t>
+          <t xml:space="preserve">全社 4.1 倍 / 補助 3.85 倍 / 他 5.22 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.03 倍 / 補助 4.93 倍 / 他 5.49 倍</t>
+          <t xml:space="preserve">全社 5.09 倍 / 補助 4.93 倍 / 他 5.78 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.21 倍 / 補助 6.28 倍 / 他 5.91 倍</t>
+          <t xml:space="preserve">全社 6.3 倍 / 補助 6.28 倍 / 他 6.39 倍</t>
         </is>
       </c>
     </row>
@@ -4633,17 +4633,17 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 63.94 %</t>
+          <t xml:space="preserve">構成比 63.72 %</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 67.35 %</t>
+          <t xml:space="preserve">構成比 66.93 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 70.59 %</t>
+          <t xml:space="preserve">構成比 69.99 %</t>
         </is>
       </c>
     </row>
@@ -4695,17 +4695,17 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21 % / 他 4 %</t>
+          <t xml:space="preserve">補助 21 % / 他 5 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21 % / 他 4.01 %</t>
+          <t xml:space="preserve">補助 21 % / 他 5 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21 % / 他 3.99 %</t>
+          <t xml:space="preserve">補助 21 % / 他 5 %</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -1.5 pt</t>
+          <t xml:space="preserve">差 -1.51 pt</t>
         </is>
       </c>
     </row>
@@ -4819,17 +4819,17 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 5.27 pt</t>
+          <t xml:space="preserve">差 5.09 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.64 pt</t>
+          <t xml:space="preserve">差 6.28 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 7.82 pt</t>
+          <t xml:space="preserve">差 7.27 pt</t>
         </is>
       </c>
     </row>
@@ -4881,17 +4881,17 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.214 億円/人 / 他 0.605 億円/人</t>
+          <t xml:space="preserve">補助 1.214 億円/人 / 他 0.608 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.413 億円/人 / 他 0.623 億円/人</t>
+          <t xml:space="preserve">補助 1.413 億円/人 / 他 0.629 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.643 億円/人 / 他 0.642 億円/人</t>
+          <t xml:space="preserve">補助 1.643 億円/人 / 他 0.651 億円/人</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.1 億円/人 / 他 0.075 億円/人</t>
+          <t xml:space="preserve">補助 0.1 億円/人 / 他 0.076 億円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.107 億円/人 / 他 0.078 億円/人</t>
+          <t xml:space="preserve">補助 0.107 億円/人 / 他 0.079 億円/人</t>
         </is>
       </c>
     </row>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.63 %</t>
+          <t xml:space="preserve">寄与率 87.66 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 92.02 %</t>
+          <t xml:space="preserve">寄与率 89.33 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 93.28 %</t>
+          <t xml:space="preserve">寄与率 90.58 %</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2">
         <v>-10</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C22" s="2">
         <v>-5</v>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
@@ -5540,7 +5540,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNCwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMDksIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDUsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbLTAuMTUsMC4yNV0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbLTAuMTUsMC4yNV0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlstMC4xNSwwLjI1XSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlstMC4xNSwwLjI1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoxNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjcwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoyOC4xLCJtYXgiOjUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6My45LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MC4xLCJtYXgiOjAuMiwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnt9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIifQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbLTAuMTUsMC4yNV0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbLTAuMTUsMC4yNV0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlstMC4xNSwwLjI1XSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlstMC4xNSwwLjI1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoxNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjcwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoyOC4xLCJtYXgiOjUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6My45LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MC4xLCJtYXgiOjAuMiwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnt9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIifQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -11,7 +11,8 @@
     <sheet name="補助事業収支" sheetId="4" r:id="rId4"/>
     <sheet name="妥当性診断" sheetId="5" r:id="rId5"/>
     <sheet name="前提・目標" sheetId="6" r:id="rId6"/>
-    <sheet name="モデルデータ" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="入力データ監査" sheetId="7" r:id="rId7"/>
+    <sheet name="モデルデータ" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -198,11 +199,15 @@
           <t xml:space="preserve">%/年</t>
         </is>
       </c>
-      <c r="D7" s="2">
-        <v>21</v>
-      </c>
-      <c r="E7" s="2">
-        <v>35</v>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -224,11 +229,15 @@
           <t xml:space="preserve">億円</t>
         </is>
       </c>
-      <c r="D8" s="2">
-        <v>82.4</v>
-      </c>
-      <c r="E8" s="2">
-        <v>150</v>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -250,11 +259,15 @@
           <t xml:space="preserve">%/年</t>
         </is>
       </c>
-      <c r="D9" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="E9" s="2">
-        <v>7</v>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -276,11 +289,15 @@
           <t xml:space="preserve">%</t>
         </is>
       </c>
-      <c r="D10" s="2">
-        <v>70</v>
-      </c>
-      <c r="E10" s="2">
-        <v>95</v>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -302,11 +319,15 @@
           <t xml:space="preserve">%/年</t>
         </is>
       </c>
-      <c r="D11" s="2">
-        <v>22</v>
-      </c>
-      <c r="E11" s="2">
-        <v>35</v>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -328,11 +349,15 @@
           <t xml:space="preserve">億円</t>
         </is>
       </c>
-      <c r="D12" s="2">
-        <v>74.8</v>
-      </c>
-      <c r="E12" s="2">
-        <v>150</v>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -354,11 +379,15 @@
           <t xml:space="preserve">%/年</t>
         </is>
       </c>
-      <c r="D13" s="2">
-        <v>21</v>
-      </c>
-      <c r="E13" s="2">
-        <v>35</v>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -380,11 +409,15 @@
           <t xml:space="preserve">億円</t>
         </is>
       </c>
-      <c r="D14" s="2">
-        <v>28.1</v>
-      </c>
-      <c r="E14" s="2">
-        <v>50</v>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -406,11 +439,15 @@
           <t xml:space="preserve">%/年</t>
         </is>
       </c>
-      <c r="D15" s="2">
-        <v>7</v>
-      </c>
-      <c r="E15" s="2">
-        <v>10</v>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -432,11 +469,15 @@
           <t xml:space="preserve">億円</t>
         </is>
       </c>
-      <c r="D16" s="2">
-        <v>3.9</v>
-      </c>
-      <c r="E16" s="2">
-        <v>7</v>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -458,11 +499,15 @@
           <t xml:space="preserve">%/年</t>
         </is>
       </c>
-      <c r="D17" s="2">
-        <v>6</v>
-      </c>
-      <c r="E17" s="2">
-        <v>10</v>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -484,11 +529,15 @@
           <t xml:space="preserve">億円</t>
         </is>
       </c>
-      <c r="D18" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.2</v>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -510,11 +559,15 @@
           <t xml:space="preserve">%</t>
         </is>
       </c>
-      <c r="D19" s="2">
-        <v>30</v>
-      </c>
-      <c r="E19" s="2">
-        <v>70</v>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -536,11 +589,15 @@
           <t xml:space="preserve">%</t>
         </is>
       </c>
-      <c r="D20" s="2">
-        <v>213</v>
-      </c>
-      <c r="E20" s="2">
-        <v>350</v>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -562,15 +619,19 @@
           <t xml:space="preserve">点</t>
         </is>
       </c>
-      <c r="D21" s="2">
-        <v>23</v>
-      </c>
-      <c r="E21" s="2">
-        <v>40</v>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">参考</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5086,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5087,11 +5148,15 @@
       <c r="B3" s="2">
         <v>5</v>
       </c>
-      <c r="C3" s="2">
-        <v>-5</v>
-      </c>
-      <c r="D3" s="2">
-        <v>30</v>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -5120,10 +5185,10 @@
         <v>7.000000000000001</v>
       </c>
       <c r="C5" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5168,10 +5233,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5216,10 +5281,10 @@
         <v>0.5</v>
       </c>
       <c r="C11" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5264,10 +5329,10 @@
         <v>0.5</v>
       </c>
       <c r="C14" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5312,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -5328,10 +5393,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -5500,22 +5565,6 @@
       </c>
       <c r="D28" s="2">
         <v>50</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ローカルベンチマーク</t>
-        </is>
-      </c>
-      <c r="B29" s="2">
-        <v>23</v>
-      </c>
-      <c r="C29" s="2">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5523,6 +5572,3219 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C213"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="72" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力データ監査（Null／0区別）</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">保存値</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力キー</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">保存値</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2023:2-1</t>
+        </is>
+      </c>
+      <c r="B3" s="2">
+        <v>136.4</v>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2023:2-11</t>
+        </is>
+      </c>
+      <c r="B4" s="2">
+        <v>12.76</v>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2023:2-14</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <v>3.18</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2023:2-3</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <v>92.75</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2023:2-7</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <v>33.21</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2023:2-8</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2024:2-1</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <v>143.2</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2024:2-11</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <v>13.38</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2024:2-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <v>3.34</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2024:2-3</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <v>97.38</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2024:2-7</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <v>34.86</v>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2024:2-8</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2025:2-1</t>
+        </is>
+      </c>
+      <c r="B15" s="2">
+        <v>150</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2025:2-11</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <v>14</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2025:2-14</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2025:2-3</t>
+        </is>
+      </c>
+      <c r="B18" s="2">
+        <v>102</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2025:2-7</t>
+        </is>
+      </c>
+      <c r="B19" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:company:2025:2-8</t>
+        </is>
+      </c>
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-1</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>72</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-10</t>
+        </is>
+      </c>
+      <c r="B22" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-13</t>
+        </is>
+      </c>
+      <c r="B23" s="2">
+        <v>90</v>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-14</t>
+        </is>
+      </c>
+      <c r="B24" s="2">
+        <v>2</v>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-4</t>
+        </is>
+      </c>
+      <c r="B25" s="2">
+        <v>23.04</v>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-6</t>
+        </is>
+      </c>
+      <c r="B26" s="2">
+        <v>6.48</v>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-8</t>
+        </is>
+      </c>
+      <c r="B27" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2023:7-9</t>
+        </is>
+      </c>
+      <c r="B28" s="2">
+        <v>0.36</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-1</t>
+        </is>
+      </c>
+      <c r="B29" s="2">
+        <v>76</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-10</t>
+        </is>
+      </c>
+      <c r="B30" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-13</t>
+        </is>
+      </c>
+      <c r="B31" s="2">
+        <v>95</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-14</t>
+        </is>
+      </c>
+      <c r="B32" s="2">
+        <v>2</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-4</t>
+        </is>
+      </c>
+      <c r="B33" s="2">
+        <v>24.32</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-6</t>
+        </is>
+      </c>
+      <c r="B34" s="2">
+        <v>6.84</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-8</t>
+        </is>
+      </c>
+      <c r="B35" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2024:7-9</t>
+        </is>
+      </c>
+      <c r="B36" s="2">
+        <v>0.38</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-1</t>
+        </is>
+      </c>
+      <c r="B37" s="2">
+        <v>80</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-10</t>
+        </is>
+      </c>
+      <c r="B38" s="2">
+        <v>2</v>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-13</t>
+        </is>
+      </c>
+      <c r="B39" s="2">
+        <v>100</v>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-14</t>
+        </is>
+      </c>
+      <c r="B40" s="2">
+        <v>2</v>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-4</t>
+        </is>
+      </c>
+      <c r="B41" s="2">
+        <v>25.6</v>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-6</t>
+        </is>
+      </c>
+      <c r="B42" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-8</t>
+        </is>
+      </c>
+      <c r="B43" s="2">
+        <v>6</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actual:project:2025:7-9</t>
+        </is>
+      </c>
+      <c r="B44" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:assets</t>
+        </is>
+      </c>
+      <c r="B45" s="2">
+        <v>132</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:buildings</t>
+        </is>
+      </c>
+      <c r="B46" s="2">
+        <v>19</v>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:capex</t>
+        </is>
+      </c>
+      <c r="B47" s="2">
+        <v>5</v>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:capital</t>
+        </is>
+      </c>
+      <c r="B48" s="2">
+        <v>10</v>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:cash</t>
+        </is>
+      </c>
+      <c r="B49" s="2">
+        <v>24</v>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
+        </is>
+      </c>
+      <c r="B50" s="2">
+        <v>67</v>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
+        </is>
+      </c>
+      <c r="B51" s="2">
+        <v>39</v>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
+        </is>
+      </c>
+      <c r="B52" s="2">
+        <v>65</v>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
+        </is>
+      </c>
+      <c r="B53" s="2">
+        <v>36</v>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
+        </is>
+      </c>
+      <c r="B54" s="2">
+        <v>7</v>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:land</t>
+        </is>
+      </c>
+      <c r="B55" s="2">
+        <v>10</v>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
+        </is>
+      </c>
+      <c r="B56" s="2">
+        <v>75</v>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
+        </is>
+      </c>
+      <c r="B57" s="2">
+        <v>29</v>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:machinery</t>
+        </is>
+      </c>
+      <c r="B58" s="2">
+        <v>24</v>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
+        </is>
+      </c>
+      <c r="B59" s="2">
+        <v>57</v>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
+        </is>
+      </c>
+      <c r="B60" s="2">
+        <v>54</v>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
+        </is>
+      </c>
+      <c r="B61" s="2">
+        <v>12</v>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:software</t>
+        </is>
+      </c>
+      <c r="B62" s="2">
+        <v>5</v>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
+        </is>
+      </c>
+      <c r="B63" s="2">
+        <v>53</v>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:assets</t>
+        </is>
+      </c>
+      <c r="B64" s="2">
+        <v>143</v>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:buildings</t>
+        </is>
+      </c>
+      <c r="B65" s="2">
+        <v>20</v>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:capex</t>
+        </is>
+      </c>
+      <c r="B66" s="2">
+        <v>8</v>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:capital</t>
+        </is>
+      </c>
+      <c r="B67" s="2">
+        <v>10</v>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:cash</t>
+        </is>
+      </c>
+      <c r="B68" s="2">
+        <v>25</v>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
+        </is>
+      </c>
+      <c r="B69" s="2">
+        <v>72</v>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
+        </is>
+      </c>
+      <c r="B70" s="2">
+        <v>41</v>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
+        </is>
+      </c>
+      <c r="B71" s="2">
+        <v>71</v>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
+        </is>
+      </c>
+      <c r="B72" s="2">
+        <v>38</v>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
+        </is>
+      </c>
+      <c r="B73" s="2">
+        <v>8</v>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:land</t>
+        </is>
+      </c>
+      <c r="B74" s="2">
+        <v>10</v>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
+        </is>
+      </c>
+      <c r="B75" s="2">
+        <v>79</v>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
+        </is>
+      </c>
+      <c r="B76" s="2">
+        <v>31</v>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:machinery</t>
+        </is>
+      </c>
+      <c r="B77" s="2">
+        <v>28</v>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
+        </is>
+      </c>
+      <c r="B78" s="2">
+        <v>64</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
+        </is>
+      </c>
+      <c r="B79" s="2">
+        <v>61</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
+        </is>
+      </c>
+      <c r="B80" s="2">
+        <v>12</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:software</t>
+        </is>
+      </c>
+      <c r="B81" s="2">
+        <v>6</v>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
+        </is>
+      </c>
+      <c r="B82" s="2">
+        <v>58</v>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:assets</t>
+        </is>
+      </c>
+      <c r="B83" s="2">
+        <v>156</v>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:buildings</t>
+        </is>
+      </c>
+      <c r="B84" s="2">
+        <v>22</v>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:capex</t>
+        </is>
+      </c>
+      <c r="B85" s="2">
+        <v>10</v>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:capital</t>
+        </is>
+      </c>
+      <c r="B86" s="2">
+        <v>10</v>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:cash</t>
+        </is>
+      </c>
+      <c r="B87" s="2">
+        <v>27</v>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
+        </is>
+      </c>
+      <c r="B88" s="2">
+        <v>78</v>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
+        </is>
+      </c>
+      <c r="B89" s="2">
+        <v>43</v>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
+        </is>
+      </c>
+      <c r="B90" s="2">
+        <v>78</v>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
+        </is>
+      </c>
+      <c r="B91" s="2">
+        <v>40</v>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
+        </is>
+      </c>
+      <c r="B92" s="2">
+        <v>9</v>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:land</t>
+        </is>
+      </c>
+      <c r="B93" s="2">
+        <v>10</v>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
+        </is>
+      </c>
+      <c r="B94" s="2">
+        <v>83</v>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
+        </is>
+      </c>
+      <c r="B95" s="2">
+        <v>32</v>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:machinery</t>
+        </is>
+      </c>
+      <c r="B96" s="2">
+        <v>32</v>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
+        </is>
+      </c>
+      <c r="B97" s="2">
+        <v>73</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
+        </is>
+      </c>
+      <c r="B98" s="2">
+        <v>70</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
+        </is>
+      </c>
+      <c r="B99" s="2">
+        <v>11</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:software</t>
+        </is>
+      </c>
+      <c r="B100" s="2">
+        <v>7</v>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
+        </is>
+      </c>
+      <c r="B101" s="2">
+        <v>64</v>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:investment:0</t>
+        </is>
+      </c>
+      <c r="B102" s="2">
+        <v>15</v>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:investment:1</t>
+        </is>
+      </c>
+      <c r="B103" s="2">
+        <v>200</v>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+        </is>
+      </c>
+      <c r="B104" s="2">
+        <v>0</v>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+        </is>
+      </c>
+      <c r="B105" s="2">
+        <v>100</v>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+        </is>
+      </c>
+      <c r="B106" s="2">
+        <v>0</v>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+        </is>
+      </c>
+      <c r="B107" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+        </is>
+      </c>
+      <c r="B108" s="2">
+        <v>0</v>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+        </is>
+      </c>
+      <c r="B109" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+        </is>
+      </c>
+      <c r="B110" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+        </is>
+      </c>
+      <c r="B111" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B112" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="C112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B113" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+        </is>
+      </c>
+      <c r="B114" s="2">
+        <v>0</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+        </is>
+      </c>
+      <c r="B115" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B116" s="2">
+        <v>0</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B117" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+        </is>
+      </c>
+      <c r="B118" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+        </is>
+      </c>
+      <c r="B119" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B120" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B121" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+        </is>
+      </c>
+      <c r="B122" s="2">
+        <v>0</v>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+        </is>
+      </c>
+      <c r="B123" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+        </is>
+      </c>
+      <c r="B124" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+        </is>
+      </c>
+      <c r="B125" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+        </is>
+      </c>
+      <c r="B126" s="2">
+        <v>0</v>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+        </is>
+      </c>
+      <c r="B127" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+        </is>
+      </c>
+      <c r="B128" s="2">
+        <v>0</v>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+        </is>
+      </c>
+      <c r="B129" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+        </is>
+      </c>
+      <c r="B130" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="C130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+        </is>
+      </c>
+      <c r="B131" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B132" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="C132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B133" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+        </is>
+      </c>
+      <c r="B134" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+        </is>
+      </c>
+      <c r="B135" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+        </is>
+      </c>
+      <c r="B136" s="2">
+        <v>0</v>
+      </c>
+      <c r="C136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+        </is>
+      </c>
+      <c r="B137" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B138" s="2">
+        <v>0</v>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B139" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+        </is>
+      </c>
+      <c r="B140" s="2">
+        <v>0.045</v>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+        </is>
+      </c>
+      <c r="B141" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B142" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B143" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+        </is>
+      </c>
+      <c r="B144" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+        </is>
+      </c>
+      <c r="B145" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+        </is>
+      </c>
+      <c r="B146" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="C146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+        </is>
+      </c>
+      <c r="B147" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+        </is>
+      </c>
+      <c r="B148" s="2">
+        <v>0</v>
+      </c>
+      <c r="C148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+        </is>
+      </c>
+      <c r="B149" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="C149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+        </is>
+      </c>
+      <c r="B150" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+        </is>
+      </c>
+      <c r="B151" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="C151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
+        </is>
+      </c>
+      <c r="B152" s="2">
+        <v>1</v>
+      </c>
+      <c r="C152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
+        </is>
+      </c>
+      <c r="B153" s="2">
+        <v>50</v>
+      </c>
+      <c r="C153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
+        </is>
+      </c>
+      <c r="B154" s="2">
+        <v>5</v>
+      </c>
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
+        </is>
+      </c>
+      <c r="B155" s="2">
+        <v>20</v>
+      </c>
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:investment</t>
+        </is>
+      </c>
+      <c r="B156" s="2">
+        <v>45</v>
+      </c>
+      <c r="C156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:localBenchmark</t>
+        </is>
+      </c>
+      <c r="B157" s="2">
+        <v>23</v>
+      </c>
+      <c r="C157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
+        </is>
+      </c>
+      <c r="B158" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="C158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+        </is>
+      </c>
+      <c r="B159" s="2">
+        <v>0.005</v>
+      </c>
+      <c r="C159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+        </is>
+      </c>
+      <c r="B160" s="2">
+        <v>0.015</v>
+      </c>
+      <c r="C160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B161" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="C161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
+        </is>
+      </c>
+      <c r="B162" s="2">
+        <v>0.045</v>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B163" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
+        </is>
+      </c>
+      <c r="B164" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="C164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B165" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+        </is>
+      </c>
+      <c r="B166" s="2">
+        <v>0.005</v>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+        </is>
+      </c>
+      <c r="B167" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+        </is>
+      </c>
+      <c r="B168" s="2">
+        <v>0</v>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+        </is>
+      </c>
+      <c r="B169" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+        </is>
+      </c>
+      <c r="B170" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B171" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
+        </is>
+      </c>
+      <c r="B172" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+        </is>
+      </c>
+      <c r="B173" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B174" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
+        </is>
+      </c>
+      <c r="B175" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B176" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
+        </is>
+      </c>
+      <c r="B177" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+        </is>
+      </c>
+      <c r="B178" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+        </is>
+      </c>
+      <c r="B179" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+        </is>
+      </c>
+      <c r="B180" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:subsidy</t>
+        </is>
+      </c>
+      <c r="B181" s="2">
+        <v>15</v>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:usefulLife</t>
+        </is>
+      </c>
+      <c r="B182" s="2">
+        <v>10</v>
+      </c>
+      <c r="C182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2">
+        <v>15</v>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2027</t>
+        </is>
+      </c>
+      <c r="B184" s="2">
+        <v>15</v>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2028</t>
+        </is>
+      </c>
+      <c r="B185" s="2">
+        <v>15</v>
+      </c>
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2029</t>
+        </is>
+      </c>
+      <c r="B186" s="2">
+        <v>0</v>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2030</t>
+        </is>
+      </c>
+      <c r="B187" s="2">
+        <v>0</v>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2031</t>
+        </is>
+      </c>
+      <c r="B188" s="2">
+        <v>0</v>
+      </c>
+      <c r="C188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
+        </is>
+      </c>
+      <c r="B189" s="2">
+        <v>7</v>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
+        </is>
+      </c>
+      <c r="B190" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B191" s="2">
+        <v>35</v>
+      </c>
+      <c r="C191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B192" s="2">
+        <v>21</v>
+      </c>
+      <c r="C192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B193" s="2">
+        <v>0</v>
+      </c>
+      <c r="C193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
+        </is>
+      </c>
+      <c r="B194" s="2">
+        <v>10</v>
+      </c>
+      <c r="C194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
+        </is>
+      </c>
+      <c r="B195" s="2">
+        <v>7</v>
+      </c>
+      <c r="C195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B196" s="2">
+        <v>0</v>
+      </c>
+      <c r="C196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+        </is>
+      </c>
+      <c r="B197" s="2">
+        <v>70</v>
+      </c>
+      <c r="C197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+        </is>
+      </c>
+      <c r="B198" s="2">
+        <v>30</v>
+      </c>
+      <c r="C198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+        </is>
+      </c>
+      <c r="B199" s="2">
+        <v>35</v>
+      </c>
+      <c r="C199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+        </is>
+      </c>
+      <c r="B200" s="2">
+        <v>21</v>
+      </c>
+      <c r="C200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B201" s="2">
+        <v>40</v>
+      </c>
+      <c r="C201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B202" s="2">
+        <v>23</v>
+      </c>
+      <c r="C202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B203" s="2">
+        <v>10</v>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B204" s="2">
+        <v>6</v>
+      </c>
+      <c r="C204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B205" s="2">
+        <v>0</v>
+      </c>
+      <c r="C205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B206" s="2">
+        <v>35</v>
+      </c>
+      <c r="C206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B207" s="2">
+        <v>22</v>
+      </c>
+      <c r="C207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B208" s="2">
+        <v>0</v>
+      </c>
+      <c r="C208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B209" s="2">
+        <v>95</v>
+      </c>
+      <c r="C209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B210" s="2">
+        <v>70</v>
+      </c>
+      <c r="C210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B211" s="2">
+        <v>0</v>
+      </c>
+      <c r="C211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B212" s="2">
+        <v>350</v>
+      </c>
+      <c r="C212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
+        </is>
+      </c>
+      <c r="B213" s="2">
+        <v>213</v>
+      </c>
+      <c r="C213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -5540,7 +8802,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wMywwLjJdLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlstMC4xNSwwLjI1XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbLTAuMTUsMC4yNV0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbLTAuMTUsMC4yNV0sInByb2plY3RTYWxlc0dyb3d0aCI6Wy0wLjA1LDAuNF0sIm90aGVyU2FsZXNHcm93dGgiOlstMC4xLDAuMl0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlstMC4xNSwwLjI1XSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlstMC4xNSwwLjI1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoxNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjMuNSwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjcwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoyOC4xLCJtYXgiOjUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6My45LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MC4xLCJtYXgiOjAuMiwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnt9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIifQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMSwwLjJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMCwwLjAzXSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnt9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLjIxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOCI6MC45MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTExIjoxMi43NiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjozLjE4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNDgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0Ljg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOCI6MC45NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTExIjoxMy4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjozLjM0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjYuODQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTgiOjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMSI6MTQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6My41LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4yLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDB9fQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -8802,7 +8802,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMSwwLjJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMCwwLjAzXSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnt9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLjIxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOCI6MC45MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTExIjoxMi43NiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjozLjE4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNDgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0Ljg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOCI6MC45NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTExIjoxMy4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjozLjM0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjYuODQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTgiOjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMSI6MTQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6My41LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4yLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDB9fQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMSwwLjJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMCwwLjAzXSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnt9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLjIxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOCI6MC45MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTExIjoxMi43NiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjozLjE4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNDgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0Ljg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOCI6MC45NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTExIjoxMy4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjozLjM0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjYuODQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTgiOjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMSI6MTQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6My41LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4yLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIiwib2ZmaWNlclBheSI6InJhdGUifX0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -161,7 +161,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">計画値</t>
+          <t xml:space="preserve">計画値（基準年→事業化報告3年目・3年間）</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -171,12 +171,12 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">目標下限</t>
+          <t xml:space="preserve">目標下限（3年間）</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">計画上限</t>
+          <t xml:space="preserve">計画上限（3年間）</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -488,15 +488,15 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">年平均役員目標賃上げ率</t>
+          <t xml:space="preserve">投資額／全社売上高</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>5.7715899735125475</v>
+        <v>30</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%/年</t>
+          <t xml:space="preserve">%</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -511,22 +511,22 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">参考</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員給与支給総額の増加額</t>
+          <t xml:space="preserve">付加価値増加額／補助金額</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>0.10999999999999999</v>
+        <v>168.5333333333333</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">%</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -548,15 +548,15 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">投資額／全社売上高</t>
+          <t xml:space="preserve">ローカルベンチマーク財務分析結果</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%</t>
+          <t xml:space="preserve">点</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
@@ -578,15 +578,15 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">付加価値増加額／補助金額</t>
+          <t xml:space="preserve">年平均役員目標賃上げ率</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>168.5333333333333</v>
+        <v>5.7715899735125475</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%</t>
+          <t xml:space="preserve">%/年</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
@@ -601,22 +601,22 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">参考</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ローカルベンチマーク財務分析結果</t>
+          <t xml:space="preserve">役員給与支給総額の増加額</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>23</v>
+        <v>0.10999999999999999</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">点</t>
+          <t xml:space="preserve">億円</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
@@ -8802,7 +8802,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMSwwLjJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMCwwLjAzXSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnt9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLjIxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOCI6MC45MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTExIjoxMi43NiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjozLjE4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNDgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0Ljg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOCI6MC45NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTExIjoxMy4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjozLjM0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjYuODQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTgiOjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMSI6MTQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6My41LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4yLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIiwib2ZmaWNlclBheSI6InJhdGUifX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMSwwLjJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMCwwLjAzXSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MzAsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnt9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLjIxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOCI6MC45MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTExIjoxMi43NiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjozLjE4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNDgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0Ljg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOCI6MC45NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTExIjoxMy4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjozLjM0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjYuODQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTgiOjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMSI6MTQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6My41LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4yLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn19</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -156,12 +156,12 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">15指標・目標</t>
+          <t xml:space="preserve">15指標・目標（指標名に第6次定義を併記）</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">計画値（基準年→事業化報告3年目・3年間）</t>
+          <t xml:space="preserve">計画値</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -171,12 +171,12 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">目標下限（3年間）</t>
+          <t xml:space="preserve">目標下限</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">計画上限（3年間）</t>
+          <t xml:space="preserve">計画上限</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
@@ -188,7 +188,7 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社年平均売上高成長率</t>
+          <t xml:space="preserve">全社年平均売上高成長率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B7" s="2">
@@ -218,7 +218,7 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社売上高増加額</t>
+          <t xml:space="preserve">全社売上高増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B8" s="2">
@@ -248,7 +248,7 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社の従業員1人当たり給与支給総額の年平均上昇率（最新決算期→基準年度）</t>
+          <t xml:space="preserve">全社の従業員1人当たり給与支給総額の年平均上昇率（最新決算期→基準年度）（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B9" s="2">
@@ -278,7 +278,7 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業売上高／全社売上高</t>
+          <t xml:space="preserve">補助事業売上高／全社売上高（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B10" s="2">
@@ -308,7 +308,7 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業年平均売上高成長率</t>
+          <t xml:space="preserve">補助事業年平均売上高成長率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B11" s="2">
@@ -338,7 +338,7 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業売上高増加額</t>
+          <t xml:space="preserve">補助事業売上高増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B12" s="2">
@@ -368,7 +368,7 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業年平均労働生産性の伸び</t>
+          <t xml:space="preserve">補助事業年平均労働生産性の伸び（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B13" s="2">
@@ -398,7 +398,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業付加価値増加額</t>
+          <t xml:space="preserve">補助事業付加価値増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -428,7 +428,7 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B15" s="2">
@@ -458,7 +458,7 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業従業員給与支給総額の増加額</t>
+          <t xml:space="preserve">補助事業従業員給与支給総額の増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B16" s="2">
@@ -488,7 +488,7 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">投資額／全社売上高</t>
+          <t xml:space="preserve">投資額／全社売上高（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B17" s="2">
@@ -518,7 +518,7 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">付加価値増加額／補助金額</t>
+          <t xml:space="preserve">付加価値増加額／補助金額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B18" s="2">
@@ -548,7 +548,7 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ローカルベンチマーク財務分析結果</t>
+          <t xml:space="preserve">ローカルベンチマーク財務分析結果（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B19" s="2">
@@ -578,7 +578,7 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">年平均役員目標賃上げ率</t>
+          <t xml:space="preserve">年平均役員目標賃上げ率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B20" s="2">
@@ -608,7 +608,7 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員給与支給総額の増加額</t>
+          <t xml:space="preserve">役員給与支給総額の増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B21" s="2">

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -192,7 +192,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <v>15.187557062867052</v>
+        <v>15.51906107932668</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
@@ -222,7 +222,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>105</v>
+        <v>107.63</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -282,7 +282,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>69.99078158951735</v>
+        <v>69.38995332441166</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -1256,13 +1256,13 @@
         <v>198.74</v>
       </c>
       <c r="H3" s="4">
-        <v>227.88</v>
+        <v>228.65999999999997</v>
       </c>
       <c r="I3" s="4">
-        <v>262.5</v>
+        <v>264.15999999999997</v>
       </c>
       <c r="J3" s="4">
-        <v>303.74</v>
+        <v>306.37</v>
       </c>
     </row>
     <row r="4">
@@ -1292,13 +1292,13 @@
         <v>27.63470554235441</v>
       </c>
       <c r="H4" s="2">
-        <v>14.66237294958237</v>
+        <v>15.054845526818927</v>
       </c>
       <c r="I4" s="2">
-        <v>15.192206424433907</v>
+        <v>15.525233971835917</v>
       </c>
       <c r="J4" s="2">
-        <v>15.710476190476186</v>
+        <v>15.978952150212011</v>
       </c>
     </row>
     <row r="5">
@@ -1326,13 +1326,13 @@
         <v>131.15</v>
       </c>
       <c r="H5" s="2">
-        <v>149.91</v>
+        <v>150.44</v>
       </c>
       <c r="I5" s="2">
-        <v>172.22</v>
+        <v>173.33</v>
       </c>
       <c r="J5" s="2">
-        <v>198.8</v>
+        <v>200.54000000000002</v>
       </c>
     </row>
     <row r="6">
@@ -1394,13 +1394,13 @@
         <v>67.59</v>
       </c>
       <c r="H7" s="4">
-        <v>77.97</v>
+        <v>78.21999999999997</v>
       </c>
       <c r="I7" s="4">
-        <v>90.28</v>
+        <v>90.82999999999996</v>
       </c>
       <c r="J7" s="4">
-        <v>104.94</v>
+        <v>105.82999999999998</v>
       </c>
     </row>
     <row r="8">
@@ -1428,13 +1428,13 @@
         <v>34.009258327463016</v>
       </c>
       <c r="H8" s="2">
-        <v>34.215376513954716</v>
+        <v>34.20799440216915</v>
       </c>
       <c r="I8" s="2">
-        <v>34.392380952380954</v>
+        <v>34.3844639612356</v>
       </c>
       <c r="J8" s="2">
-        <v>34.549285573187596</v>
+        <v>34.543199399419</v>
       </c>
     </row>
     <row r="9">
@@ -1462,13 +1462,13 @@
         <v>49.15</v>
       </c>
       <c r="H9" s="2">
-        <v>53.13</v>
+        <v>53.21</v>
       </c>
       <c r="I9" s="2">
-        <v>57.56999999999999</v>
+        <v>57.739999999999995</v>
       </c>
       <c r="J9" s="2">
-        <v>62.57</v>
+        <v>62.83</v>
       </c>
     </row>
     <row r="10">
@@ -1768,13 +1768,13 @@
         <v>18.440000000000005</v>
       </c>
       <c r="H18" s="4">
-        <v>24.839999999999996</v>
+        <v>25.00999999999997</v>
       </c>
       <c r="I18" s="4">
-        <v>32.71000000000001</v>
+        <v>33.08999999999996</v>
       </c>
       <c r="J18" s="4">
-        <v>42.36999999999999</v>
+        <v>42.99999999999998</v>
       </c>
     </row>
     <row r="19">
@@ -1802,13 +1802,13 @@
         <v>9.278454261849655</v>
       </c>
       <c r="H19" s="2">
-        <v>10.900473933649288</v>
+        <v>10.937636665791995</v>
       </c>
       <c r="I19" s="2">
-        <v>12.460952380952383</v>
+        <v>12.526499091459709</v>
       </c>
       <c r="J19" s="2">
-        <v>13.949430433923746</v>
+        <v>14.035316773835552</v>
       </c>
     </row>
     <row r="20">
@@ -1836,13 +1836,13 @@
         <v>18.440000000000005</v>
       </c>
       <c r="H20" s="4">
-        <v>24.839999999999996</v>
+        <v>25.00999999999997</v>
       </c>
       <c r="I20" s="4">
-        <v>32.71000000000001</v>
+        <v>33.08999999999996</v>
       </c>
       <c r="J20" s="4">
-        <v>42.36999999999999</v>
+        <v>42.99999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -2074,13 +2074,13 @@
         <v>60.38039649793701</v>
       </c>
       <c r="H5" s="2">
-        <v>63.717746182201154</v>
+        <v>63.50039359748097</v>
       </c>
       <c r="I5" s="2">
-        <v>66.9295238095238</v>
+        <v>66.50893397940642</v>
       </c>
       <c r="J5" s="2">
-        <v>69.99078158951735</v>
+        <v>69.38995332441166</v>
       </c>
     </row>
     <row r="6">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.66 % / 補助 21 % / 他 5 %</t>
+          <t xml:space="preserve">全社 15.05 % / 補助 21 % / 他 5.99 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.19 % / 補助 21 % / 他 5 %</t>
+          <t xml:space="preserve">全社 15.53 % / 補助 21 % / 他 6 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.71 % / 補助 21 % / 他 5 %</t>
+          <t xml:space="preserve">全社 15.98 % / 補助 21 % / 他 6 %</t>
         </is>
       </c>
     </row>
@@ -3020,17 +3020,17 @@
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.78 % / 補助 65 % / 他 67.16 %</t>
+          <t xml:space="preserve">全社 65.79 % / 補助 65 % / 他 67.17 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.61 % / 補助 65 % / 他 66.84 %</t>
+          <t xml:space="preserve">全社 65.62 % / 補助 65 % / 他 66.84 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.45 % / 補助 65 % / 他 66.51 %</t>
+          <t xml:space="preserve">全社 65.46 % / 補助 65 % / 他 66.5 %</t>
         </is>
       </c>
     </row>
@@ -3082,17 +3082,17 @@
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.22 % / 補助 35 % / 他 32.84 %</t>
+          <t xml:space="preserve">全社 34.21 % / 補助 35 % / 他 32.83 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.39 % / 補助 35 % / 他 33.16 %</t>
+          <t xml:space="preserve">全社 34.38 % / 補助 35 % / 他 33.16 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.55 % / 補助 35 % / 他 33.49 %</t>
+          <t xml:space="preserve">全社 34.54 % / 補助 35 % / 他 33.5 %</t>
         </is>
       </c>
     </row>
@@ -3144,17 +3144,17 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.31 % / 補助 22.25 % / 他 25.18 %</t>
+          <t xml:space="preserve">全社 23.27 % / 補助 22.25 % / 他 25.04 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.93 % / 補助 20.46 % / 他 24.9 %</t>
+          <t xml:space="preserve">全社 21.86 % / 補助 20.46 % / 他 24.63 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20.6 % / 補助 18.87 % / 他 24.63 %</t>
+          <t xml:space="preserve">全社 20.51 % / 補助 18.87 % / 他 24.22 %</t>
         </is>
       </c>
     </row>
@@ -3206,17 +3206,17 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.9 % / 補助 12.75 % / 他 7.66 %</t>
+          <t xml:space="preserve">全社 10.94 % / 補助 12.75 % / 他 7.79 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.46 % / 補助 14.54 % / 他 8.26 %</t>
+          <t xml:space="preserve">全社 12.53 % / 補助 14.54 % / 他 8.53 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.95 % / 補助 16.13 % / 他 8.86 %</t>
+          <t xml:space="preserve">全社 14.04 % / 補助 16.13 % / 他 9.29 %</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.41 % / 補助 17.22 % / 他 9.47 %</t>
+          <t xml:space="preserve">全社 14.44 % / 補助 17.22 % / 他 9.59 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.51 % / 補助 18.24 % / 他 9.99 %</t>
+          <t xml:space="preserve">全社 15.55 % / 補助 18.24 % / 他 10.23 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 16.58 % / 補助 19.19 % / 他 10.51 %</t>
+          <t xml:space="preserve">全社 16.65 % / 補助 19.19 % / 他 10.89 %</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.3 % / 補助 9 % / 他 10.01 %</t>
+          <t xml:space="preserve">全社 9.31 % / 補助 9 % / 他 10 %</t>
         </is>
       </c>
     </row>
@@ -3454,17 +3454,17 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.2 % / 補助 7.67 % / 他 11.89 %</t>
+          <t xml:space="preserve">全社 9.17 % / 補助 7.67 % / 他 11.78 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.69 % / 補助 7.05 % / 他 12.01 %</t>
+          <t xml:space="preserve">全社 8.63 % / 補助 7.05 % / 他 11.79 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.18 % / 補助 6.48 % / 他 12.13 %</t>
+          <t xml:space="preserve">全社 8.11 % / 補助 6.48 % / 他 11.79 %</t>
         </is>
       </c>
     </row>
@@ -3516,17 +3516,17 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.59 % / 補助 0.44 % / 他 0.86 %</t>
+          <t xml:space="preserve">全社 0.59 % / 補助 0.44 % / 他 0.85 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.54 % / 補助 0.38 % / 他 0.85 %</t>
+          <t xml:space="preserve">全社 0.53 % / 補助 0.38 % / 他 0.84 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.49 % / 補助 0.33 % / 他 0.84 %</t>
+          <t xml:space="preserve">全社 0.48 % / 補助 0.33 % / 他 0.82 %</t>
         </is>
       </c>
     </row>
@@ -3578,17 +3578,17 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.79 % / 補助 8.11 % / 他 12.75 %</t>
+          <t xml:space="preserve">全社 9.76 % / 補助 8.11 % / 他 12.63 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.23 % / 補助 7.43 % / 他 12.87 %</t>
+          <t xml:space="preserve">全社 9.17 % / 補助 7.43 % / 他 12.63 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.67 % / 補助 6.82 % / 他 12.98 %</t>
+          <t xml:space="preserve">全社 8.59 % / 補助 6.82 % / 他 12.61 %</t>
         </is>
       </c>
     </row>
@@ -3826,17 +3826,17 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 40.45 % / 補助 32 % / 他 57.38 %</t>
+          <t xml:space="preserve">全社 40.33 % / 補助 32 % / 他 56.85 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 37.3 % / 補助 28.94 % / 他 56.3 %</t>
+          <t xml:space="preserve">全社 37.08 % / 補助 28.94 % / 他 55.24 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.32 % / 補助 26.21 % / 他 55.25 %</t>
+          <t xml:space="preserve">全社 34.04 % / 補助 26.21 % / 他 53.68 %</t>
         </is>
       </c>
     </row>
@@ -3950,17 +3950,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.892 億円/人 / 補助 1.214 億円/人 / 他 0.608 億円/人</t>
+          <t xml:space="preserve">全社 0.895 億円/人 / 補助 1.214 億円/人 / 他 0.614 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1 億円/人 / 補助 1.413 億円/人 / 他 0.629 億円/人</t>
+          <t xml:space="preserve">全社 1.007 億円/人 / 補助 1.413 億円/人 / 他 0.641 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.127 億円/人 / 補助 1.643 億円/人 / 他 0.651 億円/人</t>
+          <t xml:space="preserve">全社 1.137 億円/人 / 補助 1.643 億円/人 / 他 0.67 億円/人</t>
         </is>
       </c>
     </row>
@@ -4012,17 +4012,17 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.097 億円/人 / 補助 0.155 億円/人 / 他 0.047 億円/人</t>
+          <t xml:space="preserve">全社 0.098 億円/人 / 補助 0.155 億円/人 / 他 0.048 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.125 億円/人 / 補助 0.205 億円/人 / 他 0.052 億円/人</t>
+          <t xml:space="preserve">全社 0.126 億円/人 / 補助 0.205 億円/人 / 他 0.055 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.157 億円/人 / 補助 0.265 億円/人 / 他 0.058 億円/人</t>
+          <t xml:space="preserve">全社 0.16 億円/人 / 補助 0.265 億円/人 / 他 0.062 億円/人</t>
         </is>
       </c>
     </row>
@@ -4074,17 +4074,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.302 億円/人 / 他 0.132 億円/人</t>
+          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.302 億円/人 / 他 0.133 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.243 億円/人 / 補助 0.357 億円/人 / 他 0.141 億円/人</t>
+          <t xml:space="preserve">全社 0.244 億円/人 / 補助 0.357 億円/人 / 他 0.143 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.279 億円/人 / 補助 0.421 億円/人 / 他 0.15 億円/人</t>
+          <t xml:space="preserve">全社 0.282 億円/人 / 補助 0.421 億円/人 / 他 0.154 億円/人</t>
         </is>
       </c>
     </row>
@@ -4198,17 +4198,17 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.01 pt / 補助 17 pt / 他 3.5 pt</t>
+          <t xml:space="preserve">全社 12.4 pt / 補助 17 pt / 他 4.49 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.52 pt / 補助 17 pt / 他 3.49 pt</t>
+          <t xml:space="preserve">全社 12.86 pt / 補助 17 pt / 他 4.5 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.02 pt / 補助 17 pt / 他 3.5 pt</t>
+          <t xml:space="preserve">全社 13.29 pt / 補助 17 pt / 他 4.5 pt</t>
         </is>
       </c>
     </row>
@@ -4322,17 +4322,17 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.51 % / 補助 4.48 % / 他 1.81 %</t>
+          <t xml:space="preserve">全社 3.5 % / 補助 4.48 % / 他 1.8 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.05 % / 補助 3.7 % / 他 1.73 %</t>
+          <t xml:space="preserve">全社 3.03 % / 補助 3.7 % / 他 1.7 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.63 % / 補助 3.06 % / 他 1.65 %</t>
+          <t xml:space="preserve">全社 2.61 % / 補助 3.06 % / 他 1.6 %</t>
         </is>
       </c>
     </row>
@@ -4508,17 +4508,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.1 倍 / 補助 3.85 倍 / 他 5.22 倍</t>
+          <t xml:space="preserve">全社 4.13 倍 / 補助 3.85 倍 / 他 5.33 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.09 倍 / 補助 4.93 倍 / 他 5.78 倍</t>
+          <t xml:space="preserve">全社 5.14 倍 / 補助 4.93 倍 / 他 6.03 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.3 倍 / 補助 6.28 倍 / 他 6.39 倍</t>
+          <t xml:space="preserve">全社 6.37 倍 / 補助 6.28 倍 / 他 6.81 倍</t>
         </is>
       </c>
     </row>
@@ -4694,17 +4694,17 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 63.72 %</t>
+          <t xml:space="preserve">構成比 63.5 %</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 66.93 %</t>
+          <t xml:space="preserve">構成比 66.51 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 69.99 %</t>
+          <t xml:space="preserve">構成比 69.39 %</t>
         </is>
       </c>
     </row>
@@ -4756,17 +4756,17 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21 % / 他 5 %</t>
+          <t xml:space="preserve">補助 21 % / 他 5.99 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21 % / 他 5 %</t>
+          <t xml:space="preserve">補助 21 % / 他 6 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21 % / 他 5 %</t>
+          <t xml:space="preserve">補助 21 % / 他 6 %</t>
         </is>
       </c>
     </row>
@@ -4818,17 +4818,17 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2.16 pt</t>
+          <t xml:space="preserve">差 -2.17 pt</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -1.83 pt</t>
+          <t xml:space="preserve">差 -1.84 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -1.51 pt</t>
+          <t xml:space="preserve">差 -1.5 pt</t>
         </is>
       </c>
     </row>
@@ -4880,17 +4880,17 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 5.09 pt</t>
+          <t xml:space="preserve">差 4.96 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.28 pt</t>
+          <t xml:space="preserve">差 6 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 7.27 pt</t>
+          <t xml:space="preserve">差 6.84 pt</t>
         </is>
       </c>
     </row>
@@ -4942,17 +4942,17 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.214 億円/人 / 他 0.608 億円/人</t>
+          <t xml:space="preserve">補助 1.214 億円/人 / 他 0.614 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.413 億円/人 / 他 0.629 億円/人</t>
+          <t xml:space="preserve">補助 1.413 億円/人 / 他 0.641 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.643 億円/人 / 他 0.651 億円/人</t>
+          <t xml:space="preserve">補助 1.643 億円/人 / 他 0.67 億円/人</t>
         </is>
       </c>
     </row>
@@ -5066,17 +5066,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 87.66 %</t>
+          <t xml:space="preserve">寄与率 85.39 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 89.33 %</t>
+          <t xml:space="preserve">寄与率 87 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.58 %</t>
+          <t xml:space="preserve">寄与率 88.29 %</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2">
         <v>-10</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="B164" s="2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMSwwLjJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMCwwLjAzXSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MzAsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnt9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLjIxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOCI6MC45MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTExIjoxMi43NiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjozLjE4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNDgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0Ljg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOCI6MC45NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTExIjoxMy4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjozLjM0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjYuODQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTgiOjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMSI6MTQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6My41LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4yLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn19</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMSwwLjJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMCwwLjAzXSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MzAsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnt9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLjIxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOCI6MC45MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTExIjoxMi43NiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjozLjE4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNDgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0Ljg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOCI6MC45NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTExIjoxMy4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjozLjM0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjYuODQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTgiOjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMSI6MTQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6My41LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4yLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn19</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -94,15 +94,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -153,85 +153,67 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申請区分</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一般企業（100億宣言企業以外）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">15指標・目標（指標名に第6次定義を併記）</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">計画値</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">単位</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">目標下限</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">計画上限</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">扱い</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全社年平均売上高成長率（第6次定義：undefined）</t>
-        </is>
-      </c>
-      <c r="B7" s="2">
-        <v>15.51906107932668</v>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">%/年</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">努力</t>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">制度上の必須条件</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目標値</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">判定</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社売上高増加額（第6次定義：undefined）</t>
+          <t xml:space="preserve">全社年平均売上高成長率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>107.63</v>
+        <v>15.51906107932668</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">%/年</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -241,27 +223,27 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社の従業員1人当たり給与支給総額の年平均上昇率（最新決算期→基準年度）（第6次定義：undefined）</t>
+          <t xml:space="preserve">全社売上高増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>8.341691035790255</v>
+        <v>107.63</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%/年</t>
+          <t xml:space="preserve">億円</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -271,27 +253,27 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業売上高／全社売上高（第6次定義：undefined）</t>
+          <t xml:space="preserve">全社の従業員1人当たり給与支給総額の年平均上昇率（最新決算期→基準年度）（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>69.38995332441166</v>
+        <v>8.332988192871005</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%</t>
+          <t xml:space="preserve">%/年</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
@@ -301,27 +283,27 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">参考</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業年平均売上高成長率（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業売上高／全社売上高（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>21.000508463435665</v>
+        <v>69.38995332441166</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%/年</t>
+          <t xml:space="preserve">%</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
@@ -331,27 +313,27 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業売上高増加額（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業年平均売上高成長率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>92.59</v>
+        <v>21.000508463435665</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">%/年</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
@@ -361,27 +343,27 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業年平均労働生産性の伸び（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業売上高増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>17.95685023536151</v>
+        <v>92.59</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%/年</t>
+          <t xml:space="preserve">億円</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
@@ -391,27 +373,27 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業付加価値増加額（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業年平均労働生産性の伸び（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>25.279999999999994</v>
+        <v>18.06480348374826</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">%/年</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
@@ -421,27 +403,27 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業付加価値増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>6.999648336675568</v>
+        <v>25.279999999999994</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%/年</t>
+          <t xml:space="preserve">億円</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
@@ -451,27 +433,27 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業従業員給与支給総額の増加額（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>3.7799999999999994</v>
+        <v>7.099090446266931</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">億円</t>
+          <t xml:space="preserve">%/年</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
@@ -481,27 +463,27 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">投資額／全社売上高（第6次定義：undefined）</t>
+          <t xml:space="preserve">補助事業従業員給与支給総額の増加額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>30</v>
+        <v>3.7799999999999994</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%</t>
+          <t xml:space="preserve">億円</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
@@ -511,18 +493,18 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">参考</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">付加価値増加額／補助金額（第6次定義：undefined）</t>
+          <t xml:space="preserve">投資額／全社売上高（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>168.5333333333333</v>
+        <v>30</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -531,7 +513,7 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
@@ -541,27 +523,27 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">努力</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ローカルベンチマーク財務分析結果（第6次定義：undefined）</t>
+          <t xml:space="preserve">付加価値増加額／補助金額（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>23</v>
+        <v>168.5333333333333</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">点</t>
+          <t xml:space="preserve">%</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
@@ -571,27 +553,27 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">参考</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">年平均役員目標賃上げ率（第6次定義：undefined）</t>
+          <t xml:space="preserve">ローカルベンチマーク財務分析結果（第6次定義：undefined）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>5.7715899735125475</v>
+        <v>23</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">%/年</t>
+          <t xml:space="preserve">点</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
@@ -601,37 +583,67 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">参考</t>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">年平均役員目標賃上げ率（第6次定義：undefined）</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>5.7715899735125475</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%/年</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目標未設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">役員給与支給総額の増加額（第6次定義：undefined）</t>
         </is>
       </c>
-      <c r="B21" s="2">
+      <c r="B22" s="2">
         <v>0.10999999999999999</v>
       </c>
-      <c r="C21" s="0" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">億円</t>
         </is>
       </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参考</t>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目標未設定</t>
         </is>
       </c>
     </row>
@@ -1088,13 +1100,13 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <v>1.2481644640234943</v>
+        <v>1.198871650211565</v>
       </c>
       <c r="C27" s="2">
-        <v>1.258741258741259</v>
+        <v>1.2295081967213117</v>
       </c>
       <c r="D27" s="2">
-        <v>1.0666666666666667</v>
+        <v>1.0596026490066224</v>
       </c>
     </row>
   </sheetData>
@@ -1103,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -1342,31 +1354,31 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C6" s="2">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="D6" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E6" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H6" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J6" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -1444,37 +1456,37 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>33.21</v>
+        <v>32.65</v>
       </c>
       <c r="C9" s="2">
-        <v>34.86</v>
+        <v>34.52</v>
       </c>
       <c r="D9" s="2">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>28.419999999999998</v>
+        <v>28.43</v>
       </c>
       <c r="F9" s="2">
-        <v>38.78</v>
+        <v>38.8</v>
       </c>
       <c r="G9" s="2">
-        <v>49.15</v>
+        <v>49.19</v>
       </c>
       <c r="H9" s="2">
-        <v>53.21</v>
+        <v>53.269999999999996</v>
       </c>
       <c r="I9" s="2">
-        <v>57.739999999999995</v>
+        <v>57.82</v>
       </c>
       <c r="J9" s="2">
-        <v>62.83</v>
+        <v>62.93</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-8 うち役員の人件費（億円）</t>
+          <t xml:space="preserve">2-8 うち役員の人件費（自動計算）（億円）</t>
         </is>
       </c>
       <c r="B10" s="2">
@@ -1512,31 +1524,31 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0.91</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="C11" s="2">
-        <v>0.96</v>
+        <v>0.8600000000000001</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E11" s="2">
-        <v>0.8200000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="F11" s="2">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="G11" s="2">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="H11" s="2">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="I11" s="2">
-        <v>1.4100000000000001</v>
+        <v>1.34</v>
       </c>
       <c r="J11" s="2">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -1546,44 +1558,44 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="C12" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D12" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E12" s="2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="F12" s="2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G12" s="2">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="H12" s="2">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="J12" s="2">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-11 うち従業員の人件費（億円）</t>
+          <t xml:space="preserve">2-11 うち従業員の人件費（自動計算）（億円）</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>12.760000000000002</v>
+        <v>12.29</v>
       </c>
       <c r="C13" s="2">
-        <v>13.379999999999999</v>
+        <v>13.129999999999999</v>
       </c>
       <c r="D13" s="2">
         <v>14</v>
@@ -1614,31 +1626,31 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>12.760000000000002</v>
+        <v>11.67</v>
       </c>
       <c r="C14" s="2">
-        <v>13.379999999999999</v>
+        <v>12.469999999999999</v>
       </c>
       <c r="D14" s="2">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="E14" s="2">
-        <v>11.73</v>
+        <v>11.31</v>
       </c>
       <c r="F14" s="2">
-        <v>15.5</v>
+        <v>15.06</v>
       </c>
       <c r="G14" s="2">
-        <v>19.27</v>
+        <v>18.810000000000002</v>
       </c>
       <c r="H14" s="2">
-        <v>20.96</v>
+        <v>20.47</v>
       </c>
       <c r="I14" s="2">
-        <v>22.810000000000002</v>
+        <v>22.29</v>
       </c>
       <c r="J14" s="2">
-        <v>24.84</v>
+        <v>24.29</v>
       </c>
     </row>
     <row r="15">
@@ -1648,31 +1660,31 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="C15" s="2">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="D15" s="2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E15" s="2">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="F15" s="2">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="G15" s="2">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="H15" s="2">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="J15" s="2">
-        <v>0</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="16">
@@ -1682,31 +1694,31 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>3.1799999999999997</v>
+        <v>2.45</v>
       </c>
       <c r="C16" s="2">
-        <v>3.34</v>
+        <v>2.58</v>
       </c>
       <c r="D16" s="2">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="E16" s="2">
-        <v>3.67</v>
+        <v>3.37</v>
       </c>
       <c r="F16" s="2">
-        <v>5.83</v>
+        <v>5.53</v>
       </c>
       <c r="G16" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="H16" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="I16" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J16" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="17">
@@ -1716,31 +1728,31 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="C17" s="2">
-        <v>0</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="D17" s="2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E17" s="2">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="F17" s="2">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="G17" s="2">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="H17" s="2">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="J17" s="2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18">
@@ -1750,31 +1762,31 @@
         </is>
       </c>
       <c r="B18" s="4">
-        <v>10.440000000000005</v>
+        <v>11.000000000000007</v>
       </c>
       <c r="C18" s="4">
-        <v>10.959999999999997</v>
+        <v>11.299999999999997</v>
       </c>
       <c r="D18" s="4">
-        <v>11.5</v>
+        <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>9.000000000000004</v>
+        <v>8.990000000000002</v>
       </c>
       <c r="F18" s="4">
-        <v>13.699999999999996</v>
+        <v>13.679999999999993</v>
       </c>
       <c r="G18" s="4">
-        <v>18.440000000000005</v>
+        <v>18.4</v>
       </c>
       <c r="H18" s="4">
-        <v>25.00999999999997</v>
+        <v>24.949999999999967</v>
       </c>
       <c r="I18" s="4">
-        <v>33.08999999999996</v>
+        <v>33.009999999999955</v>
       </c>
       <c r="J18" s="4">
-        <v>42.99999999999998</v>
+        <v>42.89999999999997</v>
       </c>
     </row>
     <row r="19">
@@ -1784,31 +1796,31 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>7.653958944281528</v>
+        <v>8.064516129032263</v>
       </c>
       <c r="C19" s="2">
-        <v>7.6536312849162</v>
+        <v>7.8910614525139655</v>
       </c>
       <c r="D19" s="2">
-        <v>7.666666666666666</v>
+        <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.978723404255322</v>
+        <v>7.969858156028371</v>
       </c>
       <c r="F19" s="2">
-        <v>8.79840729561364</v>
+        <v>8.785562905401061</v>
       </c>
       <c r="G19" s="2">
-        <v>9.278454261849655</v>
+        <v>9.258327463017006</v>
       </c>
       <c r="H19" s="2">
-        <v>10.937636665791995</v>
+        <v>10.911396833726918</v>
       </c>
       <c r="I19" s="2">
-        <v>12.526499091459709</v>
+        <v>12.496214415505738</v>
       </c>
       <c r="J19" s="2">
-        <v>14.035316773835552</v>
+        <v>14.002676502268487</v>
       </c>
     </row>
     <row r="20">
@@ -1818,31 +1830,687 @@
         </is>
       </c>
       <c r="B20" s="4">
-        <v>10.440000000000005</v>
+        <v>11.000000000000007</v>
       </c>
       <c r="C20" s="4">
-        <v>10.959999999999997</v>
+        <v>11.299999999999997</v>
       </c>
       <c r="D20" s="4">
-        <v>11.5</v>
+        <v>11.600000000000001</v>
       </c>
       <c r="E20" s="4">
-        <v>9.000000000000004</v>
+        <v>8.990000000000002</v>
       </c>
       <c r="F20" s="4">
-        <v>13.699999999999996</v>
+        <v>13.679999999999993</v>
       </c>
       <c r="G20" s="4">
-        <v>18.440000000000005</v>
+        <v>18.4</v>
       </c>
       <c r="H20" s="4">
-        <v>25.00999999999997</v>
+        <v>24.949999999999967</v>
       </c>
       <c r="I20" s="4">
-        <v>33.08999999999996</v>
+        <v>33.009999999999955</v>
       </c>
       <c r="J20" s="4">
-        <v>42.99999999999998</v>
+        <v>42.89999999999997</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-19 税引前当期純利益（モデル未対応）（億円）</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-20 当期純利益（モデル未対応）（億円）</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-21 給与支給総額（常時使用する従業員）（億円）</t>
+        </is>
+      </c>
+      <c r="B23" s="2">
+        <v>12.29</v>
+      </c>
+      <c r="C23" s="2">
+        <v>13.129999999999999</v>
+      </c>
+      <c r="D23" s="2">
+        <v>14</v>
+      </c>
+      <c r="E23" s="2">
+        <v>11.73</v>
+      </c>
+      <c r="F23" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="G23" s="2">
+        <v>19.27</v>
+      </c>
+      <c r="H23" s="2">
+        <v>20.96</v>
+      </c>
+      <c r="I23" s="2">
+        <v>22.810000000000002</v>
+      </c>
+      <c r="J23" s="2">
+        <v>24.84</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-22 給与支給総額（役員）（億円）</t>
+        </is>
+      </c>
+      <c r="B24" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1.27</v>
+      </c>
+      <c r="H24" s="2">
+        <v>1.35</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1.4100000000000001</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-23 減価償却費（合計）（億円）</t>
+        </is>
+      </c>
+      <c r="B25" s="2">
+        <v>3.1799999999999997</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3.34</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3.67</v>
+      </c>
+      <c r="F25" s="2">
+        <v>5.83</v>
+      </c>
+      <c r="G25" s="2">
+        <v>8</v>
+      </c>
+      <c r="H25" s="2">
+        <v>8</v>
+      </c>
+      <c r="I25" s="2">
+        <v>8</v>
+      </c>
+      <c r="J25" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-24 付加価値額（億円）</t>
+        </is>
+      </c>
+      <c r="B26" s="4">
+        <v>27.380000000000006</v>
+      </c>
+      <c r="C26" s="4">
+        <v>28.729999999999997</v>
+      </c>
+      <c r="D26" s="4">
+        <v>30.1</v>
+      </c>
+      <c r="E26" s="4">
+        <v>25.21</v>
+      </c>
+      <c r="F26" s="4">
+        <v>36.059999999999995</v>
+      </c>
+      <c r="G26" s="4">
+        <v>46.940000000000005</v>
+      </c>
+      <c r="H26" s="4">
+        <v>55.25999999999997</v>
+      </c>
+      <c r="I26" s="4">
+        <v>65.22999999999996</v>
+      </c>
+      <c r="J26" s="4">
+        <v>77.21999999999997</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-25 付加価値増加率（%）</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C27" s="2">
+        <v>4.930606281957606</v>
+      </c>
+      <c r="D27" s="2">
+        <v>4.768534632788035</v>
+      </c>
+      <c r="E27" s="2">
+        <v>-16.24584717607973</v>
+      </c>
+      <c r="F27" s="2">
+        <v>43.03847679492263</v>
+      </c>
+      <c r="G27" s="2">
+        <v>30.17193566278429</v>
+      </c>
+      <c r="H27" s="2">
+        <v>17.724755006391057</v>
+      </c>
+      <c r="I27" s="2">
+        <v>18.041983351429593</v>
+      </c>
+      <c r="J27" s="2">
+        <v>18.381112984822966</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-26 売上高付加価値率（%）</t>
+        </is>
+      </c>
+      <c r="B28" s="2">
+        <v>20.073313782991207</v>
+      </c>
+      <c r="C28" s="2">
+        <v>20.062849162011172</v>
+      </c>
+      <c r="D28" s="2">
+        <v>20.06666666666667</v>
+      </c>
+      <c r="E28" s="2">
+        <v>22.349290780141846</v>
+      </c>
+      <c r="F28" s="2">
+        <v>23.15843555327211</v>
+      </c>
+      <c r="G28" s="2">
+        <v>23.618798430109692</v>
+      </c>
+      <c r="H28" s="2">
+        <v>24.166885331933866</v>
+      </c>
+      <c r="I28" s="2">
+        <v>24.69336765596607</v>
+      </c>
+      <c r="J28" s="2">
+        <v>25.204817704083286</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-27 常時使用する従業員数（就業時間換算）（人）</t>
+        </is>
+      </c>
+      <c r="B29" s="2">
+        <v>210</v>
+      </c>
+      <c r="C29" s="2">
+        <v>220</v>
+      </c>
+      <c r="D29" s="2">
+        <v>230</v>
+      </c>
+      <c r="E29" s="2">
+        <v>169</v>
+      </c>
+      <c r="F29" s="2">
+        <v>210</v>
+      </c>
+      <c r="G29" s="2">
+        <v>249</v>
+      </c>
+      <c r="H29" s="2">
+        <v>256</v>
+      </c>
+      <c r="I29" s="2">
+        <v>262</v>
+      </c>
+      <c r="J29" s="2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-28 役員数（人）</t>
+        </is>
+      </c>
+      <c r="B30" s="2">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2">
+        <v>5</v>
+      </c>
+      <c r="E30" s="2">
+        <v>5</v>
+      </c>
+      <c r="F30" s="2">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2">
+        <v>5</v>
+      </c>
+      <c r="H30" s="2">
+        <v>5</v>
+      </c>
+      <c r="I30" s="2">
+        <v>5</v>
+      </c>
+      <c r="J30" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-29 従業員1人当たり給与支給総額（億円/人）</t>
+        </is>
+      </c>
+      <c r="B31" s="2">
+        <v>0.05852380952380952</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.059681818181818176</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.06086956521739131</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.06940828402366864</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.07380952380952381</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.07738955823293173</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0.081875</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0.08706106870229008</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0.09234200743494424</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-30 従業員1人当たり給与支給総額の上昇率（%）</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C32" s="2">
+        <v>1.9786966491604385</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1.9901321235802572</v>
+      </c>
+      <c r="E32" s="2">
+        <v>14.027895181741323</v>
+      </c>
+      <c r="F32" s="2">
+        <v>6.3410871595014795</v>
+      </c>
+      <c r="G32" s="2">
+        <v>4.850369218810724</v>
+      </c>
+      <c r="H32" s="2">
+        <v>5.795926310326949</v>
+      </c>
+      <c r="I32" s="2">
+        <v>6.334129712720693</v>
+      </c>
+      <c r="J32" s="2">
+        <v>6.0657867073888205</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-31 役員1人当たり給与支給総額（億円/人）</t>
+        </is>
+      </c>
+      <c r="B33" s="2">
+        <v>0.182</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.192</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.164</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.21000000000000002</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0.254</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0.28200000000000003</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0.296</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-32 役員1人当たり給与支給総額の上昇率（%）</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C34" s="2">
+        <v>5.494505494505497</v>
+      </c>
+      <c r="D34" s="2">
+        <v>4.166666666666674</v>
+      </c>
+      <c r="E34" s="2">
+        <v>-18.000000000000004</v>
+      </c>
+      <c r="F34" s="2">
+        <v>28.04878048780488</v>
+      </c>
+      <c r="G34" s="2">
+        <v>20.952380952380945</v>
+      </c>
+      <c r="H34" s="2">
+        <v>6.299212598425208</v>
+      </c>
+      <c r="I34" s="2">
+        <v>4.444444444444451</v>
+      </c>
+      <c r="J34" s="2">
+        <v>4.964539007092172</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-33 労働生産性（億円/人）</t>
+        </is>
+      </c>
+      <c r="B35" s="2">
+        <v>0.12734883720930235</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.12768888888888888</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0.12808510638297874</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.14488505747126437</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.16772093023255813</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0.18480314960629923</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0.21172413793103437</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0.24430711610486877</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0.28182481751824806</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-34 EBITDA（億円）</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <v>14.180000000000007</v>
+      </c>
+      <c r="C36" s="4">
+        <v>14.639999999999997</v>
+      </c>
+      <c r="D36" s="4">
+        <v>15.100000000000001</v>
+      </c>
+      <c r="E36" s="4">
+        <v>12.660000000000002</v>
+      </c>
+      <c r="F36" s="4">
+        <v>19.50999999999999</v>
+      </c>
+      <c r="G36" s="4">
+        <v>26.4</v>
+      </c>
+      <c r="H36" s="4">
+        <v>32.94999999999997</v>
+      </c>
+      <c r="I36" s="4">
+        <v>41.009999999999955</v>
+      </c>
+      <c r="J36" s="4">
+        <v>50.89999999999997</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-35 EBITDAマージン（%）</t>
+        </is>
+      </c>
+      <c r="B37" s="2">
+        <v>10.395894428152497</v>
+      </c>
+      <c r="C37" s="2">
+        <v>10.223463687150836</v>
+      </c>
+      <c r="D37" s="2">
+        <v>10.066666666666668</v>
+      </c>
+      <c r="E37" s="2">
+        <v>11.223404255319151</v>
+      </c>
+      <c r="F37" s="2">
+        <v>12.529702652366575</v>
+      </c>
+      <c r="G37" s="2">
+        <v>13.28368722954614</v>
+      </c>
+      <c r="H37" s="2">
+        <v>14.410041109070223</v>
+      </c>
+      <c r="I37" s="2">
+        <v>15.524682010902469</v>
+      </c>
+      <c r="J37" s="2">
+        <v>16.613898227633246</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2-36 EBITDA増加率（%）</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C38" s="2">
+        <v>3.2440056417488705</v>
+      </c>
+      <c r="D38" s="2">
+        <v>3.1420765027322606</v>
+      </c>
+      <c r="E38" s="2">
+        <v>-16.158940397350985</v>
+      </c>
+      <c r="F38" s="2">
+        <v>54.107424960505426</v>
+      </c>
+      <c r="G38" s="2">
+        <v>35.315222962583334</v>
+      </c>
+      <c r="H38" s="2">
+        <v>24.810606060605945</v>
+      </c>
+      <c r="I38" s="2">
+        <v>24.46130500758723</v>
+      </c>
+      <c r="J38" s="2">
+        <v>24.116069251402152</v>
       </c>
     </row>
   </sheetData>
@@ -2158,13 +2826,13 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <v>6.48</v>
+        <v>6.779999999999998</v>
       </c>
       <c r="C8" s="4">
-        <v>6.840000000000003</v>
+        <v>7.040000000000003</v>
       </c>
       <c r="D8" s="4">
-        <v>7.200000000000003</v>
+        <v>7.300000000000004</v>
       </c>
       <c r="E8" s="4">
         <v>4.300000000000001</v>
@@ -2192,13 +2860,13 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>9.000000000000002</v>
+        <v>9.416666666666664</v>
       </c>
       <c r="C9" s="2">
-        <v>9.000000000000004</v>
+        <v>9.263157894736846</v>
       </c>
       <c r="D9" s="2">
-        <v>9.000000000000004</v>
+        <v>9.125000000000005</v>
       </c>
       <c r="E9" s="2">
         <v>10.750000000000002</v>
@@ -2226,10 +2894,10 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>5.4</v>
+        <v>5.19</v>
       </c>
       <c r="C10" s="2">
-        <v>5.7</v>
+        <v>5.59</v>
       </c>
       <c r="D10" s="2">
         <v>6</v>
@@ -2328,13 +2996,13 @@
         </is>
       </c>
       <c r="B13" s="4">
-        <v>14.040000000000001</v>
+        <v>14.129999999999999</v>
       </c>
       <c r="C13" s="4">
-        <v>14.820000000000004</v>
+        <v>14.910000000000004</v>
       </c>
       <c r="D13" s="4">
-        <v>15.600000000000003</v>
+        <v>15.700000000000005</v>
       </c>
       <c r="E13" s="4">
         <v>10</v>
@@ -2367,13 +3035,13 @@
         </is>
       </c>
       <c r="C14" s="2">
-        <v>5.55555555555558</v>
+        <v>5.520169851380086</v>
       </c>
       <c r="D14" s="2">
-        <v>5.263157894736836</v>
+        <v>5.2984574111334615</v>
       </c>
       <c r="E14" s="2">
-        <v>-35.89743589743591</v>
+        <v>-36.305732484076444</v>
       </c>
       <c r="F14" s="2">
         <v>100</v>
@@ -2407,22 +3075,22 @@
         <v>100</v>
       </c>
       <c r="E15" s="2">
-        <v>38.33</v>
+        <v>38</v>
       </c>
       <c r="F15" s="2">
-        <v>76.67</v>
+        <v>77</v>
       </c>
       <c r="G15" s="2">
         <v>115</v>
       </c>
       <c r="H15" s="2">
-        <v>119.6</v>
+        <v>120</v>
       </c>
       <c r="I15" s="2">
-        <v>124.38</v>
+        <v>124</v>
       </c>
       <c r="J15" s="2">
-        <v>129.36</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">
@@ -2466,31 +3134,31 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0.060000000000000005</v>
+        <v>0.05766666666666667</v>
       </c>
       <c r="C17" s="2">
-        <v>0.060000000000000005</v>
+        <v>0.05884210526315789</v>
       </c>
       <c r="D17" s="2">
         <v>0.06</v>
       </c>
       <c r="E17" s="2">
-        <v>0.08687711974954344</v>
+        <v>0.08763157894736842</v>
       </c>
       <c r="F17" s="2">
-        <v>0.08699621755575844</v>
+        <v>0.08662337662337662</v>
       </c>
       <c r="G17" s="2">
         <v>0.08695652173913043</v>
       </c>
       <c r="H17" s="2">
-        <v>0.09306020066889634</v>
+        <v>0.09275000000000001</v>
       </c>
       <c r="I17" s="2">
-        <v>0.09953368708795628</v>
+        <v>0.09983870967741935</v>
       </c>
       <c r="J17" s="2">
-        <v>0.10652442795299936</v>
+        <v>0.10682170542635658</v>
       </c>
     </row>
     <row r="18">
@@ -2505,28 +3173,28 @@
         </is>
       </c>
       <c r="C18" s="2">
-        <v>0</v>
+        <v>2.0383328262853606</v>
       </c>
       <c r="D18" s="2">
-        <v>-1.1102230246251565e-14</v>
+        <v>1.9677996422182487</v>
       </c>
       <c r="E18" s="2">
-        <v>44.79519958257241</v>
+        <v>46.05263157894737</v>
       </c>
       <c r="F18" s="2">
-        <v>0.13708765502165043</v>
+        <v>-1.1505011505011598</v>
       </c>
       <c r="G18" s="2">
-        <v>-0.04562935923342337</v>
+        <v>0.3845903135388795</v>
       </c>
       <c r="H18" s="2">
-        <v>7.019230769230789</v>
+        <v>6.662500000000016</v>
       </c>
       <c r="I18" s="2">
-        <v>6.956235181667281</v>
+        <v>7.642813668376647</v>
       </c>
       <c r="J18" s="2">
-        <v>7.023492316591762</v>
+        <v>6.994276840615643</v>
       </c>
     </row>
     <row r="19">
@@ -2606,31 +3274,31 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>0.15260869565217391</v>
+        <v>0.15358695652173912</v>
       </c>
       <c r="C21" s="2">
-        <v>0.1527835051546392</v>
+        <v>0.1537113402061856</v>
       </c>
       <c r="D21" s="2">
-        <v>0.15294117647058827</v>
+        <v>0.15392156862745102</v>
       </c>
       <c r="E21" s="2">
-        <v>0.24795437639474338</v>
+        <v>0.25</v>
       </c>
       <c r="F21" s="2">
-        <v>0.25422651582560063</v>
+        <v>0.25316455696202533</v>
       </c>
       <c r="G21" s="2">
         <v>0.2564102564102564</v>
       </c>
       <c r="H21" s="2">
-        <v>0.30246710526315784</v>
+        <v>0.3014754098360655</v>
       </c>
       <c r="I21" s="2">
-        <v>0.35678113625573665</v>
+        <v>0.3578571428571428</v>
       </c>
       <c r="J21" s="2">
-        <v>0.4208282582216808</v>
+        <v>0.42198473282442744</v>
       </c>
     </row>
     <row r="22">
@@ -3114,47 +3782,47 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.35 % / 補助 23 % / 他 25.85 %</t>
+          <t xml:space="preserve">全社 23.94 % / 補助 22.58 % / 他 25.45 %</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.34 % / 補助 23 % / 他 25.86 %</t>
+          <t xml:space="preserve">全社 24.11 % / 補助 22.74 % / 他 25.65 %</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.33 % / 補助 23 % / 他 25.86 %</t>
+          <t xml:space="preserve">全社 24.27 % / 補助 22.88 % / 他 25.86 %</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.2 % / 補助 24.25 % / 他 25.71 %</t>
+          <t xml:space="preserve">全社 25.2 % / 補助 24.25 % / 他 25.73 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.91 % / 補助 24.25 % / 他 25.6 %</t>
+          <t xml:space="preserve">全社 24.92 % / 補助 24.25 % / 他 25.62 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.73 % / 補助 24.25 % / 他 25.46 %</t>
+          <t xml:space="preserve">全社 24.75 % / 補助 24.25 % / 他 25.51 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.27 % / 補助 22.25 % / 他 25.04 %</t>
+          <t xml:space="preserve">全社 23.3 % / 補助 22.25 % / 他 25.11 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.86 % / 補助 20.46 % / 他 24.63 %</t>
+          <t xml:space="preserve">全社 21.89 % / 補助 20.46 % / 他 24.72 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20.51 % / 補助 18.87 % / 他 24.22 %</t>
+          <t xml:space="preserve">全社 20.54 % / 補助 18.87 % / 他 24.32 %</t>
         </is>
       </c>
     </row>
@@ -3176,47 +3844,47 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.65 % / 補助 9 % / 他 6.15 %</t>
+          <t xml:space="preserve">全社 8.06 % / 補助 9.42 % / 他 6.55 %</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.65 % / 補助 9 % / 他 6.13 %</t>
+          <t xml:space="preserve">全社 7.89 % / 補助 9.26 % / 他 6.34 %</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.67 % / 補助 9 % / 他 6.14 %</t>
+          <t xml:space="preserve">全社 7.73 % / 補助 9.13 % / 他 6.14 %</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.98 % / 補助 10.75 % / 他 6.46 %</t>
+          <t xml:space="preserve">全社 7.97 % / 補助 10.75 % / 他 6.44 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.8 % / 補助 10.75 % / 他 6.74 %</t>
+          <t xml:space="preserve">全社 8.79 % / 補助 10.75 % / 他 6.71 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.28 % / 補助 10.75 % / 他 7.04 %</t>
+          <t xml:space="preserve">全社 9.26 % / 補助 10.75 % / 他 6.99 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.94 % / 補助 12.75 % / 他 7.79 %</t>
+          <t xml:space="preserve">全社 10.91 % / 補助 12.75 % / 他 7.72 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.53 % / 補助 14.54 % / 他 8.53 %</t>
+          <t xml:space="preserve">全社 12.5 % / 補助 14.54 % / 他 8.44 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.04 % / 補助 16.13 % / 他 9.29 %</t>
+          <t xml:space="preserve">全社 14 % / 補助 16.13 % / 他 9.18 %</t>
         </is>
       </c>
     </row>
@@ -3238,47 +3906,47 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.99 % / 補助 11.5 % / 他 8.29 %</t>
+          <t xml:space="preserve">全社 10.4 % / 補助 11.92 % / 他 8.7 %</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.99 % / 補助 11.5 % / 他 8.27 %</t>
+          <t xml:space="preserve">全社 10.22 % / 補助 11.76 % / 他 8.48 %</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10 % / 補助 11.5 % / 他 8.29 %</t>
+          <t xml:space="preserve">全社 10.07 % / 補助 11.63 % / 他 8.29 %</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.23 % / 補助 16.18 % / 他 8.52 %</t>
+          <t xml:space="preserve">全社 11.22 % / 補助 16.18 % / 他 8.5 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.54 % / 補助 16.16 % / 他 8.72 %</t>
+          <t xml:space="preserve">全社 12.53 % / 補助 16.16 % / 他 8.69 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.3 % / 補助 16.17 % / 他 8.94 %</t>
+          <t xml:space="preserve">全社 13.28 % / 補助 16.17 % / 他 8.89 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.44 % / 補助 17.22 % / 他 9.59 %</t>
+          <t xml:space="preserve">全社 14.41 % / 補助 17.22 % / 他 9.51 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.55 % / 補助 18.24 % / 他 10.23 %</t>
+          <t xml:space="preserve">全社 15.52 % / 補助 18.24 % / 他 10.14 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 16.65 % / 補助 19.19 % / 他 10.89 %</t>
+          <t xml:space="preserve">全社 16.61 % / 補助 19.19 % / 他 10.78 %</t>
         </is>
       </c>
     </row>
@@ -3424,12 +4092,12 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.35 % / 補助 7.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 9.01 % / 補助 7.21 % / 他 11.02 %</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.34 % / 補助 7.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 9.17 % / 補助 7.36 % / 他 11.22 %</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
@@ -3548,12 +4216,12 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.02 % / 補助 8 % / 他 12.28 %</t>
+          <t xml:space="preserve">全社 9.68 % / 補助 7.71 % / 他 11.88 %</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.01 % / 補助 8 % / 他 12.29 %</t>
+          <t xml:space="preserve">全社 9.84 % / 補助 7.86 % / 他 12.08 %</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
@@ -3610,27 +4278,27 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">全社 0.059 億円/人 / 補助 0.058 億円/人 / 他 0.059 億円/人</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全社 0.06 億円/人 / 補助 0.059 億円/人 / 他 0.06 億円/人</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">全社 0.061 億円/人 / 補助 0.06 億円/人 / 他 0.062 億円/人</t>
         </is>
       </c>
-      <c r="E15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全社 0.061 億円/人 / 補助 0.06 億円/人 / 他 0.062 億円/人</t>
-        </is>
-      </c>
-      <c r="F15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全社 0.061 億円/人 / 補助 0.06 億円/人 / 他 0.062 億円/人</t>
-        </is>
-      </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.069 億円/人 / 補助 0.087 億円/人 / 他 0.064 億円/人</t>
+          <t xml:space="preserve">全社 0.069 億円/人 / 補助 0.088 億円/人 / 他 0.064 億円/人</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.087 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.087 億円/人 / 他 0.066 億円/人</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
@@ -3739,42 +4407,42 @@
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 -0.01 % / 補助 0 % / 他 -0 %</t>
+          <t xml:space="preserve">全社 1.98 % / 補助 2.04 % / 他 1.95 %</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 -0.01 % / 補助 -0 % / 他 0 %</t>
+          <t xml:space="preserve">全社 1.99 % / 補助 1.97 % / 他 2.02 %</t>
         </is>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.6 % / 補助 44.8 % / 他 3.96 %</t>
+          <t xml:space="preserve">全社 14.03 % / 補助 46.05 % / 他 4.2 %</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.1 % / 補助 0.14 % / 他 4.08 %</t>
+          <t xml:space="preserve">全社 6.34 % / 補助 -1.15 % / 他 3.54 %</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.52 % / 補助 -0.05 % / 他 3.94 %</t>
+          <t xml:space="preserve">全社 4.85 % / 補助 0.38 % / 他 4.2 %</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.96 % / 補助 7.02 % / 他 4.47 %</t>
+          <t xml:space="preserve">全社 5.8 % / 補助 6.66 % / 他 4.48 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6 % / 補助 6.96 % / 他 4.54 %</t>
+          <t xml:space="preserve">全社 6.33 % / 補助 7.64 % / 他 4.57 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.05 % / 補助 7.02 % / 他 4.47 %</t>
+          <t xml:space="preserve">全社 6.07 % / 補助 6.99 % / 他 4.53 %</t>
         </is>
       </c>
     </row>
@@ -3796,47 +4464,47 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.09 % / 補助 41.03 % / 他 59.7 %</t>
+          <t xml:space="preserve">全社 48.21 % / 補助 39.28 % / 他 57.74 %</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.07 % / 補助 41.03 % / 他 59.77 %</t>
+          <t xml:space="preserve">全社 49.04 % / 補助 40.04 % / 他 58.76 %</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50 % / 補助 41.03 % / 他 59.72 %</t>
+          <t xml:space="preserve">全社 49.83 % / 補助 40.76 % / 他 59.72 %</t>
         </is>
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.76 % / 補助 35.3 % / 他 59.26 %</t>
+          <t xml:space="preserve">全社 49.78 % / 補助 35.3 % / 他 59.3 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.87 % / 補助 35.35 % / 他 58.96 %</t>
+          <t xml:space="preserve">全社 45.9 % / 補助 35.35 % / 他 59.03 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 43.72 % / 補助 35.33 % / 他 58.54 %</t>
+          <t xml:space="preserve">全社 43.76 % / 補助 35.33 % / 他 58.68 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 40.33 % / 補助 32 % / 他 56.85 %</t>
+          <t xml:space="preserve">全社 40.37 % / 補助 32 % / 他 57.03 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 37.08 % / 補助 28.94 % / 他 55.24 %</t>
+          <t xml:space="preserve">全社 37.13 % / 補助 28.94 % / 他 55.46 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.04 % / 補助 26.21 % / 他 53.68 %</t>
+          <t xml:space="preserve">全社 34.08 % / 補助 26.21 % / 他 53.92 %</t>
         </is>
       </c>
     </row>
@@ -3920,27 +4588,27 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">全社 0.65 億円/人 / 補助 0.8 億円/人 / 他 0.537 億円/人</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">全社 0.651 億円/人 / 補助 0.8 億円/人 / 他 0.538 億円/人</t>
         </is>
       </c>
-      <c r="E20" s="0" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">全社 0.652 億円/人 / 補助 0.8 億円/人 / 他 0.538 億円/人</t>
         </is>
       </c>
-      <c r="F20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全社 0.652 億円/人 / 補助 0.8 億円/人 / 他 0.538 億円/人</t>
-        </is>
-      </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.665 億円/人 / 補助 1.044 億円/人 / 他 0.554 億円/人</t>
+          <t xml:space="preserve">全社 0.667 億円/人 / 補助 1.053 億円/人 / 他 0.556 億円/人</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.744 億円/人 / 補助 1.043 億円/人 / 他 0.571 億円/人</t>
+          <t xml:space="preserve">全社 0.741 億円/人 / 補助 1.039 億円/人 / 他 0.569 億円/人</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
@@ -3950,17 +4618,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.895 億円/人 / 補助 1.214 億円/人 / 他 0.614 億円/人</t>
+          <t xml:space="preserve">全社 0.893 億円/人 / 補助 1.21 億円/人 / 他 0.614 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.007 億円/人 / 補助 1.413 億円/人 / 他 0.641 億円/人</t>
+          <t xml:space="preserve">全社 1.008 億円/人 / 補助 1.417 億円/人 / 他 0.641 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.137 億円/人 / 補助 1.643 億円/人 / 他 0.67 億円/人</t>
+          <t xml:space="preserve">全社 1.139 億円/人 / 補助 1.648 億円/人 / 他 0.67 億円/人</t>
         </is>
       </c>
     </row>
@@ -3982,22 +4650,22 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.072 億円/人 / 他 0.033 億円/人</t>
+          <t xml:space="preserve">全社 0.052 億円/人 / 補助 0.075 億円/人 / 他 0.035 億円/人</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.072 億円/人 / 他 0.033 億円/人</t>
+          <t xml:space="preserve">全社 0.051 億円/人 / 補助 0.074 億円/人 / 他 0.034 億円/人</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.072 億円/人 / 他 0.033 億円/人</t>
+          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.073 億円/人 / 他 0.033 億円/人</t>
         </is>
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.053 億円/人 / 補助 0.112 億円/人 / 他 0.036 億円/人</t>
+          <t xml:space="preserve">全社 0.053 億円/人 / 補助 0.113 億円/人 / 他 0.036 億円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -4012,17 +4680,17 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.098 億円/人 / 補助 0.155 億円/人 / 他 0.048 億円/人</t>
+          <t xml:space="preserve">全社 0.097 億円/人 / 補助 0.154 億円/人 / 他 0.047 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.126 億円/人 / 補助 0.205 億円/人 / 他 0.055 億円/人</t>
+          <t xml:space="preserve">全社 0.126 億円/人 / 補助 0.206 億円/人 / 他 0.054 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.16 億円/人 / 補助 0.265 億円/人 / 他 0.062 億円/人</t>
+          <t xml:space="preserve">全社 0.159 億円/人 / 補助 0.266 億円/人 / 他 0.062 億円/人</t>
         </is>
       </c>
     </row>
@@ -4044,27 +4712,27 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.127 億円/人 / 補助 0.153 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.127 億円/人 / 補助 0.154 億円/人 / 他 0.108 億円/人</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.127 億円/人 / 補助 0.153 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.154 億円/人 / 他 0.108 億円/人</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.153 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.154 億円/人 / 他 0.108 億円/人</t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.144 億円/人 / 補助 0.248 億円/人 / 他 0.113 億円/人</t>
+          <t xml:space="preserve">全社 0.145 億円/人 / 補助 0.25 億円/人 / 他 0.114 億円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.168 億円/人 / 補助 0.254 億円/人 / 他 0.119 億円/人</t>
+          <t xml:space="preserve">全社 0.168 億円/人 / 補助 0.253 億円/人 / 他 0.118 億円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
@@ -4074,17 +4742,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.302 億円/人 / 他 0.133 億円/人</t>
+          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.301 億円/人 / 他 0.133 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.244 億円/人 / 補助 0.357 億円/人 / 他 0.143 億円/人</t>
+          <t xml:space="preserve">全社 0.244 億円/人 / 補助 0.358 億円/人 / 他 0.143 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.282 億円/人 / 補助 0.421 億円/人 / 他 0.154 億円/人</t>
+          <t xml:space="preserve">全社 0.282 億円/人 / 補助 0.422 億円/人 / 他 0.153 億円/人</t>
         </is>
       </c>
     </row>
@@ -4111,42 +4779,42 @@
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.87 % / 補助 5.56 % / 他 4.35 %</t>
+          <t xml:space="preserve">全社 4.76 % / 補助 5.56 % / 他 4.17 %</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.64 % / 補助 5.26 % / 他 4.17 %</t>
+          <t xml:space="preserve">全社 4.55 % / 補助 5.26 % / 他 4 %</t>
         </is>
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 -26.25 % / 補助 -61.67 % / 他 1 %</t>
+          <t xml:space="preserve">全社 -26.52 % / 補助 -62 % / 他 0.77 %</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.37 % / 補助 100.03 % / 他 1 %</t>
+          <t xml:space="preserve">全社 24.26 % / 補助 102.63 % / 他 1.53 %</t>
         </is>
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 18.95 % / 補助 49.99 % / 他 1 %</t>
+          <t xml:space="preserve">全社 18.57 % / 補助 49.35 % / 他 0.75 %</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.66 % / 補助 4 % / 他 1.5 %</t>
+          <t xml:space="preserve">全社 2.81 % / 補助 4.35 % / 他 1.49 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.67 % / 補助 4 % / 他 1.5 %</t>
+          <t xml:space="preserve">全社 2.34 % / 補助 3.33 % / 他 1.47 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.69 % / 補助 4 % / 他 1.5 %</t>
+          <t xml:space="preserve">全社 2.67 % / 補助 4.03 % / 他 1.45 %</t>
         </is>
       </c>
     </row>
@@ -4173,42 +4841,42 @@
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.12 pt / 補助 0 pt / 他 0 pt</t>
+          <t xml:space="preserve">全社 0.22 pt / 補助 0 pt / 他 0.18 pt</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.11 pt / 補助 0 pt / 他 -0 pt</t>
+          <t xml:space="preserve">全社 0.2 pt / 補助 0 pt / 他 0.17 pt</t>
         </is>
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.45 pt / 補助 11.67 pt / 他 3 pt</t>
+          <t xml:space="preserve">全社 1.72 pt / 補助 12 pt / 他 3.23 pt</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.67 pt / 補助 -0.03 pt / 他 3 pt</t>
+          <t xml:space="preserve">全社 13.78 pt / 補助 -2.63 pt / 他 2.47 pt</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.68 pt / 補助 0.01 pt / 他 3 pt</t>
+          <t xml:space="preserve">全社 9.06 pt / 補助 0.65 pt / 他 3.25 pt</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.4 pt / 補助 17 pt / 他 4.49 pt</t>
+          <t xml:space="preserve">全社 12.24 pt / 補助 16.65 pt / 他 4.5 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.86 pt / 補助 17 pt / 他 4.5 pt</t>
+          <t xml:space="preserve">全社 13.18 pt / 補助 17.67 pt / 他 4.53 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.29 pt / 補助 17 pt / 他 4.5 pt</t>
+          <t xml:space="preserve">全社 13.31 pt / 補助 16.97 pt / 他 4.55 pt</t>
         </is>
       </c>
     </row>
@@ -4416,17 +5084,17 @@
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.37 倍</t>
+          <t xml:space="preserve">全社 0.35 倍</t>
         </is>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.56 倍</t>
+          <t xml:space="preserve">全社 0.55 倍</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 倍</t>
+          <t xml:space="preserve">全社 0.66 倍</t>
         </is>
       </c>
       <c r="G28" s="0" t="inlineStr">
@@ -4478,17 +5146,17 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.28 倍 / 補助 4.6 倍 / 他 3.87 倍</t>
+          <t xml:space="preserve">全社 4.46 倍 / 補助 4.77 倍 / 他 4.06 倍</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.28 倍 / 補助 4.6 倍 / 他 3.86 倍</t>
+          <t xml:space="preserve">全社 4.38 倍 / 補助 4.71 倍 / 他 3.96 倍</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.29 倍 / 補助 4.6 倍 / 他 3.87 倍</t>
+          <t xml:space="preserve">全社 4.31 倍 / 補助 4.65 倍 / 他 3.87 倍</t>
         </is>
       </c>
       <c r="G29" s="0" t="inlineStr">
@@ -4498,27 +5166,27 @@
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.35 倍 / 補助 2.99 倍 / 他 4.4 倍</t>
+          <t xml:space="preserve">全社 3.35 倍 / 補助 2.99 倍 / 他 4.39 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.31 倍 / 補助 2.98 倍 / 他 4.69 倍</t>
+          <t xml:space="preserve">全社 3.3 倍 / 補助 2.98 倍 / 他 4.67 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.13 倍 / 補助 3.85 倍 / 他 5.33 倍</t>
+          <t xml:space="preserve">全社 4.12 倍 / 補助 3.85 倍 / 他 5.29 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.14 倍 / 補助 4.93 倍 / 他 6.03 倍</t>
+          <t xml:space="preserve">全社 5.13 倍 / 補助 4.93 倍 / 他 5.98 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.37 倍 / 補助 6.28 倍 / 他 6.81 倍</t>
+          <t xml:space="preserve">全社 6.36 倍 / 補助 6.28 倍 / 他 6.74 倍</t>
         </is>
       </c>
     </row>
@@ -4850,47 +5518,47 @@
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.85 pt</t>
+          <t xml:space="preserve">差 2.86 pt</t>
         </is>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.87 pt</t>
+          <t xml:space="preserve">差 2.92 pt</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.86 pt</t>
+          <t xml:space="preserve">差 2.98 pt</t>
         </is>
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.29 pt</t>
+          <t xml:space="preserve">差 4.31 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.01 pt</t>
+          <t xml:space="preserve">差 4.04 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.71 pt</t>
+          <t xml:space="preserve">差 3.76 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.96 pt</t>
+          <t xml:space="preserve">差 5.03 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6 pt</t>
+          <t xml:space="preserve">差 6.09 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.84 pt</t>
+          <t xml:space="preserve">差 6.95 pt</t>
         </is>
       </c>
     </row>
@@ -4912,27 +5580,27 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">補助 0.8 億円/人 / 他 0.537 億円/人</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">補助 0.8 億円/人 / 他 0.538 億円/人</t>
         </is>
       </c>
-      <c r="E36" s="0" t="inlineStr">
+      <c r="F36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">補助 0.8 億円/人 / 他 0.538 億円/人</t>
         </is>
       </c>
-      <c r="F36" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">補助 0.8 億円/人 / 他 0.538 億円/人</t>
-        </is>
-      </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.044 億円/人 / 他 0.554 億円/人</t>
+          <t xml:space="preserve">補助 1.053 億円/人 / 他 0.556 億円/人</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.043 億円/人 / 他 0.571 億円/人</t>
+          <t xml:space="preserve">補助 1.039 億円/人 / 他 0.569 億円/人</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
@@ -4942,17 +5610,17 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.214 億円/人 / 他 0.614 億円/人</t>
+          <t xml:space="preserve">補助 1.21 億円/人 / 他 0.614 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.413 億円/人 / 他 0.641 億円/人</t>
+          <t xml:space="preserve">補助 1.417 億円/人 / 他 0.641 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.643 億円/人 / 他 0.67 億円/人</t>
+          <t xml:space="preserve">補助 1.648 億円/人 / 他 0.67 億円/人</t>
         </is>
       </c>
     </row>
@@ -4974,27 +5642,27 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">補助 0.058 億円/人 / 他 0.059 億円/人</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助 0.059 億円/人 / 他 0.06 億円/人</t>
+        </is>
+      </c>
+      <c r="F37" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">補助 0.06 億円/人 / 他 0.062 億円/人</t>
         </is>
       </c>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">補助 0.06 億円/人 / 他 0.062 億円/人</t>
-        </is>
-      </c>
-      <c r="F37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">補助 0.06 億円/人 / 他 0.062 億円/人</t>
-        </is>
-      </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.087 億円/人 / 他 0.064 億円/人</t>
+          <t xml:space="preserve">補助 0.088 億円/人 / 他 0.064 億円/人</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.087 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">補助 0.087 億円/人 / 他 0.066 億円/人</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
@@ -5041,42 +5709,42 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 69.23 %</t>
+          <t xml:space="preserve">寄与率 86.67 %</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 66.67 %</t>
+          <t xml:space="preserve">寄与率 86.67 %</t>
         </is>
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 116 %</t>
+          <t xml:space="preserve">寄与率 114.94 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 91.49 %</t>
+          <t xml:space="preserve">寄与率 91.68 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.72 %</t>
+          <t xml:space="preserve">寄与率 91.1 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 85.39 %</t>
+          <t xml:space="preserve">寄与率 85.65 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 87 %</t>
+          <t xml:space="preserve">寄与率 87.22 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 88.29 %</t>
+          <t xml:space="preserve">寄与率 88.47 %</t>
         </is>
       </c>
     </row>
@@ -5086,13 +5754,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5108,10 +5777,15 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">制度上の必須条件</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">許容下限</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">許容上限</t>
         </is>
@@ -5130,10 +5804,15 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">制度上の必須条件</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">許容下限</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">許容上限</t>
         </is>
@@ -5150,10 +5829,15 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5168,10 +5852,15 @@
       <c r="B4" s="2">
         <v>21</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
         <v>-5</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="2">
         <v>40</v>
       </c>
     </row>
@@ -5184,10 +5873,15 @@
       <c r="B5" s="2">
         <v>7.000000000000001</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
         <v>0</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5200,10 +5894,15 @@
       <c r="B6" s="2">
         <v>7.000000000000001</v>
       </c>
-      <c r="C6" s="2">
-        <v>-5</v>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
+        </is>
       </c>
       <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
         <v>10</v>
       </c>
     </row>
@@ -5216,10 +5915,15 @@
       <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
         <v>-3</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="2">
         <v>20</v>
       </c>
     </row>
@@ -5232,10 +5936,15 @@
       <c r="B8" s="2">
         <v>1</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
         <v>0</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5248,10 +5957,15 @@
       <c r="B9" s="2">
         <v>6</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
         <v>0</v>
       </c>
-      <c r="D9" s="2">
+      <c r="E9" s="2">
         <v>10</v>
       </c>
     </row>
@@ -5264,10 +5978,15 @@
       <c r="B10" s="2">
         <v>4</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
         <v>-10</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>20</v>
       </c>
     </row>
@@ -5280,10 +5999,15 @@
       <c r="B11" s="2">
         <v>0.5</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
         <v>0</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E11" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5296,10 +6020,15 @@
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
         <v>0</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E12" s="2">
         <v>8</v>
       </c>
     </row>
@@ -5312,10 +6041,15 @@
       <c r="B13" s="2">
         <v>1</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D13" s="2">
         <v>-5</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E13" s="2">
         <v>10</v>
       </c>
     </row>
@@ -5328,10 +6062,15 @@
       <c r="B14" s="2">
         <v>0.5</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E14" s="2">
         <v>2</v>
       </c>
     </row>
@@ -5344,10 +6083,15 @@
       <c r="B15" s="2">
         <v>21</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D15" s="2">
         <v>-5</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E15" s="2">
         <v>40</v>
       </c>
     </row>
@@ -5360,10 +6104,15 @@
       <c r="B16" s="2">
         <v>6</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D16" s="2">
         <v>-10</v>
       </c>
-      <c r="D16" s="2">
+      <c r="E16" s="2">
         <v>20</v>
       </c>
     </row>
@@ -5376,10 +6125,15 @@
       <c r="B17" s="2">
         <v>0</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D17" s="2">
         <v>0</v>
       </c>
-      <c r="D17" s="2">
+      <c r="E17" s="2">
         <v>3</v>
       </c>
     </row>
@@ -5392,10 +6146,15 @@
       <c r="B18" s="2">
         <v>1</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D18" s="2">
         <v>0</v>
       </c>
-      <c r="D18" s="2">
+      <c r="E18" s="2">
         <v>3</v>
       </c>
     </row>
@@ -5408,10 +6167,15 @@
       <c r="B19" s="2">
         <v>7.000000000000001</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D19" s="2">
         <v>4.5</v>
       </c>
-      <c r="D19" s="2">
+      <c r="E19" s="2">
         <v>10</v>
       </c>
     </row>
@@ -5424,10 +6188,15 @@
       <c r="B20" s="2">
         <v>4.5</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D20" s="2">
         <v>0</v>
       </c>
-      <c r="D20" s="2">
+      <c r="E20" s="2">
         <v>8</v>
       </c>
     </row>
@@ -5440,10 +6209,15 @@
       <c r="B21" s="2">
         <v>4</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D21" s="2">
         <v>-3</v>
       </c>
-      <c r="D21" s="2">
+      <c r="E21" s="2">
         <v>20</v>
       </c>
     </row>
@@ -5456,10 +6230,15 @@
       <c r="B22" s="2">
         <v>1.5</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D22" s="2">
         <v>-5</v>
       </c>
-      <c r="D22" s="2">
+      <c r="E22" s="2">
         <v>10</v>
       </c>
     </row>
@@ -5472,10 +6251,15 @@
       <c r="B23" s="2">
         <v>9</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D23" s="2">
         <v>4</v>
       </c>
-      <c r="D23" s="2">
+      <c r="E23" s="2">
         <v>25</v>
       </c>
     </row>
@@ -5488,10 +6272,15 @@
       <c r="B24" s="2">
         <v>10</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D24" s="2">
         <v>4</v>
       </c>
-      <c r="D24" s="2">
+      <c r="E24" s="2">
         <v>25</v>
       </c>
     </row>
@@ -5504,10 +6293,15 @@
       <c r="B25" s="2">
         <v>6</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D25" s="2">
         <v>0</v>
       </c>
-      <c r="D25" s="2">
+      <c r="E25" s="2">
         <v>10</v>
       </c>
     </row>
@@ -5522,10 +6316,15 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5542,10 +6341,15 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5560,11 +6364,20 @@
       <c r="B28" s="2">
         <v>15</v>
       </c>
-      <c r="C28" s="2">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2">
-        <v>50</v>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限15.00億円）</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5573,7 +6386,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C213"/>
+  <dimension ref="A1:C225"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -5633,11 +6446,11 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-11</t>
+          <t xml:space="preserve">actual:company:2023:2-10</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <v>12.76</v>
+        <v>0.09</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
@@ -5648,11 +6461,11 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-14</t>
+          <t xml:space="preserve">actual:company:2023:2-12</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>3.18</v>
+        <v>11.67</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
@@ -5663,11 +6476,11 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-3</t>
+          <t xml:space="preserve">actual:company:2023:2-13</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>92.75</v>
+        <v>0.62</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
@@ -5678,11 +6491,11 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-7</t>
+          <t xml:space="preserve">actual:company:2023:2-14</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>33.21</v>
+        <v>2.45</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
@@ -5693,11 +6506,11 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-8</t>
+          <t xml:space="preserve">actual:company:2023:2-15</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -5708,11 +6521,11 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-1</t>
+          <t xml:space="preserve">actual:company:2023:2-3</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>143.2</v>
+        <v>92.75</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -5723,11 +6536,11 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-11</t>
+          <t xml:space="preserve">actual:company:2023:2-4</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>13.38</v>
+        <v>0.73</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -5738,11 +6551,11 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-14</t>
+          <t xml:space="preserve">actual:company:2023:2-7</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>3.34</v>
+        <v>32.65</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -5753,11 +6566,11 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-3</t>
+          <t xml:space="preserve">actual:company:2023:2-9</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>97.38</v>
+        <v>0.82</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -5768,11 +6581,11 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-7</t>
+          <t xml:space="preserve">actual:company:2024:2-1</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>34.86</v>
+        <v>143.2</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -5783,11 +6596,11 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-8</t>
+          <t xml:space="preserve">actual:company:2024:2-10</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>0.96</v>
+        <v>0.1</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -5798,11 +6611,11 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-1</t>
+          <t xml:space="preserve">actual:company:2024:2-12</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>150</v>
+        <v>12.47</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -5813,11 +6626,11 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-11</t>
+          <t xml:space="preserve">actual:company:2024:2-13</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>14</v>
+        <v>0.66</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -5828,11 +6641,11 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-14</t>
+          <t xml:space="preserve">actual:company:2024:2-14</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -5843,11 +6656,11 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-3</t>
+          <t xml:space="preserve">actual:company:2024:2-15</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>102</v>
+        <v>0.67</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -5858,11 +6671,11 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-7</t>
+          <t xml:space="preserve">actual:company:2024:2-3</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>36.5</v>
+        <v>97.38</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -5873,11 +6686,11 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-8</t>
+          <t xml:space="preserve">actual:company:2024:2-4</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -5888,11 +6701,11 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-1</t>
+          <t xml:space="preserve">actual:company:2024:2-7</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>72</v>
+        <v>34.52</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -5903,11 +6716,11 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-10</t>
+          <t xml:space="preserve">actual:company:2024:2-9</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>1.8</v>
+        <v>0.86</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -5918,11 +6731,11 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-13</t>
+          <t xml:space="preserve">actual:company:2025:2-1</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -5933,11 +6746,11 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-14</t>
+          <t xml:space="preserve">actual:company:2025:2-10</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -5948,11 +6761,11 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-4</t>
+          <t xml:space="preserve">actual:company:2025:2-12</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>23.04</v>
+        <v>13.3</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -5963,11 +6776,11 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-6</t>
+          <t xml:space="preserve">actual:company:2025:2-13</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>6.48</v>
+        <v>0.7</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
@@ -5978,11 +6791,11 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-8</t>
+          <t xml:space="preserve">actual:company:2025:2-14</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -5993,11 +6806,11 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-9</t>
+          <t xml:space="preserve">actual:company:2025:2-15</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>0.36</v>
+        <v>0.7</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
@@ -6008,11 +6821,11 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-1</t>
+          <t xml:space="preserve">actual:company:2025:2-3</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6023,11 +6836,11 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-10</t>
+          <t xml:space="preserve">actual:company:2025:2-4</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -6038,11 +6851,11 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-13</t>
+          <t xml:space="preserve">actual:company:2025:2-7</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>95</v>
+        <v>36.4</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -6053,11 +6866,11 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-14</t>
+          <t xml:space="preserve">actual:company:2025:2-9</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -6068,11 +6881,11 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-4</t>
+          <t xml:space="preserve">actual:project:2023:7-1</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>24.32</v>
+        <v>72</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -6083,11 +6896,11 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-6</t>
+          <t xml:space="preserve">actual:project:2023:7-10</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <v>6.84</v>
+        <v>1.8</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
@@ -6098,11 +6911,11 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-8</t>
+          <t xml:space="preserve">actual:project:2023:7-13</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>5.7</v>
+        <v>90</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
@@ -6113,11 +6926,11 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-9</t>
+          <t xml:space="preserve">actual:project:2023:7-14</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <v>0.38</v>
+        <v>2</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -6128,11 +6941,11 @@
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-1</t>
+          <t xml:space="preserve">actual:project:2023:7-4</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>80</v>
+        <v>23.04</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
@@ -6143,11 +6956,11 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-10</t>
+          <t xml:space="preserve">actual:project:2023:7-6</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>2</v>
+        <v>6.78</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -6158,11 +6971,11 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-13</t>
+          <t xml:space="preserve">actual:project:2023:7-8</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>100</v>
+        <v>5.19</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -6173,11 +6986,11 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-14</t>
+          <t xml:space="preserve">actual:project:2023:7-9</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>2</v>
+        <v>0.36</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -6188,11 +7001,11 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-4</t>
+          <t xml:space="preserve">actual:project:2024:7-1</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>25.6</v>
+        <v>76</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
@@ -6203,11 +7016,11 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-6</t>
+          <t xml:space="preserve">actual:project:2024:7-10</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
@@ -6218,11 +7031,11 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-8</t>
+          <t xml:space="preserve">actual:project:2024:7-13</t>
         </is>
       </c>
       <c r="B43" s="2">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
@@ -6233,11 +7046,11 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-9</t>
+          <t xml:space="preserve">actual:project:2024:7-14</t>
         </is>
       </c>
       <c r="B44" s="2">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
@@ -6248,11 +7061,11 @@
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:assets</t>
+          <t xml:space="preserve">actual:project:2024:7-4</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <v>132</v>
+        <v>24.32</v>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
@@ -6263,11 +7076,11 @@
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:buildings</t>
+          <t xml:space="preserve">actual:project:2024:7-6</t>
         </is>
       </c>
       <c r="B46" s="2">
-        <v>19</v>
+        <v>7.04</v>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
@@ -6278,11 +7091,11 @@
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capex</t>
+          <t xml:space="preserve">actual:project:2024:7-8</t>
         </is>
       </c>
       <c r="B47" s="2">
-        <v>5</v>
+        <v>5.59</v>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
@@ -6293,11 +7106,11 @@
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capital</t>
+          <t xml:space="preserve">actual:project:2024:7-9</t>
         </is>
       </c>
       <c r="B48" s="2">
-        <v>10</v>
+        <v>0.38</v>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
@@ -6308,11 +7121,11 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:cash</t>
+          <t xml:space="preserve">actual:project:2025:7-1</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
@@ -6323,11 +7136,11 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-10</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
@@ -6338,11 +7151,11 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
+          <t xml:space="preserve">actual:project:2025:7-13</t>
         </is>
       </c>
       <c r="B51" s="2">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
@@ -6353,11 +7166,11 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-14</t>
         </is>
       </c>
       <c r="B52" s="2">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
@@ -6368,11 +7181,11 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
+          <t xml:space="preserve">actual:project:2025:7-4</t>
         </is>
       </c>
       <c r="B53" s="2">
-        <v>36</v>
+        <v>25.6</v>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
@@ -6383,11 +7196,11 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-6</t>
         </is>
       </c>
       <c r="B54" s="2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
@@ -6398,11 +7211,11 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:land</t>
+          <t xml:space="preserve">actual:project:2025:7-8</t>
         </is>
       </c>
       <c r="B55" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
@@ -6413,11 +7226,11 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
+          <t xml:space="preserve">actual:project:2025:7-9</t>
         </is>
       </c>
       <c r="B56" s="2">
-        <v>75</v>
+        <v>0.4</v>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
@@ -6428,11 +7241,11 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:assets</t>
         </is>
       </c>
       <c r="B57" s="2">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
@@ -6443,11 +7256,11 @@
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:machinery</t>
+          <t xml:space="preserve">balance-sheet:2023:buildings</t>
         </is>
       </c>
       <c r="B58" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
@@ -6458,11 +7271,11 @@
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:capex</t>
         </is>
       </c>
       <c r="B59" s="2">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
@@ -6473,11 +7286,11 @@
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2023:capital</t>
         </is>
       </c>
       <c r="B60" s="2">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
@@ -6488,11 +7301,11 @@
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:cash</t>
         </is>
       </c>
       <c r="B61" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
@@ -6503,11 +7316,11 @@
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:software</t>
+          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
         </is>
       </c>
       <c r="B62" s="2">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
@@ -6518,11 +7331,11 @@
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
         </is>
       </c>
       <c r="B63" s="2">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
@@ -6533,11 +7346,11 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:assets</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
         </is>
       </c>
       <c r="B64" s="2">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
@@ -6548,11 +7361,11 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:buildings</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
         </is>
       </c>
       <c r="B65" s="2">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
@@ -6563,11 +7376,11 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capex</t>
+          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
         </is>
       </c>
       <c r="B66" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
@@ -6578,7 +7391,7 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capital</t>
+          <t xml:space="preserve">balance-sheet:2023:land</t>
         </is>
       </c>
       <c r="B67" s="2">
@@ -6593,11 +7406,11 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:cash</t>
+          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
         </is>
       </c>
       <c r="B68" s="2">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
@@ -6608,11 +7421,11 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
         </is>
       </c>
       <c r="B69" s="2">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
@@ -6623,11 +7436,11 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:machinery</t>
         </is>
       </c>
       <c r="B70" s="2">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
@@ -6638,11 +7451,11 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
         </is>
       </c>
       <c r="B71" s="2">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
@@ -6653,11 +7466,11 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
@@ -6668,11 +7481,11 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
         </is>
       </c>
       <c r="B73" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
@@ -6683,11 +7496,11 @@
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:land</t>
+          <t xml:space="preserve">balance-sheet:2023:software</t>
         </is>
       </c>
       <c r="B74" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
@@ -6698,11 +7511,11 @@
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
         </is>
       </c>
       <c r="B75" s="2">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
@@ -6713,11 +7526,11 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:assets</t>
         </is>
       </c>
       <c r="B76" s="2">
-        <v>31</v>
+        <v>143</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
@@ -6728,11 +7541,11 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:machinery</t>
+          <t xml:space="preserve">balance-sheet:2024:buildings</t>
         </is>
       </c>
       <c r="B77" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
@@ -6743,11 +7556,11 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:capex</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
@@ -6758,11 +7571,11 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2024:capital</t>
         </is>
       </c>
       <c r="B79" s="2">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
@@ -6773,11 +7586,11 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:cash</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
@@ -6788,11 +7601,11 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:software</t>
+          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
@@ -6803,11 +7616,11 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
         </is>
       </c>
       <c r="B82" s="2">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
@@ -6818,11 +7631,11 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:assets</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
         </is>
       </c>
       <c r="B83" s="2">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
@@ -6833,11 +7646,11 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:buildings</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
@@ -6848,11 +7661,11 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capex</t>
+          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
         </is>
       </c>
       <c r="B85" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
@@ -6863,7 +7676,7 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capital</t>
+          <t xml:space="preserve">balance-sheet:2024:land</t>
         </is>
       </c>
       <c r="B86" s="2">
@@ -6878,11 +7691,11 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:cash</t>
+          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
         </is>
       </c>
       <c r="B87" s="2">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
@@ -6893,11 +7706,11 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
         </is>
       </c>
       <c r="B88" s="2">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
@@ -6908,11 +7721,11 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:machinery</t>
         </is>
       </c>
       <c r="B89" s="2">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
@@ -6923,11 +7736,11 @@
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
         </is>
       </c>
       <c r="B90" s="2">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
@@ -6938,11 +7751,11 @@
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
@@ -6953,11 +7766,11 @@
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
         </is>
       </c>
       <c r="B92" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
@@ -6968,11 +7781,11 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:land</t>
+          <t xml:space="preserve">balance-sheet:2024:software</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
@@ -6983,11 +7796,11 @@
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
         </is>
       </c>
       <c r="B94" s="2">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
@@ -6998,11 +7811,11 @@
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:assets</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
@@ -7013,11 +7826,11 @@
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:machinery</t>
+          <t xml:space="preserve">balance-sheet:2025:buildings</t>
         </is>
       </c>
       <c r="B96" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
@@ -7028,11 +7841,11 @@
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:capex</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
@@ -7043,11 +7856,11 @@
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2025:capital</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
@@ -7058,11 +7871,11 @@
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:cash</t>
         </is>
       </c>
       <c r="B99" s="2">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
@@ -7073,11 +7886,11 @@
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:software</t>
+          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
         </is>
       </c>
       <c r="B100" s="2">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
@@ -7088,11 +7901,11 @@
     <row r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
         </is>
       </c>
       <c r="B101" s="2">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
@@ -7103,11 +7916,11 @@
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:0</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
         </is>
       </c>
       <c r="B102" s="2">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
@@ -7118,11 +7931,11 @@
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:1</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
         </is>
       </c>
       <c r="B103" s="2">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
@@ -7133,26 +7946,26 @@
     <row r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
         </is>
       </c>
       <c r="B104" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+          <t xml:space="preserve">balance-sheet:2025:land</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
@@ -7163,26 +7976,26 @@
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
         </is>
       </c>
       <c r="B106" s="2">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
         </is>
       </c>
       <c r="B107" s="2">
-        <v>0.03</v>
+        <v>32</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
@@ -7193,26 +8006,26 @@
     <row r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:machinery</t>
         </is>
       </c>
       <c r="B108" s="2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
         </is>
       </c>
       <c r="B109" s="2">
-        <v>0.02</v>
+        <v>73</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
@@ -7223,11 +8036,11 @@
     <row r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>-0.05</v>
+        <v>70</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
@@ -7238,11 +8051,11 @@
     <row r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
         </is>
       </c>
       <c r="B111" s="2">
-        <v>0.1</v>
+        <v>11</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
@@ -7253,11 +8066,11 @@
     <row r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:software</t>
         </is>
       </c>
       <c r="B112" s="2">
-        <v>-0.05</v>
+        <v>7</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
@@ -7268,11 +8081,11 @@
     <row r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
         </is>
       </c>
       <c r="B113" s="2">
-        <v>0.1</v>
+        <v>64</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
@@ -7283,26 +8096,26 @@
     <row r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:investment:0</t>
         </is>
       </c>
       <c r="B114" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:investment:1</t>
         </is>
       </c>
       <c r="B115" s="2">
-        <v>0.08</v>
+        <v>200</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
@@ -7313,7 +8126,7 @@
     <row r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
         </is>
       </c>
       <c r="B116" s="2">
@@ -7328,11 +8141,11 @@
     <row r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
         </is>
       </c>
       <c r="B117" s="2">
-        <v>0.08</v>
+        <v>100</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
@@ -7343,26 +8156,26 @@
     <row r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B118" s="2">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B119" s="2">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -7373,26 +8186,26 @@
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B120" s="2">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
@@ -7403,26 +8216,26 @@
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B122" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B123" s="2">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -7433,11 +8246,11 @@
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -7448,11 +8261,11 @@
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B125" s="2">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -7463,7 +8276,7 @@
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B126" s="2">
@@ -7478,11 +8291,11 @@
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B127" s="2">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -7493,7 +8306,7 @@
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B128" s="2">
@@ -7508,11 +8321,11 @@
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
@@ -7523,11 +8336,11 @@
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B130" s="2">
-        <v>-0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -7538,7 +8351,7 @@
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B131" s="2">
@@ -7553,11 +8366,11 @@
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>-0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
@@ -7568,7 +8381,7 @@
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B133" s="2">
@@ -7583,26 +8396,26 @@
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B135" s="2">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
@@ -7613,26 +8426,26 @@
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
@@ -7643,7 +8456,7 @@
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B138" s="2">
@@ -7658,11 +8471,11 @@
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
@@ -7673,26 +8486,26 @@
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
@@ -7703,11 +8516,11 @@
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
@@ -7718,11 +8531,11 @@
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
@@ -7733,11 +8546,11 @@
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -7748,11 +8561,11 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
@@ -7763,7 +8576,7 @@
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B146" s="2">
@@ -7778,11 +8591,11 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
@@ -7793,7 +8606,7 @@
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B148" s="2">
@@ -7808,11 +8621,11 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
@@ -7823,26 +8636,26 @@
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -7853,11 +8666,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>1</v>
+        <v>0.045</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -7868,11 +8681,11 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>50</v>
+        <v>0.1</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
@@ -7883,26 +8696,26 @@
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>20</v>
+        <v>0.1</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
@@ -7913,11 +8726,11 @@
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>45</v>
+        <v>-0.05</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
@@ -7928,11 +8741,11 @@
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B157" s="2">
-        <v>23</v>
+        <v>0.4</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
@@ -7943,11 +8756,11 @@
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
@@ -7958,11 +8771,11 @@
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.005</v>
+        <v>0.4</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -7973,26 +8786,26 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
@@ -8003,11 +8816,11 @@
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -8018,11 +8831,11 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
@@ -8033,11 +8846,11 @@
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -8048,11 +8861,11 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>0.04</v>
+        <v>50</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
@@ -8063,11 +8876,11 @@
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>0.005</v>
+        <v>5</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
@@ -8078,11 +8891,11 @@
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>0.1</v>
+        <v>20</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
@@ -8093,26 +8906,26 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>0.07</v>
+        <v>23</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
@@ -8123,11 +8936,11 @@
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
@@ -8138,11 +8951,11 @@
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0.04</v>
+        <v>0.005</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
@@ -8153,11 +8966,11 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.05</v>
+        <v>0.015</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
@@ -8168,11 +8981,11 @@
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
@@ -8183,11 +8996,11 @@
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.06</v>
+        <v>0.045</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -8198,11 +9011,11 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
@@ -8213,11 +9026,11 @@
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
@@ -8228,11 +9041,11 @@
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0.21</v>
+        <v>0.04</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -8243,11 +9056,11 @@
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0.21</v>
+        <v>0.005</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
@@ -8258,11 +9071,11 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -8273,26 +9086,26 @@
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>15</v>
+        <v>0.07</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -8303,11 +9116,11 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>10</v>
+        <v>0.04</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -8318,11 +9131,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>15</v>
+        <v>0.04</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -8333,11 +9146,11 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>15</v>
+        <v>0.05</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
@@ -8348,11 +9161,11 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>15</v>
+        <v>0.06</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
@@ -8363,56 +9176,56 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>7</v>
+        <v>0.21</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -8423,11 +9236,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>3.5</v>
+        <v>0.21</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -8438,11 +9251,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>35</v>
+        <v>0.01</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -8453,11 +9266,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>21</v>
+        <v>0.09</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -8468,22 +9281,22 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">driver:usefulLife</t>
         </is>
       </c>
       <c r="B194" s="2">
@@ -8498,11 +9311,11 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">future-capex:2026</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -8513,26 +9326,26 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">future-capex:2027</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">future-capex:2028</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
@@ -8543,56 +9356,56 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">future-capex:2029</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">future-capex:2030</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">future-capex:2031</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -8603,11 +9416,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>23</v>
+        <v>3.5</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -8618,11 +9431,11 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
@@ -8633,11 +9446,11 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -8648,7 +9461,7 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B205" s="2">
@@ -8663,11 +9476,11 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
@@ -8678,11 +9491,11 @@
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -8693,7 +9506,7 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B208" s="2">
@@ -8708,11 +9521,11 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
@@ -8723,11 +9536,11 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
@@ -8738,26 +9551,26 @@
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
@@ -8768,13 +9581,193 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B213" s="2">
+        <v>40</v>
+      </c>
+      <c r="C213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B214" s="2">
+        <v>23</v>
+      </c>
+      <c r="C214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B215" s="2">
+        <v>10</v>
+      </c>
+      <c r="C215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B216" s="2">
+        <v>6</v>
+      </c>
+      <c r="C216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B217" s="2">
+        <v>0</v>
+      </c>
+      <c r="C217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B218" s="2">
+        <v>35</v>
+      </c>
+      <c r="C218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B219" s="2">
+        <v>22</v>
+      </c>
+      <c r="C219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B220" s="2">
+        <v>0</v>
+      </c>
+      <c r="C220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B221" s="2">
+        <v>95</v>
+      </c>
+      <c r="C221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B222" s="2">
+        <v>70</v>
+      </c>
+      <c r="C222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B223" s="2">
+        <v>0</v>
+      </c>
+      <c r="C223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B224" s="2">
+        <v>350</v>
+      </c>
+      <c r="C224" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B213" s="2">
+      <c r="B225" s="2">
         <v>213</v>
       </c>
-      <c r="C213" s="0" t="inlineStr">
+      <c r="C225" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -8802,7 +9795,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjQsIm9mZmljZXJQYXkiOjAuMzYsImRlcHJlY2lhdGlvbiI6MS44LCJvdGhlclNnYSI6OSwiaGVhZGNvdW50Ijo5MCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4zNiwib2ZmaWNlclBheSI6MC41NSwiZGVwcmVjaWF0aW9uIjoxLjM4LCJvdGhlclNnYSI6Ny4zNiwiaGVhZGNvdW50IjoxMTkuNiwib2ZmaWNlckNvdW50IjozfX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjcsIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjJ9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNjgsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI0LjgsIm9mZmljZXJDb3VudCI6M319LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6Niwib2ZmaWNlclBheSI6MC40LCJkZXByZWNpYXRpb24iOjIsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsIm9mZmljZXJQYXkiOjAuNiwiZGVwcmVjaWF0aW9uIjoxLjUsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbLTAuMDUsMC4xXSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjAzLDAuMl0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbLTAuMSwwLjJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMl0sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlstMC4wNSwwLjFdLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbLTAuMDUsMC40XSwib3RoZXJTYWxlc0dyb3d0aCI6Wy0wLjEsMC4yXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMCwwLjAzXSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDQ1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMCwwLjA4XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6Wy0wLjAzLDAuMl0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbLTAuMDUsMC4xXSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA0LDAuMjVdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAsMC4xXSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6My41LCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NzAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MzAsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnt9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMzLjIxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItOCI6MC45MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTExIjoxMi43NiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjozLjE4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNDgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0Ljg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItOCI6MC45NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTExIjoxMy4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjozLjM0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjYuODQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTgiOjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMSI6MTQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6My41LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4yLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wMywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjAxLCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjEsImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjQsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjotMC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjIsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMywiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDQ1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wOCwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjIsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wMTUsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjA5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMjUsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjEsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50Ijo0NSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjE1LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjozLjUsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjcwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MzAsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjB9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn19</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6e30sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuNCwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMiwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMiwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4xLCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjQ1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6MTUsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NzAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjozMCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwifQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>15.51906107932668</v>
+        <v>20.152518023637867</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -234,7 +234,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>107.63</v>
+        <v>127.10000000000002</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -264,7 +264,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>8.332988192871005</v>
+        <v>2.0136531491304233</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -294,7 +294,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>69.38995332441166</v>
+        <v>67.97614287618285</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -324,7 +324,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>21.000508463435665</v>
+        <v>29.614246350044503</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -354,7 +354,7 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>92.59</v>
+        <v>110.32</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>18.06480348374826</v>
+        <v>32.737848619973995</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>25.279999999999994</v>
+        <v>28.59999999999998</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>7.099090446266931</v>
+        <v>7.018093513861001</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>3.7799999999999994</v>
+        <v>2.3899999999999997</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>15.333333333333332</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>168.5333333333333</v>
+        <v>372.8813559322032</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>5.7715899735125475</v>
+        <v>5.379211308937237</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>0.10999999999999999</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -1259,22 +1259,22 @@
         <v>150</v>
       </c>
       <c r="E3" s="4">
-        <v>112.8</v>
+        <v>157.31</v>
       </c>
       <c r="F3" s="4">
-        <v>155.70999999999998</v>
+        <v>164.98000000000002</v>
       </c>
       <c r="G3" s="4">
-        <v>198.74</v>
+        <v>173.01999999999998</v>
       </c>
       <c r="H3" s="4">
-        <v>228.65999999999997</v>
+        <v>206.57</v>
       </c>
       <c r="I3" s="4">
-        <v>264.15999999999997</v>
+        <v>247.85000000000002</v>
       </c>
       <c r="J3" s="4">
-        <v>306.37</v>
+        <v>300.12</v>
       </c>
     </row>
     <row r="4">
@@ -1295,22 +1295,22 @@
         <v>4.748603351955305</v>
       </c>
       <c r="E4" s="2">
-        <v>-24.8</v>
+        <v>4.8733333333333295</v>
       </c>
       <c r="F4" s="2">
-        <v>38.04078014184395</v>
+        <v>4.875723094526752</v>
       </c>
       <c r="G4" s="2">
-        <v>27.63470554235441</v>
+        <v>4.873317977936686</v>
       </c>
       <c r="H4" s="2">
-        <v>15.054845526818927</v>
+        <v>19.39082187030401</v>
       </c>
       <c r="I4" s="2">
-        <v>15.525233971835917</v>
+        <v>19.983540688386526</v>
       </c>
       <c r="J4" s="2">
-        <v>15.978952150212011</v>
+        <v>21.089368569699406</v>
       </c>
     </row>
     <row r="5">
@@ -1329,22 +1329,22 @@
         <v>102</v>
       </c>
       <c r="E5" s="2">
-        <v>75.38</v>
+        <v>106.97</v>
       </c>
       <c r="F5" s="2">
-        <v>103.22999999999999</v>
+        <v>112.18</v>
       </c>
       <c r="G5" s="2">
-        <v>131.15</v>
+        <v>117.66</v>
       </c>
       <c r="H5" s="2">
-        <v>150.44</v>
+        <v>139.13</v>
       </c>
       <c r="I5" s="2">
-        <v>173.33</v>
+        <v>166</v>
       </c>
       <c r="J5" s="2">
-        <v>200.54000000000002</v>
+        <v>199.78000000000003</v>
       </c>
     </row>
     <row r="6">
@@ -1363,22 +1363,22 @@
         <v>0.8</v>
       </c>
       <c r="E6" s="2">
-        <v>0.3</v>
+        <v>0.99</v>
       </c>
       <c r="F6" s="2">
-        <v>0.3</v>
+        <v>1.18</v>
       </c>
       <c r="G6" s="2">
-        <v>0.3</v>
+        <v>1.37</v>
       </c>
       <c r="H6" s="2">
-        <v>0.3</v>
+        <v>1.37</v>
       </c>
       <c r="I6" s="2">
-        <v>0.3</v>
+        <v>1.37</v>
       </c>
       <c r="J6" s="2">
-        <v>0.3</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="7">
@@ -1397,22 +1397,22 @@
         <v>48</v>
       </c>
       <c r="E7" s="4">
-        <v>37.42</v>
+        <v>50.34</v>
       </c>
       <c r="F7" s="4">
-        <v>52.47999999999999</v>
+        <v>52.80000000000001</v>
       </c>
       <c r="G7" s="4">
-        <v>67.59</v>
+        <v>55.359999999999985</v>
       </c>
       <c r="H7" s="4">
-        <v>78.21999999999997</v>
+        <v>67.44</v>
       </c>
       <c r="I7" s="4">
-        <v>90.82999999999996</v>
+        <v>81.85000000000002</v>
       </c>
       <c r="J7" s="4">
-        <v>105.82999999999998</v>
+        <v>100.33999999999997</v>
       </c>
     </row>
     <row r="8">
@@ -1431,22 +1431,22 @@
         <v>32</v>
       </c>
       <c r="E8" s="2">
-        <v>33.17375886524823</v>
+        <v>32.00050854999682</v>
       </c>
       <c r="F8" s="2">
-        <v>33.703679917795895</v>
+        <v>32.00387925809189</v>
       </c>
       <c r="G8" s="2">
-        <v>34.009258327463016</v>
+        <v>31.99630100566408</v>
       </c>
       <c r="H8" s="2">
-        <v>34.20799440216915</v>
+        <v>32.64752868277097</v>
       </c>
       <c r="I8" s="2">
-        <v>34.3844639612356</v>
+        <v>33.02400645551746</v>
       </c>
       <c r="J8" s="2">
-        <v>34.543199399419</v>
+        <v>33.433293349326924</v>
       </c>
     </row>
     <row r="9">
@@ -1465,22 +1465,22 @@
         <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>28.43</v>
+        <v>38.87</v>
       </c>
       <c r="F9" s="2">
-        <v>38.8</v>
+        <v>41.449999999999996</v>
       </c>
       <c r="G9" s="2">
-        <v>49.19</v>
+        <v>44.19</v>
       </c>
       <c r="H9" s="2">
-        <v>53.269999999999996</v>
+        <v>48.489999999999995</v>
       </c>
       <c r="I9" s="2">
-        <v>57.82</v>
+        <v>53.92999999999999</v>
       </c>
       <c r="J9" s="2">
-        <v>62.93</v>
+        <v>60.18</v>
       </c>
     </row>
     <row r="10">
@@ -1499,22 +1499,22 @@
         <v>1</v>
       </c>
       <c r="E10" s="2">
-        <v>0.8200000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="F10" s="2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G10" s="2">
-        <v>1.27</v>
+        <v>1.1099999999999999</v>
       </c>
       <c r="H10" s="2">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="I10" s="2">
-        <v>1.4100000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="J10" s="2">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="11">
@@ -1533,22 +1533,22 @@
         <v>0.9</v>
       </c>
       <c r="E11" s="2">
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="F11" s="2">
-        <v>0.99</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="G11" s="2">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="I11" s="2">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="J11" s="2">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="12">
@@ -1567,22 +1567,22 @@
         <v>0.1</v>
       </c>
       <c r="E12" s="2">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="F12" s="2">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G12" s="2">
-        <v>0.07</v>
+        <v>0.11</v>
       </c>
       <c r="H12" s="2">
-        <v>0.07</v>
+        <v>0.11</v>
       </c>
       <c r="I12" s="2">
-        <v>0.07</v>
+        <v>0.13</v>
       </c>
       <c r="J12" s="2">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="13">
@@ -1601,22 +1601,22 @@
         <v>14</v>
       </c>
       <c r="E13" s="2">
-        <v>11.73</v>
+        <v>14.95</v>
       </c>
       <c r="F13" s="2">
-        <v>15.5</v>
+        <v>15.96</v>
       </c>
       <c r="G13" s="2">
-        <v>19.27</v>
+        <v>17.06</v>
       </c>
       <c r="H13" s="2">
-        <v>20.96</v>
+        <v>18.16</v>
       </c>
       <c r="I13" s="2">
-        <v>22.810000000000002</v>
+        <v>19.83</v>
       </c>
       <c r="J13" s="2">
-        <v>24.84</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="14">
@@ -1635,22 +1635,22 @@
         <v>13.3</v>
       </c>
       <c r="E14" s="2">
-        <v>11.31</v>
+        <v>14.2</v>
       </c>
       <c r="F14" s="2">
-        <v>15.06</v>
+        <v>15.16</v>
       </c>
       <c r="G14" s="2">
-        <v>18.810000000000002</v>
+        <v>16.21</v>
       </c>
       <c r="H14" s="2">
-        <v>20.47</v>
+        <v>17.7</v>
       </c>
       <c r="I14" s="2">
-        <v>22.29</v>
+        <v>19.33</v>
       </c>
       <c r="J14" s="2">
-        <v>24.29</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="15">
@@ -1669,22 +1669,22 @@
         <v>0.7</v>
       </c>
       <c r="E15" s="2">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="F15" s="2">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="G15" s="2">
-        <v>0.46</v>
+        <v>0.85</v>
       </c>
       <c r="H15" s="2">
-        <v>0.49</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="I15" s="2">
-        <v>0.52</v>
+        <v>1.01</v>
       </c>
       <c r="J15" s="2">
-        <v>0.55</v>
+        <v>1.1099999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1703,22 +1703,22 @@
         <v>2.7</v>
       </c>
       <c r="E16" s="2">
-        <v>3.37</v>
+        <v>3.2800000000000002</v>
       </c>
       <c r="F16" s="2">
-        <v>5.53</v>
+        <v>3.8499999999999996</v>
       </c>
       <c r="G16" s="2">
-        <v>7.7</v>
+        <v>4.43</v>
       </c>
       <c r="H16" s="2">
-        <v>7.7</v>
+        <v>4.43</v>
       </c>
       <c r="I16" s="2">
-        <v>7.7</v>
+        <v>4.43</v>
       </c>
       <c r="J16" s="2">
-        <v>7.7</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="17">
@@ -1737,22 +1737,22 @@
         <v>0.7</v>
       </c>
       <c r="E17" s="2">
-        <v>0.31</v>
+        <v>0.73</v>
       </c>
       <c r="F17" s="2">
-        <v>0.32</v>
+        <v>0.77</v>
       </c>
       <c r="G17" s="2">
-        <v>0.34</v>
+        <v>0.81</v>
       </c>
       <c r="H17" s="2">
-        <v>0.36</v>
+        <v>0.97</v>
       </c>
       <c r="I17" s="2">
-        <v>0.38</v>
+        <v>1.17</v>
       </c>
       <c r="J17" s="2">
-        <v>0.4</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="18">
@@ -1771,22 +1771,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>8.990000000000002</v>
+        <v>11.469999999999999</v>
       </c>
       <c r="F18" s="4">
-        <v>13.679999999999993</v>
+        <v>11.350000000000009</v>
       </c>
       <c r="G18" s="4">
-        <v>18.4</v>
+        <v>11.169999999999984</v>
       </c>
       <c r="H18" s="4">
-        <v>24.949999999999967</v>
+        <v>18.950000000000003</v>
       </c>
       <c r="I18" s="4">
-        <v>33.009999999999955</v>
+        <v>27.920000000000027</v>
       </c>
       <c r="J18" s="4">
-        <v>42.89999999999997</v>
+        <v>40.159999999999975</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.969858156028371</v>
+        <v>7.291335579429152</v>
       </c>
       <c r="F19" s="2">
-        <v>8.785562905401061</v>
+        <v>6.879621772336045</v>
       </c>
       <c r="G19" s="2">
-        <v>9.258327463017006</v>
+        <v>6.455901051901505</v>
       </c>
       <c r="H19" s="2">
-        <v>10.911396833726918</v>
+        <v>9.173645737522392</v>
       </c>
       <c r="I19" s="2">
-        <v>12.496214415505738</v>
+        <v>11.26487795037322</v>
       </c>
       <c r="J19" s="2">
-        <v>14.002676502268487</v>
+        <v>13.381314141010254</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E20" s="4">
-        <v>8.990000000000002</v>
+        <v>11.469999999999999</v>
       </c>
       <c r="F20" s="4">
-        <v>13.679999999999993</v>
+        <v>11.350000000000009</v>
       </c>
       <c r="G20" s="4">
-        <v>18.4</v>
+        <v>11.169999999999984</v>
       </c>
       <c r="H20" s="4">
-        <v>24.949999999999967</v>
+        <v>18.950000000000003</v>
       </c>
       <c r="I20" s="4">
-        <v>33.009999999999955</v>
+        <v>27.920000000000027</v>
       </c>
       <c r="J20" s="4">
-        <v>42.89999999999997</v>
+        <v>40.159999999999975</v>
       </c>
     </row>
     <row r="21">
@@ -1977,22 +1977,22 @@
         <v>14</v>
       </c>
       <c r="E23" s="2">
-        <v>11.73</v>
+        <v>14.95</v>
       </c>
       <c r="F23" s="2">
-        <v>15.5</v>
+        <v>15.96</v>
       </c>
       <c r="G23" s="2">
-        <v>19.27</v>
+        <v>17.06</v>
       </c>
       <c r="H23" s="2">
-        <v>20.96</v>
+        <v>18.16</v>
       </c>
       <c r="I23" s="2">
-        <v>22.810000000000002</v>
+        <v>19.83</v>
       </c>
       <c r="J23" s="2">
-        <v>24.84</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="24">
@@ -2011,22 +2011,22 @@
         <v>1</v>
       </c>
       <c r="E24" s="2">
-        <v>0.8200000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="F24" s="2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G24" s="2">
-        <v>1.27</v>
+        <v>1.1099999999999999</v>
       </c>
       <c r="H24" s="2">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="I24" s="2">
-        <v>1.4100000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="J24" s="2">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="25">
@@ -2045,22 +2045,22 @@
         <v>3.5</v>
       </c>
       <c r="E25" s="2">
-        <v>3.67</v>
+        <v>4.27</v>
       </c>
       <c r="F25" s="2">
-        <v>5.83</v>
+        <v>5.029999999999999</v>
       </c>
       <c r="G25" s="2">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="H25" s="2">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="I25" s="2">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="J25" s="2">
-        <v>8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="26">
@@ -2079,22 +2079,22 @@
         <v>30.1</v>
       </c>
       <c r="E26" s="4">
-        <v>25.21</v>
+        <v>31.72</v>
       </c>
       <c r="F26" s="4">
-        <v>36.059999999999995</v>
+        <v>33.400000000000006</v>
       </c>
       <c r="G26" s="4">
-        <v>46.940000000000005</v>
+        <v>35.13999999999998</v>
       </c>
       <c r="H26" s="4">
-        <v>55.25999999999997</v>
+        <v>44.059999999999995</v>
       </c>
       <c r="I26" s="4">
-        <v>65.22999999999996</v>
+        <v>54.74000000000002</v>
       </c>
       <c r="J26" s="4">
-        <v>77.21999999999997</v>
+        <v>68.84999999999998</v>
       </c>
     </row>
     <row r="27">
@@ -2115,22 +2115,22 @@
         <v>4.768534632788035</v>
       </c>
       <c r="E27" s="2">
-        <v>-16.24584717607973</v>
+        <v>5.3820598006644405</v>
       </c>
       <c r="F27" s="2">
-        <v>43.03847679492263</v>
+        <v>5.29634300126105</v>
       </c>
       <c r="G27" s="2">
-        <v>30.17193566278429</v>
+        <v>5.20958083832328</v>
       </c>
       <c r="H27" s="2">
-        <v>17.724755006391057</v>
+        <v>25.384177575412693</v>
       </c>
       <c r="I27" s="2">
-        <v>18.041983351429593</v>
+        <v>24.23967317294604</v>
       </c>
       <c r="J27" s="2">
-        <v>18.381112984822966</v>
+        <v>25.776397515527872</v>
       </c>
     </row>
     <row r="28">
@@ -2149,22 +2149,22 @@
         <v>20.06666666666667</v>
       </c>
       <c r="E28" s="2">
-        <v>22.349290780141846</v>
+        <v>20.164007373974954</v>
       </c>
       <c r="F28" s="2">
-        <v>23.15843555327211</v>
+        <v>20.244878167050555</v>
       </c>
       <c r="G28" s="2">
-        <v>23.618798430109692</v>
+        <v>20.309790775632866</v>
       </c>
       <c r="H28" s="2">
-        <v>24.166885331933866</v>
+        <v>21.32933146149005</v>
       </c>
       <c r="I28" s="2">
-        <v>24.69336765596607</v>
+        <v>22.085939076054075</v>
       </c>
       <c r="J28" s="2">
-        <v>25.204817704083286</v>
+        <v>22.940823670531778</v>
       </c>
     </row>
     <row r="29">
@@ -2183,22 +2183,22 @@
         <v>230</v>
       </c>
       <c r="E29" s="2">
-        <v>169</v>
+        <v>240</v>
       </c>
       <c r="F29" s="2">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="G29" s="2">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="H29" s="2">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="I29" s="2">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="J29" s="2">
-        <v>269</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30">
@@ -2251,22 +2251,22 @@
         <v>0.06086956521739131</v>
       </c>
       <c r="E31" s="2">
-        <v>0.06940828402366864</v>
+        <v>0.06229166666666666</v>
       </c>
       <c r="F31" s="2">
-        <v>0.07380952380952381</v>
+        <v>0.06333333333333334</v>
       </c>
       <c r="G31" s="2">
-        <v>0.07738955823293173</v>
+        <v>0.06462121212121212</v>
       </c>
       <c r="H31" s="2">
-        <v>0.081875</v>
+        <v>0.06627737226277372</v>
       </c>
       <c r="I31" s="2">
-        <v>0.08706106870229008</v>
+        <v>0.06982394366197182</v>
       </c>
       <c r="J31" s="2">
-        <v>0.09234200743494424</v>
+        <v>0.0736734693877551</v>
       </c>
     </row>
     <row r="32">
@@ -2287,22 +2287,22 @@
         <v>1.9901321235802572</v>
       </c>
       <c r="E32" s="2">
-        <v>14.027895181741323</v>
+        <v>2.336309523809521</v>
       </c>
       <c r="F32" s="2">
-        <v>6.3410871595014795</v>
+        <v>1.6722408026756064</v>
       </c>
       <c r="G32" s="2">
-        <v>4.850369218810724</v>
+        <v>2.0334928229664984</v>
       </c>
       <c r="H32" s="2">
-        <v>5.795926310326949</v>
+        <v>2.562873841572455</v>
       </c>
       <c r="I32" s="2">
-        <v>6.334129712720693</v>
+        <v>5.3511044239002326</v>
       </c>
       <c r="J32" s="2">
-        <v>6.0657867073888205</v>
+        <v>5.513188634001254</v>
       </c>
     </row>
     <row r="33">
@@ -2321,22 +2321,22 @@
         <v>0.2</v>
       </c>
       <c r="E33" s="2">
-        <v>0.164</v>
+        <v>0.20600000000000002</v>
       </c>
       <c r="F33" s="2">
-        <v>0.21000000000000002</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="G33" s="2">
-        <v>0.254</v>
+        <v>0.22199999999999998</v>
       </c>
       <c r="H33" s="2">
-        <v>0.27</v>
+        <v>0.22999999999999998</v>
       </c>
       <c r="I33" s="2">
-        <v>0.28200000000000003</v>
+        <v>0.238</v>
       </c>
       <c r="J33" s="2">
-        <v>0.296</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="34">
@@ -2357,22 +2357,22 @@
         <v>4.166666666666674</v>
       </c>
       <c r="E34" s="2">
-        <v>-18.000000000000004</v>
+        <v>3.0000000000000027</v>
       </c>
       <c r="F34" s="2">
-        <v>28.04878048780488</v>
+        <v>2.9126213592232997</v>
       </c>
       <c r="G34" s="2">
-        <v>20.952380952380945</v>
+        <v>4.7169811320754595</v>
       </c>
       <c r="H34" s="2">
-        <v>6.299212598425208</v>
+        <v>3.603603603603611</v>
       </c>
       <c r="I34" s="2">
-        <v>4.444444444444451</v>
+        <v>3.4782608695652195</v>
       </c>
       <c r="J34" s="2">
-        <v>4.964539007092172</v>
+        <v>3.3613445378151363</v>
       </c>
     </row>
     <row r="35">
@@ -2391,22 +2391,22 @@
         <v>0.12808510638297874</v>
       </c>
       <c r="E35" s="2">
-        <v>0.14488505747126437</v>
+        <v>0.12946938775510203</v>
       </c>
       <c r="F35" s="2">
-        <v>0.16772093023255813</v>
+        <v>0.12996108949416343</v>
       </c>
       <c r="G35" s="2">
-        <v>0.18480314960629923</v>
+        <v>0.13063197026022297</v>
       </c>
       <c r="H35" s="2">
-        <v>0.21172413793103437</v>
+        <v>0.157921146953405</v>
       </c>
       <c r="I35" s="2">
-        <v>0.24430711610486877</v>
+        <v>0.18941176470588245</v>
       </c>
       <c r="J35" s="2">
-        <v>0.28182481751824806</v>
+        <v>0.23026755852842803</v>
       </c>
     </row>
     <row r="36">
@@ -2425,22 +2425,22 @@
         <v>15.100000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>12.660000000000002</v>
+        <v>15.739999999999998</v>
       </c>
       <c r="F36" s="4">
-        <v>19.50999999999999</v>
+        <v>16.38000000000001</v>
       </c>
       <c r="G36" s="4">
-        <v>26.4</v>
+        <v>16.969999999999985</v>
       </c>
       <c r="H36" s="4">
-        <v>32.94999999999997</v>
+        <v>24.750000000000004</v>
       </c>
       <c r="I36" s="4">
-        <v>41.009999999999955</v>
+        <v>33.72000000000003</v>
       </c>
       <c r="J36" s="4">
-        <v>50.89999999999997</v>
+        <v>45.95999999999997</v>
       </c>
     </row>
     <row r="37">
@@ -2459,22 +2459,22 @@
         <v>10.066666666666668</v>
       </c>
       <c r="E37" s="2">
-        <v>11.223404255319151</v>
+        <v>10.005721187464243</v>
       </c>
       <c r="F37" s="2">
-        <v>12.529702652366575</v>
+        <v>9.928476178930785</v>
       </c>
       <c r="G37" s="2">
-        <v>13.28368722954614</v>
+        <v>9.808114668824405</v>
       </c>
       <c r="H37" s="2">
-        <v>14.410041109070223</v>
+        <v>11.981410659824759</v>
       </c>
       <c r="I37" s="2">
-        <v>15.524682010902469</v>
+        <v>13.605003026023816</v>
       </c>
       <c r="J37" s="2">
-        <v>16.613898227633246</v>
+        <v>15.313874450219902</v>
       </c>
     </row>
     <row r="38">
@@ -2495,22 +2495,22 @@
         <v>3.1420765027322606</v>
       </c>
       <c r="E38" s="2">
-        <v>-16.158940397350985</v>
+        <v>4.238410596026476</v>
       </c>
       <c r="F38" s="2">
-        <v>54.107424960505426</v>
+        <v>4.066073697585848</v>
       </c>
       <c r="G38" s="2">
-        <v>35.315222962583334</v>
+        <v>3.601953601953456</v>
       </c>
       <c r="H38" s="2">
-        <v>24.810606060605945</v>
+        <v>45.84560989982338</v>
       </c>
       <c r="I38" s="2">
-        <v>24.46130500758723</v>
+        <v>36.24242424242434</v>
       </c>
       <c r="J38" s="2">
-        <v>24.116069251402152</v>
+        <v>36.298932384341455</v>
       </c>
     </row>
   </sheetData>
@@ -2663,22 +2663,22 @@
         <v>80</v>
       </c>
       <c r="E3" s="4">
-        <v>40</v>
+        <v>84.33</v>
       </c>
       <c r="F3" s="4">
-        <v>80</v>
+        <v>88.89</v>
       </c>
       <c r="G3" s="4">
-        <v>120</v>
+        <v>93.69</v>
       </c>
       <c r="H3" s="4">
-        <v>145.2</v>
+        <v>121.44</v>
       </c>
       <c r="I3" s="4">
-        <v>175.69</v>
+        <v>157.4</v>
       </c>
       <c r="J3" s="4">
-        <v>212.59</v>
+        <v>204.01</v>
       </c>
     </row>
     <row r="4">
@@ -2699,22 +2699,22 @@
         <v>5.263157894736836</v>
       </c>
       <c r="E4" s="2">
-        <v>-50</v>
+        <v>5.412499999999998</v>
       </c>
       <c r="F4" s="2">
-        <v>100</v>
+        <v>5.407328352899321</v>
       </c>
       <c r="G4" s="2">
-        <v>50</v>
+        <v>5.39993250084374</v>
       </c>
       <c r="H4" s="2">
-        <v>20.999999999999996</v>
+        <v>29.618956131924424</v>
       </c>
       <c r="I4" s="2">
-        <v>20.998622589531692</v>
+        <v>29.61133069828723</v>
       </c>
       <c r="J4" s="2">
-        <v>21.002902840229964</v>
+        <v>29.61245235069885</v>
       </c>
     </row>
     <row r="5">
@@ -2733,22 +2733,22 @@
         <v>53.333333333333336</v>
       </c>
       <c r="E5" s="2">
-        <v>35.46099290780142</v>
+        <v>53.60752653995296</v>
       </c>
       <c r="F5" s="2">
-        <v>51.37756085029864</v>
+        <v>53.87925809188992</v>
       </c>
       <c r="G5" s="2">
-        <v>60.38039649793701</v>
+        <v>54.14980927060456</v>
       </c>
       <c r="H5" s="2">
-        <v>63.50039359748097</v>
+        <v>58.788788304206804</v>
       </c>
       <c r="I5" s="2">
-        <v>66.50893397940642</v>
+        <v>63.50615291506959</v>
       </c>
       <c r="J5" s="2">
-        <v>69.38995332441166</v>
+        <v>67.97614287618285</v>
       </c>
     </row>
     <row r="6">
@@ -2767,22 +2767,22 @@
         <v>25.6</v>
       </c>
       <c r="E6" s="4">
-        <v>14</v>
+        <v>26.989999999999995</v>
       </c>
       <c r="F6" s="4">
-        <v>28</v>
+        <v>28.450000000000003</v>
       </c>
       <c r="G6" s="4">
-        <v>42</v>
+        <v>29.979999999999997</v>
       </c>
       <c r="H6" s="4">
-        <v>50.81999999999999</v>
+        <v>39.489999999999995</v>
       </c>
       <c r="I6" s="4">
-        <v>61.489999999999995</v>
+        <v>52</v>
       </c>
       <c r="J6" s="4">
-        <v>74.41</v>
+        <v>68.45999999999998</v>
       </c>
     </row>
     <row r="7">
@@ -2801,22 +2801,22 @@
         <v>32</v>
       </c>
       <c r="E7" s="2">
-        <v>35</v>
+        <v>32.005217597533495</v>
       </c>
       <c r="F7" s="2">
-        <v>35</v>
+        <v>32.00584992687592</v>
       </c>
       <c r="G7" s="2">
-        <v>35</v>
+        <v>31.999146120183582</v>
       </c>
       <c r="H7" s="2">
-        <v>35</v>
+        <v>32.51811594202898</v>
       </c>
       <c r="I7" s="2">
-        <v>34.99914622346177</v>
+        <v>33.03684879288437</v>
       </c>
       <c r="J7" s="2">
-        <v>35.00164636154099</v>
+        <v>33.557178569677944</v>
       </c>
     </row>
     <row r="8">
@@ -2835,22 +2835,22 @@
         <v>7.300000000000004</v>
       </c>
       <c r="E8" s="4">
-        <v>4.300000000000001</v>
+        <v>7.079999999999991</v>
       </c>
       <c r="F8" s="4">
-        <v>8.600000000000001</v>
+        <v>6.870000000000001</v>
       </c>
       <c r="G8" s="4">
-        <v>12.899999999999999</v>
+        <v>6.629999999999999</v>
       </c>
       <c r="H8" s="4">
-        <v>18.50999999999999</v>
+        <v>12.969999999999995</v>
       </c>
       <c r="I8" s="4">
-        <v>25.539999999999992</v>
+        <v>21.26</v>
       </c>
       <c r="J8" s="4">
-        <v>34.28999999999999</v>
+        <v>32.759999999999984</v>
       </c>
     </row>
     <row r="9">
@@ -2869,22 +2869,22 @@
         <v>9.125000000000005</v>
       </c>
       <c r="E9" s="2">
-        <v>10.750000000000002</v>
+        <v>8.395588758448941</v>
       </c>
       <c r="F9" s="2">
-        <v>10.750000000000002</v>
+        <v>7.728653391832603</v>
       </c>
       <c r="G9" s="2">
-        <v>10.749999999999998</v>
+        <v>7.076528978546269</v>
       </c>
       <c r="H9" s="2">
-        <v>12.747933884297517</v>
+        <v>10.68017127799736</v>
       </c>
       <c r="I9" s="2">
-        <v>14.536968524104953</v>
+        <v>13.506988564167727</v>
       </c>
       <c r="J9" s="2">
-        <v>16.129639211628014</v>
+        <v>16.058036370766132</v>
       </c>
     </row>
     <row r="10">
@@ -2903,22 +2903,22 @@
         <v>6</v>
       </c>
       <c r="E10" s="2">
-        <v>3.33</v>
+        <v>6.45</v>
       </c>
       <c r="F10" s="2">
-        <v>6.67</v>
+        <v>6.94</v>
       </c>
       <c r="G10" s="2">
-        <v>10</v>
+        <v>7.47</v>
       </c>
       <c r="H10" s="2">
-        <v>11.13</v>
+        <v>7.89</v>
       </c>
       <c r="I10" s="2">
-        <v>12.38</v>
+        <v>8.82</v>
       </c>
       <c r="J10" s="2">
-        <v>13.78</v>
+        <v>9.86</v>
       </c>
     </row>
     <row r="11">
@@ -2937,22 +2937,22 @@
         <v>0.4</v>
       </c>
       <c r="E11" s="2">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="F11" s="2">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="G11" s="2">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="H11" s="2">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="2">
-        <v>0.67</v>
+        <v>0.52</v>
       </c>
       <c r="J11" s="2">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="12">
@@ -2971,22 +2971,22 @@
         <v>2</v>
       </c>
       <c r="E12" s="2">
-        <v>2.17</v>
+        <v>2.77</v>
       </c>
       <c r="F12" s="2">
-        <v>4.33</v>
+        <v>3.53</v>
       </c>
       <c r="G12" s="2">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="H12" s="2">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="I12" s="2">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="J12" s="2">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="13">
@@ -3005,22 +3005,22 @@
         <v>15.700000000000005</v>
       </c>
       <c r="E13" s="4">
-        <v>10</v>
+        <v>16.71999999999999</v>
       </c>
       <c r="F13" s="4">
-        <v>20</v>
+        <v>17.78</v>
       </c>
       <c r="G13" s="4">
-        <v>30</v>
+        <v>18.869999999999997</v>
       </c>
       <c r="H13" s="4">
-        <v>36.779999999999994</v>
+        <v>25.659999999999997</v>
       </c>
       <c r="I13" s="4">
-        <v>45.089999999999996</v>
+        <v>34.9</v>
       </c>
       <c r="J13" s="4">
-        <v>55.279999999999994</v>
+        <v>47.46999999999998</v>
       </c>
     </row>
     <row r="14">
@@ -3041,22 +3041,22 @@
         <v>5.2984574111334615</v>
       </c>
       <c r="E14" s="2">
-        <v>-36.305732484076444</v>
+        <v>6.496815286624114</v>
       </c>
       <c r="F14" s="2">
-        <v>100</v>
+        <v>6.339712918660356</v>
       </c>
       <c r="G14" s="2">
-        <v>50</v>
+        <v>6.13048368953879</v>
       </c>
       <c r="H14" s="2">
-        <v>22.599999999999977</v>
+        <v>35.9830418653948</v>
       </c>
       <c r="I14" s="2">
-        <v>22.59380097879282</v>
+        <v>36.00935307872175</v>
       </c>
       <c r="J14" s="2">
-        <v>22.59924595253937</v>
+        <v>36.01719197707731</v>
       </c>
     </row>
     <row r="15">
@@ -3075,22 +3075,22 @@
         <v>100</v>
       </c>
       <c r="E15" s="2">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="F15" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="G15" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H15" s="2">
         <v>120</v>
       </c>
       <c r="I15" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J15" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
@@ -3143,22 +3143,22 @@
         <v>0.06</v>
       </c>
       <c r="E17" s="2">
-        <v>0.08763157894736842</v>
+        <v>0.06142857142857143</v>
       </c>
       <c r="F17" s="2">
-        <v>0.08662337662337662</v>
+        <v>0.06252252252252252</v>
       </c>
       <c r="G17" s="2">
-        <v>0.08695652173913043</v>
+        <v>0.06384615384615384</v>
       </c>
       <c r="H17" s="2">
-        <v>0.09275000000000001</v>
+        <v>0.06575</v>
       </c>
       <c r="I17" s="2">
-        <v>0.09983870967741935</v>
+        <v>0.07170731707317074</v>
       </c>
       <c r="J17" s="2">
-        <v>0.10682170542635658</v>
+        <v>0.07825396825396826</v>
       </c>
     </row>
     <row r="18">
@@ -3179,22 +3179,22 @@
         <v>1.9677996422182487</v>
       </c>
       <c r="E18" s="2">
-        <v>46.05263157894737</v>
+        <v>2.3809523809523947</v>
       </c>
       <c r="F18" s="2">
-        <v>-1.1505011505011598</v>
+        <v>1.780850618059926</v>
       </c>
       <c r="G18" s="2">
-        <v>0.3845903135388795</v>
+        <v>2.1170472179117716</v>
       </c>
       <c r="H18" s="2">
-        <v>6.662500000000016</v>
+        <v>2.9819277108433795</v>
       </c>
       <c r="I18" s="2">
-        <v>7.642813668376647</v>
+        <v>9.060558286191235</v>
       </c>
       <c r="J18" s="2">
-        <v>6.994276840615643</v>
+        <v>9.129683619479522</v>
       </c>
     </row>
     <row r="19">
@@ -3213,22 +3213,22 @@
         <v>0.2</v>
       </c>
       <c r="E19" s="2">
-        <v>0.1</v>
+        <v>0.21</v>
       </c>
       <c r="F19" s="2">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="G19" s="2">
-        <v>0.3</v>
+        <v>0.235</v>
       </c>
       <c r="H19" s="2">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="I19" s="2">
-        <v>0.335</v>
+        <v>0.26</v>
       </c>
       <c r="J19" s="2">
-        <v>0.355</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="20">
@@ -3249,22 +3249,22 @@
         <v>5.263157894736836</v>
       </c>
       <c r="E20" s="2">
-        <v>-50</v>
+        <v>4.999999999999982</v>
       </c>
       <c r="F20" s="2">
-        <v>100</v>
+        <v>4.761904761904767</v>
       </c>
       <c r="G20" s="2">
-        <v>49.99999999999998</v>
+        <v>6.818181818181812</v>
       </c>
       <c r="H20" s="2">
-        <v>6.666666666666665</v>
+        <v>6.382978723404253</v>
       </c>
       <c r="I20" s="2">
-        <v>4.6875</v>
+        <v>4.0000000000000036</v>
       </c>
       <c r="J20" s="2">
-        <v>5.970149253731338</v>
+        <v>5.769230769230771</v>
       </c>
     </row>
     <row r="21">
@@ -3283,22 +3283,22 @@
         <v>0.15392156862745102</v>
       </c>
       <c r="E21" s="2">
-        <v>0.25</v>
+        <v>0.15626168224299058</v>
       </c>
       <c r="F21" s="2">
-        <v>0.25316455696202533</v>
+        <v>0.15734513274336284</v>
       </c>
       <c r="G21" s="2">
-        <v>0.2564102564102564</v>
+        <v>0.15857142857142856</v>
       </c>
       <c r="H21" s="2">
-        <v>0.3014754098360655</v>
+        <v>0.210327868852459</v>
       </c>
       <c r="I21" s="2">
-        <v>0.3578571428571428</v>
+        <v>0.2792</v>
       </c>
       <c r="J21" s="2">
-        <v>0.42198473282442744</v>
+        <v>0.3708593749999998</v>
       </c>
     </row>
     <row r="22">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 -24.8 % / 補助 -50 % / 他 4 %</t>
+          <t xml:space="preserve">全社 4.87 % / 補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.04 % / 補助 100 % / 他 4 %</t>
+          <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 27.63 % / 補助 50 % / 他 4 %</t>
+          <t xml:space="preserve">全社 4.87 % / 補助 5.4 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.05 % / 補助 21 % / 他 5.99 %</t>
+          <t xml:space="preserve">全社 19.39 % / 補助 29.62 % / 他 7.31 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.53 % / 補助 21 % / 他 6 %</t>
+          <t xml:space="preserve">全社 19.98 % / 補助 29.61 % / 他 6.25 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.98 % / 補助 21 % / 他 6 %</t>
+          <t xml:space="preserve">全社 21.09 % / 補助 29.61 % / 他 6.26 %</t>
         </is>
       </c>
     </row>
@@ -3673,32 +3673,32 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.83 % / 補助 65 % / 他 67.83 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 67.99 % / 他 68 %</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.3 % / 補助 65 % / 他 67.67 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 67.99 % / 他 68 %</t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.99 % / 補助 65 % / 他 67.5 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68.01 %</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.79 % / 補助 65 % / 他 67.17 %</t>
+          <t xml:space="preserve">全社 67.35 % / 補助 67.48 % / 他 67.17 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.62 % / 補助 65 % / 他 66.84 %</t>
+          <t xml:space="preserve">全社 66.98 % / 補助 66.96 % / 他 67 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 65.46 % / 補助 65 % / 他 66.5 %</t>
+          <t xml:space="preserve">全社 66.57 % / 補助 66.44 % / 他 66.83 %</t>
         </is>
       </c>
     </row>
@@ -3735,32 +3735,32 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.17 % / 補助 35 % / 他 32.17 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32.01 % / 他 32 %</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.7 % / 補助 35 % / 他 32.33 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32.01 % / 他 32 %</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.01 % / 補助 35 % / 他 32.5 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 31.99 %</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.21 % / 補助 35 % / 他 32.83 %</t>
+          <t xml:space="preserve">全社 32.65 % / 補助 32.52 % / 他 32.83 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.38 % / 補助 35 % / 他 33.16 %</t>
+          <t xml:space="preserve">全社 33.02 % / 補助 33.04 % / 他 33 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.54 % / 補助 35 % / 他 33.5 %</t>
+          <t xml:space="preserve">全社 33.43 % / 補助 33.56 % / 他 33.17 %</t>
         </is>
       </c>
     </row>
@@ -3797,32 +3797,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.2 % / 補助 24.25 % / 他 25.73 %</t>
+          <t xml:space="preserve">全社 24.71 % / 補助 23.61 % / 他 25.98 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.92 % / 補助 24.25 % / 他 25.62 %</t>
+          <t xml:space="preserve">全社 25.12 % / 補助 24.28 % / 他 26.11 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.75 % / 補助 24.25 % / 他 25.51 %</t>
+          <t xml:space="preserve">全社 25.54 % / 補助 24.92 % / 他 26.27 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.3 % / 補助 22.25 % / 他 25.11 %</t>
+          <t xml:space="preserve">全社 23.47 % / 補助 21.84 % / 他 25.81 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.89 % / 補助 20.46 % / 他 24.72 %</t>
+          <t xml:space="preserve">全社 21.76 % / 補助 19.53 % / 他 25.64 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20.54 % / 補助 18.87 % / 他 24.32 %</t>
+          <t xml:space="preserve">全社 20.05 % / 補助 17.5 % / 他 25.47 %</t>
         </is>
       </c>
     </row>
@@ -3859,32 +3859,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.97 % / 補助 10.75 % / 他 6.44 %</t>
+          <t xml:space="preserve">全社 7.29 % / 補助 8.4 % / 他 6.02 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.79 % / 補助 10.75 % / 他 6.71 %</t>
+          <t xml:space="preserve">全社 6.88 % / 補助 7.73 % / 他 5.89 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.26 % / 補助 10.75 % / 他 6.99 %</t>
+          <t xml:space="preserve">全社 6.46 % / 補助 7.08 % / 他 5.72 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.91 % / 補助 12.75 % / 他 7.72 %</t>
+          <t xml:space="preserve">全社 9.17 % / 補助 10.68 % / 他 7.02 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.5 % / 補助 14.54 % / 他 8.44 %</t>
+          <t xml:space="preserve">全社 11.26 % / 補助 13.51 % / 他 7.36 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14 % / 補助 16.13 % / 他 9.18 %</t>
+          <t xml:space="preserve">全社 13.38 % / 補助 16.06 % / 他 7.7 %</t>
         </is>
       </c>
     </row>
@@ -3921,32 +3921,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.22 % / 補助 16.18 % / 他 8.5 %</t>
+          <t xml:space="preserve">全社 10.01 % / 補助 11.68 % / 他 8.07 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.53 % / 補助 16.16 % / 他 8.69 %</t>
+          <t xml:space="preserve">全社 9.93 % / 補助 11.7 % / 他 7.86 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.28 % / 補助 16.17 % / 他 8.89 %</t>
+          <t xml:space="preserve">全社 9.81 % / 補助 11.67 % / 他 7.61 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.41 % / 補助 17.22 % / 他 9.51 %</t>
+          <t xml:space="preserve">全社 11.98 % / 補助 14.22 % / 他 8.79 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.52 % / 補助 18.24 % / 他 10.14 %</t>
+          <t xml:space="preserve">全社 13.61 % / 補助 16.24 % / 他 9.02 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 16.61 % / 補助 19.19 % / 他 10.78 %</t>
+          <t xml:space="preserve">全社 15.31 % / 補助 18.17 % / 他 9.26 %</t>
         </is>
       </c>
     </row>
@@ -3983,32 +3983,32 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.82 % / 補助 10 % / 他 11.26 %</t>
+          <t xml:space="preserve">全社 12 % / 補助 12.5 % / 他 11.43 %</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.53 % / 補助 10 % / 他 11.09 %</t>
+          <t xml:space="preserve">全社 12.01 % / 補助 12.5 % / 他 11.43 %</t>
         </is>
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.37 % / 補助 10 % / 他 10.93 %</t>
+          <t xml:space="preserve">全社 12.01 % / 補助 12.5 % / 他 11.43 %</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.01 % / 補助 9.67 % / 他 10.62 %</t>
+          <t xml:space="preserve">全社 11.51 % / 補助 11.77 % / 他 11.15 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.66 % / 補助 9.33 % / 他 10.31 %</t>
+          <t xml:space="preserve">全社 11.02 % / 補助 11.04 % / 他 10.98 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.31 % / 補助 9 % / 他 10 %</t>
+          <t xml:space="preserve">全社 10.47 % / 補助 10.31 % / 他 10.81 %</t>
         </is>
       </c>
     </row>
@@ -4107,32 +4107,32 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.4 % / 補助 8.33 % / 他 11.54 %</t>
+          <t xml:space="preserve">全社 9.5 % / 補助 7.65 % / 他 11.65 %</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.95 % / 補助 8.34 % / 他 11.66 %</t>
+          <t xml:space="preserve">全社 9.67 % / 補助 7.81 % / 他 11.85 %</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.7 % / 補助 8.33 % / 他 11.77 %</t>
+          <t xml:space="preserve">全社 9.86 % / 補助 7.97 % / 他 12.09 %</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.17 % / 補助 7.67 % / 他 11.78 %</t>
+          <t xml:space="preserve">全社 8.79 % / 補助 6.5 % / 他 12.06 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.63 % / 補助 7.05 % / 他 11.79 %</t>
+          <t xml:space="preserve">全社 8 % / 補助 5.6 % / 他 12.17 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.11 % / 補助 6.48 % / 他 11.79 %</t>
+          <t xml:space="preserve">全社 7.22 % / 補助 4.83 % / 他 12.28 %</t>
         </is>
       </c>
     </row>
@@ -4169,32 +4169,32 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.73 % / 補助 0.5 % / 他 0.85 %</t>
+          <t xml:space="preserve">全社 0.65 % / 補助 0.5 % / 他 0.84 %</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / 他 0.86 %</t>
+          <t xml:space="preserve">全社 0.64 % / 補助 0.49 % / 他 0.81 %</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.64 % / 補助 0.5 % / 他 0.85 %</t>
+          <t xml:space="preserve">全社 0.64 % / 補助 0.5 % / 他 0.81 %</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.59 % / 補助 0.44 % / 他 0.85 %</t>
+          <t xml:space="preserve">全社 0.56 % / 補助 0.41 % / 他 0.76 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.53 % / 補助 0.38 % / 他 0.84 %</t>
+          <t xml:space="preserve">全社 0.48 % / 補助 0.33 % / 他 0.74 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.48 % / 補助 0.33 % / 他 0.82 %</t>
+          <t xml:space="preserve">全社 0.41 % / 補助 0.27 % / 他 0.71 %</t>
         </is>
       </c>
     </row>
@@ -4231,32 +4231,32 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.13 % / 補助 8.83 % / 他 12.39 %</t>
+          <t xml:space="preserve">全社 10.16 % / 補助 8.15 % / 他 12.48 %</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.63 % / 補助 8.84 % / 他 12.52 %</t>
+          <t xml:space="preserve">全社 10.32 % / 補助 8.3 % / 他 12.67 %</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.34 % / 補助 8.83 % / 他 12.62 %</t>
+          <t xml:space="preserve">全社 10.5 % / 補助 8.47 % / 他 12.9 %</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.76 % / 補助 8.11 % / 他 12.63 %</t>
+          <t xml:space="preserve">全社 9.35 % / 補助 6.91 % / 他 12.83 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.17 % / 補助 7.43 % / 他 12.63 %</t>
+          <t xml:space="preserve">全社 8.48 % / 補助 5.93 % / 他 12.91 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.59 % / 補助 6.82 % / 他 12.61 %</t>
+          <t xml:space="preserve">全社 7.63 % / 補助 5.1 % / 他 12.99 %</t>
         </is>
       </c>
     </row>
@@ -4293,32 +4293,32 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.069 億円/人 / 補助 0.088 億円/人 / 他 0.064 億円/人</t>
+          <t xml:space="preserve">全社 0.062 億円/人 / 補助 0.061 億円/人 / 他 0.063 億円/人</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.087 億円/人 / 他 0.066 億円/人</t>
+          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.063 億円/人 / 他 0.064 億円/人</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.077 億円/人 / 補助 0.087 億円/人 / 他 0.069 億円/人</t>
+          <t xml:space="preserve">全社 0.065 億円/人 / 補助 0.064 億円/人 / 他 0.065 億円/人</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.093 億円/人 / 他 0.072 億円/人</t>
+          <t xml:space="preserve">全社 0.066 億円/人 / 補助 0.066 億円/人 / 他 0.067 億円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.087 億円/人 / 補助 0.1 億円/人 / 他 0.076 億円/人</t>
+          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.072 億円/人 / 他 0.068 億円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.092 億円/人 / 補助 0.107 億円/人 / 他 0.079 億円/人</t>
+          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.078 億円/人 / 他 0.07 億円/人</t>
         </is>
       </c>
     </row>
@@ -4355,32 +4355,32 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.164 億円/人 / 補助 0.1 億円/人 / 他 0.207 億円/人</t>
+          <t xml:space="preserve">全社 0.206 億円/人 / 補助 0.21 億円/人 / 他 0.203 億円/人</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.21 億円/人 / 補助 0.2 億円/人 / 他 0.217 億円/人</t>
+          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.22 億円/人 / 他 0.207 億円/人</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.254 億円/人 / 補助 0.3 億円/人 / 他 0.223 億円/人</t>
+          <t xml:space="preserve">全社 0.222 億円/人 / 補助 0.235 億円/人 / 他 0.213 億円/人</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.27 億円/人 / 補助 0.32 億円/人 / 他 0.237 億円/人</t>
+          <t xml:space="preserve">全社 0.23 億円/人 / 補助 0.25 億円/人 / 他 0.217 億円/人</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.282 億円/人 / 補助 0.335 億円/人 / 他 0.247 億円/人</t>
+          <t xml:space="preserve">全社 0.238 億円/人 / 補助 0.26 億円/人 / 他 0.223 億円/人</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.296 億円/人 / 補助 0.355 億円/人 / 他 0.257 億円/人</t>
+          <t xml:space="preserve">全社 0.246 億円/人 / 補助 0.275 億円/人 / 他 0.227 億円/人</t>
         </is>
       </c>
     </row>
@@ -4417,32 +4417,32 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 14.03 % / 補助 46.05 % / 他 4.2 %</t>
+          <t xml:space="preserve">全社 2.34 % / 補助 2.38 % / 他 2.31 %</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.34 % / 補助 -1.15 % / 他 3.54 %</t>
+          <t xml:space="preserve">全社 1.67 % / 補助 1.78 % / 他 1.6 %</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.85 % / 補助 0.38 % / 他 4.2 %</t>
+          <t xml:space="preserve">全社 2.03 % / 補助 2.12 % / 他 1.98 %</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.8 % / 補助 6.66 % / 他 4.48 %</t>
+          <t xml:space="preserve">全社 2.56 % / 補助 2.98 % / 他 2.22 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.33 % / 補助 7.64 % / 他 4.57 %</t>
+          <t xml:space="preserve">全社 5.35 % / 補助 9.06 % / 他 2.54 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.07 % / 補助 6.99 % / 他 4.53 %</t>
+          <t xml:space="preserve">全社 5.51 % / 補助 9.13 % / 他 2.71 %</t>
         </is>
       </c>
     </row>
@@ -4479,32 +4479,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.78 % / 補助 35.3 % / 他 59.3 %</t>
+          <t xml:space="preserve">全社 50.38 % / 補助 41.09 % / 他 60.73 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.9 % / 補助 35.35 % / 他 59.03 %</t>
+          <t xml:space="preserve">全社 50.96 % / 補助 41.51 % / 他 61.72 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 43.76 % / 補助 35.33 % / 他 58.68 %</t>
+          <t xml:space="preserve">全社 51.71 % / 補助 42.08 % / 他 62.88 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 40.37 % / 補助 32 % / 他 57.03 %</t>
+          <t xml:space="preserve">全社 43.83 % / 補助 32.7 % / 他 59.35 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 37.13 % / 補助 28.94 % / 他 55.46 %</t>
+          <t xml:space="preserve">全社 38.4 % / 補助 26.76 % / 他 58.87 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 34.08 % / 補助 26.21 % / 他 53.92 %</t>
+          <t xml:space="preserve">全社 33.25 % / 補助 21.93 % / 他 58.37 %</t>
         </is>
       </c>
     </row>
@@ -4603,32 +4603,32 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.667 億円/人 / 補助 1.053 億円/人 / 他 0.556 億円/人</t>
+          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.803 億円/人 / 他 0.541 億円/人</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.741 億円/人 / 補助 1.039 億円/人 / 他 0.569 億円/人</t>
+          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.801 億円/人 / 他 0.54 億円/人</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.798 億円/人 / 補助 1.043 億円/人 / 他 0.588 億円/人</t>
+          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.801 億円/人 / 他 0.54 億円/人</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.893 億円/人 / 補助 1.21 億円/人 / 他 0.614 億円/人</t>
+          <t xml:space="preserve">全社 0.754 億円/人 / 補助 1.012 億円/人 / 他 0.553 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.008 億円/人 / 補助 1.417 億円/人 / 他 0.641 億円/人</t>
+          <t xml:space="preserve">全社 0.873 億円/人 / 補助 1.28 億円/人 / 他 0.562 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.139 億円/人 / 補助 1.648 億円/人 / 他 0.67 億円/人</t>
+          <t xml:space="preserve">全社 1.021 億円/人 / 補助 1.619 億円/人 / 他 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -4665,32 +4665,32 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.053 億円/人 / 補助 0.113 億円/人 / 他 0.036 億円/人</t>
+          <t xml:space="preserve">全社 0.048 億円/人 / 補助 0.067 億円/人 / 他 0.033 億円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.065 億円/人 / 補助 0.112 億円/人 / 他 0.038 億円/人</t>
+          <t xml:space="preserve">全社 0.045 億円/人 / 補助 0.062 億円/人 / 他 0.032 億円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.112 億円/人 / 他 0.041 億円/人</t>
+          <t xml:space="preserve">全社 0.042 億円/人 / 補助 0.057 億円/人 / 他 0.031 億円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.097 億円/人 / 補助 0.154 億円/人 / 他 0.047 億円/人</t>
+          <t xml:space="preserve">全社 0.069 億円/人 / 補助 0.108 億円/人 / 他 0.039 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.126 億円/人 / 補助 0.206 億円/人 / 他 0.054 億円/人</t>
+          <t xml:space="preserve">全社 0.098 億円/人 / 補助 0.173 億円/人 / 他 0.041 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.159 億円/人 / 補助 0.266 億円/人 / 他 0.062 億円/人</t>
+          <t xml:space="preserve">全社 0.137 億円/人 / 補助 0.26 億円/人 / 他 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -4727,32 +4727,32 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.145 億円/人 / 補助 0.25 億円/人 / 他 0.114 億円/人</t>
+          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.156 億円/人 / 他 0.109 億円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.168 億円/人 / 補助 0.253 億円/人 / 他 0.118 億円/人</t>
+          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.157 億円/人 / 他 0.108 億円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.185 億円/人 / 補助 0.256 億円/人 / 他 0.124 億円/人</t>
+          <t xml:space="preserve">全社 0.131 億円/人 / 補助 0.159 億円/人 / 他 0.108 億円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.301 億円/人 / 他 0.133 億円/人</t>
+          <t xml:space="preserve">全社 0.158 億円/人 / 補助 0.21 億円/人 / 他 0.117 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.244 億円/人 / 補助 0.358 億円/人 / 他 0.143 億円/人</t>
+          <t xml:space="preserve">全社 0.189 億円/人 / 補助 0.279 億円/人 / 他 0.121 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.282 億円/人 / 補助 0.422 億円/人 / 他 0.153 億円/人</t>
+          <t xml:space="preserve">全社 0.23 億円/人 / 補助 0.371 億円/人 / 他 0.125 億円/人</t>
         </is>
       </c>
     </row>
@@ -4789,32 +4789,32 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 -26.52 % / 補助 -62 % / 他 0.77 %</t>
+          <t xml:space="preserve">全社 4.35 % / 補助 5 % / 他 3.85 %</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.26 % / 補助 102.63 % / 他 1.53 %</t>
+          <t xml:space="preserve">全社 5 % / 補助 5.71 % / 他 4.44 %</t>
         </is>
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 18.57 % / 補助 49.35 % / 他 0.75 %</t>
+          <t xml:space="preserve">全社 4.76 % / 補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.81 % / 補助 4.35 % / 他 1.49 %</t>
+          <t xml:space="preserve">全社 3.79 % / 補助 2.56 % / 他 4.76 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.34 % / 補助 3.33 % / 他 1.47 %</t>
+          <t xml:space="preserve">全社 3.65 % / 補助 2.5 % / 他 4.55 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.67 % / 補助 4.03 % / 他 1.45 %</t>
+          <t xml:space="preserve">全社 3.52 % / 補助 2.44 % / 他 4.35 %</t>
         </is>
       </c>
     </row>
@@ -4851,32 +4851,32 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.72 pt / 補助 12 pt / 他 3.23 pt</t>
+          <t xml:space="preserve">全社 0.53 pt / 補助 0.41 pt / 他 0.41 pt</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.78 pt / 補助 -2.63 pt / 他 2.47 pt</t>
+          <t xml:space="preserve">全社 -0.12 pt / 補助 -0.31 pt / 他 -0.18 pt</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.06 pt / 補助 0.65 pt / 他 3.25 pt</t>
+          <t xml:space="preserve">全社 0.11 pt / 補助 -0.01 pt / 他 0 pt</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.24 pt / 補助 16.65 pt / 他 4.5 pt</t>
+          <t xml:space="preserve">全社 15.6 pt / 補助 27.05 pt / 他 2.55 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.18 pt / 補助 17.67 pt / 他 4.53 pt</t>
+          <t xml:space="preserve">全社 16.33 pt / 補助 27.11 pt / 他 1.7 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.31 pt / 補助 16.97 pt / 他 4.55 pt</t>
+          <t xml:space="preserve">全社 17.57 pt / 補助 27.17 pt / 他 1.91 pt</t>
         </is>
       </c>
     </row>
@@ -4975,32 +4975,32 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.25 % / 補助 5.43 % / 他 2.06 %</t>
+          <t xml:space="preserve">全社 2.71 % / 補助 3.28 % / 他 2.06 %</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.74 % / 補助 5.41 % / 他 1.98 %</t>
+          <t xml:space="preserve">全社 3.05 % / 補助 3.97 % / 他 1.97 %</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.03 % / 補助 5.42 % / 他 1.91 %</t>
+          <t xml:space="preserve">全社 3.35 % / 補助 4.59 % / 他 1.89 %</t>
         </is>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.5 % / 補助 4.48 % / 他 1.8 %</t>
+          <t xml:space="preserve">全社 2.81 % / 補助 3.54 % / 他 1.76 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.03 % / 補助 3.7 % / 他 1.7 %</t>
+          <t xml:space="preserve">全社 2.34 % / 補助 2.73 % / 他 1.66 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.61 % / 補助 3.06 % / 他 1.6 %</t>
+          <t xml:space="preserve">全社 1.93 % / 補助 2.11 % / 他 1.56 %</t>
         </is>
       </c>
     </row>
@@ -5037,17 +5037,17 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.3 %</t>
+          <t xml:space="preserve">全社 9.54 %</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.63 %</t>
+          <t xml:space="preserve">全社 9.09 %</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.55 %</t>
+          <t xml:space="preserve">全社 8.67 %</t>
         </is>
       </c>
       <c r="J27" s="0" t="inlineStr">
@@ -5099,17 +5099,17 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.18 倍</t>
+          <t xml:space="preserve">全社 0.95 倍</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.77 倍</t>
+          <t xml:space="preserve">全社 0.92 倍</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.57 倍</t>
+          <t xml:space="preserve">全社 0.88 倍</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
@@ -5161,32 +5161,32 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.45 倍 / 補助 2.98 倍 / 他 4.13 倍</t>
+          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / 他 3.93 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.35 倍 / 補助 2.99 倍 / 他 4.39 倍</t>
+          <t xml:space="preserve">全社 3.26 倍 / 補助 2.95 倍 / 他 3.99 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.3 倍 / 補助 2.98 倍 / 他 4.67 倍</t>
+          <t xml:space="preserve">全社 2.93 倍 / 補助 2.54 倍 / 他 4.03 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.12 倍 / 補助 3.85 倍 / 他 5.29 倍</t>
+          <t xml:space="preserve">全社 4.27 倍 / 補助 4.02 倍 / 他 4.99 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.13 倍 / 補助 4.93 倍 / 他 5.98 倍</t>
+          <t xml:space="preserve">全社 5.81 倍 / 補助 5.94 倍 / 他 5.44 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.36 倍 / 補助 6.28 倍 / 他 6.74 倍</t>
+          <t xml:space="preserve">全社 7.92 倍 / 補助 8.62 倍 / 他 5.93 倍</t>
         </is>
       </c>
     </row>
@@ -5223,17 +5223,17 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 -2.48 倍</t>
+          <t xml:space="preserve">全社 0.49 倍</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.86 倍</t>
+          <t xml:space="preserve">全社 0.51 倍</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.87 倍</t>
+          <t xml:space="preserve">全社 0.54 倍</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 35.46 %</t>
+          <t xml:space="preserve">構成比 53.61 %</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 51.38 %</t>
+          <t xml:space="preserve">構成比 53.88 %</t>
         </is>
       </c>
       <c r="I32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 60.38 %</t>
+          <t xml:space="preserve">構成比 54.15 %</t>
         </is>
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 63.5 %</t>
+          <t xml:space="preserve">構成比 58.79 %</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 66.51 %</t>
+          <t xml:space="preserve">構成比 63.51 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 69.39 %</t>
+          <t xml:space="preserve">構成比 67.98 %</t>
         </is>
       </c>
     </row>
@@ -5409,32 +5409,32 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 -50 % / 他 4 %</t>
+          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 100 % / 他 4 %</t>
+          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 50 % / 他 4 %</t>
+          <t xml:space="preserve">補助 5.4 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21 % / 他 5.99 %</t>
+          <t xml:space="preserve">補助 29.62 % / 他 7.31 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21 % / 他 6 %</t>
+          <t xml:space="preserve">補助 29.61 % / 他 6.25 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 21 % / 他 6 %</t>
+          <t xml:space="preserve">補助 29.61 % / 他 6.26 %</t>
         </is>
       </c>
     </row>
@@ -5471,32 +5471,32 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2.83 pt</t>
+          <t xml:space="preserve">差 -0.01 pt</t>
         </is>
       </c>
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2.67 pt</t>
+          <t xml:space="preserve">差 -0 pt</t>
         </is>
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2.5 pt</t>
+          <t xml:space="preserve">差 -0.01 pt</t>
         </is>
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -2.17 pt</t>
+          <t xml:space="preserve">差 0.31 pt</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -1.84 pt</t>
+          <t xml:space="preserve">差 -0.04 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -1.5 pt</t>
+          <t xml:space="preserve">差 -0.39 pt</t>
         </is>
       </c>
     </row>
@@ -5533,32 +5533,32 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.31 pt</t>
+          <t xml:space="preserve">差 2.38 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.04 pt</t>
+          <t xml:space="preserve">差 1.84 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.76 pt</t>
+          <t xml:space="preserve">差 1.35 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 5.03 pt</t>
+          <t xml:space="preserve">差 3.66 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.09 pt</t>
+          <t xml:space="preserve">差 6.14 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.95 pt</t>
+          <t xml:space="preserve">差 8.36 pt</t>
         </is>
       </c>
     </row>
@@ -5595,32 +5595,32 @@
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.053 億円/人 / 他 0.556 億円/人</t>
+          <t xml:space="preserve">補助 0.803 億円/人 / 他 0.541 億円/人</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.039 億円/人 / 他 0.569 億円/人</t>
+          <t xml:space="preserve">補助 0.801 億円/人 / 他 0.54 億円/人</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.043 億円/人 / 他 0.588 億円/人</t>
+          <t xml:space="preserve">補助 0.801 億円/人 / 他 0.54 億円/人</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.21 億円/人 / 他 0.614 億円/人</t>
+          <t xml:space="preserve">補助 1.012 億円/人 / 他 0.553 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.417 億円/人 / 他 0.641 億円/人</t>
+          <t xml:space="preserve">補助 1.28 億円/人 / 他 0.562 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.648 億円/人 / 他 0.67 億円/人</t>
+          <t xml:space="preserve">補助 1.619 億円/人 / 他 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -5657,32 +5657,32 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.088 億円/人 / 他 0.064 億円/人</t>
+          <t xml:space="preserve">補助 0.061 億円/人 / 他 0.063 億円/人</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.087 億円/人 / 他 0.066 億円/人</t>
+          <t xml:space="preserve">補助 0.063 億円/人 / 他 0.064 億円/人</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.087 億円/人 / 他 0.069 億円/人</t>
+          <t xml:space="preserve">補助 0.064 億円/人 / 他 0.065 億円/人</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.093 億円/人 / 他 0.072 億円/人</t>
+          <t xml:space="preserve">補助 0.066 億円/人 / 他 0.067 億円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.1 億円/人 / 他 0.076 億円/人</t>
+          <t xml:space="preserve">補助 0.072 億円/人 / 他 0.068 億円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.107 億円/人 / 他 0.079 億円/人</t>
+          <t xml:space="preserve">補助 0.078 億円/人 / 他 0.07 億円/人</t>
         </is>
       </c>
     </row>
@@ -5719,32 +5719,32 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 114.94 %</t>
+          <t xml:space="preserve">寄与率 169.23 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 91.68 %</t>
+          <t xml:space="preserve">寄与率 175 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 91.1 %</t>
+          <t xml:space="preserve">寄与率 133.33 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 85.65 %</t>
+          <t xml:space="preserve">寄与率 81.49 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 87.22 %</t>
+          <t xml:space="preserve">寄与率 92.42 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 88.47 %</t>
+          <t xml:space="preserve">寄与率 93.95 %</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <v>21</v>
+        <v>5.407072368421051</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="D4" s="2">
-        <v>-5</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E4" s="2">
-        <v>40</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="5">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <v>7.000000000000001</v>
+        <v>1.174186491064466e-14</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>2</v>
+        <v>1.6653345369377348e-14</v>
       </c>
     </row>
     <row r="6">
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <v>7.000000000000001</v>
+        <v>2.0019816287178878</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="D6" s="2">
-        <v>0</v>
+        <v>1.9325330501846927</v>
       </c>
       <c r="E6" s="2">
-        <v>10</v>
+        <v>2.0735994183189166</v>
       </c>
     </row>
     <row r="7">
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <v>4</v>
+        <v>5.444853630675327</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="D7" s="2">
-        <v>-3</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E7" s="2">
-        <v>20</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="8">
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>6</v>
+        <v>5.40609337027898</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="D9" s="2">
-        <v>0</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E9" s="2">
-        <v>10</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="10">
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>4</v>
+        <v>4.260731658392249</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="D10" s="2">
-        <v>-10</v>
+        <v>4.076086956521719</v>
       </c>
       <c r="E10" s="2">
-        <v>20</v>
+        <v>4.438405797101453</v>
       </c>
     </row>
     <row r="11">
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="2">
-        <v>2</v>
+        <v>0.013457556935819737</v>
       </c>
     </row>
     <row r="12">
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>4</v>
+        <v>1.9809059504605664</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -6026,10 +6026,10 @@
         </is>
       </c>
       <c r="D12" s="2">
-        <v>0</v>
+        <v>1.9139457023717443</v>
       </c>
       <c r="E12" s="2">
-        <v>8</v>
+        <v>2.0553459914763095</v>
       </c>
     </row>
     <row r="13">
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>1</v>
+        <v>4.149377724930645</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6047,10 +6047,10 @@
         </is>
       </c>
       <c r="D13" s="2">
-        <v>-5</v>
+        <v>3.9166666666666683</v>
       </c>
       <c r="E13" s="2">
-        <v>10</v>
+        <v>4.250000000000009</v>
       </c>
     </row>
     <row r="14">
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>21</v>
+        <v>29.61371439006574</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="D15" s="2">
-        <v>-5</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>6</v>
+        <v>6.249525817103336</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6110,10 +6110,10 @@
         </is>
       </c>
       <c r="D16" s="2">
-        <v>-10</v>
+        <v>6.076086956521719</v>
       </c>
       <c r="E16" s="2">
-        <v>20</v>
+        <v>6.438405797101453</v>
       </c>
     </row>
     <row r="17">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0</v>
+        <v>1.5550427257977284</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -6152,10 +6152,10 @@
         </is>
       </c>
       <c r="D18" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E18" s="2">
-        <v>3</v>
+        <v>0.5134575569358197</v>
       </c>
     </row>
     <row r="19">
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>7.000000000000001</v>
+        <v>8.894384122463512</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="D19" s="2">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2">
         <v>10</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <v>4.5</v>
+        <v>2.484215290694131</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <v>0</v>
+        <v>2.4139457023717443</v>
       </c>
       <c r="E20" s="2">
-        <v>8</v>
+        <v>2.5553459914763095</v>
       </c>
     </row>
     <row r="21">
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>4</v>
+        <v>2.6240752485890892</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="D21" s="2">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>1.5</v>
+        <v>4.5872376921363385</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6236,10 +6236,10 @@
         </is>
       </c>
       <c r="D22" s="2">
-        <v>-5</v>
+        <v>4.416666666666668</v>
       </c>
       <c r="E22" s="2">
-        <v>10</v>
+        <v>4.750000000000009</v>
       </c>
     </row>
     <row r="23">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <v>9</v>
+        <v>10.315299543741322</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="E23" s="2">
-        <v>25</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="24">
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <v>10</v>
+        <v>10.92261646516366</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="D24" s="2">
-        <v>4</v>
+        <v>8.928571428571427</v>
       </c>
       <c r="E24" s="2">
-        <v>25</v>
+        <v>11.928571428571427</v>
       </c>
     </row>
     <row r="25">
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <v>6</v>
+        <v>5.371923167958349</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>0</v>
+        <v>4.263157894736836</v>
       </c>
       <c r="E25" s="2">
-        <v>10</v>
+        <v>6.555555555555557</v>
       </c>
     </row>
     <row r="26">
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="B27" s="2">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6362,11 +6362,11 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <v>15</v>
+        <v>7.67</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限15.00億円）</t>
+          <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限7.67億円）</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -6386,7 +6386,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C225"/>
+  <dimension ref="A1:C229"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -8160,11 +8160,11 @@
         </is>
       </c>
       <c r="B118" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B119" s="2">
-        <v>0.03</v>
+        <v>0.0051345755693581975</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="B121" s="2">
-        <v>0.02</v>
+        <v>0.00013457556935819737</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="B122" s="2">
-        <v>-0.05</v>
+        <v>0.04416666666666668</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="B123" s="2">
-        <v>0.1</v>
+        <v>0.04750000000000009</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="B124" s="2">
-        <v>-0.05</v>
+        <v>0.03916666666666668</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="B125" s="2">
-        <v>0.1</v>
+        <v>0.04250000000000009</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -8280,11 +8280,11 @@
         </is>
       </c>
       <c r="B126" s="2">
-        <v>0</v>
+        <v>0.024139457023717444</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="B127" s="2">
-        <v>0.08</v>
+        <v>0.025553459914763096</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="B128" s="2">
-        <v>0</v>
+        <v>0.019139457023717443</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="B129" s="2">
-        <v>0.08</v>
+        <v>0.020553459914763095</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="B130" s="2">
-        <v>-0.1</v>
+        <v>0.06076086956521719</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="B131" s="2">
-        <v>0.2</v>
+        <v>0.06438405797101453</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B132" s="2">
-        <v>-0.1</v>
+        <v>0.040760869565217184</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="B133" s="2">
-        <v>0.2</v>
+        <v>0.04438405797101452</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
@@ -8415,11 +8415,11 @@
         </is>
       </c>
       <c r="B135" s="2">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0.04</v>
+        <v>0.08928571428571427</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0.25</v>
+        <v>0.11928571428571427</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0.02</v>
+        <v>1.6653345369377348e-16</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
@@ -8520,11 +8520,11 @@
         </is>
       </c>
       <c r="B142" s="2">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         </is>
       </c>
       <c r="B144" s="2">
-        <v>-0.03</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0.2</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0</v>
+        <v>0.04263157894736836</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0.1</v>
+        <v>0.06555555555555558</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
@@ -8640,11 +8640,11 @@
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.1</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.045</v>
+        <v>0.05</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -8700,11 +8700,11 @@
         </is>
       </c>
       <c r="B154" s="2">
-        <v>0</v>
+        <v>0.019325330501846927</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0.1</v>
+        <v>0.020735994183189166</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="B156" s="2">
-        <v>-0.05</v>
+        <v>0.15</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="B157" s="2">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B158" s="2">
-        <v>-0.05</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.4</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -8805,11 +8805,11 @@
         </is>
       </c>
       <c r="B161" s="2">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.04</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0.25</v>
+        <v>0.135</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="B168" s="2">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
@@ -8955,11 +8955,11 @@
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.015</v>
+        <v>0.04587237692136338</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0.01</v>
+        <v>0.041493777249306446</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.045</v>
+        <v>0.024842152906941306</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.04</v>
+        <v>0.019809059504605663</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.06</v>
+        <v>0.062495258171033366</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0.04</v>
+        <v>0.04260731658392249</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -9060,11 +9060,11 @@
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0.1</v>
+        <v>0.10922616465163659</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -9090,11 +9090,11 @@
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0</v>
+        <v>0.015550427257977284</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="B181" s="2">
-        <v>0.07</v>
+        <v>1.174186491064466e-16</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="B182" s="2">
-        <v>0.04</v>
+        <v>0.026240752485890893</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="B183" s="2">
-        <v>0.04</v>
+        <v>0.054448536306753274</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0.06</v>
+        <v>0.05371923167958349</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0.06</v>
+        <v>0.054060933702789804</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.07</v>
+        <v>0.08894384122463511</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.07</v>
+        <v>0.020019816287178877</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0.21</v>
+        <v>0.29613714390065743</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="B190" s="2">
-        <v>0.21</v>
+        <v>0.05407072368421051</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9255,11 +9255,11 @@
         </is>
       </c>
       <c r="B191" s="2">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="B192" s="2">
-        <v>0.09</v>
+        <v>0.10315299543741321</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="B193" s="2">
-        <v>15</v>
+        <v>7.67</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         </is>
       </c>
       <c r="B202" s="2">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="B204" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9461,26 +9461,26 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0</v>
+        <v>252.69</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>10</v>
+        <v>133.5</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
@@ -9491,11 +9491,11 @@
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -9506,26 +9506,26 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>70</v>
+        <v>3.74</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
@@ -9536,11 +9536,11 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>30</v>
+        <v>2.85</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
@@ -9551,11 +9551,11 @@
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9566,11 +9566,11 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
@@ -9581,11 +9581,11 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
@@ -9596,11 +9596,11 @@
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
@@ -9611,11 +9611,11 @@
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -9626,11 +9626,11 @@
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -9641,26 +9641,26 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -9671,41 +9671,41 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -9716,11 +9716,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>70</v>
+        <v>136.84</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -9731,26 +9731,26 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>0</v>
+        <v>76.44</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>350</v>
+        <v>95</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -9761,13 +9761,73 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B225" s="2">
+        <v>65</v>
+      </c>
+      <c r="C225" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+        </is>
+      </c>
+      <c r="B226" s="2">
+        <v>33.43</v>
+      </c>
+      <c r="C226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B227" s="2">
+        <v>18.78</v>
+      </c>
+      <c r="C227" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B228" s="2">
+        <v>350</v>
+      </c>
+      <c r="C228" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B225" s="2">
+      <c r="B229" s="2">
         <v>213</v>
       </c>
-      <c r="C225" s="0" t="inlineStr">
+      <c r="C229" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -9795,7 +9855,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjIxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjowLjA3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjA3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA2LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wMSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MC4wMDUsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMSwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MCwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDEsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDE1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4wOSwib3RoZXJTZ2FSYXRlRW5kIjowLjEsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6NDUsInN1YnNpZHkiOjE1LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuNF0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjFdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbLTAuMDMsMC4yXSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlstMC4xLDAuMl0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAyXSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6Wy0wLjA1LDAuMV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDJdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlstMC4wNSwwLjRdLCJvdGhlclNhbGVzR3Jvd3RoIjpbLTAuMSwwLjJdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLDAuMDNdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLDAuMDhdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbLTAuMDMsMC4yXSwib3RoZXJIZWFkY291bnRHcm93dGgiOlstMC4wNSwwLjFdLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDQsMC4yNV0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMCwwLjFdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjozLjUsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo3MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjozMCwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6e30sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMjEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC40LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOi0wLjAzLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjIsImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4xLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6LTAuMSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4yLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDIsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDEsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjotMC4wNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLjAyLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIxLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuNCwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOi0wLjEsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMiwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAzLCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6LTAuMDMsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMiwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjAxNSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4xLCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMDksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4yNSwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjQ1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6MTUsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NzAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjozMCwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwifQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA3MDcyMzY4NDIxMDUxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDE5ODE2Mjg3MTc4ODc3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDQ0ODUzNjMwNjc1MzI3NCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwNjA5MzM3MDI3ODk4MDQsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA3MzE2NTgzOTIyNDksIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4MDkwNTk1MDQ2MDU2NjMsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MTQ5Mzc3NzI0OTMwNjQ0Niwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjI5NjEzNzE0MzkwMDY1NzQzLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjQ5NTI1ODE3MTAzMzM2NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTU1NTA0MjcyNTc5NzcyODQsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODg5NDM4NDEyMjQ2MzUxMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQyMTUyOTA2OTQxMzA2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyNjI0MDc1MjQ4NTg5MDg5Mywib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODcyMzc2OTIxMzYzMzgsInByb2plY3RTZ2FSYXRlRW5kIjowLjEwMzE1Mjk5NTQzNzQxMzIxLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjI2MTY0NjUxNjM2NTksInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzcxOTIzMTY3OTU4MzQ5LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjcsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjAsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MTMzLjUsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjoyLCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjUsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3Ni40NCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny44OX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDcwNzIzNjg0MjEwNTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDE5ODE2Mjg3MTc4ODc3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDQ0ODUzNjMwNjc1MzI3NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDYwOTMzNzAyNzg5ODA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI2MDczMTY1ODM5MjI0OSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODA5MDU5NTA0NjA1NjYzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MTQ5Mzc3NzI0OTMwNjQ0NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yOTYxMzcxNDM5MDA2NTc0MywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNDk1MjU4MTcxMDMzMzY2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTU1NTA0MjcyNTc5NzcyODQsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDg4OTQzODQxMjI0NjM1MTEsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0MjE1MjkwNjk0MTMwNiwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAuMDI0MTM5NDU3MDIzNzE3NDQ0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyNjI0MDc1MjQ4NTg5MDg5MywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTg3MjM3NjkyMTM2MzM4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMDMxNTI5OTU0Mzc0MTMyMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyMjYxNjQ2NTE2MzY1OSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM3MTkyMzE2Nzk1ODM0OSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY3LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjoxMzMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6MiwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjUsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzYuNDQsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIn0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>372.8813559322032</v>
+        <v>373.36814621409894</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -6362,11 +6362,11 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <v>7.67</v>
+        <v>7.66</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限7.67億円）</t>
+          <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限7.66億円）</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="B193" s="2">
-        <v>7.67</v>
+        <v>7.66</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA3MDcyMzY4NDIxMDUxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDE5ODE2Mjg3MTc4ODc3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDQ0ODUzNjMwNjc1MzI3NCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwNjA5MzM3MDI3ODk4MDQsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA3MzE2NTgzOTIyNDksIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4MDkwNTk1MDQ2MDU2NjMsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MTQ5Mzc3NzI0OTMwNjQ0Niwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjI5NjEzNzE0MzkwMDY1NzQzLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjQ5NTI1ODE3MTAzMzM2NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTU1NTA0MjcyNTc5NzcyODQsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODg5NDM4NDEyMjQ2MzUxMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQyMTUyOTA2OTQxMzA2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyNjI0MDc1MjQ4NTg5MDg5Mywib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODcyMzc2OTIxMzYzMzgsInByb2plY3RTZ2FSYXRlRW5kIjowLjEwMzE1Mjk5NTQzNzQxMzIxLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjI2MTY0NjUxNjM2NTksInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzcxOTIzMTY3OTU4MzQ5LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjcsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjAsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MTMzLjUsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjoyLCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjUsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3Ni40NCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny44OX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDcwNzIzNjg0MjEwNTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDE5ODE2Mjg3MTc4ODc3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDQ0ODUzNjMwNjc1MzI3NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDYwOTMzNzAyNzg5ODA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI2MDczMTY1ODM5MjI0OSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODA5MDU5NTA0NjA1NjYzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MTQ5Mzc3NzI0OTMwNjQ0NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yOTYxMzcxNDM5MDA2NTc0MywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNDk1MjU4MTcxMDMzMzY2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTU1NTA0MjcyNTc5NzcyODQsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDg4OTQzODQxMjI0NjM1MTEsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0MjE1MjkwNjk0MTMwNiwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAuMDI0MTM5NDU3MDIzNzE3NDQ0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyNjI0MDc1MjQ4NTg5MDg5MywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTg3MjM3NjkyMTM2MzM4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMDMxNTI5OTU0Mzc0MTMyMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyMjYxNjQ2NTE2MzY1OSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM3MTkyMzE2Nzk1ODM0OSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY3LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjoxMzMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6MiwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjUsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzYuNDQsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIn0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA3MDcyMzY4NDIxMDUxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDE5ODE2Mjg3MTc4ODc3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDQ0ODUzNjMwNjc1MzI3NCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwNjA5MzM3MDI3ODk4MDQsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA3MzE2NTgzOTIyNDksIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4MDkwNTk1MDQ2MDU2NjMsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MTQ5Mzc3NzI0OTMwNjQ0Niwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjI5NjEzNzE0MzkwMDY1NzQzLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjQ5NTI1ODE3MTAzMzM2NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTU1NTA0MjcyNTc5NzcyODQsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODg5NDM4NDEyMjQ2MzUxMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQyMTUyOTA2OTQxMzA2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyNjI0MDc1MjQ4NTg5MDg5Mywib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODcyMzc2OTIxMzYzMzgsInByb2plY3RTZ2FSYXRlRW5kIjowLjEwMzE1Mjk5NTQzNzQxMzIxLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjI2MTY0NjUxNjM2NTksInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzcxOTIzMTY3OTU4MzQ5LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjAsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MTMzLjUsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjoyLCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjUsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3Ni40NCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny44OX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDcwNzIzNjg0MjEwNTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDE5ODE2Mjg3MTc4ODc3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDQ0ODUzNjMwNjc1MzI3NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDYwOTMzNzAyNzg5ODA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI2MDczMTY1ODM5MjI0OSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODA5MDU5NTA0NjA1NjYzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MTQ5Mzc3NzI0OTMwNjQ0NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yOTYxMzcxNDM5MDA2NTc0MywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNDk1MjU4MTcxMDMzMzY2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTU1NTA0MjcyNTc5NzcyODQsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDg4OTQzODQxMjI0NjM1MTEsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0MjE1MjkwNjk0MTMwNiwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAuMDI0MTM5NDU3MDIzNzE3NDQ0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyNjI0MDc1MjQ4NTg5MDg5MywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTg3MjM3NjkyMTM2MzM4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMDMxNTI5OTU0Mzc0MTMyMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyMjYxNjQ2NTE2MzY1OSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM3MTkyMzE2Nzk1ODM0OSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjoxMzMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6MiwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjUsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzYuNDQsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIn0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -5850,7 +5850,7 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <v>5.407072368421051</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <v>1.174186491064466e-14</v>
+        <v>5.551115123125783e-15</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <v>2.0019816287178878</v>
+        <v>2.0030662342518046</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <v>5.444853630675327</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>5.40609337027898</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>4.260731658392249</v>
+        <v>4.257246376811585</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>1.9809059504605664</v>
+        <v>1.984645846924027</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>4.149377724930645</v>
+        <v>4.083333333333339</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>29.61371439006574</v>
+        <v>22</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>6.249525817103336</v>
+        <v>6.257246376811586</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>1.5550427257977284</v>
+        <v>1.5</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>8.894384122463512</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <v>2.484215290694131</v>
+        <v>2.484645846924027</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>2.6240752485890892</v>
+        <v>4</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>4.5872376921363385</v>
+        <v>4.583333333333338</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <v>10.315299543741322</v>
+        <v>11</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <v>10.92261646516366</v>
+        <v>10.928571428571427</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <v>5.371923167958349</v>
+        <v>5.380116959064325</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.04587237692136338</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0.041493777249306446</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.024842152906941306</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.019809059504605663</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.062495258171033366</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0.04260731658392249</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0.10922616465163659</v>
+        <v>0.10928571428571428</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0.015550427257977284</v>
+        <v>0.015</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="B181" s="2">
-        <v>1.174186491064466e-16</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="B182" s="2">
-        <v>0.026240752485890893</v>
+        <v>0.04</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="B183" s="2">
-        <v>0.054448536306753274</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0.05371923167958349</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0.054060933702789804</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.08894384122463511</v>
+        <v>0.07</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.020019816287178877</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0.29613714390065743</v>
+        <v>0.22</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="B190" s="2">
-        <v>0.05407072368421051</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="B192" s="2">
-        <v>0.10315299543741321</v>
+        <v>0.11</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA3MDcyMzY4NDIxMDUxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDE5ODE2Mjg3MTc4ODc3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDQ0ODUzNjMwNjc1MzI3NCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwNjA5MzM3MDI3ODk4MDQsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA3MzE2NTgzOTIyNDksIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4MDkwNTk1MDQ2MDU2NjMsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MTQ5Mzc3NzI0OTMwNjQ0Niwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjI5NjEzNzE0MzkwMDY1NzQzLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjQ5NTI1ODE3MTAzMzM2NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTU1NTA0MjcyNTc5NzcyODQsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODg5NDM4NDEyMjQ2MzUxMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQyMTUyOTA2OTQxMzA2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyNjI0MDc1MjQ4NTg5MDg5Mywib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODcyMzc2OTIxMzYzMzgsInByb2plY3RTZ2FSYXRlRW5kIjowLjEwMzE1Mjk5NTQzNzQxMzIxLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjI2MTY0NjUxNjM2NTksInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzcxOTIzMTY3OTU4MzQ5LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjAsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6MTMzLjUsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjoyLCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjUsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3Ni40NCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny44OX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDcwNzIzNjg0MjEwNTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDE5ODE2Mjg3MTc4ODc3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDQ0ODUzNjMwNjc1MzI3NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDYwOTMzNzAyNzg5ODA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI2MDczMTY1ODM5MjI0OSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODA5MDU5NTA0NjA1NjYzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MTQ5Mzc3NzI0OTMwNjQ0NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yOTYxMzcxNDM5MDA2NTc0MywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNDk1MjU4MTcxMDMzMzY2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTU1NTA0MjcyNTc5NzcyODQsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDg4OTQzODQxMjI0NjM1MTEsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0MjE1MjkwNjk0MTMwNiwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAuMDI0MTM5NDU3MDIzNzE3NDQ0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyNjI0MDc1MjQ4NTg5MDg5MywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTg3MjM3NjkyMTM2MzM4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMDMxNTI5OTU0Mzc0MTMyMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyMjYxNjQ2NTE2MzY1OSwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM3MTkyMzE2Nzk1ODM0OSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoyMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjoxMzMuNSwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6MiwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjUsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzYuNDQsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIn0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjIwLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjEzMy41LCJtYXgiOjI1Mi42OSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6MiwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjY1LCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzYuNDQsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuODl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wODQ5OTk5OTk5OTk5OTk5OSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMTM1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDg5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4xMTkyODU3MTQyODU3MTQyNywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjEzMy41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjoyLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2NSwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3Ni40NCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA3MDcyMzY4NDIxMDUxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDE5ODE2Mjg3MTc4ODc3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDQ0ODUzNjMwNjc1MzI3NCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwNjA5MzM3MDI3ODk4MDQsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA3MzE2NTgzOTIyNDksIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4MDkwNTk1MDQ2MDU2NjMsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MTQ5Mzc3NzI0OTMwNjQ0Niwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjI5NjEzNzE0MzkwMDY1NzQzLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjQ5NTI1ODE3MTAzMzM2NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTU1NTA0MjcyNTc5NzcyODQsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODg5NDM4NDEyMjQ2MzUxMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQyMTUyOTA2OTQxMzA2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyNjI0MDc1MjQ4NTg5MDg5Mywib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODcyMzc2OTIxMzYzMzgsInByb2plY3RTZ2FSYXRlRW5kIjowLjEwMzE1Mjk5NTQzNzQxMzIxLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjI2MTY0NjUxNjM2NTksInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzcxOTIzMTY3OTU4MzQ5LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM319</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>20.152518023637867</v>
+        <v>20.01053154331047</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -234,7 +234,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>127.10000000000002</v>
+        <v>126.03000000000003</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -294,7 +294,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>67.97614287618285</v>
+        <v>67.86048689138576</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -324,7 +324,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>29.614246350044503</v>
+        <v>29.38972537778437</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -354,7 +354,7 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>110.32</v>
+        <v>109.25</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>32.737848619973995</v>
+        <v>32.53247290200707</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>28.59999999999998</v>
+        <v>28.37999999999999</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>373.36814621409894</v>
+        <v>370.4960835509137</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1259,22 +1259,22 @@
         <v>150</v>
       </c>
       <c r="E3" s="4">
-        <v>157.31</v>
+        <v>157.3</v>
       </c>
       <c r="F3" s="4">
-        <v>164.98000000000002</v>
+        <v>164.97</v>
       </c>
       <c r="G3" s="4">
-        <v>173.01999999999998</v>
+        <v>173.01</v>
       </c>
       <c r="H3" s="4">
-        <v>206.57</v>
+        <v>206.33999999999997</v>
       </c>
       <c r="I3" s="4">
-        <v>247.85000000000002</v>
+        <v>247.28000000000003</v>
       </c>
       <c r="J3" s="4">
-        <v>300.12</v>
+        <v>299.04</v>
       </c>
     </row>
     <row r="4">
@@ -1295,22 +1295,22 @@
         <v>4.748603351955305</v>
       </c>
       <c r="E4" s="2">
-        <v>4.8733333333333295</v>
+        <v>4.866666666666664</v>
       </c>
       <c r="F4" s="2">
-        <v>4.875723094526752</v>
+        <v>4.876033057851226</v>
       </c>
       <c r="G4" s="2">
-        <v>4.873317977936686</v>
+        <v>4.873613384251674</v>
       </c>
       <c r="H4" s="2">
-        <v>19.39082187030401</v>
+        <v>19.26478238252123</v>
       </c>
       <c r="I4" s="2">
-        <v>19.983540688386526</v>
+        <v>19.841039061742794</v>
       </c>
       <c r="J4" s="2">
-        <v>21.089368569699406</v>
+        <v>20.931737301844056</v>
       </c>
     </row>
     <row r="5">
@@ -1335,16 +1335,16 @@
         <v>112.18</v>
       </c>
       <c r="G5" s="2">
-        <v>117.66</v>
+        <v>117.65</v>
       </c>
       <c r="H5" s="2">
-        <v>139.13</v>
+        <v>138.97</v>
       </c>
       <c r="I5" s="2">
-        <v>166</v>
+        <v>165.63</v>
       </c>
       <c r="J5" s="2">
-        <v>199.78000000000003</v>
+        <v>199.07</v>
       </c>
     </row>
     <row r="6">
@@ -1397,22 +1397,22 @@
         <v>48</v>
       </c>
       <c r="E7" s="4">
-        <v>50.34</v>
+        <v>50.33000000000001</v>
       </c>
       <c r="F7" s="4">
-        <v>52.80000000000001</v>
+        <v>52.78999999999999</v>
       </c>
       <c r="G7" s="4">
         <v>55.359999999999985</v>
       </c>
       <c r="H7" s="4">
-        <v>67.44</v>
+        <v>67.36999999999998</v>
       </c>
       <c r="I7" s="4">
-        <v>81.85000000000002</v>
+        <v>81.65000000000003</v>
       </c>
       <c r="J7" s="4">
-        <v>100.33999999999997</v>
+        <v>99.97000000000003</v>
       </c>
     </row>
     <row r="8">
@@ -1431,22 +1431,22 @@
         <v>32</v>
       </c>
       <c r="E8" s="2">
-        <v>32.00050854999682</v>
+        <v>31.996185632549274</v>
       </c>
       <c r="F8" s="2">
-        <v>32.00387925809189</v>
+        <v>31.99975753167242</v>
       </c>
       <c r="G8" s="2">
-        <v>31.99630100566408</v>
+        <v>31.998150395930864</v>
       </c>
       <c r="H8" s="2">
-        <v>32.64752868277097</v>
+        <v>32.64999515362992</v>
       </c>
       <c r="I8" s="2">
-        <v>33.02400645551746</v>
+        <v>33.019249433840194</v>
       </c>
       <c r="J8" s="2">
-        <v>33.433293349326924</v>
+        <v>33.43031032637775</v>
       </c>
     </row>
     <row r="9">
@@ -1474,13 +1474,13 @@
         <v>44.19</v>
       </c>
       <c r="H9" s="2">
-        <v>48.489999999999995</v>
+        <v>48.459999999999994</v>
       </c>
       <c r="I9" s="2">
-        <v>53.92999999999999</v>
+        <v>53.86</v>
       </c>
       <c r="J9" s="2">
-        <v>60.18</v>
+        <v>60.05</v>
       </c>
     </row>
     <row r="10">
@@ -1771,22 +1771,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>11.469999999999999</v>
+        <v>11.460000000000008</v>
       </c>
       <c r="F18" s="4">
-        <v>11.350000000000009</v>
+        <v>11.33999999999999</v>
       </c>
       <c r="G18" s="4">
         <v>11.169999999999984</v>
       </c>
       <c r="H18" s="4">
-        <v>18.950000000000003</v>
+        <v>18.909999999999982</v>
       </c>
       <c r="I18" s="4">
-        <v>27.920000000000027</v>
+        <v>27.790000000000035</v>
       </c>
       <c r="J18" s="4">
-        <v>40.159999999999975</v>
+        <v>39.92000000000003</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.291335579429152</v>
+        <v>7.285441830896381</v>
       </c>
       <c r="F19" s="2">
-        <v>6.879621772336045</v>
+        <v>6.8739770867430385</v>
       </c>
       <c r="G19" s="2">
-        <v>6.455901051901505</v>
+        <v>6.456274203803239</v>
       </c>
       <c r="H19" s="2">
-        <v>9.173645737522392</v>
+        <v>9.16448580013569</v>
       </c>
       <c r="I19" s="2">
-        <v>11.26487795037322</v>
+        <v>11.238272403752843</v>
       </c>
       <c r="J19" s="2">
-        <v>13.381314141010254</v>
+        <v>13.349384697699312</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E20" s="4">
-        <v>11.469999999999999</v>
+        <v>11.460000000000008</v>
       </c>
       <c r="F20" s="4">
-        <v>11.350000000000009</v>
+        <v>11.33999999999999</v>
       </c>
       <c r="G20" s="4">
         <v>11.169999999999984</v>
       </c>
       <c r="H20" s="4">
-        <v>18.950000000000003</v>
+        <v>18.909999999999982</v>
       </c>
       <c r="I20" s="4">
-        <v>27.920000000000027</v>
+        <v>27.790000000000035</v>
       </c>
       <c r="J20" s="4">
-        <v>40.159999999999975</v>
+        <v>39.92000000000003</v>
       </c>
     </row>
     <row r="21">
@@ -2079,22 +2079,22 @@
         <v>30.1</v>
       </c>
       <c r="E26" s="4">
-        <v>31.72</v>
+        <v>31.710000000000008</v>
       </c>
       <c r="F26" s="4">
-        <v>33.400000000000006</v>
+        <v>33.389999999999986</v>
       </c>
       <c r="G26" s="4">
         <v>35.13999999999998</v>
       </c>
       <c r="H26" s="4">
-        <v>44.059999999999995</v>
+        <v>44.019999999999975</v>
       </c>
       <c r="I26" s="4">
-        <v>54.74000000000002</v>
+        <v>54.61000000000003</v>
       </c>
       <c r="J26" s="4">
-        <v>68.84999999999998</v>
+        <v>68.61000000000003</v>
       </c>
     </row>
     <row r="27">
@@ -2115,22 +2115,22 @@
         <v>4.768534632788035</v>
       </c>
       <c r="E27" s="2">
-        <v>5.3820598006644405</v>
+        <v>5.348837209302348</v>
       </c>
       <c r="F27" s="2">
-        <v>5.29634300126105</v>
+        <v>5.298013245033051</v>
       </c>
       <c r="G27" s="2">
-        <v>5.20958083832328</v>
+        <v>5.2410901467505155</v>
       </c>
       <c r="H27" s="2">
-        <v>25.384177575412693</v>
+        <v>25.270347182697783</v>
       </c>
       <c r="I27" s="2">
-        <v>24.23967317294604</v>
+        <v>24.057246706042832</v>
       </c>
       <c r="J27" s="2">
-        <v>25.776397515527872</v>
+        <v>25.636330342428117</v>
       </c>
     </row>
     <row r="28">
@@ -2149,22 +2149,22 @@
         <v>20.06666666666667</v>
       </c>
       <c r="E28" s="2">
-        <v>20.164007373974954</v>
+        <v>20.1589319771138</v>
       </c>
       <c r="F28" s="2">
-        <v>20.244878167050555</v>
+        <v>20.240043644298954</v>
       </c>
       <c r="G28" s="2">
-        <v>20.309790775632866</v>
+        <v>20.310964684122293</v>
       </c>
       <c r="H28" s="2">
-        <v>21.32933146149005</v>
+        <v>21.33372104293883</v>
       </c>
       <c r="I28" s="2">
-        <v>22.085939076054075</v>
+        <v>22.08427693303139</v>
       </c>
       <c r="J28" s="2">
-        <v>22.940823670531778</v>
+        <v>22.94341894060996</v>
       </c>
     </row>
     <row r="29">
@@ -2391,22 +2391,22 @@
         <v>0.12808510638297874</v>
       </c>
       <c r="E35" s="2">
-        <v>0.12946938775510203</v>
+        <v>0.12942857142857145</v>
       </c>
       <c r="F35" s="2">
-        <v>0.12996108949416343</v>
+        <v>0.1299221789883268</v>
       </c>
       <c r="G35" s="2">
         <v>0.13063197026022297</v>
       </c>
       <c r="H35" s="2">
-        <v>0.157921146953405</v>
+        <v>0.15777777777777768</v>
       </c>
       <c r="I35" s="2">
-        <v>0.18941176470588245</v>
+        <v>0.18896193771626307</v>
       </c>
       <c r="J35" s="2">
-        <v>0.23026755852842803</v>
+        <v>0.2294648829431439</v>
       </c>
     </row>
     <row r="36">
@@ -2425,22 +2425,22 @@
         <v>15.100000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>15.739999999999998</v>
+        <v>15.730000000000008</v>
       </c>
       <c r="F36" s="4">
-        <v>16.38000000000001</v>
+        <v>16.36999999999999</v>
       </c>
       <c r="G36" s="4">
         <v>16.969999999999985</v>
       </c>
       <c r="H36" s="4">
-        <v>24.750000000000004</v>
+        <v>24.709999999999983</v>
       </c>
       <c r="I36" s="4">
-        <v>33.72000000000003</v>
+        <v>33.59000000000003</v>
       </c>
       <c r="J36" s="4">
-        <v>45.95999999999997</v>
+        <v>45.72000000000003</v>
       </c>
     </row>
     <row r="37">
@@ -2459,22 +2459,22 @@
         <v>10.066666666666668</v>
       </c>
       <c r="E37" s="2">
-        <v>10.005721187464243</v>
+        <v>10.000000000000005</v>
       </c>
       <c r="F37" s="2">
-        <v>9.928476178930785</v>
+        <v>9.923016305995024</v>
       </c>
       <c r="G37" s="2">
-        <v>9.808114668824405</v>
+        <v>9.808681579099465</v>
       </c>
       <c r="H37" s="2">
-        <v>11.981410659824759</v>
+        <v>11.975380440050396</v>
       </c>
       <c r="I37" s="2">
-        <v>13.605003026023816</v>
+        <v>13.583791653186683</v>
       </c>
       <c r="J37" s="2">
-        <v>15.313874450219902</v>
+        <v>15.288924558587489</v>
       </c>
     </row>
     <row r="38">
@@ -2495,22 +2495,22 @@
         <v>3.1420765027322606</v>
       </c>
       <c r="E38" s="2">
-        <v>4.238410596026476</v>
+        <v>4.172185430463626</v>
       </c>
       <c r="F38" s="2">
-        <v>4.066073697585848</v>
+        <v>4.068658614113052</v>
       </c>
       <c r="G38" s="2">
-        <v>3.601953601953456</v>
+        <v>3.665241295051902</v>
       </c>
       <c r="H38" s="2">
-        <v>45.84560989982338</v>
+        <v>45.60989982321748</v>
       </c>
       <c r="I38" s="2">
-        <v>36.24242424242434</v>
+        <v>35.93686766491322</v>
       </c>
       <c r="J38" s="2">
-        <v>36.298932384341455</v>
+        <v>36.11193807680853</v>
       </c>
     </row>
   </sheetData>
@@ -2663,22 +2663,22 @@
         <v>80</v>
       </c>
       <c r="E3" s="4">
-        <v>84.33</v>
+        <v>84.32</v>
       </c>
       <c r="F3" s="4">
-        <v>88.89</v>
+        <v>88.88</v>
       </c>
       <c r="G3" s="4">
-        <v>93.69</v>
+        <v>93.68</v>
       </c>
       <c r="H3" s="4">
-        <v>121.44</v>
+        <v>121.21</v>
       </c>
       <c r="I3" s="4">
-        <v>157.4</v>
+        <v>156.83</v>
       </c>
       <c r="J3" s="4">
-        <v>204.01</v>
+        <v>202.93</v>
       </c>
     </row>
     <row r="4">
@@ -2699,22 +2699,22 @@
         <v>5.263157894736836</v>
       </c>
       <c r="E4" s="2">
-        <v>5.412499999999998</v>
+        <v>5.399999999999983</v>
       </c>
       <c r="F4" s="2">
-        <v>5.407328352899321</v>
+        <v>5.407969639468702</v>
       </c>
       <c r="G4" s="2">
-        <v>5.39993250084374</v>
+        <v>5.400540054005409</v>
       </c>
       <c r="H4" s="2">
-        <v>29.618956131924424</v>
+        <v>29.387275832621683</v>
       </c>
       <c r="I4" s="2">
-        <v>29.61133069828723</v>
+        <v>29.387014272749788</v>
       </c>
       <c r="J4" s="2">
-        <v>29.61245235069885</v>
+        <v>29.3948861824906</v>
       </c>
     </row>
     <row r="5">
@@ -2733,22 +2733,22 @@
         <v>53.333333333333336</v>
       </c>
       <c r="E5" s="2">
-        <v>53.60752653995296</v>
+        <v>53.60457724094086</v>
       </c>
       <c r="F5" s="2">
-        <v>53.87925809188992</v>
+        <v>53.87646238710069</v>
       </c>
       <c r="G5" s="2">
-        <v>54.14980927060456</v>
+        <v>54.14715912375008</v>
       </c>
       <c r="H5" s="2">
-        <v>58.788788304206804</v>
+        <v>58.74285160414849</v>
       </c>
       <c r="I5" s="2">
-        <v>63.50615291506959</v>
+        <v>63.42203170494985</v>
       </c>
       <c r="J5" s="2">
-        <v>67.97614287618285</v>
+        <v>67.86048689138576</v>
       </c>
     </row>
     <row r="6">
@@ -2767,22 +2767,22 @@
         <v>25.6</v>
       </c>
       <c r="E6" s="4">
-        <v>26.989999999999995</v>
+        <v>26.97999999999999</v>
       </c>
       <c r="F6" s="4">
-        <v>28.450000000000003</v>
+        <v>28.439999999999998</v>
       </c>
       <c r="G6" s="4">
-        <v>29.979999999999997</v>
+        <v>29.980000000000004</v>
       </c>
       <c r="H6" s="4">
-        <v>39.489999999999995</v>
+        <v>39.41999999999999</v>
       </c>
       <c r="I6" s="4">
-        <v>52</v>
+        <v>51.81000000000002</v>
       </c>
       <c r="J6" s="4">
-        <v>68.45999999999998</v>
+        <v>68.1</v>
       </c>
     </row>
     <row r="7">
@@ -2801,22 +2801,22 @@
         <v>32</v>
       </c>
       <c r="E7" s="2">
-        <v>32.005217597533495</v>
+        <v>31.997153700189745</v>
       </c>
       <c r="F7" s="2">
-        <v>32.00584992687592</v>
+        <v>31.998199819982</v>
       </c>
       <c r="G7" s="2">
-        <v>31.999146120183582</v>
+        <v>32.00256191289496</v>
       </c>
       <c r="H7" s="2">
-        <v>32.51811594202898</v>
+        <v>32.52206913620987</v>
       </c>
       <c r="I7" s="2">
-        <v>33.03684879288437</v>
+        <v>33.0357712172416</v>
       </c>
       <c r="J7" s="2">
-        <v>33.557178569677944</v>
+        <v>33.55836988123983</v>
       </c>
     </row>
     <row r="8">
@@ -2835,22 +2835,22 @@
         <v>7.300000000000004</v>
       </c>
       <c r="E8" s="4">
-        <v>7.079999999999991</v>
+        <v>7.069999999999986</v>
       </c>
       <c r="F8" s="4">
-        <v>6.870000000000001</v>
+        <v>6.859999999999996</v>
       </c>
       <c r="G8" s="4">
-        <v>6.629999999999999</v>
+        <v>6.630000000000006</v>
       </c>
       <c r="H8" s="4">
-        <v>12.969999999999995</v>
+        <v>12.929999999999987</v>
       </c>
       <c r="I8" s="4">
-        <v>21.26</v>
+        <v>21.150000000000016</v>
       </c>
       <c r="J8" s="4">
-        <v>32.759999999999984</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="9">
@@ -2869,22 +2869,22 @@
         <v>9.125000000000005</v>
       </c>
       <c r="E9" s="2">
-        <v>8.395588758448941</v>
+        <v>8.384724857684994</v>
       </c>
       <c r="F9" s="2">
-        <v>7.728653391832603</v>
+        <v>7.718271827182714</v>
       </c>
       <c r="G9" s="2">
-        <v>7.076528978546269</v>
+        <v>7.077284372331347</v>
       </c>
       <c r="H9" s="2">
-        <v>10.68017127799736</v>
+        <v>10.667436680141892</v>
       </c>
       <c r="I9" s="2">
-        <v>13.506988564167727</v>
+        <v>13.485940190014675</v>
       </c>
       <c r="J9" s="2">
-        <v>16.058036370766132</v>
+        <v>16.03508599024294</v>
       </c>
     </row>
     <row r="10">
@@ -3005,22 +3005,22 @@
         <v>15.700000000000005</v>
       </c>
       <c r="E13" s="4">
-        <v>16.71999999999999</v>
+        <v>16.709999999999987</v>
       </c>
       <c r="F13" s="4">
-        <v>17.78</v>
+        <v>17.769999999999996</v>
       </c>
       <c r="G13" s="4">
-        <v>18.869999999999997</v>
+        <v>18.870000000000005</v>
       </c>
       <c r="H13" s="4">
-        <v>25.659999999999997</v>
+        <v>25.619999999999987</v>
       </c>
       <c r="I13" s="4">
-        <v>34.9</v>
+        <v>34.79000000000001</v>
       </c>
       <c r="J13" s="4">
-        <v>47.46999999999998</v>
+        <v>47.24999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -3041,22 +3041,22 @@
         <v>5.2984574111334615</v>
       </c>
       <c r="E14" s="2">
-        <v>6.496815286624114</v>
+        <v>6.433121019108157</v>
       </c>
       <c r="F14" s="2">
-        <v>6.339712918660356</v>
+        <v>6.3435068821065865</v>
       </c>
       <c r="G14" s="2">
-        <v>6.13048368953879</v>
+        <v>6.190208216094595</v>
       </c>
       <c r="H14" s="2">
-        <v>35.9830418653948</v>
+        <v>35.77106518282977</v>
       </c>
       <c r="I14" s="2">
-        <v>36.00935307872175</v>
+        <v>35.792349726776074</v>
       </c>
       <c r="J14" s="2">
-        <v>36.01719197707731</v>
+        <v>35.81488933601602</v>
       </c>
     </row>
     <row r="15">
@@ -3283,22 +3283,22 @@
         <v>0.15392156862745102</v>
       </c>
       <c r="E21" s="2">
-        <v>0.15626168224299058</v>
+        <v>0.1561682242990653</v>
       </c>
       <c r="F21" s="2">
-        <v>0.15734513274336284</v>
+        <v>0.15725663716814156</v>
       </c>
       <c r="G21" s="2">
-        <v>0.15857142857142856</v>
+        <v>0.1585714285714286</v>
       </c>
       <c r="H21" s="2">
-        <v>0.210327868852459</v>
+        <v>0.20999999999999988</v>
       </c>
       <c r="I21" s="2">
-        <v>0.2792</v>
+        <v>0.2783200000000001</v>
       </c>
       <c r="J21" s="2">
-        <v>0.3708593749999998</v>
+        <v>0.36914062499999994</v>
       </c>
     </row>
     <row r="22">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.87 % / 補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 4.87 % / 補助 5.4 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -3626,17 +3626,17 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 19.39 % / 補助 29.62 % / 他 7.31 %</t>
+          <t xml:space="preserve">全社 19.26 % / 補助 29.39 % / 他 7.31 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 19.98 % / 補助 29.61 % / 他 6.25 %</t>
+          <t xml:space="preserve">全社 19.84 % / 補助 29.39 % / 他 6.25 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.09 % / 補助 29.61 % / 他 6.26 %</t>
+          <t xml:space="preserve">全社 20.93 % / 補助 29.39 % / 他 6.26 %</t>
         </is>
       </c>
     </row>
@@ -3673,12 +3673,12 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 67.99 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68 %</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 67.99 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68 %</t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.98 % / 補助 66.96 % / 他 67 %</t>
+          <t xml:space="preserve">全社 66.98 % / 補助 66.96 % / 他 67.01 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.57 % / 補助 66.44 % / 他 66.83 %</t>
+          <t xml:space="preserve">全社 66.57 % / 補助 66.44 % / 他 66.84 %</t>
         </is>
       </c>
     </row>
@@ -3735,12 +3735,12 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32.01 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 32 %</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32.01 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 32 %</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.02 % / 補助 33.04 % / 他 33 %</t>
+          <t xml:space="preserve">全社 33.02 % / 補助 33.04 % / 他 32.99 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.43 % / 補助 33.56 % / 他 33.17 %</t>
+          <t xml:space="preserve">全社 33.43 % / 補助 33.56 % / 他 33.16 %</t>
         </is>
       </c>
     </row>
@@ -3802,27 +3802,27 @@
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.12 % / 補助 24.28 % / 他 26.11 %</t>
+          <t xml:space="preserve">全社 25.13 % / 補助 24.28 % / 他 26.11 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.54 % / 補助 24.92 % / 他 26.27 %</t>
+          <t xml:space="preserve">全社 25.54 % / 補助 24.93 % / 他 26.27 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.47 % / 補助 21.84 % / 他 25.81 %</t>
+          <t xml:space="preserve">全社 23.49 % / 補助 21.85 % / 他 25.81 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.76 % / 補助 19.53 % / 他 25.64 %</t>
+          <t xml:space="preserve">全社 21.78 % / 補助 19.55 % / 他 25.65 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20.05 % / 補助 17.5 % / 他 25.47 %</t>
+          <t xml:space="preserve">全社 20.08 % / 補助 17.52 % / 他 25.48 %</t>
         </is>
       </c>
     </row>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.29 % / 補助 8.4 % / 他 6.02 %</t>
+          <t xml:space="preserve">全社 7.29 % / 補助 8.38 % / 他 6.02 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.88 % / 補助 7.73 % / 他 5.89 %</t>
+          <t xml:space="preserve">全社 6.87 % / 補助 7.72 % / 他 5.89 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
@@ -3874,17 +3874,17 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.17 % / 補助 10.68 % / 他 7.02 %</t>
+          <t xml:space="preserve">全社 9.16 % / 補助 10.67 % / 他 7.02 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.26 % / 補助 13.51 % / 他 7.36 %</t>
+          <t xml:space="preserve">全社 11.24 % / 補助 13.49 % / 他 7.34 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.38 % / 補助 16.06 % / 他 7.7 %</t>
+          <t xml:space="preserve">全社 13.35 % / 補助 16.04 % / 他 7.68 %</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.01 % / 補助 11.68 % / 他 8.07 %</t>
+          <t xml:space="preserve">全社 10 % / 補助 11.67 % / 他 8.07 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.93 % / 補助 11.7 % / 他 7.86 %</t>
+          <t xml:space="preserve">全社 9.92 % / 補助 11.69 % / 他 7.86 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
@@ -3936,17 +3936,17 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.98 % / 補助 14.22 % / 他 8.79 %</t>
+          <t xml:space="preserve">全社 11.98 % / 補助 14.21 % / 他 8.79 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.61 % / 補助 16.24 % / 他 9.02 %</t>
+          <t xml:space="preserve">全社 13.58 % / 補助 16.23 % / 他 9 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.31 % / 補助 18.17 % / 他 9.26 %</t>
+          <t xml:space="preserve">全社 15.29 % / 補助 18.15 % / 他 9.24 %</t>
         </is>
       </c>
     </row>
@@ -3998,17 +3998,17 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.51 % / 補助 11.77 % / 他 11.15 %</t>
+          <t xml:space="preserve">全社 11.51 % / 補助 11.76 % / 他 11.15 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.02 % / 補助 11.04 % / 他 10.98 %</t>
+          <t xml:space="preserve">全社 11.02 % / 補助 11.03 % / 他 10.99 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.47 % / 補助 10.31 % / 他 10.81 %</t>
+          <t xml:space="preserve">全社 10.47 % / 補助 10.3 % / 他 10.82 %</t>
         </is>
       </c>
     </row>
@@ -4122,17 +4122,17 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.79 % / 補助 6.5 % / 他 12.06 %</t>
+          <t xml:space="preserve">全社 8.8 % / 補助 6.51 % / 他 12.06 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8 % / 補助 5.6 % / 他 12.17 %</t>
+          <t xml:space="preserve">全社 8.02 % / 補助 5.62 % / 他 12.17 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.22 % / 補助 4.83 % / 他 12.28 %</t>
+          <t xml:space="preserve">全社 7.24 % / 補助 4.86 % / 他 12.28 %</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.64 % / 補助 0.49 % / 他 0.81 %</t>
+          <t xml:space="preserve">全社 0.64 % / 補助 0.5 % / 他 0.81 %</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
@@ -4241,22 +4241,22 @@
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.5 % / 補助 8.47 % / 他 12.9 %</t>
+          <t xml:space="preserve">全社 10.5 % / 補助 8.48 % / 他 12.9 %</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.35 % / 補助 6.91 % / 他 12.83 %</t>
+          <t xml:space="preserve">全社 9.36 % / 補助 6.92 % / 他 12.83 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.48 % / 補助 5.93 % / 他 12.91 %</t>
+          <t xml:space="preserve">全社 8.5 % / 補助 5.96 % / 他 12.91 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.63 % / 補助 5.1 % / 他 12.99 %</t>
+          <t xml:space="preserve">全社 7.65 % / 補助 5.13 % / 他 12.99 %</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.38 % / 補助 41.09 % / 他 60.73 %</t>
+          <t xml:space="preserve">全社 50.39 % / 補助 41.11 % / 他 60.73 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.96 % / 補助 41.51 % / 他 61.72 %</t>
+          <t xml:space="preserve">全社 50.97 % / 補助 41.53 % / 他 61.72 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
@@ -4494,17 +4494,17 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 43.83 % / 補助 32.7 % / 他 59.35 %</t>
+          <t xml:space="preserve">全社 43.87 % / 補助 32.75 % / 他 59.35 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.4 % / 補助 26.76 % / 他 58.87 %</t>
+          <t xml:space="preserve">全社 38.49 % / 補助 26.85 % / 他 58.93 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.25 % / 補助 21.93 % / 他 58.37 %</t>
+          <t xml:space="preserve">全社 33.36 % / 補助 22.03 % / 他 58.43 %</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.754 億円/人 / 補助 1.012 億円/人 / 他 0.553 億円/人</t>
+          <t xml:space="preserve">全社 0.753 億円/人 / 補助 1.01 億円/人 / 他 0.553 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.873 億円/人 / 補助 1.28 億円/人 / 他 0.562 億円/人</t>
+          <t xml:space="preserve">全社 0.871 億円/人 / 補助 1.275 億円/人 / 他 0.562 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.021 億円/人 / 補助 1.619 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">全社 1.017 億円/人 / 補助 1.611 億円/人 / 他 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -4685,12 +4685,12 @@
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.098 億円/人 / 補助 0.173 億円/人 / 他 0.041 億円/人</t>
+          <t xml:space="preserve">全社 0.098 億円/人 / 補助 0.172 億円/人 / 他 0.041 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.137 億円/人 / 補助 0.26 億円/人 / 他 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.136 億円/人 / 補助 0.258 億円/人 / 他 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -4747,12 +4747,12 @@
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.189 億円/人 / 補助 0.279 億円/人 / 他 0.121 億円/人</t>
+          <t xml:space="preserve">全社 0.189 億円/人 / 補助 0.278 億円/人 / 他 0.121 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.23 億円/人 / 補助 0.371 億円/人 / 他 0.125 億円/人</t>
+          <t xml:space="preserve">全社 0.229 億円/人 / 補助 0.369 億円/人 / 他 0.125 億円/人</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.53 pt / 補助 0.41 pt / 他 0.41 pt</t>
+          <t xml:space="preserve">全社 0.52 pt / 補助 0.4 pt / 他 0.41 pt</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -4861,22 +4861,22 @@
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.11 pt / 補助 -0.01 pt / 他 0 pt</t>
+          <t xml:space="preserve">全社 0.11 pt / 補助 -0 pt / 他 0 pt</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.6 pt / 補助 27.05 pt / 他 2.55 pt</t>
+          <t xml:space="preserve">全社 15.48 pt / 補助 26.82 pt / 他 2.55 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 16.33 pt / 補助 27.11 pt / 他 1.7 pt</t>
+          <t xml:space="preserve">全社 16.19 pt / 補助 26.89 pt / 他 1.7 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 17.57 pt / 補助 27.17 pt / 他 1.91 pt</t>
+          <t xml:space="preserve">全社 17.41 pt / 補助 26.96 pt / 他 1.91 pt</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.71 % / 補助 3.28 % / 他 2.06 %</t>
+          <t xml:space="preserve">全社 2.71 % / 補助 3.29 % / 他 2.06 %</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -4990,17 +4990,17 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.81 % / 補助 3.54 % / 他 1.76 %</t>
+          <t xml:space="preserve">全社 2.81 % / 補助 3.55 % / 他 1.76 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.34 % / 補助 2.73 % / 他 1.66 %</t>
+          <t xml:space="preserve">全社 2.35 % / 補助 2.74 % / 他 1.66 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.93 % / 補助 2.11 % / 他 1.56 %</t>
+          <t xml:space="preserve">全社 1.94 % / 補助 2.12 % / 他 1.56 %</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / 他 3.93 倍</t>
+          <t xml:space="preserve">全社 3.68 倍 / 補助 3.55 倍 / 他 3.93 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.26 倍 / 補助 2.95 倍 / 他 3.99 倍</t>
+          <t xml:space="preserve">全社 3.25 倍 / 補助 2.94 倍 / 他 3.99 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.27 倍 / 補助 4.02 倍 / 他 4.99 倍</t>
+          <t xml:space="preserve">全社 4.26 倍 / 補助 4.01 倍 / 他 4.99 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.81 倍 / 補助 5.94 倍 / 他 5.44 倍</t>
+          <t xml:space="preserve">全社 5.79 倍 / 補助 5.92 倍 / 他 5.43 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.92 倍 / 補助 8.62 倍 / 他 5.93 倍</t>
+          <t xml:space="preserve">全社 7.88 倍 / 補助 8.57 倍 / 他 5.92 倍</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 53.61 %</t>
+          <t xml:space="preserve">構成比 53.6 %</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -5362,17 +5362,17 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 58.79 %</t>
+          <t xml:space="preserve">構成比 58.74 %</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 63.51 %</t>
+          <t xml:space="preserve">構成比 63.42 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 67.98 %</t>
+          <t xml:space="preserve">構成比 67.86 %</t>
         </is>
       </c>
     </row>
@@ -5409,14 +5409,14 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">補助 5.4 % / 他 4.26 %</t>
+        </is>
+      </c>
+      <c r="H33" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
-      <c r="H33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
-        </is>
-      </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">補助 5.4 % / 他 4.26 %</t>
@@ -5424,17 +5424,17 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 29.62 % / 他 7.31 %</t>
+          <t xml:space="preserve">補助 29.39 % / 他 7.31 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 29.61 % / 他 6.25 %</t>
+          <t xml:space="preserve">補助 29.39 % / 他 6.25 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 29.61 % / 他 6.26 %</t>
+          <t xml:space="preserve">補助 29.39 % / 他 6.26 %</t>
         </is>
       </c>
     </row>
@@ -5471,19 +5471,19 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">差 -0 pt</t>
+        </is>
+      </c>
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">差 0 pt</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">差 -0.01 pt</t>
         </is>
       </c>
-      <c r="H34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">差 -0 pt</t>
-        </is>
-      </c>
-      <c r="I34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">差 -0.01 pt</t>
-        </is>
-      </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">差 0.31 pt</t>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0.04 pt</t>
+          <t xml:space="preserve">差 -0.05 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0.39 pt</t>
+          <t xml:space="preserve">差 -0.4 pt</t>
         </is>
       </c>
     </row>
@@ -5533,12 +5533,12 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.38 pt</t>
+          <t xml:space="preserve">差 2.37 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.84 pt</t>
+          <t xml:space="preserve">差 1.83 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.66 pt</t>
+          <t xml:space="preserve">差 3.64 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
@@ -5610,17 +5610,17 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.012 億円/人 / 他 0.553 億円/人</t>
+          <t xml:space="preserve">補助 1.01 億円/人 / 他 0.553 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.28 億円/人 / 他 0.562 億円/人</t>
+          <t xml:space="preserve">補助 1.275 億円/人 / 他 0.562 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.619 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">補助 1.611 億円/人 / 他 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 169.23 %</t>
+          <t xml:space="preserve">寄与率 164.29 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -5729,22 +5729,22 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 133.33 %</t>
+          <t xml:space="preserve">寄与率 135.29 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 81.49 %</t>
+          <t xml:space="preserve">寄与率 81.4 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 92.42 %</t>
+          <t xml:space="preserve">寄与率 92.57 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 93.95 %</t>
+          <t xml:space="preserve">寄与率 93.9 %</t>
         </is>
       </c>
     </row>
@@ -9855,7 +9855,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjIwLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjEzMy41LCJtYXgiOjI1Mi42OSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6MiwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjY1LCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzYuNDQsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuODl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wODQ5OTk5OTk5OTk5OTk5OSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMTM1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDg5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4xMTkyODU3MTQyODU3MTQyNywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjEzMy41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjoyLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2NSwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3Ni40NCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA3MDcyMzY4NDIxMDUxLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDE5ODE2Mjg3MTc4ODc3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDQ0ODUzNjMwNjc1MzI3NCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwNjA5MzM3MDI3ODk4MDQsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA3MzE2NTgzOTIyNDksIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4MDkwNTk1MDQ2MDU2NjMsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MTQ5Mzc3NzI0OTMwNjQ0Niwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjI5NjEzNzE0MzkwMDY1NzQzLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjQ5NTI1ODE3MTAzMzM2NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTU1NTA0MjcyNTc5NzcyODQsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODg5NDM4NDEyMjQ2MzUxMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQyMTUyOTA2OTQxMzA2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyNjI0MDc1MjQ4NTg5MDg5Mywib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODcyMzc2OTIxMzYzMzgsInByb2plY3RTZ2FSYXRlRW5kIjowLjEwMzE1Mjk5NTQzNzQxMzIxLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjI2MTY0NjUxNjM2NTksInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzcxOTIzMTY3OTU4MzQ5LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM319</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjIwLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjEzMy41LCJtYXgiOjI1Mi42OSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6MiwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjY1LCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzYuNDQsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuODl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wODQ5OTk5OTk5OTk5OTk5OSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMTM1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDg5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4xMTkyODU3MTQyODU3MTQyNywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjEzMy41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjoyLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2NSwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3Ni40NCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDAzNjgwNTU1NTU1NTU0LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDE5ODE2Mjg3MTc4ODc3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDQ0ODUzNjMwNjc1MzI3NCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwNjA5MzM3MDI3ODk4MDQsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA3MzE2NTgzOTIyNDksIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4MDkwNTk1MDQ2MDU2NjMsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MTQ5Mzc3NzI0OTMwNjQ0Niwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjI5Mzg4NzE0MzkwMDY1NzQsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTQwMTg1NzA3MjY1MjYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1NTUwNDI3MjU3OTc3Mjg0LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDg4OTQzODQxMjI0NjM1MTEsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDgxMTgzMzI1Mzg2Njc4NywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMjYyNDA3NTI0ODU4OTA4OTMsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTg3MjM3NjkyMTM2MzM4LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMDMwMDI5OTU0Mzc0MTMyMiwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTMyNjE2NDY1MTYzNjYsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgxOTIzMTY3OTU4MzQ5NiwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>20.01053154331047</v>
+        <v>15.448906650814621</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -234,7 +234,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>126.03000000000003</v>
+        <v>93.21000000000004</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -294,7 +294,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>67.86048689138576</v>
+        <v>63.89827961836075</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -324,7 +324,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>29.38972537778437</v>
+        <v>22.000324971691864</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -354,7 +354,7 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>109.25</v>
+        <v>76.43</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>32.53247290200707</v>
+        <v>22.016675856213674</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>28.37999999999999</v>
+        <v>19.73000000000001</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>7.018093513861001</v>
+        <v>7.019737997987985</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>2.3899999999999997</v>
+        <v>2.8600000000000003</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>370.4960835509137</v>
+        <v>257.5718015665798</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1268,13 +1268,13 @@
         <v>173.01</v>
       </c>
       <c r="H3" s="4">
-        <v>206.33999999999997</v>
+        <v>199.42000000000002</v>
       </c>
       <c r="I3" s="4">
-        <v>247.28000000000003</v>
+        <v>229.88</v>
       </c>
       <c r="J3" s="4">
-        <v>299.04</v>
+        <v>266.22</v>
       </c>
     </row>
     <row r="4">
@@ -1304,13 +1304,13 @@
         <v>4.873613384251674</v>
       </c>
       <c r="H4" s="2">
-        <v>19.26478238252123</v>
+        <v>15.265013583029896</v>
       </c>
       <c r="I4" s="2">
-        <v>19.841039061742794</v>
+        <v>15.27429545682477</v>
       </c>
       <c r="J4" s="2">
-        <v>20.931737301844056</v>
+        <v>15.8082477814512</v>
       </c>
     </row>
     <row r="5">
@@ -1338,13 +1338,13 @@
         <v>117.65</v>
       </c>
       <c r="H5" s="2">
-        <v>138.97</v>
+        <v>134.3</v>
       </c>
       <c r="I5" s="2">
-        <v>165.63</v>
+        <v>153.98000000000002</v>
       </c>
       <c r="J5" s="2">
-        <v>199.07</v>
+        <v>177.26</v>
       </c>
     </row>
     <row r="6">
@@ -1406,13 +1406,13 @@
         <v>55.359999999999985</v>
       </c>
       <c r="H7" s="4">
-        <v>67.36999999999998</v>
+        <v>65.12</v>
       </c>
       <c r="I7" s="4">
-        <v>81.65000000000003</v>
+        <v>75.89999999999998</v>
       </c>
       <c r="J7" s="4">
-        <v>99.97000000000003</v>
+        <v>88.96000000000004</v>
       </c>
     </row>
     <row r="8">
@@ -1440,13 +1440,13 @@
         <v>31.998150395930864</v>
       </c>
       <c r="H8" s="2">
-        <v>32.64999515362992</v>
+        <v>32.654698626015445</v>
       </c>
       <c r="I8" s="2">
-        <v>33.019249433840194</v>
+        <v>33.01722637898033</v>
       </c>
       <c r="J8" s="2">
-        <v>33.43031032637775</v>
+        <v>33.415971752685756</v>
       </c>
     </row>
     <row r="9">
@@ -1474,13 +1474,13 @@
         <v>44.19</v>
       </c>
       <c r="H9" s="2">
-        <v>48.459999999999994</v>
+        <v>47.89</v>
       </c>
       <c r="I9" s="2">
-        <v>53.86</v>
+        <v>52.74</v>
       </c>
       <c r="J9" s="2">
-        <v>60.05</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="10">
@@ -1514,7 +1514,7 @@
         <v>1.19</v>
       </c>
       <c r="J10" s="2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="11">
@@ -1548,7 +1548,7 @@
         <v>1.06</v>
       </c>
       <c r="J11" s="2">
-        <v>1.1</v>
+        <v>1.1099999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1610,13 +1610,13 @@
         <v>17.06</v>
       </c>
       <c r="H13" s="2">
-        <v>18.16</v>
+        <v>18.18</v>
       </c>
       <c r="I13" s="2">
-        <v>19.83</v>
+        <v>20.07</v>
       </c>
       <c r="J13" s="2">
-        <v>21.66</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="14">
@@ -1644,13 +1644,13 @@
         <v>16.21</v>
       </c>
       <c r="H14" s="2">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="I14" s="2">
-        <v>19.33</v>
+        <v>19.78</v>
       </c>
       <c r="J14" s="2">
-        <v>21.12</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="15">
@@ -1678,13 +1678,13 @@
         <v>0.85</v>
       </c>
       <c r="H15" s="2">
-        <v>0.9199999999999999</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="I15" s="2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="J15" s="2">
-        <v>1.1099999999999999</v>
+        <v>1.1400000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1746,13 +1746,13 @@
         <v>0.81</v>
       </c>
       <c r="H17" s="2">
-        <v>0.97</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="I17" s="2">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="J17" s="2">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="18">
@@ -1780,13 +1780,13 @@
         <v>11.169999999999984</v>
       </c>
       <c r="H18" s="4">
-        <v>18.909999999999982</v>
+        <v>17.230000000000004</v>
       </c>
       <c r="I18" s="4">
-        <v>27.790000000000035</v>
+        <v>23.159999999999982</v>
       </c>
       <c r="J18" s="4">
-        <v>39.92000000000003</v>
+        <v>30.760000000000048</v>
       </c>
     </row>
     <row r="19">
@@ -1814,13 +1814,13 @@
         <v>6.456274203803239</v>
       </c>
       <c r="H19" s="2">
-        <v>9.16448580013569</v>
+        <v>8.64005616287233</v>
       </c>
       <c r="I19" s="2">
-        <v>11.238272403752843</v>
+        <v>10.074821646076208</v>
       </c>
       <c r="J19" s="2">
-        <v>13.349384697699312</v>
+        <v>11.554353542183174</v>
       </c>
     </row>
     <row r="20">
@@ -1848,13 +1848,13 @@
         <v>11.169999999999984</v>
       </c>
       <c r="H20" s="4">
-        <v>18.909999999999982</v>
+        <v>17.230000000000004</v>
       </c>
       <c r="I20" s="4">
-        <v>27.790000000000035</v>
+        <v>23.159999999999982</v>
       </c>
       <c r="J20" s="4">
-        <v>39.92000000000003</v>
+        <v>30.760000000000048</v>
       </c>
     </row>
     <row r="21">
@@ -1986,13 +1986,13 @@
         <v>17.06</v>
       </c>
       <c r="H23" s="2">
-        <v>18.16</v>
+        <v>18.18</v>
       </c>
       <c r="I23" s="2">
-        <v>19.83</v>
+        <v>20.07</v>
       </c>
       <c r="J23" s="2">
-        <v>21.66</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="24">
@@ -2026,7 +2026,7 @@
         <v>1.19</v>
       </c>
       <c r="J24" s="2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="25">
@@ -2088,13 +2088,13 @@
         <v>35.13999999999998</v>
       </c>
       <c r="H26" s="4">
-        <v>44.019999999999975</v>
+        <v>42.36</v>
       </c>
       <c r="I26" s="4">
-        <v>54.61000000000003</v>
+        <v>50.21999999999998</v>
       </c>
       <c r="J26" s="4">
-        <v>68.61000000000003</v>
+        <v>59.96000000000004</v>
       </c>
     </row>
     <row r="27">
@@ -2124,13 +2124,13 @@
         <v>5.2410901467505155</v>
       </c>
       <c r="H27" s="2">
-        <v>25.270347182697783</v>
+        <v>20.54638588503137</v>
       </c>
       <c r="I27" s="2">
-        <v>24.057246706042832</v>
+        <v>18.55524079320108</v>
       </c>
       <c r="J27" s="2">
-        <v>25.636330342428117</v>
+        <v>19.394663480685125</v>
       </c>
     </row>
     <row r="28">
@@ -2158,13 +2158,13 @@
         <v>20.310964684122293</v>
       </c>
       <c r="H28" s="2">
-        <v>21.33372104293883</v>
+        <v>21.241600641861396</v>
       </c>
       <c r="I28" s="2">
-        <v>22.08427693303139</v>
+        <v>21.846180615973545</v>
       </c>
       <c r="J28" s="2">
-        <v>22.94341894060996</v>
+        <v>22.522725565321927</v>
       </c>
     </row>
     <row r="29">
@@ -2192,13 +2192,13 @@
         <v>264</v>
       </c>
       <c r="H29" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I29" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="J29" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30">
@@ -2260,13 +2260,13 @@
         <v>0.06462121212121212</v>
       </c>
       <c r="H31" s="2">
-        <v>0.06627737226277372</v>
+        <v>0.0658695652173913</v>
       </c>
       <c r="I31" s="2">
-        <v>0.06982394366197182</v>
+        <v>0.0696875</v>
       </c>
       <c r="J31" s="2">
-        <v>0.0736734693877551</v>
+        <v>0.07386666666666666</v>
       </c>
     </row>
     <row r="32">
@@ -2296,13 +2296,13 @@
         <v>2.0334928229664984</v>
       </c>
       <c r="H32" s="2">
-        <v>2.562873841572455</v>
+        <v>1.9318008053417657</v>
       </c>
       <c r="I32" s="2">
-        <v>5.3511044239002326</v>
+        <v>5.796204620462042</v>
       </c>
       <c r="J32" s="2">
-        <v>5.513188634001254</v>
+        <v>5.997010463378172</v>
       </c>
     </row>
     <row r="33">
@@ -2336,7 +2336,7 @@
         <v>0.238</v>
       </c>
       <c r="J33" s="2">
-        <v>0.246</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="34">
@@ -2372,7 +2372,7 @@
         <v>3.4782608695652195</v>
       </c>
       <c r="J34" s="2">
-        <v>3.3613445378151363</v>
+        <v>4.201680672268915</v>
       </c>
     </row>
     <row r="35">
@@ -2400,13 +2400,13 @@
         <v>0.13063197026022297</v>
       </c>
       <c r="H35" s="2">
-        <v>0.15777777777777768</v>
+        <v>0.1507473309608541</v>
       </c>
       <c r="I35" s="2">
-        <v>0.18896193771626307</v>
+        <v>0.17139931740614328</v>
       </c>
       <c r="J35" s="2">
-        <v>0.2294648829431439</v>
+        <v>0.19659016393442638</v>
       </c>
     </row>
     <row r="36">
@@ -2434,13 +2434,13 @@
         <v>16.969999999999985</v>
       </c>
       <c r="H36" s="4">
-        <v>24.709999999999983</v>
+        <v>23.030000000000005</v>
       </c>
       <c r="I36" s="4">
-        <v>33.59000000000003</v>
+        <v>28.959999999999983</v>
       </c>
       <c r="J36" s="4">
-        <v>45.72000000000003</v>
+        <v>36.560000000000045</v>
       </c>
     </row>
     <row r="37">
@@ -2468,13 +2468,13 @@
         <v>9.808681579099465</v>
       </c>
       <c r="H37" s="2">
-        <v>11.975380440050396</v>
+        <v>11.548490622806138</v>
       </c>
       <c r="I37" s="2">
-        <v>13.583791653186683</v>
+        <v>12.597877153297365</v>
       </c>
       <c r="J37" s="2">
-        <v>15.288924558587489</v>
+        <v>13.733002779655939</v>
       </c>
     </row>
     <row r="38">
@@ -2504,13 +2504,13 @@
         <v>3.665241295051902</v>
       </c>
       <c r="H38" s="2">
-        <v>45.60989982321748</v>
+        <v>35.71007660577506</v>
       </c>
       <c r="I38" s="2">
-        <v>35.93686766491322</v>
+        <v>25.749023013460604</v>
       </c>
       <c r="J38" s="2">
-        <v>36.11193807680853</v>
+        <v>26.24309392265216</v>
       </c>
     </row>
   </sheetData>
@@ -2672,13 +2672,13 @@
         <v>93.68</v>
       </c>
       <c r="H3" s="4">
-        <v>121.21</v>
+        <v>114.29</v>
       </c>
       <c r="I3" s="4">
-        <v>156.83</v>
+        <v>139.43</v>
       </c>
       <c r="J3" s="4">
-        <v>202.93</v>
+        <v>170.11</v>
       </c>
     </row>
     <row r="4">
@@ -2708,13 +2708,13 @@
         <v>5.400540054005409</v>
       </c>
       <c r="H4" s="2">
-        <v>29.387275832621683</v>
+        <v>22.000426985482502</v>
       </c>
       <c r="I4" s="2">
-        <v>29.387014272749788</v>
+        <v>21.996675124682817</v>
       </c>
       <c r="J4" s="2">
-        <v>29.3948861824906</v>
+        <v>22.00387291113821</v>
       </c>
     </row>
     <row r="5">
@@ -2742,13 +2742,13 @@
         <v>54.14715912375008</v>
       </c>
       <c r="H5" s="2">
-        <v>58.74285160414849</v>
+        <v>57.31120248721292</v>
       </c>
       <c r="I5" s="2">
-        <v>63.42203170494985</v>
+        <v>60.653384374456245</v>
       </c>
       <c r="J5" s="2">
-        <v>67.86048689138576</v>
+        <v>63.89827961836075</v>
       </c>
     </row>
     <row r="6">
@@ -2776,13 +2776,13 @@
         <v>29.980000000000004</v>
       </c>
       <c r="H6" s="4">
-        <v>39.41999999999999</v>
+        <v>37.17</v>
       </c>
       <c r="I6" s="4">
-        <v>51.81000000000002</v>
+        <v>46.06</v>
       </c>
       <c r="J6" s="4">
-        <v>68.1</v>
+        <v>57.09000000000002</v>
       </c>
     </row>
     <row r="7">
@@ -2810,13 +2810,13 @@
         <v>32.00256191289496</v>
       </c>
       <c r="H7" s="2">
-        <v>32.52206913620987</v>
+        <v>32.522530405109805</v>
       </c>
       <c r="I7" s="2">
-        <v>33.0357712172416</v>
+        <v>33.034497597360684</v>
       </c>
       <c r="J7" s="2">
-        <v>33.55836988123983</v>
+        <v>33.56063723473048</v>
       </c>
     </row>
     <row r="8">
@@ -2844,13 +2844,13 @@
         <v>6.630000000000006</v>
       </c>
       <c r="H8" s="4">
-        <v>12.929999999999987</v>
+        <v>11.260000000000002</v>
       </c>
       <c r="I8" s="4">
-        <v>21.150000000000016</v>
+        <v>16.54</v>
       </c>
       <c r="J8" s="4">
-        <v>32.54</v>
+        <v>23.420000000000023</v>
       </c>
     </row>
     <row r="9">
@@ -2878,13 +2878,13 @@
         <v>7.077284372331347</v>
       </c>
       <c r="H9" s="2">
-        <v>10.667436680141892</v>
+        <v>9.85213054510456</v>
       </c>
       <c r="I9" s="2">
-        <v>13.485940190014675</v>
+        <v>11.862583375170335</v>
       </c>
       <c r="J9" s="2">
-        <v>16.03508599024294</v>
+        <v>13.767562165657528</v>
       </c>
     </row>
     <row r="10">
@@ -2912,13 +2912,13 @@
         <v>7.47</v>
       </c>
       <c r="H10" s="2">
-        <v>7.89</v>
+        <v>7.9</v>
       </c>
       <c r="I10" s="2">
-        <v>8.82</v>
+        <v>9.04</v>
       </c>
       <c r="J10" s="2">
-        <v>9.86</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="11">
@@ -3014,13 +3014,13 @@
         <v>18.870000000000005</v>
       </c>
       <c r="H13" s="4">
-        <v>25.619999999999987</v>
+        <v>23.960000000000004</v>
       </c>
       <c r="I13" s="4">
-        <v>34.79000000000001</v>
+        <v>30.4</v>
       </c>
       <c r="J13" s="4">
-        <v>47.24999999999999</v>
+        <v>38.600000000000016</v>
       </c>
     </row>
     <row r="14">
@@ -3050,13 +3050,13 @@
         <v>6.190208216094595</v>
       </c>
       <c r="H14" s="2">
-        <v>35.77106518282977</v>
+        <v>26.974032856385797</v>
       </c>
       <c r="I14" s="2">
-        <v>35.792349726776074</v>
+        <v>26.878130217028364</v>
       </c>
       <c r="J14" s="2">
-        <v>35.81488933601602</v>
+        <v>26.973684210526372</v>
       </c>
     </row>
     <row r="15">
@@ -3084,13 +3084,13 @@
         <v>117</v>
       </c>
       <c r="H15" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I15" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J15" s="2">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16">
@@ -3152,13 +3152,13 @@
         <v>0.06384615384615384</v>
       </c>
       <c r="H17" s="2">
-        <v>0.06575</v>
+        <v>0.06475409836065574</v>
       </c>
       <c r="I17" s="2">
-        <v>0.07170731707317074</v>
+        <v>0.07118110236220472</v>
       </c>
       <c r="J17" s="2">
-        <v>0.07825396825396826</v>
+        <v>0.07825757575757576</v>
       </c>
     </row>
     <row r="18">
@@ -3188,13 +3188,13 @@
         <v>2.1170472179117716</v>
       </c>
       <c r="H18" s="2">
-        <v>2.9819277108433795</v>
+        <v>1.4220817697017551</v>
       </c>
       <c r="I18" s="2">
-        <v>9.060558286191235</v>
+        <v>9.925246685936395</v>
       </c>
       <c r="J18" s="2">
-        <v>9.129683619479522</v>
+        <v>9.941505765620828</v>
       </c>
     </row>
     <row r="19">
@@ -3292,13 +3292,13 @@
         <v>0.1585714285714286</v>
       </c>
       <c r="H21" s="2">
-        <v>0.20999999999999988</v>
+        <v>0.19322580645161294</v>
       </c>
       <c r="I21" s="2">
-        <v>0.2783200000000001</v>
+        <v>0.23565891472868217</v>
       </c>
       <c r="J21" s="2">
-        <v>0.36914062499999994</v>
+        <v>0.28805970149253746</v>
       </c>
     </row>
     <row r="22">
@@ -3626,17 +3626,17 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 19.26 % / 補助 29.39 % / 他 7.31 %</t>
+          <t xml:space="preserve">全社 15.27 % / 補助 22 % / 他 7.31 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 19.84 % / 補助 29.39 % / 他 6.25 %</t>
+          <t xml:space="preserve">全社 15.27 % / 補助 22 % / 他 6.25 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20.93 % / 補助 29.39 % / 他 6.26 %</t>
+          <t xml:space="preserve">全社 15.81 % / 補助 22 % / 他 6.26 %</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.98 % / 補助 66.96 % / 他 67.01 %</t>
+          <t xml:space="preserve">全社 66.98 % / 補助 66.97 % / 他 67.01 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.57 % / 補助 66.44 % / 他 66.84 %</t>
+          <t xml:space="preserve">全社 66.58 % / 補助 66.44 % / 他 66.84 %</t>
         </is>
       </c>
     </row>
@@ -3755,12 +3755,12 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.02 % / 補助 33.04 % / 他 32.99 %</t>
+          <t xml:space="preserve">全社 33.02 % / 補助 33.03 % / 他 32.99 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.43 % / 補助 33.56 % / 他 33.16 %</t>
+          <t xml:space="preserve">全社 33.42 % / 補助 33.56 % / 他 33.16 %</t>
         </is>
       </c>
     </row>
@@ -3812,17 +3812,17 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.49 % / 補助 21.85 % / 他 25.81 %</t>
+          <t xml:space="preserve">全社 24.01 % / 補助 22.67 % / 他 25.82 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.78 % / 補助 19.55 % / 他 25.65 %</t>
+          <t xml:space="preserve">全社 22.94 % / 補助 21.17 % / 他 25.67 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 20.08 % / 補助 17.52 % / 他 25.48 %</t>
+          <t xml:space="preserve">全社 21.86 % / 補助 19.79 % / 他 25.52 %</t>
         </is>
       </c>
     </row>
@@ -3874,17 +3874,17 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.16 % / 補助 10.67 % / 他 7.02 %</t>
+          <t xml:space="preserve">全社 8.64 % / 補助 9.85 % / 他 7.01 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.24 % / 補助 13.49 % / 他 7.34 %</t>
+          <t xml:space="preserve">全社 10.07 % / 補助 11.86 % / 他 7.32 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.35 % / 補助 16.04 % / 他 7.68 %</t>
+          <t xml:space="preserve">全社 11.55 % / 補助 13.77 % / 他 7.64 %</t>
         </is>
       </c>
     </row>
@@ -3936,17 +3936,17 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.98 % / 補助 14.21 % / 他 8.79 %</t>
+          <t xml:space="preserve">全社 11.55 % / 補助 13.61 % / 他 8.77 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.58 % / 補助 16.23 % / 他 9 %</t>
+          <t xml:space="preserve">全社 12.6 % / 補助 14.95 % / 他 8.98 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.29 % / 補助 18.15 % / 他 9.24 %</t>
+          <t xml:space="preserve">全社 13.73 % / 補助 16.3 % / 他 9.2 %</t>
         </is>
       </c>
     </row>
@@ -3998,17 +3998,17 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.51 % / 補助 11.76 % / 他 11.15 %</t>
+          <t xml:space="preserve">全社 11.63 % / 補助 12 % / 他 11.15 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.02 % / 補助 11.03 % / 他 10.99 %</t>
+          <t xml:space="preserve">全社 11.3 % / 補助 11.5 % / 他 10.99 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.47 % / 補助 10.3 % / 他 10.82 %</t>
+          <t xml:space="preserve">全社 10.93 % / 補助 11 % / 他 10.82 %</t>
         </is>
       </c>
     </row>
@@ -4122,17 +4122,17 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.8 % / 補助 6.51 % / 他 12.06 %</t>
+          <t xml:space="preserve">全社 9.12 % / 補助 6.91 % / 他 12.08 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.02 % / 補助 5.62 % / 他 12.17 %</t>
+          <t xml:space="preserve">全社 8.73 % / 補助 6.48 % / 他 12.19 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.24 % / 補助 4.86 % / 他 12.28 %</t>
+          <t xml:space="preserve">全社 8.32 % / 補助 6.07 % / 他 12.31 %</t>
         </is>
       </c>
     </row>
@@ -4184,17 +4184,17 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.56 % / 補助 0.41 % / 他 0.76 %</t>
+          <t xml:space="preserve">全社 0.58 % / 補助 0.44 % / 他 0.76 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.48 % / 補助 0.33 % / 他 0.74 %</t>
+          <t xml:space="preserve">全社 0.52 % / 補助 0.37 % / 他 0.74 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.41 % / 補助 0.27 % / 他 0.71 %</t>
+          <t xml:space="preserve">全社 0.47 % / 補助 0.32 % / 他 0.72 %</t>
         </is>
       </c>
     </row>
@@ -4246,17 +4246,17 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.36 % / 補助 6.92 % / 他 12.83 %</t>
+          <t xml:space="preserve">全社 9.69 % / 補助 7.35 % / 他 12.84 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.5 % / 補助 5.96 % / 他 12.91 %</t>
+          <t xml:space="preserve">全社 9.25 % / 補助 6.86 % / 他 12.94 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.65 % / 補助 5.13 % / 他 12.99 %</t>
+          <t xml:space="preserve">全社 8.79 % / 補助 6.4 % / 他 13.03 %</t>
         </is>
       </c>
     </row>
@@ -4308,12 +4308,12 @@
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.066 億円/人 / 補助 0.066 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">全社 0.066 億円/人 / 補助 0.065 億円/人 / 他 0.067 億円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.072 億円/人 / 他 0.068 億円/人</t>
+          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.071 億円/人 / 他 0.069 億円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.246 億円/人 / 補助 0.275 億円/人 / 他 0.227 億円/人</t>
+          <t xml:space="preserve">全社 0.248 億円/人 / 補助 0.275 億円/人 / 他 0.23 億円/人</t>
         </is>
       </c>
     </row>
@@ -4432,17 +4432,17 @@
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.56 % / 補助 2.98 % / 他 2.22 %</t>
+          <t xml:space="preserve">全社 1.93 % / 補助 1.42 % / 他 2.32 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.35 % / 補助 9.06 % / 他 2.54 %</t>
+          <t xml:space="preserve">全社 5.8 % / 補助 9.93 % / 他 2.63 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.51 % / 補助 9.13 % / 他 2.71 %</t>
+          <t xml:space="preserve">全社 6 % / 補助 9.94 % / 他 2.78 %</t>
         </is>
       </c>
     </row>
@@ -4494,17 +4494,17 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 43.87 % / 補助 32.75 % / 他 59.35 %</t>
+          <t xml:space="preserve">全社 45.63 % / 補助 35.06 % / 他 59.4 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.49 % / 補助 26.85 % / 他 58.93 %</t>
+          <t xml:space="preserve">全社 42.33 % / 補助 31.45 % / 他 59.03 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.36 % / 補助 22.03 % / 他 58.43 %</t>
+          <t xml:space="preserve">全社 39.03 % / 補助 28.19 % / 他 58.61 %</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.753 億円/人 / 補助 1.01 億円/人 / 他 0.553 億円/人</t>
+          <t xml:space="preserve">全社 0.723 億円/人 / 補助 0.937 億円/人 / 他 0.553 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.871 億円/人 / 補助 1.275 億円/人 / 他 0.562 億円/人</t>
+          <t xml:space="preserve">全社 0.798 億円/人 / 補助 1.098 億円/人 / 他 0.562 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.017 億円/人 / 補助 1.611 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">全社 0.887 億円/人 / 補助 1.289 億円/人 / 他 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -4680,17 +4680,17 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.069 億円/人 / 補助 0.108 億円/人 / 他 0.039 億円/人</t>
+          <t xml:space="preserve">全社 0.062 億円/人 / 補助 0.092 億円/人 / 他 0.039 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.098 億円/人 / 補助 0.172 億円/人 / 他 0.041 億円/人</t>
+          <t xml:space="preserve">全社 0.08 億円/人 / 補助 0.13 億円/人 / 他 0.041 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.136 億円/人 / 補助 0.258 億円/人 / 他 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.103 億円/人 / 補助 0.177 億円/人 / 他 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -4742,17 +4742,17 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.158 億円/人 / 補助 0.21 億円/人 / 他 0.117 億円/人</t>
+          <t xml:space="preserve">全社 0.151 億円/人 / 補助 0.193 億円/人 / 他 0.117 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.189 億円/人 / 補助 0.278 億円/人 / 他 0.121 億円/人</t>
+          <t xml:space="preserve">全社 0.171 億円/人 / 補助 0.236 億円/人 / 他 0.121 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.229 億円/人 / 補助 0.369 億円/人 / 他 0.125 億円/人</t>
+          <t xml:space="preserve">全社 0.197 億円/人 / 補助 0.288 億円/人 / 他 0.125 億円/人</t>
         </is>
       </c>
     </row>
@@ -4804,17 +4804,17 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.79 % / 補助 2.56 % / 他 4.76 %</t>
+          <t xml:space="preserve">全社 4.55 % / 補助 4.27 % / 他 4.76 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.65 % / 補助 2.5 % / 他 4.55 %</t>
+          <t xml:space="preserve">全社 4.35 % / 補助 4.1 % / 他 4.55 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.52 % / 補助 2.44 % / 他 4.35 %</t>
+          <t xml:space="preserve">全社 4.17 % / 補助 3.94 % / 他 4.35 %</t>
         </is>
       </c>
     </row>
@@ -4866,17 +4866,17 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.48 pt / 補助 26.82 pt / 他 2.55 pt</t>
+          <t xml:space="preserve">全社 10.72 pt / 補助 17.73 pt / 他 2.55 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 16.19 pt / 補助 26.89 pt / 他 1.7 pt</t>
+          <t xml:space="preserve">全社 10.93 pt / 補助 17.9 pt / 他 1.7 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 17.41 pt / 補助 26.96 pt / 他 1.91 pt</t>
+          <t xml:space="preserve">全社 11.64 pt / 補助 18.07 pt / 他 1.91 pt</t>
         </is>
       </c>
     </row>
@@ -4990,17 +4990,17 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.81 % / 補助 3.55 % / 他 1.76 %</t>
+          <t xml:space="preserve">全社 2.91 % / 補助 3.76 % / 他 1.76 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.35 % / 補助 2.74 % / 他 1.66 %</t>
+          <t xml:space="preserve">全社 2.52 % / 補助 3.08 % / 他 1.66 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.94 % / 補助 2.12 % / 他 1.56 %</t>
+          <t xml:space="preserve">全社 2.18 % / 補助 2.53 % / 他 1.56 %</t>
         </is>
       </c>
     </row>
@@ -5176,17 +5176,17 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.26 倍 / 補助 4.01 倍 / 他 4.99 倍</t>
+          <t xml:space="preserve">全社 3.97 倍 / 補助 3.62 倍 / 他 4.98 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.79 倍 / 補助 5.92 倍 / 他 5.43 倍</t>
+          <t xml:space="preserve">全社 4.99 倍 / 補助 4.85 倍 / 他 5.41 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.88 倍 / 補助 8.57 倍 / 他 5.92 倍</t>
+          <t xml:space="preserve">全社 6.3 倍 / 補助 6.45 倍 / 他 5.89 倍</t>
         </is>
       </c>
     </row>
@@ -5362,17 +5362,17 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 58.74 %</t>
+          <t xml:space="preserve">構成比 57.31 %</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 63.42 %</t>
+          <t xml:space="preserve">構成比 60.65 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 67.86 %</t>
+          <t xml:space="preserve">構成比 63.9 %</t>
         </is>
       </c>
     </row>
@@ -5424,17 +5424,17 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 29.39 % / 他 7.31 %</t>
+          <t xml:space="preserve">補助 22 % / 他 7.31 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 29.39 % / 他 6.25 %</t>
+          <t xml:space="preserve">補助 22 % / 他 6.25 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 29.39 % / 他 6.26 %</t>
+          <t xml:space="preserve">補助 22 % / 他 6.26 %</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0.05 pt</t>
+          <t xml:space="preserve">差 -0.04 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
@@ -5548,17 +5548,17 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 3.64 pt</t>
+          <t xml:space="preserve">差 2.84 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.14 pt</t>
+          <t xml:space="preserve">差 4.54 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 8.36 pt</t>
+          <t xml:space="preserve">差 6.13 pt</t>
         </is>
       </c>
     </row>
@@ -5610,17 +5610,17 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.01 億円/人 / 他 0.553 億円/人</t>
+          <t xml:space="preserve">補助 0.937 億円/人 / 他 0.553 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.275 億円/人 / 他 0.562 億円/人</t>
+          <t xml:space="preserve">補助 1.098 億円/人 / 他 0.562 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.611 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">補助 1.289 億円/人 / 他 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -5672,12 +5672,12 @@
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.066 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">補助 0.065 億円/人 / 他 0.067 億円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.072 億円/人 / 他 0.068 億円/人</t>
+          <t xml:space="preserve">補助 0.071 億円/人 / 他 0.069 億円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
@@ -5734,17 +5734,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 81.4 %</t>
+          <t xml:space="preserve">寄与率 76.4 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 92.57 %</t>
+          <t xml:space="preserve">寄与率 89.04 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 93.9 %</t>
+          <t xml:space="preserve">寄与率 90.53 %</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="B204" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="B206" s="2">
-        <v>133.5</v>
+        <v>82.4</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B223" s="2">
-        <v>76.44</v>
+        <v>74.8</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         </is>
       </c>
       <c r="B225" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjIwLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjEzMy41LCJtYXgiOjI1Mi42OSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6MiwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjY1LCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzYuNDQsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuODl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wODQ5OTk5OTk5OTk5OTk5OSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMTM1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDg5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4xMTkyODU3MTQyODU3MTQyNywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjIwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjEzMy41LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjoyLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2NSwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3Ni40NCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDAzNjgwNTU1NTU1NTU0LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDE5ODE2Mjg3MTc4ODc3LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDQ0ODUzNjMwNjc1MzI3NCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwNjA5MzM3MDI3ODk4MDQsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA3MzE2NTgzOTIyNDksIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4MDkwNTk1MDQ2MDU2NjMsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MTQ5Mzc3NzI0OTMwNjQ0Niwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjI5Mzg4NzE0MzkwMDY1NzQsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTQwMTg1NzA3MjY1MjYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1NTUwNDI3MjU3OTc3Mjg0LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDg4OTQzODQxMjI0NjM1MTEsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDgxMTgzMzI1Mzg2Njc4NywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMjYyNDA3NTI0ODU4OTA4OTMsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTg3MjM3NjkyMTM2MzM4LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMDMwMDI5OTU0Mzc0MTMyMiwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTMyNjE2NDY1MTYzNjYsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgxOTIzMTY3OTU4MzQ5NiwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjoyLCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjEzNi44NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjE4Ljc4LCJtYXgiOjMzLjQzLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6Mi44NSwibWF4IjozLjc0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1LjEzLCIyMDI5OnByb2plY3Q6Ny04Ijo3Ljl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wODQ5OTk5OTk5OTk5OTk5OSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMTM1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDg5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4xMTkyODU3MTQyODU3MTQyNywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyLjQsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjIsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwMzY4MDU1NTU1NTU1NCwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAxOTgxNjI4NzE3ODg3NywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQ0NDg1MzYzMDY3NTMyNzQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDYwOTMzNzAyNzg5ODA0LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjYwNzMxNjU4MzkyMjQ5LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODA5MDU5NTA0NjA1NjYzLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDE0OTM3NzcyNDkzMDY0NDYsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NDAxODU3MDcyNjUyNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTU1NTA0MjcyNTc5NzcyODQsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4xLCJvdGhlclBheUdyb3d0aCI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTg3MjM3NjkyMTM2MzM4LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTMyNjE2NDY1MTYzNjYsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgxOTIzMTY3OTU4MzQ5NiwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>15.448906650814621</v>
+        <v>15.464691482957393</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -234,7 +234,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>93.21000000000004</v>
+        <v>93.33000000000001</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -264,7 +264,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>2.0136531491304233</v>
+        <v>2.0628917862888008</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -294,7 +294,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>63.89827961836075</v>
+        <v>63.91350052560445</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -324,7 +324,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>22.000324971691864</v>
+        <v>22.02271203454029</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -354,7 +354,7 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>76.43</v>
+        <v>76.54</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>22.016675856213674</v>
+        <v>23.49843476135365</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>19.73000000000001</v>
+        <v>19.660000000000004</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>7.019737997987985</v>
+        <v>7.000299957045453</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>2.8600000000000003</v>
+        <v>2.46</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>257.5718015665798</v>
+        <v>256.6579634464752</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1259,22 +1259,22 @@
         <v>150</v>
       </c>
       <c r="E3" s="4">
-        <v>157.3</v>
+        <v>157.31</v>
       </c>
       <c r="F3" s="4">
-        <v>164.97</v>
+        <v>164.98000000000002</v>
       </c>
       <c r="G3" s="4">
-        <v>173.01</v>
+        <v>173.03</v>
       </c>
       <c r="H3" s="4">
-        <v>199.42000000000002</v>
+        <v>199.47</v>
       </c>
       <c r="I3" s="4">
-        <v>229.88</v>
+        <v>229.95999999999998</v>
       </c>
       <c r="J3" s="4">
-        <v>266.22</v>
+        <v>266.36</v>
       </c>
     </row>
     <row r="4">
@@ -1295,22 +1295,22 @@
         <v>4.748603351955305</v>
       </c>
       <c r="E4" s="2">
-        <v>4.866666666666664</v>
+        <v>4.8733333333333295</v>
       </c>
       <c r="F4" s="2">
-        <v>4.876033057851226</v>
+        <v>4.875723094526752</v>
       </c>
       <c r="G4" s="2">
-        <v>4.873613384251674</v>
+        <v>4.879379318705279</v>
       </c>
       <c r="H4" s="2">
-        <v>15.265013583029896</v>
+        <v>15.28058718141363</v>
       </c>
       <c r="I4" s="2">
-        <v>15.27429545682477</v>
+        <v>15.285506592470032</v>
       </c>
       <c r="J4" s="2">
-        <v>15.8082477814512</v>
+        <v>15.828839798225802</v>
       </c>
     </row>
     <row r="5">
@@ -1332,19 +1332,19 @@
         <v>106.97</v>
       </c>
       <c r="F5" s="2">
-        <v>112.18</v>
+        <v>112.19</v>
       </c>
       <c r="G5" s="2">
-        <v>117.65</v>
+        <v>117.67</v>
       </c>
       <c r="H5" s="2">
-        <v>134.3</v>
+        <v>134.36</v>
       </c>
       <c r="I5" s="2">
-        <v>153.98000000000002</v>
+        <v>154.09</v>
       </c>
       <c r="J5" s="2">
-        <v>177.26</v>
+        <v>177.45999999999998</v>
       </c>
     </row>
     <row r="6">
@@ -1397,22 +1397,22 @@
         <v>48</v>
       </c>
       <c r="E7" s="4">
-        <v>50.33000000000001</v>
+        <v>50.34</v>
       </c>
       <c r="F7" s="4">
-        <v>52.78999999999999</v>
+        <v>52.79000000000002</v>
       </c>
       <c r="G7" s="4">
-        <v>55.359999999999985</v>
+        <v>55.36</v>
       </c>
       <c r="H7" s="4">
-        <v>65.12</v>
+        <v>65.10999999999999</v>
       </c>
       <c r="I7" s="4">
-        <v>75.89999999999998</v>
+        <v>75.86999999999998</v>
       </c>
       <c r="J7" s="4">
-        <v>88.96000000000004</v>
+        <v>88.90000000000003</v>
       </c>
     </row>
     <row r="8">
@@ -1431,22 +1431,22 @@
         <v>32</v>
       </c>
       <c r="E8" s="2">
-        <v>31.996185632549274</v>
+        <v>32.00050854999682</v>
       </c>
       <c r="F8" s="2">
-        <v>31.99975753167242</v>
+        <v>31.997817917323324</v>
       </c>
       <c r="G8" s="2">
-        <v>31.998150395930864</v>
+        <v>31.994451829162575</v>
       </c>
       <c r="H8" s="2">
-        <v>32.654698626015445</v>
+        <v>32.641499974933566</v>
       </c>
       <c r="I8" s="2">
-        <v>33.01722637898033</v>
+        <v>32.99269438163158</v>
       </c>
       <c r="J8" s="2">
-        <v>33.415971752685756</v>
+        <v>33.37588226460431</v>
       </c>
     </row>
     <row r="9">
@@ -1465,22 +1465,22 @@
         <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>38.87</v>
+        <v>38.86</v>
       </c>
       <c r="F9" s="2">
-        <v>41.449999999999996</v>
+        <v>41.44</v>
       </c>
       <c r="G9" s="2">
-        <v>44.19</v>
+        <v>44.15</v>
       </c>
       <c r="H9" s="2">
-        <v>47.89</v>
+        <v>47.87</v>
       </c>
       <c r="I9" s="2">
-        <v>52.74</v>
+        <v>52.519999999999996</v>
       </c>
       <c r="J9" s="2">
-        <v>58.2</v>
+        <v>57.73</v>
       </c>
     </row>
     <row r="10">
@@ -1601,22 +1601,22 @@
         <v>14</v>
       </c>
       <c r="E13" s="2">
-        <v>14.95</v>
+        <v>14.940000000000001</v>
       </c>
       <c r="F13" s="2">
-        <v>15.96</v>
+        <v>15.95</v>
       </c>
       <c r="G13" s="2">
-        <v>17.06</v>
+        <v>17.02</v>
       </c>
       <c r="H13" s="2">
-        <v>18.18</v>
+        <v>18.15</v>
       </c>
       <c r="I13" s="2">
-        <v>20.07</v>
+        <v>19.84</v>
       </c>
       <c r="J13" s="2">
-        <v>22.16</v>
+        <v>21.689999999999998</v>
       </c>
     </row>
     <row r="14">
@@ -1638,19 +1638,19 @@
         <v>14.2</v>
       </c>
       <c r="F14" s="2">
-        <v>15.16</v>
+        <v>15.15</v>
       </c>
       <c r="G14" s="2">
-        <v>16.21</v>
+        <v>16.17</v>
       </c>
       <c r="H14" s="2">
-        <v>17.9</v>
+        <v>17.69</v>
       </c>
       <c r="I14" s="2">
-        <v>19.78</v>
+        <v>19.35</v>
       </c>
       <c r="J14" s="2">
-        <v>21.87</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="15">
@@ -1669,7 +1669,7 @@
         <v>0.7</v>
       </c>
       <c r="E15" s="2">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="F15" s="2">
         <v>0.8</v>
@@ -1678,13 +1678,13 @@
         <v>0.85</v>
       </c>
       <c r="H15" s="2">
-        <v>0.9299999999999999</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="I15" s="2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="J15" s="2">
-        <v>1.1400000000000001</v>
+        <v>1.1099999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1771,22 +1771,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>11.460000000000008</v>
+        <v>11.480000000000004</v>
       </c>
       <c r="F18" s="4">
-        <v>11.33999999999999</v>
+        <v>11.350000000000016</v>
       </c>
       <c r="G18" s="4">
-        <v>11.169999999999984</v>
+        <v>11.210000000000004</v>
       </c>
       <c r="H18" s="4">
-        <v>17.230000000000004</v>
+        <v>17.239999999999988</v>
       </c>
       <c r="I18" s="4">
-        <v>23.159999999999982</v>
+        <v>23.34999999999998</v>
       </c>
       <c r="J18" s="4">
-        <v>30.760000000000048</v>
+        <v>31.170000000000044</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.285441830896381</v>
+        <v>7.297692454389424</v>
       </c>
       <c r="F19" s="2">
-        <v>6.8739770867430385</v>
+        <v>6.879621772336049</v>
       </c>
       <c r="G19" s="2">
-        <v>6.456274203803239</v>
+        <v>6.478645321620531</v>
       </c>
       <c r="H19" s="2">
-        <v>8.64005616287233</v>
+        <v>8.64290369479119</v>
       </c>
       <c r="I19" s="2">
-        <v>10.074821646076208</v>
+        <v>10.1539398156201</v>
       </c>
       <c r="J19" s="2">
-        <v>11.554353542183174</v>
+        <v>11.702207538669485</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E20" s="4">
-        <v>11.460000000000008</v>
+        <v>11.480000000000004</v>
       </c>
       <c r="F20" s="4">
-        <v>11.33999999999999</v>
+        <v>11.350000000000016</v>
       </c>
       <c r="G20" s="4">
-        <v>11.169999999999984</v>
+        <v>11.210000000000004</v>
       </c>
       <c r="H20" s="4">
-        <v>17.230000000000004</v>
+        <v>17.239999999999988</v>
       </c>
       <c r="I20" s="4">
-        <v>23.159999999999982</v>
+        <v>23.34999999999998</v>
       </c>
       <c r="J20" s="4">
-        <v>30.760000000000048</v>
+        <v>31.170000000000044</v>
       </c>
     </row>
     <row r="21">
@@ -1977,22 +1977,22 @@
         <v>14</v>
       </c>
       <c r="E23" s="2">
-        <v>14.95</v>
+        <v>14.940000000000001</v>
       </c>
       <c r="F23" s="2">
-        <v>15.96</v>
+        <v>15.95</v>
       </c>
       <c r="G23" s="2">
-        <v>17.06</v>
+        <v>17.02</v>
       </c>
       <c r="H23" s="2">
-        <v>18.18</v>
+        <v>18.15</v>
       </c>
       <c r="I23" s="2">
-        <v>20.07</v>
+        <v>19.84</v>
       </c>
       <c r="J23" s="2">
-        <v>22.16</v>
+        <v>21.689999999999998</v>
       </c>
     </row>
     <row r="24">
@@ -2079,22 +2079,22 @@
         <v>30.1</v>
       </c>
       <c r="E26" s="4">
-        <v>31.710000000000008</v>
+        <v>31.720000000000006</v>
       </c>
       <c r="F26" s="4">
-        <v>33.389999999999986</v>
+        <v>33.390000000000015</v>
       </c>
       <c r="G26" s="4">
-        <v>35.13999999999998</v>
+        <v>35.14</v>
       </c>
       <c r="H26" s="4">
-        <v>42.36</v>
+        <v>42.33999999999998</v>
       </c>
       <c r="I26" s="4">
-        <v>50.21999999999998</v>
+        <v>50.17999999999998</v>
       </c>
       <c r="J26" s="4">
-        <v>59.96000000000004</v>
+        <v>59.90000000000004</v>
       </c>
     </row>
     <row r="27">
@@ -2115,22 +2115,22 @@
         <v>4.768534632788035</v>
       </c>
       <c r="E27" s="2">
-        <v>5.348837209302348</v>
+        <v>5.382059800664463</v>
       </c>
       <c r="F27" s="2">
-        <v>5.298013245033051</v>
+        <v>5.264817150063084</v>
       </c>
       <c r="G27" s="2">
-        <v>5.2410901467505155</v>
+        <v>5.241090146750471</v>
       </c>
       <c r="H27" s="2">
-        <v>20.54638588503137</v>
+        <v>20.489470688673816</v>
       </c>
       <c r="I27" s="2">
-        <v>18.55524079320108</v>
+        <v>18.516769012753898</v>
       </c>
       <c r="J27" s="2">
-        <v>19.394663480685125</v>
+        <v>19.37026703866096</v>
       </c>
     </row>
     <row r="28">
@@ -2149,22 +2149,22 @@
         <v>20.06666666666667</v>
       </c>
       <c r="E28" s="2">
-        <v>20.1589319771138</v>
+        <v>20.164007373974957</v>
       </c>
       <c r="F28" s="2">
-        <v>20.240043644298954</v>
+        <v>20.23881682628198</v>
       </c>
       <c r="G28" s="2">
-        <v>20.310964684122293</v>
+        <v>20.30861700283188</v>
       </c>
       <c r="H28" s="2">
-        <v>21.241600641861396</v>
+        <v>21.226249561337536</v>
       </c>
       <c r="I28" s="2">
-        <v>21.846180615973545</v>
+        <v>21.821186293268386</v>
       </c>
       <c r="J28" s="2">
-        <v>22.522725565321927</v>
+        <v>22.488361615858253</v>
       </c>
     </row>
     <row r="29">
@@ -2189,16 +2189,16 @@
         <v>252</v>
       </c>
       <c r="G29" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H29" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I29" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="J29" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30">
@@ -2251,22 +2251,22 @@
         <v>0.06086956521739131</v>
       </c>
       <c r="E31" s="2">
-        <v>0.06229166666666666</v>
+        <v>0.06225000000000001</v>
       </c>
       <c r="F31" s="2">
-        <v>0.06333333333333334</v>
+        <v>0.06329365079365079</v>
       </c>
       <c r="G31" s="2">
-        <v>0.06462121212121212</v>
+        <v>0.0647148288973384</v>
       </c>
       <c r="H31" s="2">
-        <v>0.0658695652173913</v>
+        <v>0.06648351648351648</v>
       </c>
       <c r="I31" s="2">
-        <v>0.0696875</v>
+        <v>0.06985915492957746</v>
       </c>
       <c r="J31" s="2">
-        <v>0.07386666666666666</v>
+        <v>0.07352542372881356</v>
       </c>
     </row>
     <row r="32">
@@ -2287,22 +2287,22 @@
         <v>1.9901321235802572</v>
       </c>
       <c r="E32" s="2">
-        <v>2.336309523809521</v>
+        <v>2.267857142857155</v>
       </c>
       <c r="F32" s="2">
-        <v>1.6722408026756064</v>
+        <v>1.6765474596799779</v>
       </c>
       <c r="G32" s="2">
-        <v>2.0334928229664984</v>
+        <v>2.2453723017509475</v>
       </c>
       <c r="H32" s="2">
-        <v>1.9318008053417657</v>
+        <v>2.733048385222303</v>
       </c>
       <c r="I32" s="2">
-        <v>5.796204620462042</v>
+        <v>5.077406588290079</v>
       </c>
       <c r="J32" s="2">
-        <v>5.997010463378172</v>
+        <v>5.24808638600327</v>
       </c>
     </row>
     <row r="33">
@@ -2391,22 +2391,22 @@
         <v>0.12808510638297874</v>
       </c>
       <c r="E35" s="2">
-        <v>0.12942857142857145</v>
+        <v>0.12946938775510206</v>
       </c>
       <c r="F35" s="2">
-        <v>0.1299221789883268</v>
+        <v>0.12992217898832692</v>
       </c>
       <c r="G35" s="2">
-        <v>0.13063197026022297</v>
+        <v>0.13111940298507463</v>
       </c>
       <c r="H35" s="2">
-        <v>0.1507473309608541</v>
+        <v>0.15230215827338123</v>
       </c>
       <c r="I35" s="2">
-        <v>0.17139931740614328</v>
+        <v>0.1736332179930795</v>
       </c>
       <c r="J35" s="2">
-        <v>0.19659016393442638</v>
+        <v>0.1996666666666668</v>
       </c>
     </row>
     <row r="36">
@@ -2425,22 +2425,22 @@
         <v>15.100000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>15.730000000000008</v>
+        <v>15.750000000000004</v>
       </c>
       <c r="F36" s="4">
-        <v>16.36999999999999</v>
+        <v>16.380000000000017</v>
       </c>
       <c r="G36" s="4">
-        <v>16.969999999999985</v>
+        <v>17.010000000000005</v>
       </c>
       <c r="H36" s="4">
-        <v>23.030000000000005</v>
+        <v>23.03999999999999</v>
       </c>
       <c r="I36" s="4">
-        <v>28.959999999999983</v>
+        <v>29.14999999999998</v>
       </c>
       <c r="J36" s="4">
-        <v>36.560000000000045</v>
+        <v>36.97000000000004</v>
       </c>
     </row>
     <row r="37">
@@ -2459,22 +2459,22 @@
         <v>10.066666666666668</v>
       </c>
       <c r="E37" s="2">
-        <v>10.000000000000005</v>
+        <v>10.012078062424514</v>
       </c>
       <c r="F37" s="2">
-        <v>9.923016305995024</v>
+        <v>9.928476178930788</v>
       </c>
       <c r="G37" s="2">
-        <v>9.808681579099465</v>
+        <v>9.830665202566031</v>
       </c>
       <c r="H37" s="2">
-        <v>11.548490622806138</v>
+        <v>11.550609114152497</v>
       </c>
       <c r="I37" s="2">
-        <v>12.597877153297365</v>
+        <v>12.676117585667065</v>
       </c>
       <c r="J37" s="2">
-        <v>13.733002779655939</v>
+        <v>13.879711668418695</v>
       </c>
     </row>
     <row r="38">
@@ -2495,22 +2495,22 @@
         <v>3.1420765027322606</v>
       </c>
       <c r="E38" s="2">
-        <v>4.172185430463626</v>
+        <v>4.304635761589415</v>
       </c>
       <c r="F38" s="2">
-        <v>4.068658614113052</v>
+        <v>4.000000000000092</v>
       </c>
       <c r="G38" s="2">
-        <v>3.665241295051902</v>
+        <v>3.846153846153766</v>
       </c>
       <c r="H38" s="2">
-        <v>35.71007660577506</v>
+        <v>35.44973544973533</v>
       </c>
       <c r="I38" s="2">
-        <v>25.749023013460604</v>
+        <v>26.51909722222221</v>
       </c>
       <c r="J38" s="2">
-        <v>26.24309392265216</v>
+        <v>26.826758147513097</v>
       </c>
     </row>
   </sheetData>
@@ -2663,22 +2663,22 @@
         <v>80</v>
       </c>
       <c r="E3" s="4">
-        <v>84.32</v>
+        <v>84.33</v>
       </c>
       <c r="F3" s="4">
-        <v>88.88</v>
+        <v>88.89</v>
       </c>
       <c r="G3" s="4">
-        <v>93.68</v>
+        <v>93.7</v>
       </c>
       <c r="H3" s="4">
-        <v>114.29</v>
+        <v>114.34</v>
       </c>
       <c r="I3" s="4">
-        <v>139.43</v>
+        <v>139.51</v>
       </c>
       <c r="J3" s="4">
-        <v>170.11</v>
+        <v>170.24</v>
       </c>
     </row>
     <row r="4">
@@ -2699,22 +2699,22 @@
         <v>5.263157894736836</v>
       </c>
       <c r="E4" s="2">
-        <v>5.399999999999983</v>
+        <v>5.412499999999998</v>
       </c>
       <c r="F4" s="2">
-        <v>5.407969639468702</v>
+        <v>5.407328352899321</v>
       </c>
       <c r="G4" s="2">
-        <v>5.400540054005409</v>
+        <v>5.41118236022049</v>
       </c>
       <c r="H4" s="2">
-        <v>22.000426985482502</v>
+        <v>22.027748132337255</v>
       </c>
       <c r="I4" s="2">
-        <v>21.996675124682817</v>
+        <v>22.01329368549938</v>
       </c>
       <c r="J4" s="2">
-        <v>22.00387291113821</v>
+        <v>22.027094831911697</v>
       </c>
     </row>
     <row r="5">
@@ -2733,22 +2733,22 @@
         <v>53.333333333333336</v>
       </c>
       <c r="E5" s="2">
-        <v>53.60457724094086</v>
+        <v>53.60752653995296</v>
       </c>
       <c r="F5" s="2">
-        <v>53.87646238710069</v>
+        <v>53.87925809188992</v>
       </c>
       <c r="G5" s="2">
-        <v>54.14715912375008</v>
+        <v>54.1524591111368</v>
       </c>
       <c r="H5" s="2">
-        <v>57.31120248721292</v>
+        <v>57.321903043064125</v>
       </c>
       <c r="I5" s="2">
-        <v>60.653384374456245</v>
+        <v>60.66707253435381</v>
       </c>
       <c r="J5" s="2">
-        <v>63.89827961836075</v>
+        <v>63.91350052560445</v>
       </c>
     </row>
     <row r="6">
@@ -2767,7 +2767,7 @@
         <v>25.6</v>
       </c>
       <c r="E6" s="4">
-        <v>26.97999999999999</v>
+        <v>26.989999999999995</v>
       </c>
       <c r="F6" s="4">
         <v>28.439999999999998</v>
@@ -2776,13 +2776,13 @@
         <v>29.980000000000004</v>
       </c>
       <c r="H6" s="4">
-        <v>37.17</v>
+        <v>37.16</v>
       </c>
       <c r="I6" s="4">
-        <v>46.06</v>
+        <v>46.02999999999999</v>
       </c>
       <c r="J6" s="4">
-        <v>57.09000000000002</v>
+        <v>57.02000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2801,22 +2801,22 @@
         <v>32</v>
       </c>
       <c r="E7" s="2">
-        <v>31.997153700189745</v>
+        <v>32.005217597533495</v>
       </c>
       <c r="F7" s="2">
-        <v>31.998199819982</v>
+        <v>31.994600067499153</v>
       </c>
       <c r="G7" s="2">
-        <v>32.00256191289496</v>
+        <v>31.995731056563503</v>
       </c>
       <c r="H7" s="2">
-        <v>32.522530405109805</v>
+        <v>32.49956270771383</v>
       </c>
       <c r="I7" s="2">
-        <v>33.034497597360684</v>
+        <v>32.99405060569134</v>
       </c>
       <c r="J7" s="2">
-        <v>33.56063723473048</v>
+        <v>33.49389097744361</v>
       </c>
     </row>
     <row r="8">
@@ -2835,22 +2835,22 @@
         <v>7.300000000000004</v>
       </c>
       <c r="E8" s="4">
-        <v>7.069999999999986</v>
+        <v>7.079999999999991</v>
       </c>
       <c r="F8" s="4">
         <v>6.859999999999996</v>
       </c>
       <c r="G8" s="4">
-        <v>6.630000000000006</v>
+        <v>6.640000000000004</v>
       </c>
       <c r="H8" s="4">
-        <v>11.260000000000002</v>
+        <v>11.239999999999997</v>
       </c>
       <c r="I8" s="4">
-        <v>16.54</v>
+        <v>16.689999999999984</v>
       </c>
       <c r="J8" s="4">
-        <v>23.420000000000023</v>
+        <v>23.760000000000012</v>
       </c>
     </row>
     <row r="9">
@@ -2869,22 +2869,22 @@
         <v>9.125000000000005</v>
       </c>
       <c r="E9" s="2">
-        <v>8.384724857684994</v>
+        <v>8.395588758448941</v>
       </c>
       <c r="F9" s="2">
-        <v>7.718271827182714</v>
+        <v>7.717403532455839</v>
       </c>
       <c r="G9" s="2">
-        <v>7.077284372331347</v>
+        <v>7.086446104589118</v>
       </c>
       <c r="H9" s="2">
-        <v>9.85213054510456</v>
+        <v>9.830330592968336</v>
       </c>
       <c r="I9" s="2">
-        <v>11.862583375170335</v>
+        <v>11.963300121855053</v>
       </c>
       <c r="J9" s="2">
-        <v>13.767562165657528</v>
+        <v>13.95676691729324</v>
       </c>
     </row>
     <row r="10">
@@ -2909,16 +2909,16 @@
         <v>6.94</v>
       </c>
       <c r="G10" s="2">
-        <v>7.47</v>
+        <v>7.46</v>
       </c>
       <c r="H10" s="2">
         <v>7.9</v>
       </c>
       <c r="I10" s="2">
-        <v>9.04</v>
+        <v>8.85</v>
       </c>
       <c r="J10" s="2">
-        <v>10.33</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="11">
@@ -3005,7 +3005,7 @@
         <v>15.700000000000005</v>
       </c>
       <c r="E13" s="4">
-        <v>16.709999999999987</v>
+        <v>16.71999999999999</v>
       </c>
       <c r="F13" s="4">
         <v>17.769999999999996</v>
@@ -3014,13 +3014,13 @@
         <v>18.870000000000005</v>
       </c>
       <c r="H13" s="4">
-        <v>23.960000000000004</v>
+        <v>23.939999999999998</v>
       </c>
       <c r="I13" s="4">
-        <v>30.4</v>
+        <v>30.359999999999985</v>
       </c>
       <c r="J13" s="4">
-        <v>38.600000000000016</v>
+        <v>38.53000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -3041,22 +3041,22 @@
         <v>5.2984574111334615</v>
       </c>
       <c r="E14" s="2">
-        <v>6.433121019108157</v>
+        <v>6.496815286624114</v>
       </c>
       <c r="F14" s="2">
-        <v>6.3435068821065865</v>
+        <v>6.279904306220119</v>
       </c>
       <c r="G14" s="2">
         <v>6.190208216094595</v>
       </c>
       <c r="H14" s="2">
-        <v>26.974032856385797</v>
+        <v>26.868044515103296</v>
       </c>
       <c r="I14" s="2">
-        <v>26.878130217028364</v>
+        <v>26.81704260651625</v>
       </c>
       <c r="J14" s="2">
-        <v>26.973684210526372</v>
+        <v>26.910408432147648</v>
       </c>
     </row>
     <row r="15">
@@ -3084,13 +3084,13 @@
         <v>117</v>
       </c>
       <c r="H15" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I15" s="2">
+        <v>124</v>
+      </c>
+      <c r="J15" s="2">
         <v>127</v>
-      </c>
-      <c r="J15" s="2">
-        <v>132</v>
       </c>
     </row>
     <row r="16">
@@ -3149,16 +3149,16 @@
         <v>0.06252252252252252</v>
       </c>
       <c r="G17" s="2">
-        <v>0.06384615384615384</v>
+        <v>0.06376068376068376</v>
       </c>
       <c r="H17" s="2">
-        <v>0.06475409836065574</v>
+        <v>0.06583333333333334</v>
       </c>
       <c r="I17" s="2">
-        <v>0.07118110236220472</v>
+        <v>0.07137096774193548</v>
       </c>
       <c r="J17" s="2">
-        <v>0.07825757575757576</v>
+        <v>0.07811023622047245</v>
       </c>
     </row>
     <row r="18">
@@ -3185,16 +3185,16 @@
         <v>1.780850618059926</v>
       </c>
       <c r="G18" s="2">
-        <v>2.1170472179117716</v>
+        <v>1.9803443434567525</v>
       </c>
       <c r="H18" s="2">
-        <v>1.4220817697017551</v>
+        <v>3.250670241286868</v>
       </c>
       <c r="I18" s="2">
-        <v>9.925246685936395</v>
+        <v>8.411596570028568</v>
       </c>
       <c r="J18" s="2">
-        <v>9.941505765620828</v>
+        <v>9.442590862582879</v>
       </c>
     </row>
     <row r="19">
@@ -3283,7 +3283,7 @@
         <v>0.15392156862745102</v>
       </c>
       <c r="E21" s="2">
-        <v>0.1561682242990653</v>
+        <v>0.15626168224299058</v>
       </c>
       <c r="F21" s="2">
         <v>0.15725663716814156</v>
@@ -3292,13 +3292,13 @@
         <v>0.1585714285714286</v>
       </c>
       <c r="H21" s="2">
-        <v>0.19322580645161294</v>
+        <v>0.1962295081967213</v>
       </c>
       <c r="I21" s="2">
-        <v>0.23565891472868217</v>
+        <v>0.24095238095238083</v>
       </c>
       <c r="J21" s="2">
-        <v>0.28805970149253746</v>
+        <v>0.29868217054263574</v>
       </c>
     </row>
     <row r="22">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.87 % / 補助 5.4 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 4.87 % / 補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -3621,22 +3621,22 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.87 % / 補助 5.4 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.27 % / 補助 22 % / 他 7.31 %</t>
+          <t xml:space="preserve">全社 15.28 % / 補助 22.03 % / 他 7.31 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.27 % / 補助 22 % / 他 6.25 %</t>
+          <t xml:space="preserve">全社 15.29 % / 補助 22.01 % / 他 6.25 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.81 % / 補助 22 % / 他 6.26 %</t>
+          <t xml:space="preserve">全社 15.83 % / 補助 22.03 % / 他 6.27 %</t>
         </is>
       </c>
     </row>
@@ -3673,32 +3673,32 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 67.99 % / 他 68 %</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68.01 % / 他 68 %</t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68.01 %</t>
+          <t xml:space="preserve">全社 68.01 % / 補助 68 % / 他 68.01 %</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.35 % / 補助 67.48 % / 他 67.17 %</t>
+          <t xml:space="preserve">全社 67.36 % / 補助 67.5 % / 他 67.17 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.98 % / 補助 66.97 % / 他 67.01 %</t>
+          <t xml:space="preserve">全社 67.01 % / 補助 67.01 % / 他 67.01 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.58 % / 補助 66.44 % / 他 66.84 %</t>
+          <t xml:space="preserve">全社 66.62 % / 補助 66.51 % / 他 66.83 %</t>
         </is>
       </c>
     </row>
@@ -3735,32 +3735,32 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32.01 % / 他 32 %</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 31.99 % / 他 32 %</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 31.99 %</t>
+          <t xml:space="preserve">全社 31.99 % / 補助 32 % / 他 31.99 %</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.65 % / 補助 32.52 % / 他 32.83 %</t>
+          <t xml:space="preserve">全社 32.64 % / 補助 32.5 % / 他 32.83 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.02 % / 補助 33.03 % / 他 32.99 %</t>
+          <t xml:space="preserve">全社 32.99 % / 補助 32.99 % / 他 32.99 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.42 % / 補助 33.56 % / 他 33.16 %</t>
+          <t xml:space="preserve">全社 33.38 % / 補助 33.49 % / 他 33.17 %</t>
         </is>
       </c>
     </row>
@@ -3797,32 +3797,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.71 % / 補助 23.61 % / 他 25.98 %</t>
+          <t xml:space="preserve">全社 24.7 % / 補助 23.61 % / 他 25.97 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.13 % / 補助 24.28 % / 他 26.11 %</t>
+          <t xml:space="preserve">全社 25.12 % / 補助 24.28 % / 他 26.1 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.54 % / 補助 24.93 % / 他 26.27 %</t>
+          <t xml:space="preserve">全社 25.52 % / 補助 24.91 % / 他 26.23 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.01 % / 補助 22.67 % / 他 25.82 %</t>
+          <t xml:space="preserve">全社 24 % / 補助 22.67 % / 他 25.78 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.94 % / 補助 21.17 % / 他 25.67 %</t>
+          <t xml:space="preserve">全社 22.84 % / 補助 21.03 % / 他 25.63 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.86 % / 補助 19.79 % / 他 25.52 %</t>
+          <t xml:space="preserve">全社 21.67 % / 補助 19.54 % / 他 25.46 %</t>
         </is>
       </c>
     </row>
@@ -3859,32 +3859,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.29 % / 補助 8.38 % / 他 6.02 %</t>
+          <t xml:space="preserve">全社 7.3 % / 補助 8.4 % / 他 6.03 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.87 % / 補助 7.72 % / 他 5.89 %</t>
+          <t xml:space="preserve">全社 6.88 % / 補助 7.72 % / 他 5.9 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.46 % / 補助 7.08 % / 他 5.72 %</t>
+          <t xml:space="preserve">全社 6.48 % / 補助 7.09 % / 他 5.76 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.64 % / 補助 9.85 % / 他 7.01 %</t>
+          <t xml:space="preserve">全社 8.64 % / 補助 9.83 % / 他 7.05 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.07 % / 補助 11.86 % / 他 7.32 %</t>
+          <t xml:space="preserve">全社 10.15 % / 補助 11.96 % / 他 7.36 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.55 % / 補助 13.77 % / 他 7.64 %</t>
+          <t xml:space="preserve">全社 11.7 % / 補助 13.96 % / 他 7.71 %</t>
         </is>
       </c>
     </row>
@@ -3921,32 +3921,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10 % / 補助 11.67 % / 他 8.07 %</t>
+          <t xml:space="preserve">全社 10.01 % / 補助 11.68 % / 他 8.08 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.92 % / 補助 11.69 % / 他 7.86 %</t>
+          <t xml:space="preserve">全社 9.93 % / 補助 11.69 % / 他 7.87 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.81 % / 補助 11.67 % / 他 7.61 %</t>
+          <t xml:space="preserve">全社 9.83 % / 補助 11.68 % / 他 7.65 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.55 % / 補助 13.61 % / 他 8.77 %</t>
+          <t xml:space="preserve">全社 11.55 % / 補助 13.59 % / 他 8.81 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.6 % / 補助 14.95 % / 他 8.98 %</t>
+          <t xml:space="preserve">全社 12.68 % / 補助 15.05 % / 他 9.02 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.73 % / 補助 16.3 % / 他 9.2 %</t>
+          <t xml:space="preserve">全社 13.88 % / 補助 16.48 % / 他 9.27 %</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.63 % / 補助 12 % / 他 11.15 %</t>
+          <t xml:space="preserve">全社 11.64 % / 補助 12 % / 他 11.15 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.93 % / 補助 11 % / 他 10.82 %</t>
+          <t xml:space="preserve">全社 10.93 % / 補助 10.99 % / 他 10.82 %</t>
         </is>
       </c>
     </row>
@@ -4107,32 +4107,32 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.5 % / 補助 7.65 % / 他 11.65 %</t>
+          <t xml:space="preserve">全社 9.5 % / 補助 7.65 % / 他 11.63 %</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.67 % / 補助 7.81 % / 他 11.85 %</t>
+          <t xml:space="preserve">全社 9.67 % / 補助 7.81 % / 他 11.84 %</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.86 % / 補助 7.97 % / 他 12.09 %</t>
+          <t xml:space="preserve">全社 9.84 % / 補助 7.96 % / 他 12.05 %</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.12 % / 補助 6.91 % / 他 12.08 %</t>
+          <t xml:space="preserve">全社 9.1 % / 補助 6.91 % / 他 12.04 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.73 % / 補助 6.48 % / 他 12.19 %</t>
+          <t xml:space="preserve">全社 8.63 % / 補助 6.34 % / 他 12.15 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.32 % / 補助 6.07 % / 他 12.31 %</t>
+          <t xml:space="preserve">全社 8.14 % / 補助 5.83 % / 他 12.25 %</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.64 % / 補助 0.5 % / 他 0.81 %</t>
+          <t xml:space="preserve">全社 0.64 % / 補助 0.49 % / 他 0.81 %</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.16 % / 補助 8.15 % / 他 12.48 %</t>
+          <t xml:space="preserve">全社 10.15 % / 補助 8.15 % / 他 12.47 %</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.32 % / 補助 8.3 % / 他 12.67 %</t>
+          <t xml:space="preserve">全社 10.31 % / 補助 8.3 % / 他 12.66 %</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.5 % / 補助 8.48 % / 他 12.9 %</t>
+          <t xml:space="preserve">全社 10.48 % / 補助 8.46 % / 他 12.86 %</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.69 % / 補助 7.35 % / 他 12.84 %</t>
+          <t xml:space="preserve">全社 9.68 % / 補助 7.35 % / 他 12.8 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.25 % / 補助 6.86 % / 他 12.94 %</t>
+          <t xml:space="preserve">全社 9.15 % / 補助 6.72 % / 他 12.89 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.79 % / 補助 6.4 % / 他 13.03 %</t>
+          <t xml:space="preserve">全社 8.61 % / 補助 6.15 % / 他 12.96 %</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.066 億円/人 / 補助 0.065 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">全社 0.066 億円/人 / 補助 0.066 億円/人 / 他 0.067 億円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
@@ -4417,32 +4417,32 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.34 % / 補助 2.38 % / 他 2.31 %</t>
+          <t xml:space="preserve">全社 2.27 % / 補助 2.38 % / 他 2.19 %</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.67 % / 補助 1.78 % / 他 1.6 %</t>
+          <t xml:space="preserve">全社 1.68 % / 補助 1.78 % / 他 1.61 %</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.03 % / 補助 2.12 % / 他 1.98 %</t>
+          <t xml:space="preserve">全社 2.25 % / 補助 1.98 % / 他 2.47 %</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.93 % / 補助 1.42 % / 他 2.32 %</t>
+          <t xml:space="preserve">全社 2.73 % / 補助 3.25 % / 他 2.31 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.8 % / 補助 9.93 % / 他 2.63 %</t>
+          <t xml:space="preserve">全社 5.08 % / 補助 8.41 % / 他 2.53 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6 % / 補助 9.94 % / 他 2.78 %</t>
+          <t xml:space="preserve">全社 5.25 % / 補助 9.44 % / 他 2 %</t>
         </is>
       </c>
     </row>
@@ -4479,32 +4479,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.39 % / 補助 41.11 % / 他 60.73 %</t>
+          <t xml:space="preserve">全社 50.35 % / 補助 41.09 % / 他 60.67 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.97 % / 補助 41.53 % / 他 61.72 %</t>
+          <t xml:space="preserve">全社 50.94 % / 補助 41.53 % / 他 61.65 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.71 % / 補助 42.08 % / 他 62.88 %</t>
+          <t xml:space="preserve">全社 51.59 % / 補助 42.02 % / 他 62.69 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.63 % / 補助 35.06 % / 他 59.4 %</t>
+          <t xml:space="preserve">全社 45.58 % / 補助 35.09 % / 他 59.24 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.33 % / 補助 31.45 % / 他 59.03 %</t>
+          <t xml:space="preserve">全社 41.91 % / 補助 30.86 % / 他 58.83 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 39.03 % / 補助 28.19 % / 他 58.61 %</t>
+          <t xml:space="preserve">全社 38.28 % / 補助 27.17 % / 他 58.31 %</t>
         </is>
       </c>
     </row>
@@ -4613,22 +4613,22 @@
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.801 億円/人 / 他 0.54 億円/人</t>
+          <t xml:space="preserve">全社 0.658 億円/人 / 補助 0.801 億円/人 / 他 0.543 億円/人</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.723 億円/人 / 補助 0.937 億円/人 / 他 0.553 億円/人</t>
+          <t xml:space="preserve">全社 0.731 億円/人 / 補助 0.953 億円/人 / 他 0.556 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.798 億円/人 / 補助 1.098 億円/人 / 他 0.562 億円/人</t>
+          <t xml:space="preserve">全社 0.81 億円/人 / 補助 1.125 億円/人 / 他 0.565 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.887 億円/人 / 補助 1.289 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">全社 0.903 億円/人 / 補助 1.34 億円/人 / 他 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -4675,22 +4675,22 @@
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.042 億円/人 / 補助 0.057 億円/人 / 他 0.031 億円/人</t>
+          <t xml:space="preserve">全社 0.043 億円/人 / 補助 0.057 億円/人 / 他 0.031 億円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.062 億円/人 / 補助 0.092 億円/人 / 他 0.039 億円/人</t>
+          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.094 億円/人 / 他 0.039 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.08 億円/人 / 補助 0.13 億円/人 / 他 0.041 億円/人</t>
+          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.135 億円/人 / 他 0.042 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.103 億円/人 / 補助 0.177 億円/人 / 他 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.106 億円/人 / 補助 0.187 億円/人 / 他 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -4737,22 +4737,22 @@
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.131 億円/人 / 補助 0.159 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.131 億円/人 / 補助 0.159 億円/人 / 他 0.109 億円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.151 億円/人 / 補助 0.193 億円/人 / 他 0.117 億円/人</t>
+          <t xml:space="preserve">全社 0.152 億円/人 / 補助 0.196 億円/人 / 他 0.118 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.171 億円/人 / 補助 0.236 億円/人 / 他 0.121 億円/人</t>
+          <t xml:space="preserve">全社 0.174 億円/人 / 補助 0.241 億円/人 / 他 0.122 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.197 億円/人 / 補助 0.288 億円/人 / 他 0.125 億円/人</t>
+          <t xml:space="preserve">全社 0.2 億円/人 / 補助 0.299 億円/人 / 他 0.125 億円/人</t>
         </is>
       </c>
     </row>
@@ -4799,22 +4799,22 @@
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.76 % / 補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 4.37 % / 補助 5.41 % / 他 3.55 %</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.55 % / 補助 4.27 % / 他 4.76 %</t>
+          <t xml:space="preserve">全社 3.8 % / 補助 2.56 % / 他 4.79 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.35 % / 補助 4.1 % / 他 4.55 %</t>
+          <t xml:space="preserve">全社 4.03 % / 補助 3.33 % / 他 4.58 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.17 % / 補助 3.94 % / 他 4.35 %</t>
+          <t xml:space="preserve">全社 3.87 % / 補助 2.42 % / 他 5 %</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.52 pt / 補助 0.4 pt / 他 0.41 pt</t>
+          <t xml:space="preserve">全社 0.53 pt / 補助 0.41 pt / 他 0.41 pt</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -4861,22 +4861,22 @@
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.11 pt / 補助 -0 pt / 他 0 pt</t>
+          <t xml:space="preserve">全社 0.51 pt / 補助 0.01 pt / 他 0.71 pt</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.72 pt / 補助 17.73 pt / 他 2.55 pt</t>
+          <t xml:space="preserve">全社 11.48 pt / 補助 19.46 pt / 他 2.52 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.93 pt / 補助 17.9 pt / 他 1.7 pt</t>
+          <t xml:space="preserve">全社 11.26 pt / 補助 18.68 pt / 他 1.67 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.64 pt / 補助 18.07 pt / 他 1.91 pt</t>
+          <t xml:space="preserve">全社 11.96 pt / 補助 19.61 pt / 他 1.27 pt</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.71 % / 補助 3.29 % / 他 2.06 %</t>
+          <t xml:space="preserve">全社 2.71 % / 補助 3.28 % / 他 2.06 %</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -5161,32 +5161,32 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.68 倍 / 補助 3.55 倍 / 他 3.93 倍</t>
+          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / 他 3.93 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.25 倍 / 補助 2.94 倍 / 他 3.99 倍</t>
+          <t xml:space="preserve">全社 3.26 倍 / 補助 2.94 倍 / 他 3.99 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.93 倍 / 補助 2.54 倍 / 他 4.03 倍</t>
+          <t xml:space="preserve">全社 2.93 倍 / 補助 2.54 倍 / 他 4.05 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.97 倍 / 補助 3.62 倍 / 他 4.98 倍</t>
+          <t xml:space="preserve">全社 3.97 倍 / 補助 3.61 倍 / 他 5 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.99 倍 / 補助 4.85 倍 / 他 5.41 倍</t>
+          <t xml:space="preserve">全社 5.03 倍 / 補助 4.88 倍 / 他 5.44 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.3 倍 / 補助 6.45 倍 / 他 5.89 倍</t>
+          <t xml:space="preserve">全社 6.37 倍 / 補助 6.53 倍 / 他 5.94 倍</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 53.6 %</t>
+          <t xml:space="preserve">構成比 53.61 %</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -5362,17 +5362,17 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 57.31 %</t>
+          <t xml:space="preserve">構成比 57.32 %</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 60.65 %</t>
+          <t xml:space="preserve">構成比 60.67 %</t>
         </is>
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 63.9 %</t>
+          <t xml:space="preserve">構成比 63.91 %</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.4 % / 他 4.26 %</t>
+          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -5419,22 +5419,22 @@
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.4 % / 他 4.26 %</t>
+          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22 % / 他 7.31 %</t>
+          <t xml:space="preserve">補助 22.03 % / 他 7.31 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22 % / 他 6.25 %</t>
+          <t xml:space="preserve">補助 22.01 % / 他 6.25 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22 % / 他 6.26 %</t>
+          <t xml:space="preserve">補助 22.03 % / 他 6.27 %</t>
         </is>
       </c>
     </row>
@@ -5471,32 +5471,32 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">差 -0.01 pt</t>
+        </is>
+      </c>
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">差 0.01 pt</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">差 -0 pt</t>
         </is>
       </c>
-      <c r="H34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">差 0 pt</t>
-        </is>
-      </c>
-      <c r="I34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">差 -0.01 pt</t>
-        </is>
-      </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 0.31 pt</t>
+          <t xml:space="preserve">差 0.33 pt</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0.04 pt</t>
+          <t xml:space="preserve">差 -0 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0.4 pt</t>
+          <t xml:space="preserve">差 -0.33 pt</t>
         </is>
       </c>
     </row>
@@ -5538,27 +5538,27 @@
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.83 pt</t>
+          <t xml:space="preserve">差 1.82 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.35 pt</t>
+          <t xml:space="preserve">差 1.33 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.84 pt</t>
+          <t xml:space="preserve">差 2.78 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.54 pt</t>
+          <t xml:space="preserve">差 4.6 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.13 pt</t>
+          <t xml:space="preserve">差 6.25 pt</t>
         </is>
       </c>
     </row>
@@ -5605,22 +5605,22 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.801 億円/人 / 他 0.54 億円/人</t>
+          <t xml:space="preserve">補助 0.801 億円/人 / 他 0.543 億円/人</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.937 億円/人 / 他 0.553 億円/人</t>
+          <t xml:space="preserve">補助 0.953 億円/人 / 他 0.556 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.098 億円/人 / 他 0.562 億円/人</t>
+          <t xml:space="preserve">補助 1.125 億円/人 / 他 0.565 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.289 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">補助 1.34 億円/人 / 他 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.065 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">補助 0.066 億円/人 / 他 0.067 億円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
@@ -5719,32 +5719,32 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 164.29 %</t>
+          <t xml:space="preserve">寄与率 183.33 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 175 %</t>
+          <t xml:space="preserve">寄与率 169.23 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 135.29 %</t>
+          <t xml:space="preserve">寄与率 157.14 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 76.4 %</t>
+          <t xml:space="preserve">寄与率 76.29 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 89.04 %</t>
+          <t xml:space="preserve">寄与率 89.2 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.53 %</t>
+          <t xml:space="preserve">寄与率 90.41 %</t>
         </is>
       </c>
     </row>
@@ -9855,7 +9855,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjoyLCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjEzNi44NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjE4Ljc4LCJtYXgiOjMzLjQzLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6Mi44NSwibWF4IjozLjc0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1LjEzLCIyMDI5OnByb2plY3Q6Ny04Ijo3Ljl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wODQ5OTk5OTk5OTk5OTk5OSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMTM1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDg5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4xMTkyODU3MTQyODU3MTQyNywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyLjQsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjIsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwMzY4MDU1NTU1NTU1NCwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAxOTgxNjI4NzE3ODg3NywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQ0NDg1MzYzMDY3NTMyNzQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDYwOTMzNzAyNzg5ODA0LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjYwNzMxNjU4MzkyMjQ5LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODA5MDU5NTA0NjA1NjYzLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDE0OTM3NzcyNDkzMDY0NDYsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NDAxODU3MDcyNjUyNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTU1NTA0MjcyNTc5NzcyODQsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4xLCJvdGhlclBheUdyb3d0aCI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTg3MjM3NjkyMTM2MzM4LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTMyNjE2NDY1MTYzNjYsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgxOTIzMTY3OTU4MzQ5NiwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjoyLCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjEzNi44NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjE4Ljc4LCJtYXgiOjMzLjQzLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6Mi44NSwibWF4IjozLjc0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1LjEzLCIyMDI5OnByb2plY3Q6Ny04Ijo3Ljl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wODQ5OTk5OTk5OTk5OTk5OSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMTM1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDg5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4xMTkyODU3MTQyODU3MTQyNywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyLjQsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjIsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQxMDU5NTc2MDIzMzkxNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAxOTk4MjEzNTUxMTg3OTg3MywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwNjM5MDEyNDk3MjI5MzQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MTIwNDUxMzMzMTU3NjMsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA1NTE2MjczMDA1MjcsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4ODEzNjc1MDA5MTcxMTcsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYwOTM1Mzk0MzcxNzg1NSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyMDIyNDg3MjE2OTQ2NjczLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU2NTE3ODU5NDUyMTc5LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNDk5MDQ4MTM0MTI2NTU1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDg5MDA2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODg3NzYxNzEwMzMzMDMsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDI5MDQ1NDgyMzk3MjA1MDU1LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU3ODQ4MTQ3MzIzMDg2NjUsInByb2plY3RTZ2FSYXRlRW5kIjowLjEwOTkzMTgwOTE2NDg0ODI0LCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjcyNTg5ODcyMTI4MjMsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1Mzc3ODA1NzYyODcxNjMyLCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM319</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -1830,135 +1830,99 @@
         </is>
       </c>
       <c r="B20" s="4">
-        <v>11.000000000000007</v>
+        <v>10.73</v>
       </c>
       <c r="C20" s="4">
-        <v>11.299999999999997</v>
+        <v>11.01</v>
       </c>
       <c r="D20" s="4">
-        <v>11.600000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="E20" s="4">
-        <v>11.480000000000004</v>
+        <v>11.17</v>
       </c>
       <c r="F20" s="4">
-        <v>11.350000000000016</v>
+        <v>11.02</v>
       </c>
       <c r="G20" s="4">
-        <v>11.210000000000004</v>
+        <v>10.86</v>
       </c>
       <c r="H20" s="4">
-        <v>17.239999999999988</v>
+        <v>15.55</v>
       </c>
       <c r="I20" s="4">
-        <v>23.34999999999998</v>
+        <v>21.49</v>
       </c>
       <c r="J20" s="4">
-        <v>31.170000000000044</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-19 税引前当期純利益（モデル未対応）（億円）</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">2-19 税引前当期純利益（億円）</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>10.73</v>
+      </c>
+      <c r="C21" s="2">
+        <v>11.01</v>
+      </c>
+      <c r="D21" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>11.17</v>
+      </c>
+      <c r="F21" s="2">
+        <v>11.02</v>
+      </c>
+      <c r="G21" s="2">
+        <v>10.86</v>
+      </c>
+      <c r="H21" s="2">
+        <v>15.55</v>
+      </c>
+      <c r="I21" s="2">
+        <v>21.49</v>
+      </c>
+      <c r="J21" s="2">
+        <v>29.12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-20 当期純利益（モデル未対応）（億円）</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">2-20 当期純利益（億円）</t>
+        </is>
+      </c>
+      <c r="B22" s="2">
+        <v>7.51</v>
+      </c>
+      <c r="C22" s="2">
+        <v>7.71</v>
+      </c>
+      <c r="D22" s="2">
+        <v>7.91</v>
+      </c>
+      <c r="E22" s="2">
+        <v>7.82</v>
+      </c>
+      <c r="F22" s="2">
+        <v>7.71</v>
+      </c>
+      <c r="G22" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="H22" s="2">
+        <v>10.88</v>
+      </c>
+      <c r="I22" s="2">
+        <v>15.04</v>
+      </c>
+      <c r="J22" s="2">
+        <v>20.38</v>
       </c>
     </row>
     <row r="23">
@@ -6386,7 +6350,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C229"/>
+  <dimension ref="A1:C244"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -6521,11 +6485,11 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-3</t>
+          <t xml:space="preserve">actual:company:2023:2-18</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>92.75</v>
+        <v>10.73</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -6536,11 +6500,11 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-4</t>
+          <t xml:space="preserve">actual:company:2023:2-19</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>0.73</v>
+        <v>10.73</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -6551,11 +6515,11 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-7</t>
+          <t xml:space="preserve">actual:company:2023:2-20</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>32.65</v>
+        <v>7.51</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -6566,11 +6530,11 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2023:2-9</t>
+          <t xml:space="preserve">actual:company:2023:2-27</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0.82</v>
+        <v>210</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -6581,11 +6545,11 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-1</t>
+          <t xml:space="preserve">actual:company:2023:2-28</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>143.2</v>
+        <v>5</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6596,11 +6560,11 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-10</t>
+          <t xml:space="preserve">actual:company:2023:2-3</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>0.1</v>
+        <v>92.75</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -6611,11 +6575,11 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-12</t>
+          <t xml:space="preserve">actual:company:2023:2-4</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>12.47</v>
+        <v>0.73</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6626,11 +6590,11 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-13</t>
+          <t xml:space="preserve">actual:company:2023:2-7</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>0.66</v>
+        <v>32.65</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6641,11 +6605,11 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-14</t>
+          <t xml:space="preserve">actual:company:2023:2-9</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>2.58</v>
+        <v>0.82</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -6656,11 +6620,11 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-15</t>
+          <t xml:space="preserve">actual:company:2024:2-1</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>0.67</v>
+        <v>143.2</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -6671,11 +6635,11 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-3</t>
+          <t xml:space="preserve">actual:company:2024:2-10</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>97.38</v>
+        <v>0.1</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -6686,11 +6650,11 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-4</t>
+          <t xml:space="preserve">actual:company:2024:2-12</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>0.76</v>
+        <v>12.47</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6701,11 +6665,11 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-7</t>
+          <t xml:space="preserve">actual:company:2024:2-13</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>34.52</v>
+        <v>0.66</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -6716,11 +6680,11 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2024:2-9</t>
+          <t xml:space="preserve">actual:company:2024:2-14</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>0.86</v>
+        <v>2.58</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6731,11 +6695,11 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-1</t>
+          <t xml:space="preserve">actual:company:2024:2-15</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>150</v>
+        <v>0.67</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6746,11 +6710,11 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-10</t>
+          <t xml:space="preserve">actual:company:2024:2-18</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>0.1</v>
+        <v>11.01</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6761,11 +6725,11 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-12</t>
+          <t xml:space="preserve">actual:company:2024:2-19</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>13.3</v>
+        <v>11.01</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6776,11 +6740,11 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-13</t>
+          <t xml:space="preserve">actual:company:2024:2-20</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>0.7</v>
+        <v>7.71</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
@@ -6791,11 +6755,11 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-14</t>
+          <t xml:space="preserve">actual:company:2024:2-27</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>2.7</v>
+        <v>220</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6806,11 +6770,11 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-15</t>
+          <t xml:space="preserve">actual:company:2024:2-28</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
@@ -6821,11 +6785,11 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-3</t>
+          <t xml:space="preserve">actual:company:2024:2-3</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>102</v>
+        <v>97.38</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6836,11 +6800,11 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-4</t>
+          <t xml:space="preserve">actual:company:2024:2-4</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -6851,11 +6815,11 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-7</t>
+          <t xml:space="preserve">actual:company:2024:2-7</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>36.4</v>
+        <v>34.52</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -6866,11 +6830,11 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:company:2025:2-9</t>
+          <t xml:space="preserve">actual:company:2024:2-9</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -6881,11 +6845,11 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-1</t>
+          <t xml:space="preserve">actual:company:2025:2-1</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -6896,11 +6860,11 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-10</t>
+          <t xml:space="preserve">actual:company:2025:2-10</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
@@ -6911,11 +6875,11 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-13</t>
+          <t xml:space="preserve">actual:company:2025:2-12</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>90</v>
+        <v>13.3</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
@@ -6926,11 +6890,11 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-14</t>
+          <t xml:space="preserve">actual:company:2025:2-13</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -6941,11 +6905,11 @@
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-4</t>
+          <t xml:space="preserve">actual:company:2025:2-14</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>23.04</v>
+        <v>2.7</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
@@ -6956,11 +6920,11 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-6</t>
+          <t xml:space="preserve">actual:company:2025:2-15</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>6.78</v>
+        <v>0.7</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -6971,11 +6935,11 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-8</t>
+          <t xml:space="preserve">actual:company:2025:2-18</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>5.19</v>
+        <v>11.3</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -6986,11 +6950,11 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-9</t>
+          <t xml:space="preserve">actual:company:2025:2-19</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>0.36</v>
+        <v>11.3</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -7001,11 +6965,11 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-1</t>
+          <t xml:space="preserve">actual:company:2025:2-20</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>76</v>
+        <v>7.91</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
@@ -7016,11 +6980,11 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-10</t>
+          <t xml:space="preserve">actual:company:2025:2-27</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>1.9</v>
+        <v>230</v>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
@@ -7031,11 +6995,11 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-13</t>
+          <t xml:space="preserve">actual:company:2025:2-28</t>
         </is>
       </c>
       <c r="B43" s="2">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
@@ -7046,11 +7010,11 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-14</t>
+          <t xml:space="preserve">actual:company:2025:2-3</t>
         </is>
       </c>
       <c r="B44" s="2">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
@@ -7061,11 +7025,11 @@
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-4</t>
+          <t xml:space="preserve">actual:company:2025:2-4</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <v>24.32</v>
+        <v>0.8</v>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
@@ -7076,11 +7040,11 @@
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-6</t>
+          <t xml:space="preserve">actual:company:2025:2-7</t>
         </is>
       </c>
       <c r="B46" s="2">
-        <v>7.04</v>
+        <v>36.4</v>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
@@ -7091,11 +7055,11 @@
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-8</t>
+          <t xml:space="preserve">actual:company:2025:2-9</t>
         </is>
       </c>
       <c r="B47" s="2">
-        <v>5.59</v>
+        <v>0.9</v>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
@@ -7106,11 +7070,11 @@
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-9</t>
+          <t xml:space="preserve">actual:project:2023:7-1</t>
         </is>
       </c>
       <c r="B48" s="2">
-        <v>0.38</v>
+        <v>72</v>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
@@ -7121,11 +7085,11 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-1</t>
+          <t xml:space="preserve">actual:project:2023:7-10</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <v>80</v>
+        <v>1.8</v>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
@@ -7136,11 +7100,11 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-10</t>
+          <t xml:space="preserve">actual:project:2023:7-13</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
@@ -7151,11 +7115,11 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-13</t>
+          <t xml:space="preserve">actual:project:2023:7-14</t>
         </is>
       </c>
       <c r="B51" s="2">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
@@ -7166,11 +7130,11 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-14</t>
+          <t xml:space="preserve">actual:project:2023:7-4</t>
         </is>
       </c>
       <c r="B52" s="2">
-        <v>2</v>
+        <v>23.04</v>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
@@ -7181,11 +7145,11 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-4</t>
+          <t xml:space="preserve">actual:project:2023:7-6</t>
         </is>
       </c>
       <c r="B53" s="2">
-        <v>25.6</v>
+        <v>6.78</v>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
@@ -7196,11 +7160,11 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-6</t>
+          <t xml:space="preserve">actual:project:2023:7-8</t>
         </is>
       </c>
       <c r="B54" s="2">
-        <v>7.3</v>
+        <v>5.19</v>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
@@ -7211,11 +7175,11 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-8</t>
+          <t xml:space="preserve">actual:project:2023:7-9</t>
         </is>
       </c>
       <c r="B55" s="2">
-        <v>6</v>
+        <v>0.36</v>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
@@ -7226,11 +7190,11 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-9</t>
+          <t xml:space="preserve">actual:project:2024:7-1</t>
         </is>
       </c>
       <c r="B56" s="2">
-        <v>0.4</v>
+        <v>76</v>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
@@ -7241,11 +7205,11 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:assets</t>
+          <t xml:space="preserve">actual:project:2024:7-10</t>
         </is>
       </c>
       <c r="B57" s="2">
-        <v>132</v>
+        <v>1.9</v>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
@@ -7256,11 +7220,11 @@
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:buildings</t>
+          <t xml:space="preserve">actual:project:2024:7-13</t>
         </is>
       </c>
       <c r="B58" s="2">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
@@ -7271,11 +7235,11 @@
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capex</t>
+          <t xml:space="preserve">actual:project:2024:7-14</t>
         </is>
       </c>
       <c r="B59" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
@@ -7286,11 +7250,11 @@
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capital</t>
+          <t xml:space="preserve">actual:project:2024:7-4</t>
         </is>
       </c>
       <c r="B60" s="2">
-        <v>10</v>
+        <v>24.32</v>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
@@ -7301,11 +7265,11 @@
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:cash</t>
+          <t xml:space="preserve">actual:project:2024:7-6</t>
         </is>
       </c>
       <c r="B61" s="2">
-        <v>24</v>
+        <v>7.04</v>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
@@ -7316,11 +7280,11 @@
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
+          <t xml:space="preserve">actual:project:2024:7-8</t>
         </is>
       </c>
       <c r="B62" s="2">
-        <v>67</v>
+        <v>5.59</v>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
@@ -7331,11 +7295,11 @@
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
+          <t xml:space="preserve">actual:project:2024:7-9</t>
         </is>
       </c>
       <c r="B63" s="2">
-        <v>39</v>
+        <v>0.38</v>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
@@ -7346,11 +7310,11 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-1</t>
         </is>
       </c>
       <c r="B64" s="2">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
@@ -7361,11 +7325,11 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
+          <t xml:space="preserve">actual:project:2025:7-10</t>
         </is>
       </c>
       <c r="B65" s="2">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
@@ -7376,11 +7340,11 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-13</t>
         </is>
       </c>
       <c r="B66" s="2">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
@@ -7391,11 +7355,11 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:land</t>
+          <t xml:space="preserve">actual:project:2025:7-14</t>
         </is>
       </c>
       <c r="B67" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
@@ -7406,11 +7370,11 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
+          <t xml:space="preserve">actual:project:2025:7-4</t>
         </is>
       </c>
       <c r="B68" s="2">
-        <v>75</v>
+        <v>25.6</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
@@ -7421,11 +7385,11 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
+          <t xml:space="preserve">actual:project:2025:7-6</t>
         </is>
       </c>
       <c r="B69" s="2">
-        <v>29</v>
+        <v>7.3</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
@@ -7436,11 +7400,11 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:machinery</t>
+          <t xml:space="preserve">actual:project:2025:7-8</t>
         </is>
       </c>
       <c r="B70" s="2">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
@@ -7451,11 +7415,11 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
+          <t xml:space="preserve">actual:project:2025:7-9</t>
         </is>
       </c>
       <c r="B71" s="2">
-        <v>57</v>
+        <v>0.4</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
@@ -7466,11 +7430,11 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2023:assets</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
@@ -7481,11 +7445,11 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:buildings</t>
         </is>
       </c>
       <c r="B73" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
@@ -7496,7 +7460,7 @@
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:software</t>
+          <t xml:space="preserve">balance-sheet:2023:capex</t>
         </is>
       </c>
       <c r="B74" s="2">
@@ -7511,11 +7475,11 @@
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:capital</t>
         </is>
       </c>
       <c r="B75" s="2">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
@@ -7526,11 +7490,11 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:assets</t>
+          <t xml:space="preserve">balance-sheet:2023:cash</t>
         </is>
       </c>
       <c r="B76" s="2">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
@@ -7541,11 +7505,11 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:buildings</t>
+          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
         </is>
       </c>
       <c r="B77" s="2">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
@@ -7556,11 +7520,11 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capex</t>
+          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
@@ -7571,11 +7535,11 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capital</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
         </is>
       </c>
       <c r="B79" s="2">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
@@ -7586,11 +7550,11 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:cash</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
@@ -7601,11 +7565,11 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
@@ -7616,11 +7580,11 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:land</t>
         </is>
       </c>
       <c r="B82" s="2">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
@@ -7631,11 +7595,11 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
         </is>
       </c>
       <c r="B83" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
@@ -7646,11 +7610,11 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
@@ -7661,11 +7625,11 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:machinery</t>
         </is>
       </c>
       <c r="B85" s="2">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
@@ -7676,11 +7640,11 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:land</t>
+          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
         </is>
       </c>
       <c r="B86" s="2">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
@@ -7691,11 +7655,11 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
         </is>
       </c>
       <c r="B87" s="2">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
@@ -7706,11 +7670,11 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
         </is>
       </c>
       <c r="B88" s="2">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
@@ -7721,11 +7685,11 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:machinery</t>
+          <t xml:space="preserve">balance-sheet:2023:software</t>
         </is>
       </c>
       <c r="B89" s="2">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
@@ -7736,11 +7700,11 @@
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
         </is>
       </c>
       <c r="B90" s="2">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
@@ -7751,11 +7715,11 @@
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2024:assets</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
@@ -7766,11 +7730,11 @@
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:buildings</t>
         </is>
       </c>
       <c r="B92" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
@@ -7781,11 +7745,11 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:software</t>
+          <t xml:space="preserve">balance-sheet:2024:capex</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
@@ -7796,11 +7760,11 @@
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:capital</t>
         </is>
       </c>
       <c r="B94" s="2">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
@@ -7811,11 +7775,11 @@
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:assets</t>
+          <t xml:space="preserve">balance-sheet:2024:cash</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
@@ -7826,11 +7790,11 @@
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:buildings</t>
+          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
         </is>
       </c>
       <c r="B96" s="2">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
@@ -7841,11 +7805,11 @@
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capex</t>
+          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
@@ -7856,11 +7820,11 @@
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capital</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
@@ -7871,11 +7835,11 @@
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:cash</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
         </is>
       </c>
       <c r="B99" s="2">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
@@ -7886,11 +7850,11 @@
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
         </is>
       </c>
       <c r="B100" s="2">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
@@ -7901,11 +7865,11 @@
     <row r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:land</t>
         </is>
       </c>
       <c r="B101" s="2">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
@@ -7916,11 +7880,11 @@
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
         </is>
       </c>
       <c r="B102" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
@@ -7931,11 +7895,11 @@
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
         </is>
       </c>
       <c r="B103" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
@@ -7946,11 +7910,11 @@
     <row r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:machinery</t>
         </is>
       </c>
       <c r="B104" s="2">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
@@ -7961,11 +7925,11 @@
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:land</t>
+          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
@@ -7976,11 +7940,11 @@
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
         </is>
       </c>
       <c r="B106" s="2">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
@@ -7991,11 +7955,11 @@
     <row r="107">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
         </is>
       </c>
       <c r="B107" s="2">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
@@ -8006,11 +7970,11 @@
     <row r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:machinery</t>
+          <t xml:space="preserve">balance-sheet:2024:software</t>
         </is>
       </c>
       <c r="B108" s="2">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
@@ -8021,11 +7985,11 @@
     <row r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
         </is>
       </c>
       <c r="B109" s="2">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
@@ -8036,11 +8000,11 @@
     <row r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2025:assets</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>70</v>
+        <v>156</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
@@ -8051,11 +8015,11 @@
     <row r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:buildings</t>
         </is>
       </c>
       <c r="B111" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
@@ -8066,11 +8030,11 @@
     <row r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:software</t>
+          <t xml:space="preserve">balance-sheet:2025:capex</t>
         </is>
       </c>
       <c r="B112" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
@@ -8081,11 +8045,11 @@
     <row r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:capital</t>
         </is>
       </c>
       <c r="B113" s="2">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
@@ -8096,11 +8060,11 @@
     <row r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:0</t>
+          <t xml:space="preserve">balance-sheet:2025:cash</t>
         </is>
       </c>
       <c r="B114" s="2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
@@ -8111,11 +8075,11 @@
     <row r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:1</t>
+          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
         </is>
       </c>
       <c r="B115" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
@@ -8126,26 +8090,26 @@
     <row r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
         </is>
       </c>
       <c r="B116" s="2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
         </is>
       </c>
       <c r="B117" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
@@ -8156,11 +8120,11 @@
     <row r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
         </is>
       </c>
       <c r="B118" s="2">
-        <v>0.005</v>
+        <v>40</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
@@ -8171,11 +8135,11 @@
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
         </is>
       </c>
       <c r="B119" s="2">
-        <v>0.0051345755693581975</v>
+        <v>9</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -8186,26 +8150,26 @@
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:land</t>
         </is>
       </c>
       <c r="B120" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>0.00013457556935819737</v>
+        <v>83</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
@@ -8216,11 +8180,11 @@
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
         </is>
       </c>
       <c r="B122" s="2">
-        <v>0.04416666666666668</v>
+        <v>32</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
@@ -8231,11 +8195,11 @@
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">balance-sheet:2025:machinery</t>
         </is>
       </c>
       <c r="B123" s="2">
-        <v>0.04750000000000009</v>
+        <v>32</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -8246,11 +8210,11 @@
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>0.03916666666666668</v>
+        <v>73</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -8261,11 +8225,11 @@
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
         </is>
       </c>
       <c r="B125" s="2">
-        <v>0.04250000000000009</v>
+        <v>70</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -8276,11 +8240,11 @@
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
         </is>
       </c>
       <c r="B126" s="2">
-        <v>0.024139457023717444</v>
+        <v>11</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
@@ -8291,11 +8255,11 @@
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">balance-sheet:2025:software</t>
         </is>
       </c>
       <c r="B127" s="2">
-        <v>0.025553459914763096</v>
+        <v>7</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -8306,11 +8270,11 @@
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
         </is>
       </c>
       <c r="B128" s="2">
-        <v>0.019139457023717443</v>
+        <v>64</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
@@ -8321,11 +8285,11 @@
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:investment:0</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>0.020553459914763095</v>
+        <v>15</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
@@ -8336,11 +8300,11 @@
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:investment:1</t>
         </is>
       </c>
       <c r="B130" s="2">
-        <v>0.06076086956521719</v>
+        <v>200</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8351,26 +8315,26 @@
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
         </is>
       </c>
       <c r="B131" s="2">
-        <v>0.06438405797101453</v>
+        <v>0</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>0.040760869565217184</v>
+        <v>100</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
@@ -8381,11 +8345,11 @@
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B133" s="2">
-        <v>0.04438405797101452</v>
+        <v>0.005</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
@@ -8396,22 +8360,22 @@
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>0</v>
+        <v>0.0051345755693581975</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B135" s="2">
@@ -8426,11 +8390,11 @@
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0.08928571428571427</v>
+        <v>0.00013457556935819737</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
@@ -8441,11 +8405,11 @@
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0.11928571428571427</v>
+        <v>0.04416666666666668</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
@@ -8456,26 +8420,26 @@
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0</v>
+        <v>0.04750000000000009</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>0.03</v>
+        <v>0.03916666666666668</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
@@ -8486,26 +8450,26 @@
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0</v>
+        <v>0.04250000000000009</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>1.6653345369377348e-16</v>
+        <v>0.024139457023717444</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
@@ -8516,26 +8480,26 @@
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0</v>
+        <v>0.025553459914763096</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0.08</v>
+        <v>0.019139457023717443</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
@@ -8546,11 +8510,11 @@
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0.051169590643274754</v>
+        <v>0.020553459914763095</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -8561,11 +8525,11 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.06076086956521719</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
@@ -8576,11 +8540,11 @@
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>-0.05</v>
+        <v>0.06438405797101453</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
@@ -8591,11 +8555,11 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0.3</v>
+        <v>0.040760869565217184</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
@@ -8606,11 +8570,11 @@
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0.04263157894736836</v>
+        <v>0.04438405797101452</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
@@ -8621,41 +8585,41 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0.06555555555555558</v>
+        <v>0</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.08928571428571427</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -8666,11 +8630,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.05</v>
+        <v>0.11928571428571427</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -8681,26 +8645,26 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>0.019325330501846927</v>
+        <v>0.03</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -8711,26 +8675,26 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0.020735994183189166</v>
+        <v>0</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>0.15</v>
+        <v>1.6653345369377348e-16</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
@@ -8741,26 +8705,26 @@
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B157" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0.051169590643274754</v>
+        <v>0.08</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
@@ -8771,11 +8735,11 @@
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -8786,41 +8750,41 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.08499999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -8831,11 +8795,11 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0.135</v>
+        <v>0.04263157894736836</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
@@ -8846,11 +8810,11 @@
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>1</v>
+        <v>0.06555555555555558</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -8861,11 +8825,11 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>50</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
@@ -8876,11 +8840,11 @@
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>5</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
@@ -8891,11 +8855,11 @@
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>20</v>
+        <v>0.05</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
@@ -8906,11 +8870,11 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>23</v>
+        <v>0.1</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
@@ -8921,11 +8885,11 @@
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>23</v>
+        <v>0.019325330501846927</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
@@ -8936,11 +8900,11 @@
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.005</v>
+        <v>0.020735994183189166</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
@@ -8951,26 +8915,26 @@
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.045833333333333386</v>
+        <v>0.3</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
@@ -8981,11 +8945,11 @@
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0.04083333333333339</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
@@ -8996,11 +8960,11 @@
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.02484645846924027</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -9011,41 +8975,41 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.01984645846924027</v>
+        <v>0</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.06257246376811586</v>
+        <v>0</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0.042572463768115854</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -9056,26 +9020,26 @@
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0.10928571428571428</v>
+        <v>1</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -9086,11 +9050,11 @@
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0.015</v>
+        <v>50</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
@@ -9101,11 +9065,11 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>5.551115123125783e-17</v>
+        <v>5</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -9116,11 +9080,11 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>0.04</v>
+        <v>20</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -9131,11 +9095,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>0.05409356725146197</v>
+        <v>23</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9146,11 +9110,11 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>0.05</v>
+        <v>23</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
@@ -9161,11 +9125,11 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0.05380116959064325</v>
+        <v>0.005</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
@@ -9176,26 +9140,26 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0.05409356725146197</v>
+        <v>0</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.07</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9206,11 +9170,11 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.020030662342518046</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9221,11 +9185,11 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0.22</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9236,11 +9200,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9251,26 +9215,26 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>0</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>0.11</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9281,26 +9245,26 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>7.66</v>
+        <v>0</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>10</v>
+        <v>0.10928571428571428</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9311,11 +9275,11 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>15</v>
+        <v>0.015</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -9326,11 +9290,11 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>15</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
@@ -9341,11 +9305,11 @@
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>15</v>
+        <v>0.04</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
@@ -9356,56 +9320,56 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>7</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9416,11 +9380,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>2</v>
+        <v>0.07</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9431,11 +9395,11 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>35</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
@@ -9446,11 +9410,11 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>15</v>
+        <v>0.22</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9461,11 +9425,11 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>252.69</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9476,26 +9440,26 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>82.4</v>
+        <v>0</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>10</v>
+        <v>0.11</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -9506,11 +9470,11 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>7</v>
+        <v>7.66</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -9521,11 +9485,11 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">driver:usefulLife</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>3.74</v>
+        <v>10</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
@@ -9536,11 +9500,11 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">future-capex:2026</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>2.85</v>
+        <v>15</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
@@ -9551,11 +9515,11 @@
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">future-capex:2027</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9566,7 +9530,7 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">future-capex:2028</t>
         </is>
       </c>
       <c r="B212" s="2">
@@ -9581,56 +9545,56 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">future-capex:2029</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">future-capex:2030</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">future-capex:2031</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -9641,11 +9605,11 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -9656,11 +9620,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -9671,26 +9635,26 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>35</v>
+        <v>252.69</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -9701,11 +9665,11 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>22</v>
+        <v>82.4</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -9716,11 +9680,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>136.84</v>
+        <v>10</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -9731,11 +9695,11 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>74.8</v>
+        <v>7</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -9746,11 +9710,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>95</v>
+        <v>3.74</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -9761,11 +9725,11 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>60</v>
+        <v>2.85</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
@@ -9776,11 +9740,11 @@
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>33.43</v>
+        <v>70</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -9791,11 +9755,11 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>18.78</v>
+        <v>15</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -9806,11 +9770,11 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>350</v>
+        <v>35</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
@@ -9821,13 +9785,238 @@
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+        </is>
+      </c>
+      <c r="B229" s="2">
+        <v>21</v>
+      </c>
+      <c r="C229" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B230" s="2">
+        <v>40</v>
+      </c>
+      <c r="C230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B231" s="2">
+        <v>23</v>
+      </c>
+      <c r="C231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B232" s="2">
+        <v>10</v>
+      </c>
+      <c r="C232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B233" s="2">
+        <v>6</v>
+      </c>
+      <c r="C233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B234" s="2">
+        <v>0</v>
+      </c>
+      <c r="C234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B235" s="2">
+        <v>35</v>
+      </c>
+      <c r="C235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B236" s="2">
+        <v>22</v>
+      </c>
+      <c r="C236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+        </is>
+      </c>
+      <c r="B237" s="2">
+        <v>136.84</v>
+      </c>
+      <c r="C237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B238" s="2">
+        <v>74.8</v>
+      </c>
+      <c r="C238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B239" s="2">
+        <v>95</v>
+      </c>
+      <c r="C239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B240" s="2">
+        <v>60</v>
+      </c>
+      <c r="C240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+        </is>
+      </c>
+      <c r="B241" s="2">
+        <v>33.43</v>
+      </c>
+      <c r="C241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B242" s="2">
+        <v>18.78</v>
+      </c>
+      <c r="C242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B243" s="2">
+        <v>350</v>
+      </c>
+      <c r="C243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B229" s="2">
+      <c r="B244" s="2">
         <v>213</v>
       </c>
-      <c r="C229" s="0" t="inlineStr">
+      <c r="C244" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -9855,7 +10044,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4fX0seyJ5ZWFyIjoyMDI0LCJyb2xlIjoicHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3NiwiY29ncyI6NTEuNjgsImVtcGxveWVlUGF5Ijo1LjU5LCJvZmZpY2VyUGF5IjowLjM4LCJkZXByZWNpYXRpb24iOjEuOSwib3RoZXJTZ2EiOjkuNSwiaGVhZGNvdW50Ijo5NSwib2ZmaWNlckNvdW50IjoyLCJlbXBsb3llZVNhbGFyeSI6NS4zMSwiZW1wbG95ZWVCb251cyI6MC4yOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNCwib2ZmaWNlckJvbnVzIjowLjA0LCJjb2dzRGVwcmVjaWF0aW9uIjowLjQ3LCJzZ2FEZXByZWNpYXRpb24iOjEuNDMsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMzh9LCJvdGhlciI6eyJzYWxlcyI6NjcuMiwiY29ncyI6NDUuNywiZW1wbG95ZWVQYXkiOjcuNTQsIm9mZmljZXJQYXkiOjAuNTgsImRlcHJlY2lhdGlvbiI6MS40NCwib3RoZXJTZ2EiOjcuNjgsImhlYWRjb3VudCI6MTI1LCJvZmZpY2VyQ291bnQiOjMsImVtcGxveWVlU2FsYXJ5Ijo3LjE2LCJlbXBsb3llZUJvbnVzIjowLjM4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjUyLCJvZmZpY2VyQm9udXMiOjAuMDYsImNvZ3NEZXByZWNpYXRpb24iOjAuMjksInNnYURlcHJlY2lhdGlvbiI6MS4xNSwicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4yOX19LHsieWVhciI6MjAyNSwicm9sZSI6ImxhdGVzdCIsInByb2plY3QiOnsic2FsZXMiOjgwLCJjb2dzIjo1NC40LCJlbXBsb3llZVBheSI6NiwiZW1wbG95ZWVTYWxhcnkiOjUuNywiZW1wbG95ZWVCb251cyI6MC4zLCJvZmZpY2VyUGF5IjowLjQsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzYsIm9mZmljZXJCb251cyI6MC4wNCwiZGVwcmVjaWF0aW9uIjoyLCJjb2dzRGVwcmVjaWF0aW9uIjowLjUsInNnYURlcHJlY2lhdGlvbiI6MS41LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjQsIm90aGVyU2dhIjoxMCwiaGVhZGNvdW50IjoxMDAsIm9mZmljZXJDb3VudCI6Mn0sIm90aGVyIjp7InNhbGVzIjo3MCwiY29ncyI6NDcuNiwiZW1wbG95ZWVQYXkiOjgsImVtcGxveWVlU2FsYXJ5Ijo3LjYsImVtcGxveWVlQm9udXMiOjAuNCwib2ZmaWNlclBheSI6MC42LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjU0LCJvZmZpY2VyQm9udXMiOjAuMDYsImRlcHJlY2lhdGlvbiI6MS41LCJjb2dzRGVwcmVjaWF0aW9uIjowLjMsInNnYURlcHJlY2lhdGlvbiI6MS4yLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjMsIm90aGVyU2dhIjo4LCJoZWFkY291bnQiOjEzMCwib2ZmaWNlckNvdW50IjozfX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjoyLCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjEzNi44NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjE4Ljc4LCJtYXgiOjMzLjQzLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6Mi44NSwibWF4IjozLjc0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1LjEzLCIyMDI5OnByb2plY3Q6Ny04Ijo3Ljl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjciOjE1LCJmdXR1cmUtY2FwZXg6MjAyOCI6MTUsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjEuNjY1MzM0NTM2OTM3NzM0OGUtMTYsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkzMjUzMzA1MDE4NDY5MjcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNzM1OTk0MTgzMTg5MTY2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDU3MDE3NTQzODU5NjQ5MTksImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNDA3NjA4Njk1NjUyMTcxODQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjEiOjAuMDQ0Mzg0MDU3OTcxMDE0NTIsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjowLjAwMDEzNDU3NTU2OTM1ODE5NzM3LCJkcml2ZXI6b3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZTowIjowLjAxOTEzOTQ1NzAyMzcxNzQ0MywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDIwNTUzNDU5OTE0NzYzMDk1LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDowIjowLjA0NDE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MSI6MC4wNDc1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOnByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MCI6MC4wODQ5OTk5OTk5OTk5OTk5OSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjEiOjAuMTM1LCJkcml2ZXI6b3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjAiOjAuMDg5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MSI6MC4xMTkyODU3MTQyODU3MTQyNywiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MCI6MC4wNDI2MzE1Nzg5NDczNjgzNiwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDY1NTU1NTU1NTU1NTU1NTgsImRyaXZlcjp1c2VmdWxMaWZlIjoxMCwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MCI6NSwiZHJpdmVyLXJhbmdlOnVzZWZ1bExpZmU6MSI6MjAsImRyaXZlcjppbnZlc3RtZW50IjoyMywiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MCI6MTUsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjEiOjIwMCwiZHJpdmVyOnN1YnNpZHkiOjcuNjYsImRyaXZlci1yYW5nZTpzdWJzaWR5OjAiOjEsImRyaXZlci1yYW5nZTpzdWJzaWR5OjEiOjUwLCJkcml2ZXI6bG9jYWxCZW5jaG1hcmsiOjIzLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MCI6MCwiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjEiOjEwMCwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6dmFsdWUiOjE1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6dmFsdWUiOjgyLjQsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6dmFsdWUiOjIsInRhcmdldDpjb21wYW55UGF5U2NoZWR1bGU6bWF4Ijo3LCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6dmFsdWUiOjYwLCJ0YXJnZXQ6cHJvamVjdFNhbGVzU2hhcmU6bWF4Ijo5NSwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6dmFsdWUiOjIyLCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2FncjptYXgiOjM1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6dmFsdWUiOjc0LjgsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6dmFsdWUiOjIxLCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOm1heCI6MzUsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6dmFsdWUiOjE4Ljc4LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOnZhbHVlIjo3LCJ0YXJnZXQ6ZW1wbG95ZWVQYXlDYWdyOm1heCI6MTAsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOnZhbHVlIjoyLjg1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86dmFsdWUiOjE1LCJ0YXJnZXQ6aW52ZXN0bWVudFNhbGVzUmF0aW86bWF4Ijo3MCwidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86dmFsdWUiOjIxMywidGFyZ2V0OnZhbHVlQWRkZWRTdWJzaWR5UmF0aW86bWF4IjozNTAsInRhcmdldDpsb2NhbEJlbmNobWFyazp2YWx1ZSI6MjMsInRhcmdldDpsb2NhbEJlbmNobWFyazptYXgiOjQwLCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6dmFsdWUiOjYsInRhcmdldDpvZmZpY2VyUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6b2ZmaWNlclBheUluY3JlYXNlOnZhbHVlIjowLCJ0YXJnZXQ6Y29tcGFueVNhbGVzSW5jcmVhc2U6bWF4IjoyNTIuNjksInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTptYXgiOjEzNi44NCwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTptYXgiOjMzLjQzLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTptYXgiOjMuNzR9LCJtZXRyaWNHcm91cEJhc2VzIjp7ImNvbXBhbnlTYWxlcyI6InJhdGUiLCJwcm9qZWN0U2FsZXMiOiJyYXRlIiwibGFib3JQcm9kdWN0aXZpdHkiOiJyYXRlIiwiZW1wbG95ZWVQYXkiOiJyYXRlIn0sImFwcGxpY2F0aW9uQ2F0ZWdvcnkiOiJnZW5lcmFsIiwiYWRqdXN0ZWREcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQxMDU5NTc2MDIzMzkxNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAxOTk4MjEzNTUxMTg3OTg3MywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwNjM5MDEyNDk3MjI5MzQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MTIwNDUxMzMzMTU3NjMsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA1NTE2MjczMDA1MjcsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4ODEzNjc1MDA5MTcxMTcsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYwOTM1Mzk0MzcxNzg1NSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyMDIyNDg3MjE2OTQ2NjczLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU2NTE3ODU5NDUyMTc5LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNDk5MDQ4MTM0MTI2NTU1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDg5MDA2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODg3NzYxNzEwMzMzMDMsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDI5MDQ1NDgyMzk3MjA1MDU1LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU3ODQ4MTQ3MzIzMDg2NjUsInByb2plY3RTZ2FSYXRlRW5kIjowLjEwOTkzMTgwOTE2NDg0ODI0LCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjcyNTg5ODcyMTI4MjMsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1Mzc3ODA1NzYyODcxNjMyLCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM319</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6MTAuNzMsInByZVRheEluY29tZSI6MTAuNzMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjoxMS4wMSwicHJlVGF4SW5jb21lIjoxMS4wMSwibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjoxMS4zLCJwcmVUYXhJbmNvbWUiOjExLjMsIm5ldEluY29tZSI6Ny45MX19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIsImN1cnJlbnRBc3NldHMiOjY3LCJjYXNoIjoyNCwiZml4ZWRBc3NldHMiOjY1LCJ0YW5naWJsZUFzc2V0cyI6NTMsImJ1aWxkaW5ncyI6MTksIm1hY2hpbmVyeSI6MjQsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo3LCJzb2Z0d2FyZSI6NSwibGlhYmlsaXRpZXMiOjc1LCJjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzYsImxvbmdUZXJtRGVidCI6MjksIm5ldEFzc2V0cyI6NTcsInNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiY2FwaXRhbCI6MTAsImNhcGV4Ijo1fSx7InllYXIiOjIwMjQsImFzc2V0cyI6MTQzLCJjdXJyZW50QXNzZXRzIjo3MiwiY2FzaCI6MjUsImZpeGVkQXNzZXRzIjo3MSwidGFuZ2libGVBc3NldHMiOjU4LCJidWlsZGluZ3MiOjIwLCJtYWNoaW5lcnkiOjI4LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OCwic29mdHdhcmUiOjYsImxpYWJpbGl0aWVzIjo3OSwiY3VycmVudExpYWJpbGl0aWVzIjo0MSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM4LCJsb25nVGVybURlYnQiOjMxLCJuZXRBc3NldHMiOjY0LCJzaGFyZWhvbGRlckVxdWl0eSI6NjEsImNhcGl0YWwiOjEwLCJjYXBleCI6OH0seyJ5ZWFyIjoyMDI1LCJhc3NldHMiOjE1NiwiY3VycmVudEFzc2V0cyI6NzgsImNhc2giOjI3LCJmaXhlZEFzc2V0cyI6NzgsInRhbmdpYmxlQXNzZXRzIjo2NCwiYnVpbGRpbmdzIjoyMiwibWFjaGluZXJ5IjozMiwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjksInNvZnR3YXJlIjo3LCJsaWFiaWxpdGllcyI6ODMsImN1cnJlbnRMaWFiaWxpdGllcyI6NDMsInNob3J0VGVybURlYnQiOjExLCJmaXhlZExpYWJpbGl0aWVzIjo0MCwibG9uZ1Rlcm1EZWJ0IjozMiwibmV0QXNzZXRzIjo3Mywic2hhcmVob2xkZXJFcXVpdHkiOjcwLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjEwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyNywidmFsdWUiOjE1fSx7InllYXIiOjIwMjgsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfSwiZHJpdmVyUmFuZ2VzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOlstMC4wNSwwLjNdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTMyNTMzMDUwMTg0NjkyNywwLjAyMDczNTk5NDE4MzE4OTE2Nl0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDQwNzYwODY5NTY1MjE3MTg0LDAuMDQ0Mzg0MDU3OTcxMDE0NTJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMDAxMzQ1NzU1NjkzNTgxOTczN10sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkxMzk0NTcwMjM3MTc0NDMsMC4wMjA1NTM0NTk5MTQ3NjMwOTVdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDM5MTY2NjY2NjY2NjY2NjgsMC4wNDI1MDAwMDAwMDAwMDAwOV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlswLjE1LDAuM10sIm90aGVyU2FsZXNHcm93dGgiOlswLjA2MDc2MDg2OTU2NTIxNzE5LDAuMDY0Mzg0MDU3OTcxMDE0NTNdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLjAwNSwwLjAwNTEzNDU3NTU2OTM1ODE5NzVdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAuMDI0MTM5NDU3MDIzNzE3NDQ0LDAuMDI1NTUzNDU5OTE0NzYzMDk2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbMC4wNDQxNjY2NjY2NjY2NjY2OCwwLjA0NzUwMDAwMDAwMDAwMDA5XSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA4NDk5OTk5OTk5OTk5OTk5LDAuMTM1XSwib3RoZXJTZ2FSYXRlRW5kIjpbMC4wODkyODU3MTQyODU3MTQyNywwLjExOTI4NTcxNDI4NTcxNDI3XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLjA0MjYzMTU3ODk0NzM2ODM2LDAuMDY1NTU1NTU1NTU1NTU1NThdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoxNSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4Mi40LCJtYXgiOjI1Mi42OSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6MiwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjYwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny45fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzNi40LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTIuNzUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzIuNjUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny41MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6Ny43MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI3IjoyMjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo3LjkxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA4NDk5OTk5OTk5OTk5OTk5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4xMzUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wODkyODU3MTQyODU3MTQyNywiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjExOTI4NTcxNDI4NTcxNDI3LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6MiwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDEwNTk1NzYwMjMzOTE2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDE5OTgyMTM1NTExODc5ODczLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA2MzkwMTI0OTcyMjkzNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQxMjA0NTEzMzMxNTc2Mywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI2MDU1MTYyNzMwMDUyNywib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg4MTM2NzUwMDkxNzExNywib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjA5MzUzOTQzNzE3ODU1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTY1MTc4NTk0NTIxNzksInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE0OTkwNDgxMzQxMjY1NTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODkwMDYyMjk5NzUwODAxLCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4ODc3NjE3MTAzMzMwMywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMjkwNDU0ODIzOTcyMDUwNTUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTc4NDgxNDczMjMwODY2NSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTA5OTMxODA5MTY0ODQ4MjQsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -1839,22 +1839,22 @@
         <v>11.3</v>
       </c>
       <c r="E20" s="4">
-        <v>11.17</v>
+        <v>11.169999999999991</v>
       </c>
       <c r="F20" s="4">
-        <v>11.02</v>
+        <v>11.019999999999996</v>
       </c>
       <c r="G20" s="4">
-        <v>10.86</v>
+        <v>10.860000000000003</v>
       </c>
       <c r="H20" s="4">
-        <v>15.55</v>
+        <v>16.009999999999998</v>
       </c>
       <c r="I20" s="4">
-        <v>21.49</v>
+        <v>22.009999999999984</v>
       </c>
       <c r="J20" s="4">
-        <v>29.12</v>
+        <v>29.700000000000014</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>11.3</v>
       </c>
       <c r="E21" s="2">
-        <v>11.17</v>
+        <v>11.169999999999991</v>
       </c>
       <c r="F21" s="2">
-        <v>11.02</v>
+        <v>11.019999999999996</v>
       </c>
       <c r="G21" s="2">
-        <v>10.86</v>
+        <v>10.860000000000003</v>
       </c>
       <c r="H21" s="2">
-        <v>15.55</v>
+        <v>16.009999999999998</v>
       </c>
       <c r="I21" s="2">
-        <v>21.49</v>
+        <v>22.009999999999984</v>
       </c>
       <c r="J21" s="2">
-        <v>29.12</v>
+        <v>29.700000000000014</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>7.91</v>
       </c>
       <c r="E22" s="2">
-        <v>7.82</v>
+        <v>7.815999999999994</v>
       </c>
       <c r="F22" s="2">
-        <v>7.71</v>
+        <v>7.711999999999997</v>
       </c>
       <c r="G22" s="2">
-        <v>7.6</v>
+        <v>7.5980000000000025</v>
       </c>
       <c r="H22" s="2">
-        <v>10.88</v>
+        <v>11.197999999999997</v>
       </c>
       <c r="I22" s="2">
-        <v>15.04</v>
+        <v>15.402999999999988</v>
       </c>
       <c r="J22" s="2">
-        <v>20.38</v>
+        <v>20.78200000000001</v>
       </c>
     </row>
     <row r="23">
@@ -10044,7 +10044,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6MTAuNzMsInByZVRheEluY29tZSI6MTAuNzMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjoxMS4wMSwicHJlVGF4SW5jb21lIjoxMS4wMSwibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjoxMS4zLCJwcmVUYXhJbmNvbWUiOjExLjMsIm5ldEluY29tZSI6Ny45MX19XSwiYmFsYW5jZVNoZWV0cyI6W3sieWVhciI6MjAyMywiYXNzZXRzIjoxMzIsImN1cnJlbnRBc3NldHMiOjY3LCJjYXNoIjoyNCwiZml4ZWRBc3NldHMiOjY1LCJ0YW5naWJsZUFzc2V0cyI6NTMsImJ1aWxkaW5ncyI6MTksIm1hY2hpbmVyeSI6MjQsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo3LCJzb2Z0d2FyZSI6NSwibGlhYmlsaXRpZXMiOjc1LCJjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzYsImxvbmdUZXJtRGVidCI6MjksIm5ldEFzc2V0cyI6NTcsInNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiY2FwaXRhbCI6MTAsImNhcGV4Ijo1fSx7InllYXIiOjIwMjQsImFzc2V0cyI6MTQzLCJjdXJyZW50QXNzZXRzIjo3MiwiY2FzaCI6MjUsImZpeGVkQXNzZXRzIjo3MSwidGFuZ2libGVBc3NldHMiOjU4LCJidWlsZGluZ3MiOjIwLCJtYWNoaW5lcnkiOjI4LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OCwic29mdHdhcmUiOjYsImxpYWJpbGl0aWVzIjo3OSwiY3VycmVudExpYWJpbGl0aWVzIjo0MSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM4LCJsb25nVGVybURlYnQiOjMxLCJuZXRBc3NldHMiOjY0LCJzaGFyZWhvbGRlckVxdWl0eSI6NjEsImNhcGl0YWwiOjEwLCJjYXBleCI6OH0seyJ5ZWFyIjoyMDI1LCJhc3NldHMiOjE1NiwiY3VycmVudEFzc2V0cyI6NzgsImNhc2giOjI3LCJmaXhlZEFzc2V0cyI6NzgsInRhbmdpYmxlQXNzZXRzIjo2NCwiYnVpbGRpbmdzIjoyMiwibWFjaGluZXJ5IjozMiwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjksInNvZnR3YXJlIjo3LCJsaWFiaWxpdGllcyI6ODMsImN1cnJlbnRMaWFiaWxpdGllcyI6NDMsInNob3J0VGVybURlYnQiOjExLCJmaXhlZExpYWJpbGl0aWVzIjo0MCwibG9uZ1Rlcm1EZWJ0IjozMiwibmV0QXNzZXRzIjo3Mywic2hhcmVob2xkZXJFcXVpdHkiOjcwLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjEwfV0sImZ1dHVyZUNhcGV4IjpbeyJ5ZWFyIjoyMDI2LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyNywidmFsdWUiOjE1fSx7InllYXIiOjIwMjgsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI5LCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMwLCJ2YWx1ZSI6MH0seyJ5ZWFyIjoyMDMxLCJ2YWx1ZSI6MH1dLCJkcml2ZXJzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzMDY2MjM0MjUxODA0NiwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wNywib3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfSwiZHJpdmVyUmFuZ2VzIjp7InByb2plY3RNYXJrZXRHcm93dGgiOlstMC4wNSwwLjNdLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNl0sInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTMyNTMzMDUwMTg0NjkyNywwLjAyMDczNTk5NDE4MzE4OTE2Nl0sInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOlswLjA1MTE2OTU5MDY0MzI3NDc1NCwwLjA1NzAxNzU0Mzg1OTY0OTE5XSwib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDQwNzYwODY5NTY1MjE3MTg0LDAuMDQ0Mzg0MDU3OTcxMDE0NTJdLCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6WzAsMC4wMDAxMzQ1NzU1NjkzNTgxOTczN10sIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkxMzk0NTcwMjM3MTc0NDMsMC4wMjA1NTM0NTk5MTQ3NjMwOTVdLCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDM5MTY2NjY2NjY2NjY2NjgsMC4wNDI1MDAwMDAwMDAwMDAwOV0sIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0U2FsZXNHcm93dGgiOlswLjE1LDAuM10sIm90aGVyU2FsZXNHcm93dGgiOlswLjA2MDc2MDg2OTU2NTIxNzE5LDAuMDY0Mzg0MDU3OTcxMDE0NTNdLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjpbMCwwLjAzXSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOlswLjAwNSwwLjAwNTEzNDU3NTU2OTM1ODE5NzVdLCJwcm9qZWN0UGF5R3Jvd3RoIjpbMC4wNSwwLjFdLCJvdGhlclBheUdyb3d0aCI6WzAuMDI0MTM5NDU3MDIzNzE3NDQ0LDAuMDI1NTUzNDU5OTE0NzYzMDk2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6WzAsMC4wOF0sIm90aGVySGVhZGNvdW50R3Jvd3RoIjpbMC4wNDQxNjY2NjY2NjY2NjY2OCwwLjA0NzUwMDAwMDAwMDAwMDA5XSwicHJvamVjdFNnYVJhdGVFbmQiOlswLjA4NDk5OTk5OTk5OTk5OTk5LDAuMTM1XSwib3RoZXJTZ2FSYXRlRW5kIjpbMC4wODkyODU3MTQyODU3MTQyNywwLjExOTI4NTcxNDI4NTcxNDI3XSwicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOlswLjA0MjYzMTU3ODk0NzM2ODM2LDAuMDY1NTU1NTU1NTU1NTU1NThdLCJ1c2VmdWxMaWZlIjpbNSwyMF0sImludmVzdG1lbnQiOlsxNSwyMDBdLCJzdWJzaWR5IjpbMSw1MF0sImxvY2FsQmVuY2htYXJrIjpbMCwxMDBdfSwidGFyZ2V0cyI6eyJjb21wYW55U2FsZXNDYWdyIjp7InZhbHVlIjoxNSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo4Mi40LCJtYXgiOjI1Mi42OSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImNvbXBhbnlQYXlTY2hlZHVsZSI6eyJ2YWx1ZSI6MiwibWF4Ijo3LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzU2hhcmUiOnsidmFsdWUiOjYwLCJtYXgiOjk1LCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzQ2FnciI6eyJ2YWx1ZSI6MjIsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6NzQuOCwibWF4IjoxMzYuODQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsYWJvclByb2R1Y3Rpdml0eUNhZ3IiOnsidmFsdWUiOjIxLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZEluY3JlYXNlIjp7InZhbHVlIjoxOC43OCwibWF4IjozMy40MywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5Q2FnciI6eyJ2YWx1ZSI6NywibWF4IjoxMCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImVtcGxveWVlUGF5SW5jcmVhc2UiOnsidmFsdWUiOjIuODUsIm1heCI6My43NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImludmVzdG1lbnRTYWxlc1JhdGlvIjp7InZhbHVlIjoxNSwibWF4Ijo3MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRTdWJzaWR5UmF0aW8iOnsidmFsdWUiOjIxMywibWF4IjozNTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJsb2NhbEJlbmNobWFyayI6eyJ2YWx1ZSI6MjMsIm1heCI6NDAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5Q2FnciI6eyJ2YWx1ZSI6NiwibWF4IjoxMCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX19LCJmb3JlY2FzdE92ZXJyaWRlcyI6eyIyMDI5Om90aGVyOnNhbGVzIjo4NS4xMywiMjAyOTpwcm9qZWN0OjctOCI6Ny45fSwiZnV0dXJlSW5wdXRCYXNpcyI6Im90aGVyIiwiaW5wdXRWYWx1ZXMiOnsiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEiOjEzNi40LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMyI6OTIuNzUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi00IjowLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItNyI6MzIuNjUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi05IjowLjgyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTAiOjAuMDksImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMiI6MTEuNjcsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMyI6MC42MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE0IjoyLjQ1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTUiOjAuNjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOCI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xOSI6MTAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yMCI6Ny41MSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI3IjoyMTAsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEiOjcyLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNCI6MjMuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny02Ijo2Ljc4LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOCI6NS4xOSwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTkiOjAuMzYsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMCI6MS44LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTMiOjkwLCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xIjoxNDMuMiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTMiOjk3LjM4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNCI6MC43NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTciOjM0LjUyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItOSI6MC44NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMiI6MTIuNDcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMyI6MC42NiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE0IjoyLjU4LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTUiOjAuNjcsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOCI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xOSI6MTEuMDEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yMCI6Ny43MSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI3IjoyMjAsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEiOjc2LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNCI6MjQuMzIsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny02Ijo3LjA0LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOCI6NS41OSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTkiOjAuMzgsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMCI6MS45LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo3LjkxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEwIjoyLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTMiOjEwMCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTE0IjoyLCJiYWxhbmNlLXNoZWV0OjIwMjM6YXNzZXRzIjoxMzIsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50QXNzZXRzIjo2NywiYmFsYW5jZS1zaGVldDoyMDIzOmNhc2giOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRBc3NldHMiOjY1LCJiYWxhbmNlLXNoZWV0OjIwMjM6dGFuZ2libGVBc3NldHMiOjUzLCJiYWxhbmNlLXNoZWV0OjIwMjM6YnVpbGRpbmdzIjoxOSwiYmFsYW5jZS1zaGVldDoyMDIzOm1hY2hpbmVyeSI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmludGFuZ2libGVBc3NldHMiOjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzb2Z0d2FyZSI6NSwiYmFsYW5jZS1zaGVldDoyMDIzOmxpYWJpbGl0aWVzIjo3NSwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRMaWFiaWxpdGllcyI6MzksImJhbGFuY2Utc2hlZXQ6MjAyMzpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkTGlhYmlsaXRpZXMiOjM2LCJiYWxhbmNlLXNoZWV0OjIwMjM6bG9uZ1Rlcm1EZWJ0IjoyOSwiYmFsYW5jZS1zaGVldDoyMDIzOm5ldEFzc2V0cyI6NTcsImJhbGFuY2Utc2hlZXQ6MjAyMzpzaGFyZWhvbGRlckVxdWl0eSI6NTQsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGV4Ijo1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YXNzZXRzIjoxNDMsImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50QXNzZXRzIjo3MiwiYmFsYW5jZS1zaGVldDoyMDI0OmNhc2giOjI1LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRBc3NldHMiOjcxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6dGFuZ2libGVBc3NldHMiOjU4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6YnVpbGRpbmdzIjoyMCwiYmFsYW5jZS1zaGVldDoyMDI0Om1hY2hpbmVyeSI6MjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmludGFuZ2libGVBc3NldHMiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNDpzb2Z0d2FyZSI6NiwiYmFsYW5jZS1zaGVldDoyMDI0OmxpYWJpbGl0aWVzIjo3OSwiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRMaWFiaWxpdGllcyI6NDEsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaG9ydFRlcm1EZWJ0IjoxMiwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkTGlhYmlsaXRpZXMiOjM4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bG9uZ1Rlcm1EZWJ0IjozMSwiYmFsYW5jZS1zaGVldDoyMDI0Om5ldEFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNDpzaGFyZWhvbGRlckVxdWl0eSI6NjEsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGV4Ijo4LCJiYWxhbmNlLXNoZWV0OjIwMjU6YXNzZXRzIjoxNTYsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50QXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhc2giOjI3LCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6dGFuZ2libGVBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjU6YnVpbGRpbmdzIjoyMiwiYmFsYW5jZS1zaGVldDoyMDI1Om1hY2hpbmVyeSI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpsYW5kIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmludGFuZ2libGVBc3NldHMiOjksImJhbGFuY2Utc2hlZXQ6MjAyNTpzb2Z0d2FyZSI6NywiYmFsYW5jZS1zaGVldDoyMDI1OmxpYWJpbGl0aWVzIjo4MywiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRMaWFiaWxpdGllcyI6NDMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaG9ydFRlcm1EZWJ0IjoxMSwiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkTGlhYmlsaXRpZXMiOjQwLCJiYWxhbmNlLXNoZWV0OjIwMjU6bG9uZ1Rlcm1EZWJ0IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1Om5ldEFzc2V0cyI6NzMsImJhbGFuY2Utc2hlZXQ6MjAyNTpzaGFyZWhvbGRlckVxdWl0eSI6NzAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBpdGFsIjoxMCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGV4IjoxMCwiZnV0dXJlLWNhcGV4OjIwMjYiOjE1LCJmdXR1cmUtY2FwZXg6MjAyNyI6MTUsImZ1dHVyZS1jYXBleDoyMDI4IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjkiOjAsImZ1dHVyZS1jYXBleDoyMDMwIjowLCJmdXR1cmUtY2FwZXg6MjAzMSI6MCwiZHJpdmVyOnByb2plY3RNYXJrZXRHcm93dGgiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjAiOi0wLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDoxIjowLjMsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA4NDk5OTk5OTk5OTk5OTk5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4xMzUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wODkyODU3MTQyODU3MTQyNywiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjExOTI4NTcxNDI4NTcxNDI3LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6MiwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDEwNTk1NzYwMjMzOTE2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjoxLjE3NDE4NjQ5MTA2NDQ2NmUtMTYsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDE5OTgyMTM1NTExODc5ODczLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA2MzkwMTI0OTcyMjkzNCwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQxMjA0NTEzMzMxNTc2Mywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI2MDU1MTYyNzMwMDUyNywib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg4MTM2NzUwMDkxNzExNywib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjA5MzUzOTQzNzE3ODU1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTY1MTc4NTk0NTIxNzksInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE0OTkwNDgxMzQxMjY1NTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODkwMDYyMjk5NzUwODAxLCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4ODc3NjE3MTAzMzMwMywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMjkwNDU0ODIzOTcyMDUwNTUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTc4NDgxNDczMjMwODY2NSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTA5OTMxODA5MTY0ODQ4MjQsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Mi43NjQwMDAwMDAwMDAwMDJ9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2LCJjb2dzIjo1MS42OCwiZW1wbG95ZWVQYXkiOjUuNTksIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjIsImVtcGxveWVlU2FsYXJ5Ijo1LjMxLCJlbXBsb3llZUJvbnVzIjowLjI4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjM0LCJvZmZpY2VyQm9udXMiOjAuMDQsImNvZ3NEZXByZWNpYXRpb24iOjAuNDcsInNnYURlcHJlY2lhdGlvbiI6MS40MywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4zOH0sIm90aGVyIjp7InNhbGVzIjo2Ny4yLCJjb2dzIjo0NS43LCJlbXBsb3llZVBheSI6Ny41NCwib2ZmaWNlclBheSI6MC41OCwiZGVwcmVjaWF0aW9uIjoxLjQ0LCJvdGhlclNnYSI6Ny42OCwiaGVhZGNvdW50IjoxMjUsIm9mZmljZXJDb3VudCI6MywiZW1wbG95ZWVTYWxhcnkiOjcuMTYsImVtcGxveWVlQm9udXMiOjAuMzgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTIsIm9mZmljZXJCb251cyI6MC4wNiwiY29nc0RlcHJlY2lhdGlvbiI6MC4yOSwic2dhRGVwcmVjaWF0aW9uIjoxLjE1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI5LCJvcmRpbmFyeUluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsInByZVRheEluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsIm5ldEluY29tZSI6Mi43ODE5OTk5OTk5OTk5OTgzfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjIuNzk5OTk5OTk5OTk5OTk3fX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjoyLCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjEzNi44NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjE4Ljc4LCJtYXgiOjMzLjQzLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6Mi44NSwibWF4IjozLjc0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1LjEzLCIyMDI5OnByb2plY3Q6Ny04Ijo3Ljl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE4IjoxMC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjo3LjUxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjciOjIxMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjo3LjcxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjU5LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MC4zOCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjoxLjksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjcuOTEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjo4MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1LjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3LjMsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MC40LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjIsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MTAwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTQiOjIsImJhbGFuY2Utc2hlZXQ6MjAyMzphc3NldHMiOjEzMiwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FzaCI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZEFzc2V0cyI6NjUsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMsImJhbGFuY2Utc2hlZXQ6MjAyMzpidWlsZGluZ3MiOjE5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bWFjaGluZXJ5IjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6aW50YW5naWJsZUFzc2V0cyI6NywiYmFsYW5jZS1zaGVldDoyMDIzOnNvZnR3YXJlIjo1LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudExpYWJpbGl0aWVzIjozOSwiYmFsYW5jZS1zaGVldDoyMDIzOnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYsImJhbGFuY2Utc2hlZXQ6MjAyMzpsb25nVGVybURlYnQiOjI5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bmV0QXNzZXRzIjo1NywiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwZXgiOjUsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MywiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRBc3NldHMiOjcyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FzaCI6MjUsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEsImJhbGFuY2Utc2hlZXQ6MjAyNDp0YW5naWJsZUFzc2V0cyI6NTgsImJhbGFuY2Utc2hlZXQ6MjAyNDpidWlsZGluZ3MiOjIwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6aW50YW5naWJsZUFzc2V0cyI6OCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGlhYmlsaXRpZXMiOjc5LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudExpYWJpbGl0aWVzIjo0MSwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRMaWFiaWxpdGllcyI6MzgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsb25nVGVybURlYnQiOjMxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI0OnNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNTphc3NldHMiOjE1NiwiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTp0YW5naWJsZUFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bWFjaGluZXJ5IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OSwiYmFsYW5jZS1zaGVldDoyMDI1OnNvZnR3YXJlIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjU6bGlhYmlsaXRpZXMiOjgzLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MywiYmFsYW5jZS1zaGVldDoyMDI1OnNob3J0VGVybURlYnQiOjExLCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRMaWFiaWxpdGllcyI6NDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bmV0QXNzZXRzIjo3MywiYmFsYW5jZS1zaGVldDoyMDI1OnNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwZXgiOjEwLCJmdXR1cmUtY2FwZXg6MjAyNiI6MTUsImZ1dHVyZS1jYXBleDoyMDI3IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjgiOjE1LCJmdXR1cmUtY2FwZXg6MjAyOSI6MCwiZnV0dXJlLWNhcGV4OjIwMzAiOjAsImZ1dHVyZS1jYXBleDoyMDMxIjowLCJkcml2ZXI6cHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjEiOjAuMywiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wMzkxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDQyNTAwMDAwMDAwMDAwMDksImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOjAuMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC4zLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6MC4wNjA3NjA4Njk1NjUyMTcxOSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4wNjQzODQwNTc5NzEwMTQ1MywiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAwNTEzNDU3NTU2OTM1ODE5NzUsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAuMDI0MTM5NDU3MDIzNzE3NDQ0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjoyLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3NC44LCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjoxOC43OCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mi44NSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjoxNSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOm1heCI6MjUyLjY5LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6bWF4IjoxMzYuODQsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMy40MywidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6bWF4IjozLjc0fSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCIsImFkanVzdGVkRHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MTA1OTU3NjAyMzM5MTYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMTk5ODIxMzU1MTE4Nzk4NzMsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDYzOTAxMjQ5NzIyOTM0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDEyMDQ1MTMzMzE1NzYzLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjYwNTUxNjI3MzAwNTI3LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODgxMzY3NTAwOTE3MTE3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA2MDkzNTM5NDM3MTc4NTUsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMjAyMjQ4NzIxNjk0NjY3Mywib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NjUxNzg1OTQ1MjE3OSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTQ5OTA0ODEzNDEyNjU1NSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA4OTAwNjIyOTk3NTA4MDEsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg4Nzc2MTcxMDMzMzAzLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyOTA0NTQ4MjM5NzIwNTA1NSwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1Nzg0ODE0NzMyMzA4NjY1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMDk5MzE4MDkxNjQ4NDgyNCwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI3MjU4OTg3MjEyODIzLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM3NzgwNTc2Mjg3MTYzMiwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -3560,47 +3560,47 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 — / 補助 — / 他 —</t>
+          <t xml:space="preserve">全社 — / 補助 — / ベース —</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.99 % / 補助 5.56 % / 他 4.35 %</t>
+          <t xml:space="preserve">全社 4.99 % / 補助 5.56 % / ベース 4.35 %</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.75 % / 補助 5.26 % / 他 4.17 %</t>
+          <t xml:space="preserve">全社 4.75 % / 補助 5.26 % / ベース 4.17 %</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.87 % / 補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 4.87 % / 補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">全社 4.88 % / 補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.28 % / 補助 22.03 % / 他 7.31 %</t>
+          <t xml:space="preserve">全社 15.28 % / 補助 22.03 % / ベース 7.31 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.29 % / 補助 22.01 % / 他 6.25 %</t>
+          <t xml:space="preserve">全社 15.29 % / 補助 22.01 % / ベース 6.25 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.83 % / 補助 22.03 % / 他 6.27 %</t>
+          <t xml:space="preserve">全社 15.83 % / 補助 22.03 % / ベース 6.27 %</t>
         </is>
       </c>
     </row>
@@ -3622,47 +3622,47 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 68 %</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68.01 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 68.01 %</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 68 %</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 67.99 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 67.99 % / ベース 68 %</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68 % / 補助 68.01 % / 他 68 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68.01 % / ベース 68 %</t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68.01 % / 補助 68 % / 他 68.01 %</t>
+          <t xml:space="preserve">全社 68.01 % / 補助 68 % / ベース 68.01 %</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.36 % / 補助 67.5 % / 他 67.17 %</t>
+          <t xml:space="preserve">全社 67.36 % / 補助 67.5 % / ベース 67.17 %</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.01 % / 補助 67.01 % / 他 67.01 %</t>
+          <t xml:space="preserve">全社 67.01 % / 補助 67.01 % / ベース 67.01 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.62 % / 補助 66.51 % / 他 66.83 %</t>
+          <t xml:space="preserve">全社 66.62 % / 補助 66.51 % / ベース 66.83 %</t>
         </is>
       </c>
     </row>
@@ -3684,47 +3684,47 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 32 %</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 31.99 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 31.99 %</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 32 %</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 32.01 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32.01 % / ベース 32 %</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32 % / 補助 31.99 % / 他 32 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 31.99 % / ベース 32 %</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 31.99 % / 補助 32 % / 他 31.99 %</t>
+          <t xml:space="preserve">全社 31.99 % / 補助 32 % / ベース 31.99 %</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.64 % / 補助 32.5 % / 他 32.83 %</t>
+          <t xml:space="preserve">全社 32.64 % / 補助 32.5 % / ベース 32.83 %</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.99 % / 補助 32.99 % / 他 32.99 %</t>
+          <t xml:space="preserve">全社 32.99 % / 補助 32.99 % / ベース 32.99 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.38 % / 補助 33.49 % / 他 33.17 %</t>
+          <t xml:space="preserve">全社 33.38 % / 補助 33.49 % / ベース 33.17 %</t>
         </is>
       </c>
     </row>
@@ -3746,47 +3746,47 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 23.94 % / 補助 22.58 % / 他 25.45 %</t>
+          <t xml:space="preserve">全社 23.94 % / 補助 22.58 % / ベース 25.45 %</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.11 % / 補助 22.74 % / 他 25.65 %</t>
+          <t xml:space="preserve">全社 24.11 % / 補助 22.74 % / ベース 25.65 %</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.27 % / 補助 22.88 % / 他 25.86 %</t>
+          <t xml:space="preserve">全社 24.27 % / 補助 22.88 % / ベース 25.86 %</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.7 % / 補助 23.61 % / 他 25.97 %</t>
+          <t xml:space="preserve">全社 24.7 % / 補助 23.61 % / ベース 25.97 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.12 % / 補助 24.28 % / 他 26.1 %</t>
+          <t xml:space="preserve">全社 25.12 % / 補助 24.28 % / ベース 26.1 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.52 % / 補助 24.91 % / 他 26.23 %</t>
+          <t xml:space="preserve">全社 25.52 % / 補助 24.91 % / ベース 26.23 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24 % / 補助 22.67 % / 他 25.78 %</t>
+          <t xml:space="preserve">全社 24 % / 補助 22.67 % / ベース 25.78 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.84 % / 補助 21.03 % / 他 25.63 %</t>
+          <t xml:space="preserve">全社 22.84 % / 補助 21.03 % / ベース 25.63 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.67 % / 補助 19.54 % / 他 25.46 %</t>
+          <t xml:space="preserve">全社 21.67 % / 補助 19.54 % / ベース 25.46 %</t>
         </is>
       </c>
     </row>
@@ -3808,47 +3808,47 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.06 % / 補助 9.42 % / 他 6.55 %</t>
+          <t xml:space="preserve">全社 8.06 % / 補助 9.42 % / ベース 6.55 %</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.89 % / 補助 9.26 % / 他 6.34 %</t>
+          <t xml:space="preserve">全社 7.89 % / 補助 9.26 % / ベース 6.34 %</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.73 % / 補助 9.13 % / 他 6.14 %</t>
+          <t xml:space="preserve">全社 7.73 % / 補助 9.13 % / ベース 6.14 %</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.3 % / 補助 8.4 % / 他 6.03 %</t>
+          <t xml:space="preserve">全社 7.3 % / 補助 8.4 % / ベース 6.03 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.88 % / 補助 7.72 % / 他 5.9 %</t>
+          <t xml:space="preserve">全社 6.88 % / 補助 7.72 % / ベース 5.9 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.48 % / 補助 7.09 % / 他 5.76 %</t>
+          <t xml:space="preserve">全社 6.48 % / 補助 7.09 % / ベース 5.76 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.64 % / 補助 9.83 % / 他 7.05 %</t>
+          <t xml:space="preserve">全社 8.64 % / 補助 9.83 % / ベース 7.05 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.15 % / 補助 11.96 % / 他 7.36 %</t>
+          <t xml:space="preserve">全社 10.15 % / 補助 11.96 % / ベース 7.36 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.7 % / 補助 13.96 % / 他 7.71 %</t>
+          <t xml:space="preserve">全社 11.7 % / 補助 13.96 % / ベース 7.71 %</t>
         </is>
       </c>
     </row>
@@ -3870,47 +3870,47 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.4 % / 補助 11.92 % / 他 8.7 %</t>
+          <t xml:space="preserve">全社 10.4 % / 補助 11.92 % / ベース 8.7 %</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.22 % / 補助 11.76 % / 他 8.48 %</t>
+          <t xml:space="preserve">全社 10.22 % / 補助 11.76 % / ベース 8.48 %</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.07 % / 補助 11.63 % / 他 8.29 %</t>
+          <t xml:space="preserve">全社 10.07 % / 補助 11.63 % / ベース 8.29 %</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.01 % / 補助 11.68 % / 他 8.08 %</t>
+          <t xml:space="preserve">全社 10.01 % / 補助 11.68 % / ベース 8.08 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.93 % / 補助 11.69 % / 他 7.87 %</t>
+          <t xml:space="preserve">全社 9.93 % / 補助 11.69 % / ベース 7.87 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.83 % / 補助 11.68 % / 他 7.65 %</t>
+          <t xml:space="preserve">全社 9.83 % / 補助 11.68 % / ベース 7.65 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.55 % / 補助 13.59 % / 他 8.81 %</t>
+          <t xml:space="preserve">全社 11.55 % / 補助 13.59 % / ベース 8.81 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.68 % / 補助 15.05 % / 他 9.02 %</t>
+          <t xml:space="preserve">全社 12.68 % / 補助 15.05 % / ベース 9.02 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.88 % / 補助 16.48 % / 他 9.27 %</t>
+          <t xml:space="preserve">全社 13.88 % / 補助 16.48 % / ベース 9.27 %</t>
         </is>
       </c>
     </row>
@@ -3932,47 +3932,47 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.99 % / 補助 12.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 11.99 % / 補助 12.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12 % / 補助 12.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 12 % / 補助 12.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12 % / 補助 12.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 12 % / 補助 12.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12 % / 補助 12.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 12 % / 補助 12.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.01 % / 補助 12.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 12.01 % / 補助 12.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.01 % / 補助 12.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 12.01 % / 補助 12.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.64 % / 補助 12 % / 他 11.15 %</t>
+          <t xml:space="preserve">全社 11.64 % / 補助 12 % / ベース 11.15 %</t>
         </is>
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.3 % / 補助 11.5 % / 他 10.99 %</t>
+          <t xml:space="preserve">全社 11.3 % / 補助 11.5 % / ベース 10.99 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.93 % / 補助 10.99 % / 他 10.82 %</t>
+          <t xml:space="preserve">全社 10.93 % / 補助 10.99 % / ベース 10.82 %</t>
         </is>
       </c>
     </row>
@@ -4056,47 +4056,47 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.01 % / 補助 7.21 % / 他 11.02 %</t>
+          <t xml:space="preserve">全社 9.01 % / 補助 7.21 % / ベース 11.02 %</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.17 % / 補助 7.36 % / 他 11.22 %</t>
+          <t xml:space="preserve">全社 9.17 % / 補助 7.36 % / ベース 11.22 %</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.33 % / 補助 7.5 % / 他 11.43 %</t>
+          <t xml:space="preserve">全社 9.33 % / 補助 7.5 % / ベース 11.43 %</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.5 % / 補助 7.65 % / 他 11.63 %</t>
+          <t xml:space="preserve">全社 9.5 % / 補助 7.65 % / ベース 11.63 %</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.67 % / 補助 7.81 % / 他 11.84 %</t>
+          <t xml:space="preserve">全社 9.67 % / 補助 7.81 % / ベース 11.84 %</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.84 % / 補助 7.96 % / 他 12.05 %</t>
+          <t xml:space="preserve">全社 9.84 % / 補助 7.96 % / ベース 12.05 %</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.1 % / 補助 6.91 % / 他 12.04 %</t>
+          <t xml:space="preserve">全社 9.1 % / 補助 6.91 % / ベース 12.04 %</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.63 % / 補助 6.34 % / 他 12.15 %</t>
+          <t xml:space="preserve">全社 8.63 % / 補助 6.34 % / ベース 12.15 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.14 % / 補助 5.83 % / 他 12.25 %</t>
+          <t xml:space="preserve">全社 8.14 % / 補助 5.83 % / ベース 12.25 %</t>
         </is>
       </c>
     </row>
@@ -4118,47 +4118,47 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / 他 0.85 %</t>
+          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / ベース 0.85 %</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / 他 0.86 %</t>
+          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / ベース 0.86 %</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / 他 0.86 %</t>
+          <t xml:space="preserve">全社 0.67 % / 補助 0.5 % / ベース 0.86 %</t>
         </is>
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.65 % / 補助 0.5 % / 他 0.84 %</t>
+          <t xml:space="preserve">全社 0.65 % / 補助 0.5 % / ベース 0.84 %</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.64 % / 補助 0.49 % / 他 0.81 %</t>
+          <t xml:space="preserve">全社 0.64 % / 補助 0.49 % / ベース 0.81 %</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.64 % / 補助 0.5 % / 他 0.81 %</t>
+          <t xml:space="preserve">全社 0.64 % / 補助 0.5 % / ベース 0.81 %</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.58 % / 補助 0.44 % / 他 0.76 %</t>
+          <t xml:space="preserve">全社 0.58 % / 補助 0.44 % / ベース 0.76 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.52 % / 補助 0.37 % / 他 0.74 %</t>
+          <t xml:space="preserve">全社 0.52 % / 補助 0.37 % / ベース 0.74 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.47 % / 補助 0.32 % / 他 0.72 %</t>
+          <t xml:space="preserve">全社 0.47 % / 補助 0.32 % / ベース 0.72 %</t>
         </is>
       </c>
     </row>
@@ -4180,47 +4180,47 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.68 % / 補助 7.71 % / 他 11.88 %</t>
+          <t xml:space="preserve">全社 9.68 % / 補助 7.71 % / ベース 11.88 %</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.84 % / 補助 7.86 % / 他 12.08 %</t>
+          <t xml:space="preserve">全社 9.84 % / 補助 7.86 % / ベース 12.08 %</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10 % / 補助 8 % / 他 12.29 %</t>
+          <t xml:space="preserve">全社 10 % / 補助 8 % / ベース 12.29 %</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.15 % / 補助 8.15 % / 他 12.47 %</t>
+          <t xml:space="preserve">全社 10.15 % / 補助 8.15 % / ベース 12.47 %</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.31 % / 補助 8.3 % / 他 12.66 %</t>
+          <t xml:space="preserve">全社 10.31 % / 補助 8.3 % / ベース 12.66 %</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.48 % / 補助 8.46 % / 他 12.86 %</t>
+          <t xml:space="preserve">全社 10.48 % / 補助 8.46 % / ベース 12.86 %</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.68 % / 補助 7.35 % / 他 12.8 %</t>
+          <t xml:space="preserve">全社 9.68 % / 補助 7.35 % / ベース 12.8 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.15 % / 補助 6.72 % / 他 12.89 %</t>
+          <t xml:space="preserve">全社 9.15 % / 補助 6.72 % / ベース 12.89 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.61 % / 補助 6.15 % / 他 12.96 %</t>
+          <t xml:space="preserve">全社 8.61 % / 補助 6.15 % / ベース 12.96 %</t>
         </is>
       </c>
     </row>
@@ -4242,47 +4242,47 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.059 億円/人 / 補助 0.058 億円/人 / 他 0.059 億円/人</t>
+          <t xml:space="preserve">全社 0.059 億円/人 / 補助 0.058 億円/人 / ベース 0.059 億円/人</t>
         </is>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.06 億円/人 / 補助 0.059 億円/人 / 他 0.06 億円/人</t>
+          <t xml:space="preserve">全社 0.06 億円/人 / 補助 0.059 億円/人 / ベース 0.06 億円/人</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.061 億円/人 / 補助 0.06 億円/人 / 他 0.062 億円/人</t>
+          <t xml:space="preserve">全社 0.061 億円/人 / 補助 0.06 億円/人 / ベース 0.062 億円/人</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.062 億円/人 / 補助 0.061 億円/人 / 他 0.063 億円/人</t>
+          <t xml:space="preserve">全社 0.062 億円/人 / 補助 0.061 億円/人 / ベース 0.063 億円/人</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.063 億円/人 / 他 0.064 億円/人</t>
+          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.063 億円/人 / ベース 0.064 億円/人</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.065 億円/人 / 補助 0.064 億円/人 / 他 0.065 億円/人</t>
+          <t xml:space="preserve">全社 0.065 億円/人 / 補助 0.064 億円/人 / ベース 0.065 億円/人</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.066 億円/人 / 補助 0.066 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">全社 0.066 億円/人 / 補助 0.066 億円/人 / ベース 0.067 億円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.071 億円/人 / 他 0.069 億円/人</t>
+          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.071 億円/人 / ベース 0.069 億円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.078 億円/人 / 他 0.07 億円/人</t>
+          <t xml:space="preserve">全社 0.074 億円/人 / 補助 0.078 億円/人 / ベース 0.07 億円/人</t>
         </is>
       </c>
     </row>
@@ -4304,47 +4304,47 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.182 億円/人 / 補助 0.18 億円/人 / 他 0.183 億円/人</t>
+          <t xml:space="preserve">全社 0.182 億円/人 / 補助 0.18 億円/人 / ベース 0.183 億円/人</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.192 億円/人 / 補助 0.19 億円/人 / 他 0.193 億円/人</t>
+          <t xml:space="preserve">全社 0.192 億円/人 / 補助 0.19 億円/人 / ベース 0.193 億円/人</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.2 億円/人 / 補助 0.2 億円/人 / 他 0.2 億円/人</t>
+          <t xml:space="preserve">全社 0.2 億円/人 / 補助 0.2 億円/人 / ベース 0.2 億円/人</t>
         </is>
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.206 億円/人 / 補助 0.21 億円/人 / 他 0.203 億円/人</t>
+          <t xml:space="preserve">全社 0.206 億円/人 / 補助 0.21 億円/人 / ベース 0.203 億円/人</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.22 億円/人 / 他 0.207 億円/人</t>
+          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.22 億円/人 / ベース 0.207 億円/人</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.222 億円/人 / 補助 0.235 億円/人 / 他 0.213 億円/人</t>
+          <t xml:space="preserve">全社 0.222 億円/人 / 補助 0.235 億円/人 / ベース 0.213 億円/人</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.23 億円/人 / 補助 0.25 億円/人 / 他 0.217 億円/人</t>
+          <t xml:space="preserve">全社 0.23 億円/人 / 補助 0.25 億円/人 / ベース 0.217 億円/人</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.238 億円/人 / 補助 0.26 億円/人 / 他 0.223 億円/人</t>
+          <t xml:space="preserve">全社 0.238 億円/人 / 補助 0.26 億円/人 / ベース 0.223 億円/人</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.248 億円/人 / 補助 0.275 億円/人 / 他 0.23 億円/人</t>
+          <t xml:space="preserve">全社 0.248 億円/人 / 補助 0.275 億円/人 / ベース 0.23 億円/人</t>
         </is>
       </c>
     </row>
@@ -4366,47 +4366,47 @@
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 — / 補助 — / 他 —</t>
+          <t xml:space="preserve">全社 — / 補助 — / ベース —</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.98 % / 補助 2.04 % / 他 1.95 %</t>
+          <t xml:space="preserve">全社 1.98 % / 補助 2.04 % / ベース 1.95 %</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.99 % / 補助 1.97 % / 他 2.02 %</t>
+          <t xml:space="preserve">全社 1.99 % / 補助 1.97 % / ベース 2.02 %</t>
         </is>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.27 % / 補助 2.38 % / 他 2.19 %</t>
+          <t xml:space="preserve">全社 2.27 % / 補助 2.38 % / ベース 2.19 %</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.68 % / 補助 1.78 % / 他 1.61 %</t>
+          <t xml:space="preserve">全社 1.68 % / 補助 1.78 % / ベース 1.61 %</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.25 % / 補助 1.98 % / 他 2.47 %</t>
+          <t xml:space="preserve">全社 2.25 % / 補助 1.98 % / ベース 2.47 %</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.73 % / 補助 3.25 % / 他 2.31 %</t>
+          <t xml:space="preserve">全社 2.73 % / 補助 3.25 % / ベース 2.31 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.08 % / 補助 8.41 % / 他 2.53 %</t>
+          <t xml:space="preserve">全社 5.08 % / 補助 8.41 % / ベース 2.53 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.25 % / 補助 9.44 % / 他 2 %</t>
+          <t xml:space="preserve">全社 5.25 % / 補助 9.44 % / ベース 2 %</t>
         </is>
       </c>
     </row>
@@ -4428,47 +4428,47 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 48.21 % / 補助 39.28 % / 他 57.74 %</t>
+          <t xml:space="preserve">全社 48.21 % / 補助 39.28 % / ベース 57.74 %</t>
         </is>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.04 % / 補助 40.04 % / 他 58.76 %</t>
+          <t xml:space="preserve">全社 49.04 % / 補助 40.04 % / ベース 58.76 %</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 49.83 % / 補助 40.76 % / 他 59.72 %</t>
+          <t xml:space="preserve">全社 49.83 % / 補助 40.76 % / ベース 59.72 %</t>
         </is>
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.35 % / 補助 41.09 % / 他 60.67 %</t>
+          <t xml:space="preserve">全社 50.35 % / 補助 41.09 % / ベース 60.67 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.94 % / 補助 41.53 % / 他 61.65 %</t>
+          <t xml:space="preserve">全社 50.94 % / 補助 41.53 % / ベース 61.65 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.59 % / 補助 42.02 % / 他 62.69 %</t>
+          <t xml:space="preserve">全社 51.59 % / 補助 42.02 % / ベース 62.69 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.58 % / 補助 35.09 % / 他 59.24 %</t>
+          <t xml:space="preserve">全社 45.58 % / 補助 35.09 % / ベース 59.24 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 41.91 % / 補助 30.86 % / 他 58.83 %</t>
+          <t xml:space="preserve">全社 41.91 % / 補助 30.86 % / ベース 58.83 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.28 % / 補助 27.17 % / 他 58.31 %</t>
+          <t xml:space="preserve">全社 38.28 % / 補助 27.17 % / ベース 58.31 %</t>
         </is>
       </c>
     </row>
@@ -4552,47 +4552,47 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.65 億円/人 / 補助 0.8 億円/人 / 他 0.537 億円/人</t>
+          <t xml:space="preserve">全社 0.65 億円/人 / 補助 0.8 億円/人 / ベース 0.537 億円/人</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.651 億円/人 / 補助 0.8 億円/人 / 他 0.538 億円/人</t>
+          <t xml:space="preserve">全社 0.651 億円/人 / 補助 0.8 億円/人 / ベース 0.538 億円/人</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.652 億円/人 / 補助 0.8 億円/人 / 他 0.538 億円/人</t>
+          <t xml:space="preserve">全社 0.652 億円/人 / 補助 0.8 億円/人 / ベース 0.538 億円/人</t>
         </is>
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.803 億円/人 / 他 0.541 億円/人</t>
+          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.803 億円/人 / ベース 0.541 億円/人</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.801 億円/人 / 他 0.54 億円/人</t>
+          <t xml:space="preserve">全社 0.655 億円/人 / 補助 0.801 億円/人 / ベース 0.54 億円/人</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.658 億円/人 / 補助 0.801 億円/人 / 他 0.543 億円/人</t>
+          <t xml:space="preserve">全社 0.658 億円/人 / 補助 0.801 億円/人 / ベース 0.543 億円/人</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.731 億円/人 / 補助 0.953 億円/人 / 他 0.556 億円/人</t>
+          <t xml:space="preserve">全社 0.731 億円/人 / 補助 0.953 億円/人 / ベース 0.556 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.81 億円/人 / 補助 1.125 億円/人 / 他 0.565 億円/人</t>
+          <t xml:space="preserve">全社 0.81 億円/人 / 補助 1.125 億円/人 / ベース 0.565 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.903 億円/人 / 補助 1.34 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">全社 0.903 億円/人 / 補助 1.34 億円/人 / ベース 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -4614,47 +4614,47 @@
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.052 億円/人 / 補助 0.075 億円/人 / 他 0.035 億円/人</t>
+          <t xml:space="preserve">全社 0.052 億円/人 / 補助 0.075 億円/人 / ベース 0.035 億円/人</t>
         </is>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.051 億円/人 / 補助 0.074 億円/人 / 他 0.034 億円/人</t>
+          <t xml:space="preserve">全社 0.051 億円/人 / 補助 0.074 億円/人 / ベース 0.034 億円/人</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.073 億円/人 / 他 0.033 億円/人</t>
+          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.073 億円/人 / ベース 0.033 億円/人</t>
         </is>
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.048 億円/人 / 補助 0.067 億円/人 / 他 0.033 億円/人</t>
+          <t xml:space="preserve">全社 0.048 億円/人 / 補助 0.067 億円/人 / ベース 0.033 億円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.045 億円/人 / 補助 0.062 億円/人 / 他 0.032 億円/人</t>
+          <t xml:space="preserve">全社 0.045 億円/人 / 補助 0.062 億円/人 / ベース 0.032 億円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.043 億円/人 / 補助 0.057 億円/人 / 他 0.031 億円/人</t>
+          <t xml:space="preserve">全社 0.043 億円/人 / 補助 0.057 億円/人 / ベース 0.031 億円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.094 億円/人 / 他 0.039 億円/人</t>
+          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.094 億円/人 / ベース 0.039 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.135 億円/人 / 他 0.042 億円/人</t>
+          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.135 億円/人 / ベース 0.042 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.106 億円/人 / 補助 0.187 億円/人 / 他 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.106 億円/人 / 補助 0.187 億円/人 / ベース 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -4676,47 +4676,47 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.127 億円/人 / 補助 0.154 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.127 億円/人 / 補助 0.154 億円/人 / ベース 0.108 億円/人</t>
         </is>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.154 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.154 億円/人 / ベース 0.108 億円/人</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.154 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.128 億円/人 / 補助 0.154 億円/人 / ベース 0.108 億円/人</t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.156 億円/人 / 他 0.109 億円/人</t>
+          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.156 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.157 億円/人 / 他 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.157 億円/人 / ベース 0.108 億円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.131 億円/人 / 補助 0.159 億円/人 / 他 0.109 億円/人</t>
+          <t xml:space="preserve">全社 0.131 億円/人 / 補助 0.159 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.152 億円/人 / 補助 0.196 億円/人 / 他 0.118 億円/人</t>
+          <t xml:space="preserve">全社 0.152 億円/人 / 補助 0.196 億円/人 / ベース 0.118 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.174 億円/人 / 補助 0.241 億円/人 / 他 0.122 億円/人</t>
+          <t xml:space="preserve">全社 0.174 億円/人 / 補助 0.241 億円/人 / ベース 0.122 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.2 億円/人 / 補助 0.299 億円/人 / 他 0.125 億円/人</t>
+          <t xml:space="preserve">全社 0.2 億円/人 / 補助 0.299 億円/人 / ベース 0.125 億円/人</t>
         </is>
       </c>
     </row>
@@ -4738,47 +4738,47 @@
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 — / 補助 — / 他 —</t>
+          <t xml:space="preserve">全社 — / 補助 — / ベース —</t>
         </is>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.76 % / 補助 5.56 % / 他 4.17 %</t>
+          <t xml:space="preserve">全社 4.76 % / 補助 5.56 % / ベース 4.17 %</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.55 % / 補助 5.26 % / 他 4 %</t>
+          <t xml:space="preserve">全社 4.55 % / 補助 5.26 % / ベース 4 %</t>
         </is>
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.35 % / 補助 5 % / 他 3.85 %</t>
+          <t xml:space="preserve">全社 4.35 % / 補助 5 % / ベース 3.85 %</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5 % / 補助 5.71 % / 他 4.44 %</t>
+          <t xml:space="preserve">全社 5 % / 補助 5.71 % / ベース 4.44 %</t>
         </is>
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.37 % / 補助 5.41 % / 他 3.55 %</t>
+          <t xml:space="preserve">全社 4.37 % / 補助 5.41 % / ベース 3.55 %</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.8 % / 補助 2.56 % / 他 4.79 %</t>
+          <t xml:space="preserve">全社 3.8 % / 補助 2.56 % / ベース 4.79 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.03 % / 補助 3.33 % / 他 4.58 %</t>
+          <t xml:space="preserve">全社 4.03 % / 補助 3.33 % / ベース 4.58 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.87 % / 補助 2.42 % / 他 5 %</t>
+          <t xml:space="preserve">全社 3.87 % / 補助 2.42 % / ベース 5 %</t>
         </is>
       </c>
     </row>
@@ -4800,47 +4800,47 @@
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 — / 補助 — / 他 —</t>
+          <t xml:space="preserve">全社 — / 補助 — / ベース —</t>
         </is>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.22 pt / 補助 0 pt / 他 0.18 pt</t>
+          <t xml:space="preserve">全社 0.22 pt / 補助 0 pt / ベース 0.18 pt</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.2 pt / 補助 0 pt / 他 0.17 pt</t>
+          <t xml:space="preserve">全社 0.2 pt / 補助 0 pt / ベース 0.17 pt</t>
         </is>
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.53 pt / 補助 0.41 pt / 他 0.41 pt</t>
+          <t xml:space="preserve">全社 0.53 pt / 補助 0.41 pt / ベース 0.41 pt</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 -0.12 pt / 補助 -0.31 pt / 他 -0.18 pt</t>
+          <t xml:space="preserve">全社 -0.12 pt / 補助 -0.31 pt / ベース -0.18 pt</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.51 pt / 補助 0.01 pt / 他 0.71 pt</t>
+          <t xml:space="preserve">全社 0.51 pt / 補助 0.01 pt / ベース 0.71 pt</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.48 pt / 補助 19.46 pt / 他 2.52 pt</t>
+          <t xml:space="preserve">全社 11.48 pt / 補助 19.46 pt / ベース 2.52 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.26 pt / 補助 18.68 pt / 他 1.67 pt</t>
+          <t xml:space="preserve">全社 11.26 pt / 補助 18.68 pt / ベース 1.67 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.96 pt / 補助 19.61 pt / 他 1.27 pt</t>
+          <t xml:space="preserve">全社 11.96 pt / 補助 19.61 pt / ベース 1.27 pt</t>
         </is>
       </c>
     </row>
@@ -4924,47 +4924,47 @@
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.33 % / 補助 2.5 % / 他 2.14 %</t>
+          <t xml:space="preserve">全社 2.33 % / 補助 2.5 % / ベース 2.14 %</t>
         </is>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.33 % / 補助 2.5 % / 他 2.14 %</t>
+          <t xml:space="preserve">全社 2.33 % / 補助 2.5 % / ベース 2.14 %</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.33 % / 補助 2.5 % / 他 2.14 %</t>
+          <t xml:space="preserve">全社 2.33 % / 補助 2.5 % / ベース 2.14 %</t>
         </is>
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.71 % / 補助 3.28 % / 他 2.06 %</t>
+          <t xml:space="preserve">全社 2.71 % / 補助 3.28 % / ベース 2.06 %</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.05 % / 補助 3.97 % / 他 1.97 %</t>
+          <t xml:space="preserve">全社 3.05 % / 補助 3.97 % / ベース 1.97 %</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.35 % / 補助 4.59 % / 他 1.89 %</t>
+          <t xml:space="preserve">全社 3.35 % / 補助 4.59 % / ベース 1.89 %</t>
         </is>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.91 % / 補助 3.76 % / 他 1.76 %</t>
+          <t xml:space="preserve">全社 2.91 % / 補助 3.76 % / ベース 1.76 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.52 % / 補助 3.08 % / 他 1.66 %</t>
+          <t xml:space="preserve">全社 2.52 % / 補助 3.08 % / ベース 1.66 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.18 % / 補助 2.53 % / 他 1.56 %</t>
+          <t xml:space="preserve">全社 2.18 % / 補助 2.53 % / ベース 1.56 %</t>
         </is>
       </c>
     </row>
@@ -5110,47 +5110,47 @@
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.46 倍 / 補助 4.77 倍 / 他 4.06 倍</t>
+          <t xml:space="preserve">全社 4.46 倍 / 補助 4.77 倍 / ベース 4.06 倍</t>
         </is>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.38 倍 / 補助 4.71 倍 / 他 3.96 倍</t>
+          <t xml:space="preserve">全社 4.38 倍 / 補助 4.71 倍 / ベース 3.96 倍</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.31 倍 / 補助 4.65 倍 / 他 3.87 倍</t>
+          <t xml:space="preserve">全社 4.31 倍 / 補助 4.65 倍 / ベース 3.87 倍</t>
         </is>
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / 他 3.93 倍</t>
+          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / ベース 3.93 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.26 倍 / 補助 2.94 倍 / 他 3.99 倍</t>
+          <t xml:space="preserve">全社 3.26 倍 / 補助 2.94 倍 / ベース 3.99 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.93 倍 / 補助 2.54 倍 / 他 4.05 倍</t>
+          <t xml:space="preserve">全社 2.93 倍 / 補助 2.54 倍 / ベース 4.05 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.97 倍 / 補助 3.61 倍 / 他 5 倍</t>
+          <t xml:space="preserve">全社 3.97 倍 / 補助 3.61 倍 / ベース 5 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.03 倍 / 補助 4.88 倍 / 他 5.44 倍</t>
+          <t xml:space="preserve">全社 5.03 倍 / 補助 4.88 倍 / ベース 5.44 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.37 倍 / 補助 6.53 倍 / 他 5.94 倍</t>
+          <t xml:space="preserve">全社 6.37 倍 / 補助 6.53 倍 / ベース 5.94 倍</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. 補助事業とその他事業の比較</t>
+          <t xml:space="preserve">5. 補助事業とベース事業の比較</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
@@ -5358,47 +5358,47 @@
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 — / 他 —</t>
+          <t xml:space="preserve">補助 — / ベース —</t>
         </is>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.56 % / 他 4.35 %</t>
+          <t xml:space="preserve">補助 5.56 % / ベース 4.35 %</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.26 % / 他 4.17 %</t>
+          <t xml:space="preserve">補助 5.26 % / ベース 4.17 %</t>
         </is>
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 5.41 % / 他 4.26 %</t>
+          <t xml:space="preserve">補助 5.41 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.03 % / 他 7.31 %</t>
+          <t xml:space="preserve">補助 22.03 % / ベース 7.31 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.01 % / 他 6.25 %</t>
+          <t xml:space="preserve">補助 22.01 % / ベース 6.25 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.03 % / 他 6.27 %</t>
+          <t xml:space="preserve">補助 22.03 % / ベース 6.27 %</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業原価率－その他事業原価率</t>
+          <t xml:space="preserve">補助事業原価率－ベース事業原価率</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業営業利益率－その他事業営業利益率</t>
+          <t xml:space="preserve">補助事業営業利益率－ベース事業営業利益率</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -5544,47 +5544,47 @@
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.8 億円/人 / 他 0.537 億円/人</t>
+          <t xml:space="preserve">補助 0.8 億円/人 / ベース 0.537 億円/人</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.8 億円/人 / 他 0.538 億円/人</t>
+          <t xml:space="preserve">補助 0.8 億円/人 / ベース 0.538 億円/人</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.8 億円/人 / 他 0.538 億円/人</t>
+          <t xml:space="preserve">補助 0.8 億円/人 / ベース 0.538 億円/人</t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.803 億円/人 / 他 0.541 億円/人</t>
+          <t xml:space="preserve">補助 0.803 億円/人 / ベース 0.541 億円/人</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.801 億円/人 / 他 0.54 億円/人</t>
+          <t xml:space="preserve">補助 0.801 億円/人 / ベース 0.54 億円/人</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.801 億円/人 / 他 0.543 億円/人</t>
+          <t xml:space="preserve">補助 0.801 億円/人 / ベース 0.543 億円/人</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.953 億円/人 / 他 0.556 億円/人</t>
+          <t xml:space="preserve">補助 0.953 億円/人 / ベース 0.556 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.125 億円/人 / 他 0.565 億円/人</t>
+          <t xml:space="preserve">補助 1.125 億円/人 / ベース 0.565 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.34 億円/人 / 他 0.572 億円/人</t>
+          <t xml:space="preserve">補助 1.34 億円/人 / ベース 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -5606,47 +5606,47 @@
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.058 億円/人 / 他 0.059 億円/人</t>
+          <t xml:space="preserve">補助 0.058 億円/人 / ベース 0.059 億円/人</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.059 億円/人 / 他 0.06 億円/人</t>
+          <t xml:space="preserve">補助 0.059 億円/人 / ベース 0.06 億円/人</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.06 億円/人 / 他 0.062 億円/人</t>
+          <t xml:space="preserve">補助 0.06 億円/人 / ベース 0.062 億円/人</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.061 億円/人 / 他 0.063 億円/人</t>
+          <t xml:space="preserve">補助 0.061 億円/人 / ベース 0.063 億円/人</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.063 億円/人 / 他 0.064 億円/人</t>
+          <t xml:space="preserve">補助 0.063 億円/人 / ベース 0.064 億円/人</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.064 億円/人 / 他 0.065 億円/人</t>
+          <t xml:space="preserve">補助 0.064 億円/人 / ベース 0.065 億円/人</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.066 億円/人 / 他 0.067 億円/人</t>
+          <t xml:space="preserve">補助 0.066 億円/人 / ベース 0.067 億円/人</t>
         </is>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.071 億円/人 / 他 0.069 億円/人</t>
+          <t xml:space="preserve">補助 0.071 億円/人 / ベース 0.069 億円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.078 億円/人 / 他 0.07 億円/人</t>
+          <t xml:space="preserve">補助 0.078 億円/人 / ベース 0.07 億円/人</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B10" s="2">
@@ -5957,7 +5957,7 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B11" s="2">
@@ -5978,7 +5978,7 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B12" s="2">
@@ -5999,7 +5999,7 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B13" s="2">
@@ -6020,7 +6020,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6062,7 +6062,7 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B16" s="2">
@@ -6104,7 +6104,7 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B18" s="2">
@@ -6146,7 +6146,7 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B20" s="2">
@@ -6188,7 +6188,7 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -6230,7 +6230,7 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
         </is>
       </c>
       <c r="B24" s="2">

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -1465,22 +1465,22 @@
         <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>38.86</v>
+        <v>38.870000000000005</v>
       </c>
       <c r="F9" s="2">
-        <v>41.44</v>
+        <v>41.47</v>
       </c>
       <c r="G9" s="2">
-        <v>44.15</v>
+        <v>44.18</v>
       </c>
       <c r="H9" s="2">
-        <v>47.87</v>
+        <v>47.93</v>
       </c>
       <c r="I9" s="2">
-        <v>52.519999999999996</v>
+        <v>52.589999999999996</v>
       </c>
       <c r="J9" s="2">
-        <v>57.73</v>
+        <v>57.81</v>
       </c>
     </row>
     <row r="10">
@@ -1499,22 +1499,22 @@
         <v>1</v>
       </c>
       <c r="E10" s="2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="F10" s="2">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="G10" s="2">
-        <v>1.1099999999999999</v>
+        <v>1.1400000000000001</v>
       </c>
       <c r="H10" s="2">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="I10" s="2">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="J10" s="2">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="11">
@@ -1533,22 +1533,22 @@
         <v>0.9</v>
       </c>
       <c r="E11" s="2">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="F11" s="2">
-        <v>0.9600000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="G11" s="2">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="H11" s="2">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I11" s="2">
-        <v>1.06</v>
+        <v>1.1300000000000001</v>
       </c>
       <c r="J11" s="2">
-        <v>1.1099999999999999</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="12">
@@ -1573,16 +1573,16 @@
         <v>0.1</v>
       </c>
       <c r="G12" s="2">
-        <v>0.11</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="H12" s="2">
-        <v>0.11</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="I12" s="2">
         <v>0.13</v>
       </c>
       <c r="J12" s="2">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="13">
@@ -1771,22 +1771,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>11.480000000000004</v>
+        <v>11.470000000000006</v>
       </c>
       <c r="F18" s="4">
-        <v>11.350000000000016</v>
+        <v>11.320000000000014</v>
       </c>
       <c r="G18" s="4">
-        <v>11.210000000000004</v>
+        <v>11.180000000000003</v>
       </c>
       <c r="H18" s="4">
-        <v>17.239999999999988</v>
+        <v>17.179999999999986</v>
       </c>
       <c r="I18" s="4">
-        <v>23.34999999999998</v>
+        <v>23.27999999999998</v>
       </c>
       <c r="J18" s="4">
-        <v>31.170000000000044</v>
+        <v>31.090000000000046</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.297692454389424</v>
+        <v>7.291335579429156</v>
       </c>
       <c r="F19" s="2">
-        <v>6.879621772336049</v>
+        <v>6.861437750030315</v>
       </c>
       <c r="G19" s="2">
-        <v>6.478645321620531</v>
+        <v>6.46130728775357</v>
       </c>
       <c r="H19" s="2">
-        <v>8.64290369479119</v>
+        <v>8.612823983556417</v>
       </c>
       <c r="I19" s="2">
-        <v>10.1539398156201</v>
+        <v>10.12349973908505</v>
       </c>
       <c r="J19" s="2">
-        <v>11.702207538669485</v>
+        <v>11.672172998948808</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>11.3</v>
       </c>
       <c r="E20" s="4">
-        <v>11.169999999999991</v>
+        <v>11.159999999999991</v>
       </c>
       <c r="F20" s="4">
-        <v>11.019999999999996</v>
+        <v>10.989999999999995</v>
       </c>
       <c r="G20" s="4">
-        <v>10.860000000000003</v>
+        <v>10.830000000000005</v>
       </c>
       <c r="H20" s="4">
-        <v>16.009999999999998</v>
+        <v>15.949999999999996</v>
       </c>
       <c r="I20" s="4">
-        <v>22.009999999999984</v>
+        <v>21.939999999999984</v>
       </c>
       <c r="J20" s="4">
-        <v>29.700000000000014</v>
+        <v>29.62000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>11.3</v>
       </c>
       <c r="E21" s="2">
-        <v>11.169999999999991</v>
+        <v>11.159999999999991</v>
       </c>
       <c r="F21" s="2">
-        <v>11.019999999999996</v>
+        <v>10.989999999999995</v>
       </c>
       <c r="G21" s="2">
-        <v>10.860000000000003</v>
+        <v>10.830000000000005</v>
       </c>
       <c r="H21" s="2">
-        <v>16.009999999999998</v>
+        <v>15.949999999999996</v>
       </c>
       <c r="I21" s="2">
-        <v>22.009999999999984</v>
+        <v>21.939999999999984</v>
       </c>
       <c r="J21" s="2">
-        <v>29.700000000000014</v>
+        <v>29.62000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>7.91</v>
       </c>
       <c r="E22" s="2">
-        <v>7.815999999999994</v>
+        <v>7.805999999999994</v>
       </c>
       <c r="F22" s="2">
-        <v>7.711999999999997</v>
+        <v>7.691999999999997</v>
       </c>
       <c r="G22" s="2">
-        <v>7.5980000000000025</v>
+        <v>7.578000000000003</v>
       </c>
       <c r="H22" s="2">
-        <v>11.197999999999997</v>
+        <v>11.157999999999998</v>
       </c>
       <c r="I22" s="2">
-        <v>15.402999999999988</v>
+        <v>15.352999999999987</v>
       </c>
       <c r="J22" s="2">
-        <v>20.78200000000001</v>
+        <v>20.732000000000006</v>
       </c>
     </row>
     <row r="23">
@@ -1975,22 +1975,22 @@
         <v>1</v>
       </c>
       <c r="E24" s="2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="F24" s="2">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="G24" s="2">
-        <v>1.1099999999999999</v>
+        <v>1.1400000000000001</v>
       </c>
       <c r="H24" s="2">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="I24" s="2">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="J24" s="2">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="25">
@@ -2055,7 +2055,7 @@
         <v>42.33999999999998</v>
       </c>
       <c r="I26" s="4">
-        <v>50.17999999999998</v>
+        <v>50.17999999999997</v>
       </c>
       <c r="J26" s="4">
         <v>59.90000000000004</v>
@@ -2091,10 +2091,10 @@
         <v>20.489470688673816</v>
       </c>
       <c r="I27" s="2">
-        <v>18.516769012753898</v>
+        <v>18.516769012753876</v>
       </c>
       <c r="J27" s="2">
-        <v>19.37026703866096</v>
+        <v>19.370267038660984</v>
       </c>
     </row>
     <row r="28">
@@ -2285,22 +2285,22 @@
         <v>0.2</v>
       </c>
       <c r="E33" s="2">
-        <v>0.20600000000000002</v>
+        <v>0.20800000000000002</v>
       </c>
       <c r="F33" s="2">
-        <v>0.21200000000000002</v>
+        <v>0.21800000000000003</v>
       </c>
       <c r="G33" s="2">
-        <v>0.22199999999999998</v>
+        <v>0.22800000000000004</v>
       </c>
       <c r="H33" s="2">
-        <v>0.22999999999999998</v>
+        <v>0.242</v>
       </c>
       <c r="I33" s="2">
-        <v>0.238</v>
+        <v>0.252</v>
       </c>
       <c r="J33" s="2">
-        <v>0.248</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="34">
@@ -2321,22 +2321,22 @@
         <v>4.166666666666674</v>
       </c>
       <c r="E34" s="2">
-        <v>3.0000000000000027</v>
+        <v>4.0000000000000036</v>
       </c>
       <c r="F34" s="2">
-        <v>2.9126213592232997</v>
+        <v>4.807692307692313</v>
       </c>
       <c r="G34" s="2">
-        <v>4.7169811320754595</v>
+        <v>4.587155963302747</v>
       </c>
       <c r="H34" s="2">
-        <v>3.603603603603611</v>
+        <v>6.140350877192957</v>
       </c>
       <c r="I34" s="2">
-        <v>3.4782608695652195</v>
+        <v>4.132231404958686</v>
       </c>
       <c r="J34" s="2">
-        <v>4.201680672268915</v>
+        <v>4.761904761904767</v>
       </c>
     </row>
     <row r="35">
@@ -2367,7 +2367,7 @@
         <v>0.15230215827338123</v>
       </c>
       <c r="I35" s="2">
-        <v>0.1736332179930795</v>
+        <v>0.17363321799307949</v>
       </c>
       <c r="J35" s="2">
         <v>0.1996666666666668</v>
@@ -2389,22 +2389,22 @@
         <v>15.100000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>15.750000000000004</v>
+        <v>15.740000000000006</v>
       </c>
       <c r="F36" s="4">
-        <v>16.380000000000017</v>
+        <v>16.350000000000016</v>
       </c>
       <c r="G36" s="4">
-        <v>17.010000000000005</v>
+        <v>16.980000000000004</v>
       </c>
       <c r="H36" s="4">
-        <v>23.03999999999999</v>
+        <v>22.979999999999986</v>
       </c>
       <c r="I36" s="4">
-        <v>29.14999999999998</v>
+        <v>29.07999999999998</v>
       </c>
       <c r="J36" s="4">
-        <v>36.97000000000004</v>
+        <v>36.89000000000004</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666668</v>
       </c>
       <c r="E37" s="2">
-        <v>10.012078062424514</v>
+        <v>10.005721187464246</v>
       </c>
       <c r="F37" s="2">
-        <v>9.928476178930788</v>
+        <v>9.910292156625054</v>
       </c>
       <c r="G37" s="2">
-        <v>9.830665202566031</v>
+        <v>9.813327168699072</v>
       </c>
       <c r="H37" s="2">
-        <v>11.550609114152497</v>
+        <v>11.520529402917726</v>
       </c>
       <c r="I37" s="2">
-        <v>12.676117585667065</v>
+        <v>12.645677509132017</v>
       </c>
       <c r="J37" s="2">
-        <v>13.879711668418695</v>
+        <v>13.849677128698017</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>3.1420765027322606</v>
       </c>
       <c r="E38" s="2">
-        <v>4.304635761589415</v>
+        <v>4.238410596026521</v>
       </c>
       <c r="F38" s="2">
-        <v>4.000000000000092</v>
+        <v>3.875476493011498</v>
       </c>
       <c r="G38" s="2">
-        <v>3.846153846153766</v>
+        <v>3.85321100917424</v>
       </c>
       <c r="H38" s="2">
-        <v>35.44973544973533</v>
+        <v>35.33568904593629</v>
       </c>
       <c r="I38" s="2">
-        <v>26.51909722222221</v>
+        <v>26.544821583986057</v>
       </c>
       <c r="J38" s="2">
-        <v>26.826758147513097</v>
+        <v>26.856946354883316</v>
       </c>
     </row>
   </sheetData>
@@ -3761,32 +3761,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.7 % / 補助 23.61 % / ベース 25.97 %</t>
+          <t xml:space="preserve">全社 24.71 % / 補助 23.61 % / ベース 25.98 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.12 % / 補助 24.28 % / ベース 26.1 %</t>
+          <t xml:space="preserve">全社 25.14 % / 補助 24.28 % / ベース 26.14 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.52 % / 補助 24.91 % / ベース 26.23 %</t>
+          <t xml:space="preserve">全社 25.53 % / 補助 24.91 % / ベース 26.27 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24 % / 補助 22.67 % / ベース 25.78 %</t>
+          <t xml:space="preserve">全社 24.03 % / 補助 22.67 % / ベース 25.85 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.84 % / 補助 21.03 % / ベース 25.63 %</t>
+          <t xml:space="preserve">全社 22.87 % / 補助 21.03 % / ベース 25.7 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.67 % / 補助 19.54 % / ベース 25.46 %</t>
+          <t xml:space="preserve">全社 21.7 % / 補助 19.54 % / ベース 25.54 %</t>
         </is>
       </c>
     </row>
@@ -3823,32 +3823,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.3 % / 補助 8.4 % / ベース 6.03 %</t>
+          <t xml:space="preserve">全社 7.29 % / 補助 8.4 % / ベース 6.02 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.88 % / 補助 7.72 % / ベース 5.9 %</t>
+          <t xml:space="preserve">全社 6.86 % / 補助 7.72 % / ベース 5.86 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.48 % / 補助 7.09 % / ベース 5.76 %</t>
+          <t xml:space="preserve">全社 6.46 % / 補助 7.09 % / ベース 5.72 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.64 % / 補助 9.83 % / ベース 7.05 %</t>
+          <t xml:space="preserve">全社 8.61 % / 補助 9.83 % / ベース 6.98 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.15 % / 補助 11.96 % / ベース 7.36 %</t>
+          <t xml:space="preserve">全社 10.12 % / 補助 11.96 % / ベース 7.29 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.7 % / 補助 13.96 % / ベース 7.71 %</t>
+          <t xml:space="preserve">全社 11.67 % / 補助 13.96 % / ベース 7.63 %</t>
         </is>
       </c>
     </row>
@@ -3885,32 +3885,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.01 % / 補助 11.68 % / ベース 8.08 %</t>
+          <t xml:space="preserve">全社 10.01 % / 補助 11.68 % / ベース 8.07 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.93 % / 補助 11.69 % / ベース 7.87 %</t>
+          <t xml:space="preserve">全社 9.91 % / 補助 11.69 % / ベース 7.83 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.83 % / 補助 11.68 % / ベース 7.65 %</t>
+          <t xml:space="preserve">全社 9.81 % / 補助 11.68 % / ベース 7.61 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.55 % / 補助 13.59 % / ベース 8.81 %</t>
+          <t xml:space="preserve">全社 11.52 % / 補助 13.59 % / ベース 8.74 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.68 % / 補助 15.05 % / ベース 9.02 %</t>
+          <t xml:space="preserve">全社 12.65 % / 補助 15.05 % / ベース 8.94 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.88 % / 補助 16.48 % / ベース 9.27 %</t>
+          <t xml:space="preserve">全社 13.85 % / 補助 16.48 % / ベース 9.19 %</t>
         </is>
       </c>
     </row>
@@ -4133,32 +4133,32 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.65 % / 補助 0.5 % / ベース 0.84 %</t>
+          <t xml:space="preserve">全社 0.66 % / 補助 0.5 % / ベース 0.85 %</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.64 % / 補助 0.49 % / ベース 0.81 %</t>
+          <t xml:space="preserve">全社 0.66 % / 補助 0.49 % / ベース 0.85 %</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.64 % / 補助 0.5 % / ベース 0.81 %</t>
+          <t xml:space="preserve">全社 0.66 % / 補助 0.5 % / ベース 0.84 %</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.58 % / 補助 0.44 % / ベース 0.76 %</t>
+          <t xml:space="preserve">全社 0.61 % / 補助 0.44 % / ベース 0.83 %</t>
         </is>
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.52 % / 補助 0.37 % / ベース 0.74 %</t>
+          <t xml:space="preserve">全社 0.55 % / 補助 0.37 % / ベース 0.82 %</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.47 % / 補助 0.32 % / ベース 0.72 %</t>
+          <t xml:space="preserve">全社 0.5 % / 補助 0.32 % / ベース 0.8 %</t>
         </is>
       </c>
     </row>
@@ -4195,32 +4195,32 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.15 % / 補助 8.15 % / ベース 12.47 %</t>
+          <t xml:space="preserve">全社 10.16 % / 補助 8.15 % / ベース 12.48 %</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.31 % / 補助 8.3 % / ベース 12.66 %</t>
+          <t xml:space="preserve">全社 10.33 % / 補助 8.3 % / ベース 12.7 %</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.48 % / 補助 8.46 % / ベース 12.86 %</t>
+          <t xml:space="preserve">全社 10.5 % / 補助 8.46 % / ベース 12.9 %</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.68 % / 補助 7.35 % / ベース 12.8 %</t>
+          <t xml:space="preserve">全社 9.71 % / 補助 7.35 % / ベース 12.87 %</t>
         </is>
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.15 % / 補助 6.72 % / ベース 12.89 %</t>
+          <t xml:space="preserve">全社 9.18 % / 補助 6.72 % / ベース 12.97 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.61 % / 補助 6.15 % / ベース 12.96 %</t>
+          <t xml:space="preserve">全社 8.64 % / 補助 6.15 % / ベース 13.05 %</t>
         </is>
       </c>
     </row>
@@ -4319,32 +4319,32 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.206 億円/人 / 補助 0.21 億円/人 / ベース 0.203 億円/人</t>
+          <t xml:space="preserve">全社 0.208 億円/人 / 補助 0.21 億円/人 / ベース 0.207 億円/人</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.212 億円/人 / 補助 0.22 億円/人 / ベース 0.207 億円/人</t>
+          <t xml:space="preserve">全社 0.218 億円/人 / 補助 0.22 億円/人 / ベース 0.217 億円/人</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.222 億円/人 / 補助 0.235 億円/人 / ベース 0.213 億円/人</t>
+          <t xml:space="preserve">全社 0.228 億円/人 / 補助 0.235 億円/人 / ベース 0.223 億円/人</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.23 億円/人 / 補助 0.25 億円/人 / ベース 0.217 億円/人</t>
+          <t xml:space="preserve">全社 0.242 億円/人 / 補助 0.25 億円/人 / ベース 0.237 億円/人</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.238 億円/人 / 補助 0.26 億円/人 / ベース 0.223 億円/人</t>
+          <t xml:space="preserve">全社 0.252 億円/人 / 補助 0.26 億円/人 / ベース 0.247 億円/人</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.248 億円/人 / 補助 0.275 億円/人 / ベース 0.23 億円/人</t>
+          <t xml:space="preserve">全社 0.264 億円/人 / 補助 0.275 億円/人 / ベース 0.257 億円/人</t>
         </is>
       </c>
     </row>
@@ -4443,32 +4443,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.35 % / 補助 41.09 % / ベース 60.67 %</t>
+          <t xml:space="preserve">全社 50.38 % / 補助 41.09 % / ベース 60.73 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.94 % / 補助 41.53 % / ベース 61.65 %</t>
+          <t xml:space="preserve">全社 51.03 % / 補助 41.53 % / ベース 61.84 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.59 % / 補助 42.02 % / ベース 62.69 %</t>
+          <t xml:space="preserve">全社 51.68 % / 補助 42.02 % / ベース 62.88 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.58 % / 補助 35.09 % / ベース 59.24 %</t>
+          <t xml:space="preserve">全社 45.73 % / 補助 35.09 % / ベース 59.57 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 41.91 % / 補助 30.86 % / ベース 58.83 %</t>
+          <t xml:space="preserve">全社 42.05 % / 補助 30.86 % / ベース 59.18 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.28 % / 補助 27.17 % / ベース 58.31 %</t>
+          <t xml:space="preserve">全社 38.41 % / 補助 27.17 % / ベース 58.68 %</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4649,12 @@
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.135 億円/人 / ベース 0.042 億円/人</t>
+          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.135 億円/人 / ベース 0.041 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.106 億円/人 / 補助 0.187 億円/人 / ベース 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.105 億円/人 / 補助 0.187 億円/人 / ベース 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -5001,17 +5001,17 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.54 %</t>
+          <t xml:space="preserve">全社 4.88 %</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.09 %</t>
+          <t xml:space="preserve">全社 4.65 %</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.67 %</t>
+          <t xml:space="preserve">全社 4.43 %</t>
         </is>
       </c>
       <c r="J27" s="0" t="inlineStr">
@@ -5063,17 +5063,17 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.95 倍</t>
+          <t xml:space="preserve">全社 0.49 倍</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.92 倍</t>
+          <t xml:space="preserve">全社 0.47 倍</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.88 倍</t>
+          <t xml:space="preserve">全社 0.45 倍</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
@@ -5130,27 +5130,27 @@
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.26 倍 / 補助 2.94 倍 / ベース 3.99 倍</t>
+          <t xml:space="preserve">全社 3.25 倍 / 補助 2.94 倍 / ベース 3.97 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.93 倍 / 補助 2.54 倍 / ベース 4.05 倍</t>
+          <t xml:space="preserve">全社 2.93 倍 / 補助 2.54 倍 / ベース 4.03 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.97 倍 / 補助 3.61 倍 / ベース 5 倍</t>
+          <t xml:space="preserve">全社 3.96 倍 / 補助 3.61 倍 / ベース 4.96 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.03 倍 / 補助 4.88 倍 / ベース 5.44 倍</t>
+          <t xml:space="preserve">全社 5.01 倍 / 補助 4.88 倍 / ベース 5.39 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.37 倍 / 補助 6.53 倍 / ベース 5.94 倍</t>
+          <t xml:space="preserve">全社 6.36 倍 / 補助 6.53 倍 / ベース 5.89 倍</t>
         </is>
       </c>
     </row>
@@ -5187,17 +5187,17 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.49 倍</t>
+          <t xml:space="preserve">全社 0.95 倍</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.51 倍</t>
+          <t xml:space="preserve">全社 1 倍</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.54 倍</t>
+          <t xml:space="preserve">全社 1.05 倍</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
@@ -5497,32 +5497,32 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.37 pt</t>
+          <t xml:space="preserve">差 2.38 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.82 pt</t>
+          <t xml:space="preserve">差 1.86 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.33 pt</t>
+          <t xml:space="preserve">差 1.36 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.78 pt</t>
+          <t xml:space="preserve">差 2.85 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.6 pt</t>
+          <t xml:space="preserve">差 4.68 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.25 pt</t>
+          <t xml:space="preserve">差 6.33 pt</t>
         </is>
       </c>
     </row>
@@ -5683,12 +5683,12 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 183.33 %</t>
+          <t xml:space="preserve">寄与率 169.23 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 169.23 %</t>
+          <t xml:space="preserve">寄与率 146.67 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
@@ -5698,17 +5698,17 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 76.29 %</t>
+          <t xml:space="preserve">寄与率 76.67 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 89.2 %</t>
+          <t xml:space="preserve">寄与率 89.34 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.41 %</t>
+          <t xml:space="preserve">寄与率 90.52 %</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5810,11 +5810,11 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率（売上実績が0の場合の開始水準）</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <v>5.409356725146197</v>
+        <v>68</v>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
@@ -5822,20 +5822,20 @@
         </is>
       </c>
       <c r="D4" s="2">
-        <v>5.116959064327475</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>5.701754385964919</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率（売上実績が0の場合の開始水準）</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>5.551115123125783e-15</v>
+        <v>68</v>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
@@ -5846,34 +5846,34 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>1.6653345369377348e-14</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">実効税率</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>2.0030662342518046</v>
+        <v>30</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>1.9325330501846927</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2">
-        <v>2.0735994183189166</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B7" s="2">
@@ -5894,11 +5894,11 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>0</v>
+        <v>5.551115123125783e-15</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -5909,38 +5909,38 @@
         <v>0</v>
       </c>
       <c r="E8" s="2">
-        <v>0</v>
+        <v>1.6653345369377348e-14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>5.409356725146197</v>
+        <v>2.0030662342518046</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D9" s="2">
-        <v>5.116959064327475</v>
+        <v>1.9325330501846927</v>
       </c>
       <c r="E9" s="2">
-        <v>5.701754385964919</v>
+        <v>2.0735994183189166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>4.257246376811585</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -5948,16 +5948,16 @@
         </is>
       </c>
       <c r="D10" s="2">
-        <v>4.076086956521719</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E10" s="2">
-        <v>4.438405797101453</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B11" s="2">
@@ -5972,17 +5972,17 @@
         <v>0</v>
       </c>
       <c r="E11" s="2">
-        <v>0.013457556935819737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>1.984645846924027</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -5990,20 +5990,20 @@
         </is>
       </c>
       <c r="D12" s="2">
-        <v>1.9139457023717443</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E12" s="2">
-        <v>2.0553459914763095</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>4.083333333333339</v>
+        <v>4.257246376811585</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         </is>
       </c>
       <c r="D13" s="2">
-        <v>3.9166666666666683</v>
+        <v>4.076086956521719</v>
       </c>
       <c r="E13" s="2">
-        <v>4.250000000000009</v>
+        <v>4.438405797101453</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6035,17 +6035,17 @@
         <v>0</v>
       </c>
       <c r="E14" s="2">
-        <v>0</v>
+        <v>0.013457556935819737</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>22</v>
+        <v>1.984645846924027</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6053,20 +6053,20 @@
         </is>
       </c>
       <c r="D15" s="2">
-        <v>15</v>
+        <v>1.9139457023717443</v>
       </c>
       <c r="E15" s="2">
-        <v>30</v>
+        <v>2.0553459914763095</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>6.257246376811586</v>
+        <v>4</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6074,20 +6074,20 @@
         </is>
       </c>
       <c r="D16" s="2">
-        <v>6.076086956521719</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2">
-        <v>6.438405797101453</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>1.5</v>
+        <v>4.083333333333339</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -6095,20 +6095,20 @@
         </is>
       </c>
       <c r="D17" s="2">
-        <v>0</v>
+        <v>3.9166666666666683</v>
       </c>
       <c r="E17" s="2">
-        <v>3</v>
+        <v>4.250000000000009</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -6116,20 +6116,20 @@
         </is>
       </c>
       <c r="D18" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2">
-        <v>0.5134575569358197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>7.000000000000001</v>
+        <v>22</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -6137,20 +6137,20 @@
         </is>
       </c>
       <c r="D19" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E19" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>2.484645846924027</v>
+        <v>6.257246376811586</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6158,20 +6158,20 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <v>2.4139457023717443</v>
+        <v>6.076086956521719</v>
       </c>
       <c r="E20" s="2">
-        <v>2.5553459914763095</v>
+        <v>6.438405797101453</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
@@ -6182,17 +6182,17 @@
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>4.583333333333338</v>
+        <v>0.5</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6200,20 +6200,20 @@
         </is>
       </c>
       <c r="D22" s="2">
-        <v>4.416666666666668</v>
+        <v>0.5</v>
       </c>
       <c r="E22" s="2">
-        <v>4.750000000000009</v>
+        <v>0.5134575569358197</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>11</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6221,20 +6221,20 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="E23" s="2">
-        <v>13.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>10.928571428571427</v>
+        <v>2.484645846924027</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6242,20 +6242,20 @@
         </is>
       </c>
       <c r="D24" s="2">
-        <v>8.928571428571427</v>
+        <v>2.4139457023717443</v>
       </c>
       <c r="E24" s="2">
-        <v>11.928571428571427</v>
+        <v>2.5553459914763095</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>5.380116959064325</v>
+        <v>4.5</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6263,82 +6263,187 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>4.263157894736836</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2">
-        <v>6.555555555555557</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新規投資の耐用年数</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業投資額</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>23</v>
+        <v>4.583333333333338</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D27" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E27" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D27" s="2">
+        <v>4.416666666666668</v>
+      </c>
+      <c r="E27" s="2">
+        <v>4.750000000000009</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B28" s="2">
+        <v>11</v>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D28" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="E28" s="2">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B29" s="2">
+        <v>10.928571428571427</v>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D29" s="2">
+        <v>8.928571428571427</v>
+      </c>
+      <c r="E29" s="2">
+        <v>11.928571428571427</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B30" s="2">
+        <v>5.380116959064325</v>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D30" s="2">
+        <v>4.263157894736836</v>
+      </c>
+      <c r="E30" s="2">
+        <v>6.555555555555557</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新規投資の耐用年数</t>
+        </is>
+      </c>
+      <c r="B31" s="2">
+        <v>10</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業投資額</t>
+        </is>
+      </c>
+      <c r="B32" s="2">
+        <v>23</v>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
-      <c r="B28" s="2">
+      <c r="B33" s="2">
         <v>7.66</v>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限7.66億円）</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6350,7 +6455,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C244"/>
+  <dimension ref="A1:C259"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -8285,26 +8390,26 @@
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:0</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:0</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:1</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:1</t>
         </is>
       </c>
       <c r="B130" s="2">
-        <v>200</v>
+        <v>0.6</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8315,26 +8420,26 @@
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+          <t xml:space="preserve">driver-range:investment:0</t>
         </is>
       </c>
       <c r="B131" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+          <t xml:space="preserve">driver-range:investment:1</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
@@ -8345,26 +8450,26 @@
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
         </is>
       </c>
       <c r="B133" s="2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>0.0051345755693581975</v>
+        <v>100</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
@@ -8375,26 +8480,26 @@
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B135" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0.00013457556935819737</v>
+        <v>0.0051345755693581975</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
@@ -8405,26 +8510,26 @@
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0.04416666666666668</v>
+        <v>0</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0.04750000000000009</v>
+        <v>0.00013457556935819737</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
@@ -8435,26 +8540,26 @@
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>0.03916666666666668</v>
+        <v>0</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0.04250000000000009</v>
+        <v>0.99</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
@@ -8465,11 +8570,11 @@
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0.024139457023717444</v>
+        <v>0.04416666666666668</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
@@ -8480,11 +8585,11 @@
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0.025553459914763096</v>
+        <v>0.04750000000000009</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
@@ -8495,11 +8600,11 @@
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0.019139457023717443</v>
+        <v>0.03916666666666668</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
@@ -8510,11 +8615,11 @@
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0.020553459914763095</v>
+        <v>0.04250000000000009</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -8525,26 +8630,26 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0.06076086956521719</v>
+        <v>0</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>0.06438405797101453</v>
+        <v>0.08</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
@@ -8555,26 +8660,26 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0.040760869565217184</v>
+        <v>0</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0.04438405797101452</v>
+        <v>0.08</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
@@ -8585,41 +8690,41 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0</v>
+        <v>0.024139457023717444</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0</v>
+        <v>0.025553459914763096</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.08928571428571427</v>
+        <v>0.019139457023717443</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -8630,11 +8735,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.11928571428571427</v>
+        <v>0.020553459914763095</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -8645,26 +8750,26 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>0</v>
+        <v>0.06076086956521719</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>0.03</v>
+        <v>0.06438405797101453</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -8675,26 +8780,26 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0</v>
+        <v>0.040760869565217184</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>1.6653345369377348e-16</v>
+        <v>0.04438405797101452</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
@@ -8705,7 +8810,7 @@
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B157" s="2">
@@ -8720,26 +8825,26 @@
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.051169590643274754</v>
+        <v>0.08928571428571427</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -8750,11 +8855,11 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.11928571428571427</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
@@ -8765,26 +8870,26 @@
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -8795,26 +8900,26 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0.04263157894736836</v>
+        <v>0</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>0.06555555555555558</v>
+        <v>1.6653345369377348e-16</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -8825,26 +8930,26 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.99</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
@@ -8855,26 +8960,26 @@
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
@@ -8885,11 +8990,11 @@
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>0.019325330501846927</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
@@ -8900,11 +9005,11 @@
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.020735994183189166</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
@@ -8915,11 +9020,11 @@
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
@@ -8930,7 +9035,7 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B172" s="2">
@@ -8945,11 +9050,11 @@
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0.051169590643274754</v>
+        <v>0.04263157894736836</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
@@ -8960,11 +9065,11 @@
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.06555555555555558</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -8975,41 +9080,41 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0.08499999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
@@ -9020,11 +9125,11 @@
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0.135</v>
+        <v>0.1</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
@@ -9035,11 +9140,11 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>1</v>
+        <v>0.019325330501846927</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
@@ -9050,11 +9155,11 @@
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>50</v>
+        <v>0.020735994183189166</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
@@ -9065,11 +9170,11 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>5</v>
+        <v>0.15</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
@@ -9080,11 +9185,11 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>20</v>
+        <v>0.3</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -9095,11 +9200,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>23</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9110,11 +9215,11 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>23</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
@@ -9125,22 +9230,22 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B186" s="2">
@@ -9155,11 +9260,11 @@
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.045833333333333386</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9170,11 +9275,11 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.04083333333333339</v>
+        <v>0.135</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9185,11 +9290,11 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0.02484645846924027</v>
+        <v>1</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9200,11 +9305,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>0.01984645846924027</v>
+        <v>50</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9215,11 +9320,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>0.06257246376811586</v>
+        <v>5</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9230,11 +9335,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>0.042572463768115854</v>
+        <v>20</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9245,26 +9350,26 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>0.10928571428571428</v>
+        <v>23</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9275,11 +9380,11 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>0.015</v>
+        <v>23</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -9290,11 +9395,11 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>5.551115123125783e-17</v>
+        <v>0.005</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
@@ -9305,26 +9410,26 @@
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.68</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
@@ -9335,11 +9440,11 @@
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.05</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9350,11 +9455,11 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0.05380116959064325</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
@@ -9365,11 +9470,11 @@
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.045</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9380,11 +9485,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9395,11 +9500,11 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>0.020030662342518046</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
@@ -9410,11 +9515,11 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>0.22</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9425,11 +9530,11 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9440,41 +9545,41 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>7.66</v>
+        <v>0.10928571428571428</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -9485,11 +9590,11 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>10</v>
+        <v>0.015</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
@@ -9500,11 +9605,11 @@
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>15</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
@@ -9515,11 +9620,11 @@
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>15</v>
+        <v>0.68</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9530,11 +9635,11 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>15</v>
+        <v>0.04</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
@@ -9545,56 +9650,56 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>0</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>0</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>7</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -9605,11 +9710,11 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>2</v>
+        <v>0.07</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -9620,11 +9725,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>35</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -9635,11 +9740,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>15</v>
+        <v>0.22</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -9650,11 +9755,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>252.69</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -9665,26 +9770,26 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>82.4</v>
+        <v>0</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>10</v>
+        <v>0.11</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -9695,11 +9800,11 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>7</v>
+        <v>7.66</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -9710,11 +9815,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">driver:usefulLife</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>3.74</v>
+        <v>10</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -9725,11 +9830,11 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">future-capex:2026</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>2.85</v>
+        <v>7.67</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
@@ -9740,11 +9845,11 @@
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">future-capex:2027</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>70</v>
+        <v>7.67</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -9755,11 +9860,11 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">future-capex:2028</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>15</v>
+        <v>7.66</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -9770,56 +9875,56 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">future-capex:2029</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">future-capex:2030</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">future-capex:2031</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -9830,11 +9935,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -9845,11 +9950,11 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
@@ -9860,26 +9965,26 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>35</v>
+        <v>252.69</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -9890,11 +9995,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>22</v>
+        <v>82.4</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -9905,11 +10010,11 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>136.84</v>
+        <v>10</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
@@ -9920,11 +10025,11 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>74.8</v>
+        <v>7</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
@@ -9935,11 +10040,11 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>95</v>
+        <v>3.74</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -9950,11 +10055,11 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>60</v>
+        <v>2.85</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
@@ -9965,11 +10070,11 @@
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>33.43</v>
+        <v>70</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -9980,11 +10085,11 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>18.78</v>
+        <v>15</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -9995,11 +10100,11 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>350</v>
+        <v>35</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10010,13 +10115,238 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+        </is>
+      </c>
+      <c r="B244" s="2">
+        <v>21</v>
+      </c>
+      <c r="C244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B245" s="2">
+        <v>40</v>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B246" s="2">
+        <v>23</v>
+      </c>
+      <c r="C246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B247" s="2">
+        <v>10</v>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B248" s="2">
+        <v>6</v>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B249" s="2">
+        <v>0</v>
+      </c>
+      <c r="C249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B250" s="2">
+        <v>35</v>
+      </c>
+      <c r="C250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B251" s="2">
+        <v>22</v>
+      </c>
+      <c r="C251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+        </is>
+      </c>
+      <c r="B252" s="2">
+        <v>136.84</v>
+      </c>
+      <c r="C252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B253" s="2">
+        <v>74.8</v>
+      </c>
+      <c r="C253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B254" s="2">
+        <v>95</v>
+      </c>
+      <c r="C254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B255" s="2">
+        <v>60</v>
+      </c>
+      <c r="C255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+        </is>
+      </c>
+      <c r="B256" s="2">
+        <v>33.43</v>
+      </c>
+      <c r="C256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B257" s="2">
+        <v>18.78</v>
+      </c>
+      <c r="C257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B258" s="2">
+        <v>350</v>
+      </c>
+      <c r="C258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B244" s="2">
+      <c r="B259" s="2">
         <v>213</v>
       </c>
-      <c r="C244" s="0" t="inlineStr">
+      <c r="C259" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -10044,7 +10374,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Mi43NjQwMDAwMDAwMDAwMDJ9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2LCJjb2dzIjo1MS42OCwiZW1wbG95ZWVQYXkiOjUuNTksIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjIsImVtcGxveWVlU2FsYXJ5Ijo1LjMxLCJlbXBsb3llZUJvbnVzIjowLjI4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjM0LCJvZmZpY2VyQm9udXMiOjAuMDQsImNvZ3NEZXByZWNpYXRpb24iOjAuNDcsInNnYURlcHJlY2lhdGlvbiI6MS40MywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4zOH0sIm90aGVyIjp7InNhbGVzIjo2Ny4yLCJjb2dzIjo0NS43LCJlbXBsb3llZVBheSI6Ny41NCwib2ZmaWNlclBheSI6MC41OCwiZGVwcmVjaWF0aW9uIjoxLjQ0LCJvdGhlclNnYSI6Ny42OCwiaGVhZGNvdW50IjoxMjUsIm9mZmljZXJDb3VudCI6MywiZW1wbG95ZWVTYWxhcnkiOjcuMTYsImVtcGxveWVlQm9udXMiOjAuMzgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTIsIm9mZmljZXJCb251cyI6MC4wNiwiY29nc0RlcHJlY2lhdGlvbiI6MC4yOSwic2dhRGVwcmVjaWF0aW9uIjoxLjE1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI5LCJvcmRpbmFyeUluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsInByZVRheEluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsIm5ldEluY29tZSI6Mi43ODE5OTk5OTk5OTk5OTgzfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjIuNzk5OTk5OTk5OTk5OTk3fX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjoxNX0seyJ5ZWFyIjoyMDI3LCJ2YWx1ZSI6MTV9LHsieWVhciI6MjAyOCwidmFsdWUiOjE1fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI4NTcxNDI4NTcxNDI4LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9LCJkcml2ZXJSYW5nZXMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6Wy0wLjA1LDAuM10sInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwxLjY2NTMzNDUzNjkzNzczNDhlLTE2XSwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MzI1MzMwNTAxODQ2OTI3LDAuMDIwNzM1OTk0MTgzMTg5MTY2XSwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDBdLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6WzAuMDUxMTY5NTkwNjQzMjc0NzU0LDAuMDU3MDE3NTQzODU5NjQ5MTldLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNDA3NjA4Njk1NjUyMTcxODQsMC4wNDQzODQwNTc5NzEwMTQ1Ml0sIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjpbMCwwLjAwMDEzNDU3NTU2OTM1ODE5NzM3XSwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOlswLjAxOTEzOTQ1NzAyMzcxNzQ0MywwLjAyMDU1MzQ1OTkxNDc2MzA5NV0sIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wMzkxNjY2NjY2NjY2NjY2OCwwLjA0MjUwMDAwMDAwMDAwMDA5XSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RTYWxlc0dyb3d0aCI6WzAuMTUsMC4zXSwib3RoZXJTYWxlc0dyb3d0aCI6WzAuMDYwNzYwODY5NTY1MjE3MTksMC4wNjQzODQwNTc5NzEwMTQ1M10sInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOlswLDAuMDNdLCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6WzAuMDA1LDAuMDA1MTM0NTc1NTY5MzU4MTk3NV0sInByb2plY3RQYXlHcm93dGgiOlswLjA1LDAuMV0sIm90aGVyUGF5R3Jvd3RoIjpbMC4wMjQxMzk0NTcwMjM3MTc0NDQsMC4wMjU1NTM0NTk5MTQ3NjMwOTZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGgiOlswLjA0NDE2NjY2NjY2NjY2NjY4LDAuMDQ3NTAwMDAwMDAwMDAwMDldLCJwcm9qZWN0U2dhUmF0ZUVuZCI6WzAuMDg0OTk5OTk5OTk5OTk5OTksMC4xMzVdLCJvdGhlclNnYVJhdGVFbmQiOlswLjA4OTI4NTcxNDI4NTcxNDI3LDAuMTE5Mjg1NzE0Mjg1NzE0MjddLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6WzAuMDQyNjMxNTc4OTQ3MzY4MzYsMC4wNjU1NTU1NTU1NTU1NTU1OF0sInVzZWZ1bExpZmUiOls1LDIwXSwiaW52ZXN0bWVudCI6WzE1LDIwMF0sInN1YnNpZHkiOlsxLDUwXSwibG9jYWxCZW5jaG1hcmsiOlswLDEwMF19LCJ0YXJnZXRzIjp7ImNvbXBhbnlTYWxlc0NhZ3IiOnsidmFsdWUiOjE1LCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjgyLjQsIm1heCI6MjUyLjY5LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiY29tcGFueVBheVNjaGVkdWxlIjp7InZhbHVlIjoyLCJtYXgiOjcsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNTaGFyZSI6eyJ2YWx1ZSI6NjAsIm1heCI6OTUsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJwcm9qZWN0U2FsZXNDYWdyIjp7InZhbHVlIjoyMiwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0luY3JlYXNlIjp7InZhbHVlIjo3NC44LCJtYXgiOjEzNi44NCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxhYm9yUHJvZHVjdGl2aXR5Q2FnciI6eyJ2YWx1ZSI6MjEsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkSW5jcmVhc2UiOnsidmFsdWUiOjE4Ljc4LCJtYXgiOjMzLjQzLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlDYWdyIjp7InZhbHVlIjo3LCJtYXgiOjEwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiZW1wbG95ZWVQYXlJbmNyZWFzZSI6eyJ2YWx1ZSI6Mi44NSwibWF4IjozLjc0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwiaW52ZXN0bWVudFNhbGVzUmF0aW8iOnsidmFsdWUiOjE1LCJtYXgiOjcwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwidmFsdWVBZGRlZFN1YnNpZHlSYXRpbyI6eyJ2YWx1ZSI6MjEzLCJtYXgiOjM1MCwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sImxvY2FsQmVuY2htYXJrIjp7InZhbHVlIjoyMywibWF4Ijo0MCwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sIm9mZmljZXJQYXlDYWdyIjp7InZhbHVlIjo2LCJtYXgiOjEwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUluY3JlYXNlIjp7InZhbHVlIjowLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfX0sImZvcmVjYXN0T3ZlcnJpZGVzIjp7IjIwMjk6b3RoZXI6c2FsZXMiOjg1LjEzLCIyMDI5OnByb2plY3Q6Ny04Ijo3Ljl9LCJmdXR1cmVJbnB1dEJhc2lzIjoib3RoZXIiLCJpbnB1dFZhbHVlcyI6eyJhY3R1YWw6Y29tcGFueToyMDIzOjItMSI6MTM2LjQsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0zIjo5Mi43NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTQiOjAuNzMsImFjdHVhbDpjb21wYW55OjIwMjM6Mi03IjozMi42NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTkiOjAuODIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xMCI6MC4wOSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEyIjoxMS42NywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEzIjowLjYyLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTQiOjIuNDUsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNSI6MC42NCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE4IjoxMC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE5IjoxMC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTIwIjo3LjUxLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjciOjIxMCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMSI6NzIsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny00IjoyMy4wNCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTYiOjYuNzgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny04Ijo1LjE5LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctOSI6MC4zNiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEwIjoxLjgsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjo3LjcxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjU5LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MC4zOCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEwIjoxLjksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xMyI6OTUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEiOjE1MCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTMiOjEwMiwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTQiOjAuOCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTciOjM2LjQsImFjdHVhbDpjb21wYW55OjIwMjU6Mi05IjowLjksImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTIiOjEzLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMyI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTQiOjIuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE1IjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOCI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE5IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjAiOjcuOTEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yNyI6MjMwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xIjo4MCwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTQiOjI1LjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny02Ijo3LjMsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny04Ijo2LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOSI6MC40LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTAiOjIsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMyI6MTAwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMTQiOjIsImJhbGFuY2Utc2hlZXQ6MjAyMzphc3NldHMiOjEzMiwiYmFsYW5jZS1zaGVldDoyMDIzOmN1cnJlbnRBc3NldHMiOjY3LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FzaCI6MjQsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZEFzc2V0cyI6NjUsImJhbGFuY2Utc2hlZXQ6MjAyMzp0YW5naWJsZUFzc2V0cyI6NTMsImJhbGFuY2Utc2hlZXQ6MjAyMzpidWlsZGluZ3MiOjE5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bWFjaGluZXJ5IjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6aW50YW5naWJsZUFzc2V0cyI6NywiYmFsYW5jZS1zaGVldDoyMDIzOnNvZnR3YXJlIjo1LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGlhYmlsaXRpZXMiOjc1LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudExpYWJpbGl0aWVzIjozOSwiYmFsYW5jZS1zaGVldDoyMDIzOnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Zml4ZWRMaWFiaWxpdGllcyI6MzYsImJhbGFuY2Utc2hlZXQ6MjAyMzpsb25nVGVybURlYnQiOjI5LCJiYWxhbmNlLXNoZWV0OjIwMjM6bmV0QXNzZXRzIjo1NywiYmFsYW5jZS1zaGVldDoyMDIzOnNoYXJlaG9sZGVyRXF1aXR5Ijo1NCwiYmFsYW5jZS1zaGVldDoyMDIzOmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwZXgiOjUsImJhbGFuY2Utc2hlZXQ6MjAyNDphc3NldHMiOjE0MywiYmFsYW5jZS1zaGVldDoyMDI0OmN1cnJlbnRBc3NldHMiOjcyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FzaCI6MjUsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZEFzc2V0cyI6NzEsImJhbGFuY2Utc2hlZXQ6MjAyNDp0YW5naWJsZUFzc2V0cyI6NTgsImJhbGFuY2Utc2hlZXQ6MjAyNDpidWlsZGluZ3MiOjIwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bWFjaGluZXJ5IjoyOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6aW50YW5naWJsZUFzc2V0cyI6OCwiYmFsYW5jZS1zaGVldDoyMDI0OnNvZnR3YXJlIjo2LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGlhYmlsaXRpZXMiOjc5LCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudExpYWJpbGl0aWVzIjo0MSwiYmFsYW5jZS1zaGVldDoyMDI0OnNob3J0VGVybURlYnQiOjEyLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Zml4ZWRMaWFiaWxpdGllcyI6MzgsImJhbGFuY2Utc2hlZXQ6MjAyNDpsb25nVGVybURlYnQiOjMxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6bmV0QXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI0OnNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiYmFsYW5jZS1zaGVldDoyMDI0OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwZXgiOjgsImJhbGFuY2Utc2hlZXQ6MjAyNTphc3NldHMiOjE1NiwiYmFsYW5jZS1zaGVldDoyMDI1OmN1cnJlbnRBc3NldHMiOjc4LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FzaCI6MjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTp0YW5naWJsZUFzc2V0cyI6NjQsImJhbGFuY2Utc2hlZXQ6MjAyNTpidWlsZGluZ3MiOjIyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bWFjaGluZXJ5IjozMiwiYmFsYW5jZS1zaGVldDoyMDI1OmxhbmQiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6aW50YW5naWJsZUFzc2V0cyI6OSwiYmFsYW5jZS1zaGVldDoyMDI1OnNvZnR3YXJlIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjU6bGlhYmlsaXRpZXMiOjgzLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudExpYWJpbGl0aWVzIjo0MywiYmFsYW5jZS1zaGVldDoyMDI1OnNob3J0VGVybURlYnQiOjExLCJiYWxhbmNlLXNoZWV0OjIwMjU6Zml4ZWRMaWFiaWxpdGllcyI6NDAsImJhbGFuY2Utc2hlZXQ6MjAyNTpsb25nVGVybURlYnQiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bmV0QXNzZXRzIjo3MywiYmFsYW5jZS1zaGVldDoyMDI1OnNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiYmFsYW5jZS1zaGVldDoyMDI1OmNhcGl0YWwiOjEwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwZXgiOjEwLCJmdXR1cmUtY2FwZXg6MjAyNiI6MTUsImZ1dHVyZS1jYXBleDoyMDI3IjoxNSwiZnV0dXJlLWNhcGV4OjIwMjgiOjE1LCJmdXR1cmUtY2FwZXg6MjAyOSI6MCwiZnV0dXJlLWNhcGV4OjIwMzAiOjAsImZ1dHVyZS1jYXBleDoyMDMxIjowLCJkcml2ZXI6cHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MCI6LTAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0TWFya2V0R3Jvd3RoOjEiOjAuMywiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MCI6MC4wMzkxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjEiOjAuMDQyNTAwMDAwMDAwMDAwMDksImRyaXZlcjpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZToxIjowLCJkcml2ZXI6cHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjAiOjAuMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MSI6MC4zLCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NzI0NjM3NjgxMTU4NiwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MCI6MC4wNjA3NjA4Njk1NjUyMTcxOSwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGg6MSI6MC4wNjQzODQwNTc5NzEwMTQ1MywiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZToxIjowLjAzLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDoxIjowLjAwNTEzNDU3NTU2OTM1ODE5NzUsImRyaXZlcjpwcm9qZWN0UGF5R3Jvd3RoIjowLjA3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDowIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aDoxIjowLjEsImRyaXZlcjpvdGhlclBheUdyb3d0aCI6MC4wMjQ4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjAiOjAuMDI0MTM5NDU3MDIzNzE3NDQ0LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MSI6MC4wMjU1NTM0NTk5MTQ3NjMwOTYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjoyLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3NC44LCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjoxOC43OCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mi44NSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjoxNSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOm1heCI6MjUyLjY5LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6bWF4IjoxMzYuODQsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMy40MywidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6bWF4IjozLjc0fSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCIsImFkanVzdGVkRHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MTA1OTU3NjAyMzM5MTYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMTk5ODIxMzU1MTE4Nzk4NzMsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDYzOTAxMjQ5NzIyOTM0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDEyMDQ1MTMzMzE1NzYzLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjYwNTUxNjI3MzAwNTI3LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODgxMzY3NTAwOTE3MTE3LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA2MDkzNTM5NDM3MTc4NTUsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMjAyMjQ4NzIxNjk0NjY3Mywib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI1NjUxNzg1OTQ1MjE3OSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTQ5OTA0ODEzNDEyNjU1NSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA4OTAwNjIyOTk3NTA4MDEsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg4Nzc2MTcxMDMzMzAzLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjAyOTA0NTQ4MjM5NzIwNTA1NSwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1Nzg0ODE0NzMyMzA4NjY1LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMDk5MzE4MDkxNjQ4NDgyNCwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTI3MjU4OTg3MjEyODIzLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM3NzgwNTc2Mjg3MTYzMiwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Mi43NjQwMDAwMDAwMDAwMDJ9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2LCJjb2dzIjo1MS42OCwiZW1wbG95ZWVQYXkiOjUuNTksIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjIsImVtcGxveWVlU2FsYXJ5Ijo1LjMxLCJlbXBsb3llZUJvbnVzIjowLjI4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjM0LCJvZmZpY2VyQm9udXMiOjAuMDQsImNvZ3NEZXByZWNpYXRpb24iOjAuNDcsInNnYURlcHJlY2lhdGlvbiI6MS40MywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4zOH0sIm90aGVyIjp7InNhbGVzIjo2Ny4yLCJjb2dzIjo0NS43LCJlbXBsb3llZVBheSI6Ny41NCwib2ZmaWNlclBheSI6MC41OCwiZGVwcmVjaWF0aW9uIjoxLjQ0LCJvdGhlclNnYSI6Ny42OCwiaGVhZGNvdW50IjoxMjUsIm9mZmljZXJDb3VudCI6MywiZW1wbG95ZWVTYWxhcnkiOjcuMTYsImVtcGxveWVlQm9udXMiOjAuMzgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTIsIm9mZmljZXJCb251cyI6MC4wNiwiY29nc0RlcHJlY2lhdGlvbiI6MC4yOSwic2dhRGVwcmVjaWF0aW9uIjoxLjE1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI5LCJvcmRpbmFyeUluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsInByZVRheEluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsIm5ldEluY29tZSI6Mi43ODE5OTk5OTk5OTk5OTgzfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjIuNzk5OTk5OTk5OTk5OTk3fX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjo3LjY3fSx7InllYXIiOjIwMjcsInZhbHVlIjo3LjY3fSx7InllYXIiOjIwMjgsInZhbHVlIjo3LjY2fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjIsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNTEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjo3MiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjIzLjA0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Ni43OCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjUuMTksImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC41MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjQ3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6Ny45MSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2Ijo3LjY3LCJmdXR1cmUtY2FwZXg6MjAyNyI6Ny42NywiZnV0dXJlLWNhcGV4OjIwMjgiOjcuNjYsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjoyLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3NC44LCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjoxOC43OCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mi44NSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjoxNSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOm1heCI6MjUyLjY5LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6bWF4IjoxMzYuODQsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMy40MywidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6bWF4IjozLjc0fSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCIsImFkanVzdGVkRHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MTA1OTU3NjAyMzM5MTYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMTk5ODIxMzU1MTE4Nzk4NzMsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDYzOTAxMjQ5NzIyOTM0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDEyMDQ1MTMzMzE1NzYzLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjYwNTUxNjI3MzAwNTI3LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODgxMzY3NTAwOTE3MTE3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYwOTM1Mzk0MzcxNzg1NSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyMDIyNDg3MjE2OTQ2NjczLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU2NTE3ODU5NDUyMTc5LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNDk5MDQ4MTM0MTI2NTU1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDg5MDA2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODg3NzYxNzEwMzMzMDMsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDI5MDQ1NDgyMzk3MjA1MDU1LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU3ODQ4MTQ3MzIzMDg2NjUsInByb2plY3RTZ2FSYXRlRW5kIjowLjEwOTkzMTgwOTE2NDg0ODI0LCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjcyNTg5ODcyMTI4MjMsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1Mzc3ODA1NzYyODcxNjMyLCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM319</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>23.49843476135365</v>
+        <v>23.487308177598077</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>19.660000000000004</v>
+        <v>19.66</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>256.6579634464752</v>
+        <v>256.65796344647515</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1465,22 +1465,22 @@
         <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>38.870000000000005</v>
+        <v>38.85</v>
       </c>
       <c r="F9" s="2">
-        <v>41.47</v>
+        <v>41.44</v>
       </c>
       <c r="G9" s="2">
-        <v>44.18</v>
+        <v>44.15</v>
       </c>
       <c r="H9" s="2">
-        <v>47.93</v>
+        <v>47.900000000000006</v>
       </c>
       <c r="I9" s="2">
-        <v>52.589999999999996</v>
+        <v>52.56</v>
       </c>
       <c r="J9" s="2">
-        <v>57.81</v>
+        <v>57.769999999999996</v>
       </c>
     </row>
     <row r="10">
@@ -1545,10 +1545,10 @@
         <v>1.09</v>
       </c>
       <c r="I11" s="2">
-        <v>1.1300000000000001</v>
+        <v>1.1400000000000001</v>
       </c>
       <c r="J11" s="2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="12">
@@ -1579,10 +1579,10 @@
         <v>0.12000000000000001</v>
       </c>
       <c r="I12" s="2">
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="J12" s="2">
         <v>0.13</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0.14</v>
       </c>
     </row>
     <row r="13">
@@ -1644,13 +1644,13 @@
         <v>16.17</v>
       </c>
       <c r="H14" s="2">
-        <v>17.69</v>
+        <v>17.68</v>
       </c>
       <c r="I14" s="2">
-        <v>19.35</v>
+        <v>19.34</v>
       </c>
       <c r="J14" s="2">
-        <v>21.16</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="15">
@@ -1678,13 +1678,13 @@
         <v>0.85</v>
       </c>
       <c r="H15" s="2">
-        <v>0.9199999999999999</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="I15" s="2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="J15" s="2">
-        <v>1.1099999999999999</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="16">
@@ -1709,16 +1709,16 @@
         <v>3.8499999999999996</v>
       </c>
       <c r="G16" s="2">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="H16" s="2">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="I16" s="2">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="J16" s="2">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="17">
@@ -1737,22 +1737,22 @@
         <v>0.7</v>
       </c>
       <c r="E17" s="2">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="F17" s="2">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="G17" s="2">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="H17" s="2">
-        <v>0.9299999999999999</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="I17" s="2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="J17" s="2">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="18">
@@ -1771,22 +1771,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>11.470000000000006</v>
+        <v>11.490000000000006</v>
       </c>
       <c r="F18" s="4">
-        <v>11.320000000000014</v>
+        <v>11.350000000000016</v>
       </c>
       <c r="G18" s="4">
-        <v>11.180000000000003</v>
+        <v>11.21</v>
       </c>
       <c r="H18" s="4">
-        <v>17.179999999999986</v>
+        <v>17.209999999999987</v>
       </c>
       <c r="I18" s="4">
-        <v>23.27999999999998</v>
+        <v>23.309999999999974</v>
       </c>
       <c r="J18" s="4">
-        <v>31.090000000000046</v>
+        <v>31.130000000000045</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.291335579429156</v>
+        <v>7.304049329349695</v>
       </c>
       <c r="F19" s="2">
-        <v>6.861437750030315</v>
+        <v>6.879621772336049</v>
       </c>
       <c r="G19" s="2">
-        <v>6.46130728775357</v>
+        <v>6.478645321620529</v>
       </c>
       <c r="H19" s="2">
-        <v>8.612823983556417</v>
+        <v>8.627863839173804</v>
       </c>
       <c r="I19" s="2">
-        <v>10.12349973908505</v>
+        <v>10.136545486171498</v>
       </c>
       <c r="J19" s="2">
-        <v>11.672172998948808</v>
+        <v>11.687190268809147</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>11.3</v>
       </c>
       <c r="E20" s="4">
-        <v>11.159999999999991</v>
+        <v>11.129999999999999</v>
       </c>
       <c r="F20" s="4">
-        <v>10.989999999999995</v>
+        <v>10.97</v>
       </c>
       <c r="G20" s="4">
-        <v>10.830000000000005</v>
+        <v>10.81</v>
       </c>
       <c r="H20" s="4">
-        <v>15.949999999999996</v>
+        <v>15.5</v>
       </c>
       <c r="I20" s="4">
-        <v>21.939999999999984</v>
+        <v>21.46</v>
       </c>
       <c r="J20" s="4">
-        <v>29.62000000000001</v>
+        <v>29.130000000000003</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>11.3</v>
       </c>
       <c r="E21" s="2">
-        <v>11.159999999999991</v>
+        <v>11.129999999999999</v>
       </c>
       <c r="F21" s="2">
-        <v>10.989999999999995</v>
+        <v>10.97</v>
       </c>
       <c r="G21" s="2">
-        <v>10.830000000000005</v>
+        <v>10.81</v>
       </c>
       <c r="H21" s="2">
-        <v>15.949999999999996</v>
+        <v>15.5</v>
       </c>
       <c r="I21" s="2">
-        <v>21.939999999999984</v>
+        <v>21.46</v>
       </c>
       <c r="J21" s="2">
-        <v>29.62000000000001</v>
+        <v>29.130000000000003</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>7.91</v>
       </c>
       <c r="E22" s="2">
-        <v>7.805999999999994</v>
+        <v>7.79</v>
       </c>
       <c r="F22" s="2">
-        <v>7.691999999999997</v>
+        <v>7.68</v>
       </c>
       <c r="G22" s="2">
-        <v>7.578000000000003</v>
+        <v>7.57</v>
       </c>
       <c r="H22" s="2">
-        <v>11.157999999999998</v>
+        <v>10.85</v>
       </c>
       <c r="I22" s="2">
-        <v>15.352999999999987</v>
+        <v>15.030000000000001</v>
       </c>
       <c r="J22" s="2">
-        <v>20.732000000000006</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="23">
@@ -2043,22 +2043,22 @@
         <v>30.1</v>
       </c>
       <c r="E26" s="4">
-        <v>31.720000000000006</v>
+        <v>31.740000000000006</v>
       </c>
       <c r="F26" s="4">
-        <v>33.390000000000015</v>
+        <v>33.420000000000016</v>
       </c>
       <c r="G26" s="4">
-        <v>35.14</v>
+        <v>35.17</v>
       </c>
       <c r="H26" s="4">
-        <v>42.33999999999998</v>
+        <v>42.36999999999998</v>
       </c>
       <c r="I26" s="4">
-        <v>50.17999999999997</v>
+        <v>50.20999999999997</v>
       </c>
       <c r="J26" s="4">
-        <v>59.90000000000004</v>
+        <v>59.94000000000004</v>
       </c>
     </row>
     <row r="27">
@@ -2079,22 +2079,22 @@
         <v>4.768534632788035</v>
       </c>
       <c r="E27" s="2">
-        <v>5.382059800664463</v>
+        <v>5.448504983388713</v>
       </c>
       <c r="F27" s="2">
-        <v>5.264817150063084</v>
+        <v>5.293005671077533</v>
       </c>
       <c r="G27" s="2">
-        <v>5.241090146750471</v>
+        <v>5.236385397965249</v>
       </c>
       <c r="H27" s="2">
-        <v>20.489470688673816</v>
+        <v>20.47199317600221</v>
       </c>
       <c r="I27" s="2">
-        <v>18.516769012753876</v>
+        <v>18.5036582487609</v>
       </c>
       <c r="J27" s="2">
-        <v>19.370267038660984</v>
+        <v>19.378609838677697</v>
       </c>
     </row>
     <row r="28">
@@ -2113,22 +2113,22 @@
         <v>20.06666666666667</v>
       </c>
       <c r="E28" s="2">
-        <v>20.164007373974957</v>
+        <v>20.176721123895497</v>
       </c>
       <c r="F28" s="2">
-        <v>20.23881682628198</v>
+        <v>20.257000848587715</v>
       </c>
       <c r="G28" s="2">
-        <v>20.30861700283188</v>
+        <v>20.32595503669884</v>
       </c>
       <c r="H28" s="2">
-        <v>21.226249561337536</v>
+        <v>21.241289416954924</v>
       </c>
       <c r="I28" s="2">
-        <v>21.821186293268386</v>
+        <v>21.834232040354834</v>
       </c>
       <c r="J28" s="2">
-        <v>22.488361615858253</v>
+        <v>22.50337888571859</v>
       </c>
     </row>
     <row r="29">
@@ -2355,22 +2355,22 @@
         <v>0.12808510638297874</v>
       </c>
       <c r="E35" s="2">
-        <v>0.12946938775510206</v>
+        <v>0.1295510204081633</v>
       </c>
       <c r="F35" s="2">
-        <v>0.12992217898832692</v>
+        <v>0.13003891050583663</v>
       </c>
       <c r="G35" s="2">
-        <v>0.13111940298507463</v>
+        <v>0.1312313432835821</v>
       </c>
       <c r="H35" s="2">
-        <v>0.15230215827338123</v>
+        <v>0.152410071942446</v>
       </c>
       <c r="I35" s="2">
-        <v>0.17363321799307949</v>
+        <v>0.17373702422145318</v>
       </c>
       <c r="J35" s="2">
-        <v>0.1996666666666668</v>
+        <v>0.19980000000000014</v>
       </c>
     </row>
     <row r="36">
@@ -2389,22 +2389,22 @@
         <v>15.100000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>15.740000000000006</v>
+        <v>15.760000000000005</v>
       </c>
       <c r="F36" s="4">
-        <v>16.350000000000016</v>
+        <v>16.380000000000017</v>
       </c>
       <c r="G36" s="4">
-        <v>16.980000000000004</v>
+        <v>17.01</v>
       </c>
       <c r="H36" s="4">
-        <v>22.979999999999986</v>
+        <v>23.009999999999987</v>
       </c>
       <c r="I36" s="4">
-        <v>29.07999999999998</v>
+        <v>29.109999999999975</v>
       </c>
       <c r="J36" s="4">
-        <v>36.89000000000004</v>
+        <v>36.93000000000004</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666668</v>
       </c>
       <c r="E37" s="2">
-        <v>10.005721187464246</v>
+        <v>10.018434937384784</v>
       </c>
       <c r="F37" s="2">
-        <v>9.910292156625054</v>
+        <v>9.928476178930788</v>
       </c>
       <c r="G37" s="2">
-        <v>9.813327168699072</v>
+        <v>9.83066520256603</v>
       </c>
       <c r="H37" s="2">
-        <v>11.520529402917726</v>
+        <v>11.535569258535112</v>
       </c>
       <c r="I37" s="2">
-        <v>12.645677509132017</v>
+        <v>12.658723256218462</v>
       </c>
       <c r="J37" s="2">
-        <v>13.849677128698017</v>
+        <v>13.864694398558358</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>3.1420765027322606</v>
       </c>
       <c r="E38" s="2">
-        <v>4.238410596026521</v>
+        <v>4.370860927152331</v>
       </c>
       <c r="F38" s="2">
-        <v>3.875476493011498</v>
+        <v>3.9340101522843396</v>
       </c>
       <c r="G38" s="2">
-        <v>3.85321100917424</v>
+        <v>3.8461538461537437</v>
       </c>
       <c r="H38" s="2">
-        <v>35.33568904593629</v>
+        <v>35.27336860670185</v>
       </c>
       <c r="I38" s="2">
-        <v>26.544821583986057</v>
+        <v>26.510212950890867</v>
       </c>
       <c r="J38" s="2">
-        <v>26.856946354883316</v>
+        <v>26.863620748883797</v>
       </c>
     </row>
   </sheetData>
@@ -2805,16 +2805,16 @@
         <v>6.859999999999996</v>
       </c>
       <c r="G8" s="4">
-        <v>6.640000000000004</v>
+        <v>6.650000000000006</v>
       </c>
       <c r="H8" s="4">
-        <v>11.239999999999997</v>
+        <v>11.249999999999998</v>
       </c>
       <c r="I8" s="4">
-        <v>16.689999999999984</v>
+        <v>16.69999999999998</v>
       </c>
       <c r="J8" s="4">
-        <v>23.760000000000012</v>
+        <v>23.77000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2839,16 +2839,16 @@
         <v>7.717403532455839</v>
       </c>
       <c r="G9" s="2">
-        <v>7.086446104589118</v>
+        <v>7.097118463180369</v>
       </c>
       <c r="H9" s="2">
-        <v>9.830330592968336</v>
+        <v>9.83907643869162</v>
       </c>
       <c r="I9" s="2">
-        <v>11.963300121855053</v>
+        <v>11.970468066805234</v>
       </c>
       <c r="J9" s="2">
-        <v>13.95676691729324</v>
+        <v>13.962640977443613</v>
       </c>
     </row>
     <row r="10">
@@ -2975,16 +2975,16 @@
         <v>17.769999999999996</v>
       </c>
       <c r="G13" s="4">
-        <v>18.870000000000005</v>
+        <v>18.880000000000006</v>
       </c>
       <c r="H13" s="4">
-        <v>23.939999999999998</v>
+        <v>23.95</v>
       </c>
       <c r="I13" s="4">
-        <v>30.359999999999985</v>
+        <v>30.369999999999983</v>
       </c>
       <c r="J13" s="4">
-        <v>38.53000000000001</v>
+        <v>38.540000000000006</v>
       </c>
     </row>
     <row r="14">
@@ -3011,16 +3011,16 @@
         <v>6.279904306220119</v>
       </c>
       <c r="G14" s="2">
-        <v>6.190208216094595</v>
+        <v>6.246482836240919</v>
       </c>
       <c r="H14" s="2">
-        <v>26.868044515103296</v>
+        <v>26.853813559321992</v>
       </c>
       <c r="I14" s="2">
-        <v>26.81704260651625</v>
+        <v>26.805845511482197</v>
       </c>
       <c r="J14" s="2">
-        <v>26.910408432147648</v>
+        <v>26.901547579848618</v>
       </c>
     </row>
     <row r="15">
@@ -3253,16 +3253,16 @@
         <v>0.15725663716814156</v>
       </c>
       <c r="G21" s="2">
-        <v>0.1585714285714286</v>
+        <v>0.158655462184874</v>
       </c>
       <c r="H21" s="2">
-        <v>0.1962295081967213</v>
+        <v>0.19631147540983607</v>
       </c>
       <c r="I21" s="2">
-        <v>0.24095238095238083</v>
+        <v>0.2410317460317459</v>
       </c>
       <c r="J21" s="2">
-        <v>0.29868217054263574</v>
+        <v>0.29875968992248064</v>
       </c>
     </row>
     <row r="22">
@@ -3761,32 +3761,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.71 % / 補助 23.61 % / ベース 25.98 %</t>
+          <t xml:space="preserve">全社 24.7 % / 補助 23.61 % / ベース 25.95 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.14 % / 補助 24.28 % / ベース 26.14 %</t>
+          <t xml:space="preserve">全社 25.12 % / 補助 24.28 % / ベース 26.1 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.53 % / 補助 24.91 % / ベース 26.27 %</t>
+          <t xml:space="preserve">全社 25.52 % / 補助 24.9 % / ベース 26.24 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.03 % / 補助 22.67 % / ベース 25.85 %</t>
+          <t xml:space="preserve">全社 24.01 % / 補助 22.66 % / ベース 25.83 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.87 % / 補助 21.03 % / ベース 25.7 %</t>
+          <t xml:space="preserve">全社 22.86 % / 補助 21.02 % / ベース 25.68 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.7 % / 補助 19.54 % / ベース 25.54 %</t>
+          <t xml:space="preserve">全社 21.69 % / 補助 19.53 % / ベース 25.51 %</t>
         </is>
       </c>
     </row>
@@ -3823,32 +3823,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.29 % / 補助 8.4 % / ベース 6.02 %</t>
+          <t xml:space="preserve">全社 7.3 % / 補助 8.4 % / ベース 6.04 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.86 % / 補助 7.72 % / ベース 5.86 %</t>
+          <t xml:space="preserve">全社 6.88 % / 補助 7.72 % / ベース 5.9 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.46 % / 補助 7.09 % / ベース 5.72 %</t>
+          <t xml:space="preserve">全社 6.48 % / 補助 7.1 % / ベース 5.75 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.61 % / 補助 9.83 % / ベース 6.98 %</t>
+          <t xml:space="preserve">全社 8.63 % / 補助 9.84 % / ベース 7 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.12 % / 補助 11.96 % / ベース 7.29 %</t>
+          <t xml:space="preserve">全社 10.14 % / 補助 11.97 % / ベース 7.31 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.67 % / 補助 13.96 % / ベース 7.63 %</t>
+          <t xml:space="preserve">全社 11.69 % / 補助 13.96 % / ベース 7.66 %</t>
         </is>
       </c>
     </row>
@@ -3885,32 +3885,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.01 % / 補助 11.68 % / ベース 8.07 %</t>
+          <t xml:space="preserve">全社 10.02 % / 補助 11.68 % / ベース 8.1 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.91 % / 補助 11.69 % / ベース 7.83 %</t>
+          <t xml:space="preserve">全社 9.93 % / 補助 11.69 % / ベース 7.87 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.81 % / 補助 11.68 % / ベース 7.61 %</t>
+          <t xml:space="preserve">全社 9.83 % / 補助 11.69 % / ベース 7.64 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.52 % / 補助 13.59 % / ベース 8.74 %</t>
+          <t xml:space="preserve">全社 11.54 % / 補助 13.6 % / ベース 8.76 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.65 % / 補助 15.05 % / ベース 8.94 %</t>
+          <t xml:space="preserve">全社 12.66 % / 補助 15.05 % / ベース 8.97 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.85 % / 補助 16.48 % / ベース 9.19 %</t>
+          <t xml:space="preserve">全社 13.86 % / 補助 16.49 % / ベース 9.22 %</t>
         </is>
       </c>
     </row>
@@ -4443,32 +4443,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.38 % / 補助 41.09 % / ベース 60.73 %</t>
+          <t xml:space="preserve">全社 50.35 % / 補助 41.09 % / ベース 60.65 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.03 % / 補助 41.53 % / ベース 61.84 %</t>
+          <t xml:space="preserve">全社 50.99 % / 補助 41.53 % / ベース 61.73 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.68 % / 補助 42.02 % / ベース 62.88 %</t>
+          <t xml:space="preserve">全社 51.63 % / 補助 42 % / ベース 62.8 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.73 % / 補助 35.09 % / ベース 59.57 %</t>
+          <t xml:space="preserve">全社 45.69 % / 補助 35.07 % / ベース 59.5 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.05 % / 補助 30.86 % / ベース 59.18 %</t>
+          <t xml:space="preserve">全社 42.02 % / 補助 30.85 % / ベース 59.12 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.41 % / 補助 27.17 % / ベース 58.68 %</t>
+          <t xml:space="preserve">全社 38.39 % / 補助 27.17 % / ベース 58.6 %</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.105 億円/人 / 補助 0.187 億円/人 / ベース 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.106 億円/人 / 補助 0.187 億円/人 / ベース 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.156 億円/人 / ベース 0.109 億円/人</t>
+          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.156 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.157 億円/人 / ベース 0.108 億円/人</t>
+          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.157 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
@@ -5125,32 +5125,32 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / ベース 3.93 倍</t>
+          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / ベース 3.94 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.25 倍 / 補助 2.94 倍 / ベース 3.97 倍</t>
+          <t xml:space="preserve">全社 3.26 倍 / 補助 2.94 倍 / ベース 3.99 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.93 倍 / 補助 2.54 倍 / ベース 4.03 倍</t>
+          <t xml:space="preserve">全社 2.93 倍 / 補助 2.55 倍 / ベース 4.04 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.96 倍 / 補助 3.61 倍 / ベース 4.96 倍</t>
+          <t xml:space="preserve">全社 3.97 倍 / 補助 3.62 倍 / ベース 4.97 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.01 倍 / 補助 4.88 倍 / ベース 5.39 倍</t>
+          <t xml:space="preserve">全社 5.02 倍 / 補助 4.88 倍 / ベース 5.41 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.36 倍 / 補助 6.53 倍 / ベース 5.89 倍</t>
+          <t xml:space="preserve">全社 6.37 倍 / 補助 6.53 倍 / ベース 5.91 倍</t>
         </is>
       </c>
     </row>
@@ -5497,32 +5497,32 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.38 pt</t>
+          <t xml:space="preserve">差 2.35 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.86 pt</t>
+          <t xml:space="preserve">差 1.82 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.36 pt</t>
+          <t xml:space="preserve">差 1.35 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.85 pt</t>
+          <t xml:space="preserve">差 2.84 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.68 pt</t>
+          <t xml:space="preserve">差 4.66 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.33 pt</t>
+          <t xml:space="preserve">差 6.31 pt</t>
         </is>
       </c>
     </row>
@@ -5683,17 +5683,17 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 169.23 %</t>
+          <t xml:space="preserve">寄与率 200 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 146.67 %</t>
+          <t xml:space="preserve">寄与率 157.14 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 157.14 %</t>
+          <t xml:space="preserve">寄与率 150 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.52 %</t>
+          <t xml:space="preserve">寄与率 90.41 %</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5821,11 +5821,15 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>99</v>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -5842,185 +5846,221 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>99</v>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">実効税率</t>
+          <t xml:space="preserve">補助事業 従業員給与総額に占める給与の割合</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>60</v>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 従業員給与総額に占める給与の割合</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>5.409356725146197</v>
+        <v>95</v>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D7" s="2">
-        <v>5.116959064327475</v>
-      </c>
-      <c r="E7" s="2">
-        <v>5.701754385964919</v>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 役員給与総額に占める役員報酬の割合</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>5.551115123125783e-15</v>
+        <v>90</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1.6653345369377348e-14</v>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 役員給与総額に占める役員報酬の割合</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>2.0030662342518046</v>
+        <v>90</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>1.9325330501846927</v>
-      </c>
-      <c r="E9" s="2">
-        <v>2.0735994183189166</v>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 減価償却費のうち売上原価に含める割合</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>5.409356725146197</v>
+        <v>25</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D10" s="2">
-        <v>5.116959064327475</v>
-      </c>
-      <c r="E10" s="2">
-        <v>5.701754385964919</v>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 減価償却費のうち売上原価に含める割合</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>5.409356725146197</v>
+        <v>0.5</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D12" s="2">
-        <v>5.116959064327475</v>
-      </c>
-      <c r="E12" s="2">
-        <v>5.701754385964919</v>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>4.257246376811585</v>
+        <v>0.4</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D13" s="2">
-        <v>4.076086956521719</v>
-      </c>
-      <c r="E13" s="2">
-        <v>4.438405797101453</v>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6031,105 +6071,125 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.013457556935819737</v>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>1.984645846924027</v>
+        <v>-0.5</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D15" s="2">
-        <v>1.9139457023717443</v>
-      </c>
-      <c r="E15" s="2">
-        <v>2.0553459914763095</v>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>8</v>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>4.083333333333339</v>
+        <v>0</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D17" s="2">
-        <v>3.9166666666666683</v>
-      </c>
-      <c r="E17" s="2">
-        <v>4.250000000000009</v>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>22</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -6137,20 +6197,20 @@
         </is>
       </c>
       <c r="D19" s="2">
-        <v>15</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E19" s="2">
-        <v>30</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>6.257246376811586</v>
+        <v>5.551115123125783e-15</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6158,41 +6218,41 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <v>6.076086956521719</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2">
-        <v>6.438405797101453</v>
+        <v>1.6653345369377348e-14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>1.5</v>
+        <v>2.0030662342518046</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D21" s="2">
-        <v>0</v>
+        <v>1.9325330501846927</v>
       </c>
       <c r="E21" s="2">
-        <v>3</v>
+        <v>2.0735994183189166</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>0.5</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
@@ -6200,20 +6260,20 @@
         </is>
       </c>
       <c r="D22" s="2">
-        <v>0.5</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E22" s="2">
-        <v>0.5134575569358197</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>7.000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6221,20 +6281,20 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>2.484645846924027</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6242,20 +6302,20 @@
         </is>
       </c>
       <c r="D24" s="2">
-        <v>2.4139457023717443</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E24" s="2">
-        <v>2.5553459914763095</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>4.5</v>
+        <v>4.257246376811585</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6263,20 +6323,20 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>0</v>
+        <v>4.076086956521719</v>
       </c>
       <c r="E25" s="2">
-        <v>8</v>
+        <v>4.438405797101453</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
@@ -6287,17 +6347,17 @@
         <v>0</v>
       </c>
       <c r="E26" s="2">
-        <v>8</v>
+        <v>0.013457556935819737</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>4.583333333333338</v>
+        <v>1.984645846924027</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6305,41 +6365,45 @@
         </is>
       </c>
       <c r="D27" s="2">
-        <v>4.416666666666668</v>
+        <v>1.9139457023717443</v>
       </c>
       <c r="E27" s="2">
-        <v>4.750000000000009</v>
+        <v>2.0553459914763095</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D28" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="E28" s="2">
-        <v>13.5</v>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>10.928571428571427</v>
+        <v>4.083333333333339</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6347,20 +6411,20 @@
         </is>
       </c>
       <c r="D29" s="2">
-        <v>8.928571428571427</v>
+        <v>3.9166666666666683</v>
       </c>
       <c r="E29" s="2">
-        <v>11.928571428571427</v>
+        <v>4.250000000000009</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>5.380116959064325</v>
+        <v>0</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -6368,82 +6432,338 @@
         </is>
       </c>
       <c r="D30" s="2">
-        <v>4.263157894736836</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2">
-        <v>6.555555555555557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新規投資の耐用年数</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D31" s="2">
+        <v>15</v>
+      </c>
+      <c r="E31" s="2">
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業投資額</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>23</v>
+        <v>6.257246376811586</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D32" s="2">
+        <v>6.076086956521719</v>
+      </c>
+      <c r="E32" s="2">
+        <v>6.438405797101453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B33" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B34" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D34" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.5134575569358197</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B35" s="2">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D35" s="2">
+        <v>5</v>
+      </c>
+      <c r="E35" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B36" s="2">
+        <v>2.484645846924027</v>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D36" s="2">
+        <v>2.4139457023717443</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2.5553459914763095</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B37" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+        </is>
+      </c>
+      <c r="B38" s="2">
+        <v>4</v>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+        </is>
+      </c>
+      <c r="B39" s="2">
+        <v>4.583333333333338</v>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D39" s="2">
+        <v>4.416666666666668</v>
+      </c>
+      <c r="E39" s="2">
+        <v>4.750000000000009</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B40" s="2">
+        <v>11</v>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D40" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="E40" s="2">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+        </is>
+      </c>
+      <c r="B41" s="2">
+        <v>10.928571428571427</v>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D41" s="2">
+        <v>8.928571428571427</v>
+      </c>
+      <c r="E41" s="2">
+        <v>11.928571428571427</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+        </is>
+      </c>
+      <c r="B42" s="2">
+        <v>5.380116959064325</v>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D42" s="2">
+        <v>4.263157894736836</v>
+      </c>
+      <c r="E42" s="2">
+        <v>6.555555555555557</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新規投資の耐用年数</t>
+        </is>
+      </c>
+      <c r="B43" s="2">
+        <v>10</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">補助事業投資額</t>
+        </is>
+      </c>
+      <c r="B44" s="2">
+        <v>23</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
-      <c r="B33" s="2">
+      <c r="B45" s="2">
         <v>7.66</v>
       </c>
-      <c r="C33" s="0" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限7.66億円）</t>
         </is>
       </c>
-      <c r="D33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E33" s="0" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6455,7 +6775,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C259"/>
+  <dimension ref="A1:C295"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -8480,26 +8800,26 @@
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B135" s="2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0.0051345755693581975</v>
+        <v>1</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
@@ -8510,26 +8830,26 @@
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0.00013457556935819737</v>
+        <v>0.0051345755693581975</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
@@ -8540,7 +8860,7 @@
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B139" s="2">
@@ -8555,11 +8875,11 @@
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0.99</v>
+        <v>0.00013457556935819737</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
@@ -8570,26 +8890,26 @@
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0.04416666666666668</v>
+        <v>0</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0.04750000000000009</v>
+        <v>0.99</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
@@ -8600,26 +8920,26 @@
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0.03916666666666668</v>
+        <v>0</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0.04250000000000009</v>
+        <v>1</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
@@ -8630,26 +8950,26 @@
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
@@ -8660,26 +8980,26 @@
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0</v>
+        <v>0.04416666666666668</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0.08</v>
+        <v>0.04750000000000009</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
@@ -8690,11 +9010,11 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0.024139457023717444</v>
+        <v>0.03916666666666668</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
@@ -8705,11 +9025,11 @@
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0.025553459914763096</v>
+        <v>0.04250000000000009</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
@@ -8720,11 +9040,11 @@
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>0.019139457023717443</v>
+        <v>-0.5</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -8735,11 +9055,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.020553459914763095</v>
+        <v>0.5</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -8750,26 +9070,26 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>0.06076086956521719</v>
+        <v>0</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>0.06438405797101453</v>
+        <v>1</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -8780,26 +9100,26 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0.040760869565217184</v>
+        <v>0</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>0.04438405797101452</v>
+        <v>0.08</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
@@ -8810,7 +9130,7 @@
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B157" s="2">
@@ -8825,26 +9145,26 @@
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.08928571428571427</v>
+        <v>0.024139457023717444</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -8855,11 +9175,11 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0.11928571428571427</v>
+        <v>0.025553459914763096</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
@@ -8870,26 +9190,26 @@
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>0</v>
+        <v>0.019139457023717443</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.03</v>
+        <v>0.020553459914763095</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -8900,7 +9220,7 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B163" s="2">
@@ -8915,11 +9235,11 @@
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>1.6653345369377348e-16</v>
+        <v>0.3</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -8930,26 +9250,26 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>0</v>
+        <v>0.06076086956521719</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>0.99</v>
+        <v>0.06438405797101453</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
@@ -8960,26 +9280,26 @@
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>0</v>
+        <v>0.040760869565217184</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>0.08</v>
+        <v>0.04438405797101452</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
@@ -8990,41 +9310,41 @@
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0.05701754385964919</v>
+        <v>0</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>-0.05</v>
+        <v>0.08928571428571427</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
@@ -9035,11 +9355,11 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.3</v>
+        <v>0.11928571428571427</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
@@ -9050,26 +9370,26 @@
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0.04263157894736836</v>
+        <v>0</v>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>0.06555555555555558</v>
+        <v>1</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -9080,26 +9400,26 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0.051169590643274754</v>
+        <v>0</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.03</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
@@ -9110,26 +9430,26 @@
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0.1</v>
+        <v>1.6653345369377348e-16</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
@@ -9140,26 +9460,26 @@
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0.019325330501846927</v>
+        <v>0</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0.020735994183189166</v>
+        <v>0.99</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
@@ -9170,26 +9490,26 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
@@ -9200,11 +9520,11 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>0.051169590643274754</v>
+        <v>-0.5</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9215,11 +9535,11 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.5</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
@@ -9230,7 +9550,7 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B185" s="2">
@@ -9245,26 +9565,26 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.08499999999999999</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9275,11 +9595,11 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.135</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
@@ -9290,11 +9610,11 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>1</v>
+        <v>-0.05</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9305,11 +9625,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>50</v>
+        <v>0.3</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9320,11 +9640,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>5</v>
+        <v>-0.5</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9335,11 +9655,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9350,26 +9670,26 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9380,11 +9700,11 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>23</v>
+        <v>0.04263157894736836</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -9395,11 +9715,11 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>0.005</v>
+        <v>0.06555555555555558</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
@@ -9410,26 +9730,26 @@
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>0</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0.68</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
@@ -9440,11 +9760,11 @@
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.045833333333333386</v>
+        <v>0.05</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9455,11 +9775,11 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0.04083333333333339</v>
+        <v>0.1</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
@@ -9470,11 +9790,11 @@
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>0.045</v>
+        <v>0.019325330501846927</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9485,11 +9805,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0.04</v>
+        <v>0.020735994183189166</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9500,26 +9820,26 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>0.02484645846924027</v>
+        <v>0</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>0.01984645846924027</v>
+        <v>0.3</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9530,11 +9850,11 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0.06257246376811586</v>
+        <v>0.15</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9545,11 +9865,11 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0.042572463768115854</v>
+        <v>0.3</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
@@ -9560,26 +9880,26 @@
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>0</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>0.10928571428571428</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -9590,41 +9910,41 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0.68</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9635,11 +9955,11 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>0.04</v>
+        <v>0.135</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
@@ -9650,11 +9970,11 @@
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>0.05409356725146197</v>
+        <v>1</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
@@ -9665,11 +9985,11 @@
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>0.05</v>
+        <v>50</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
@@ -9680,11 +10000,11 @@
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>0.05380116959064325</v>
+        <v>5</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -9695,11 +10015,11 @@
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>0.05409356725146197</v>
+        <v>20</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -9710,11 +10030,11 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>0.07</v>
+        <v>0.3</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -9725,11 +10045,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>0.020030662342518046</v>
+        <v>23</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -9740,11 +10060,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>0.22</v>
+        <v>23</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -9755,11 +10075,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.2</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -9770,41 +10090,41 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>7.66</v>
+        <v>0.68</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -9815,11 +10135,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>10</v>
+        <v>0.95</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -9830,26 +10150,26 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>7.67</v>
+        <v>0</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>7.67</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -9860,11 +10180,11 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>7.66</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -9875,56 +10195,56 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>7</v>
+        <v>0.04</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -9935,11 +10255,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>2</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -9950,11 +10270,11 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>35</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
@@ -9965,11 +10285,11 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>15</v>
+        <v>0.004</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
@@ -9980,11 +10300,11 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>252.69</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -9995,11 +10315,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>82.4</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -10010,26 +10330,26 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>7</v>
+        <v>0.10928571428571428</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
@@ -10040,11 +10360,11 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>3.74</v>
+        <v>0.25</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10055,11 +10375,11 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>2.85</v>
+        <v>0.015</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
@@ -10070,11 +10390,11 @@
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>70</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -10085,11 +10405,11 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>15</v>
+        <v>0.68</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -10100,11 +10420,11 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>35</v>
+        <v>0.95</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10115,26 +10435,26 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>40</v>
+        <v>0.04</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
@@ -10145,11 +10465,11 @@
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>23</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10160,11 +10480,11 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>10</v>
+        <v>0.05</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
@@ -10175,41 +10495,41 @@
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B249" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>35</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
@@ -10220,11 +10540,11 @@
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>22</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
@@ -10235,11 +10555,11 @@
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>136.84</v>
+        <v>0.07</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10250,11 +10570,11 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>74.8</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
@@ -10265,11 +10585,11 @@
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>95</v>
+        <v>0.005</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
@@ -10280,11 +10600,11 @@
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B255" s="2">
-        <v>60</v>
+        <v>0.22</v>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
@@ -10295,11 +10615,11 @@
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B256" s="2">
-        <v>33.43</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
@@ -10310,26 +10630,26 @@
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B257" s="2">
-        <v>18.78</v>
+        <v>0</v>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B258" s="2">
-        <v>350</v>
+        <v>0.11</v>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
@@ -10340,13 +10660,553 @@
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">driver:subsidy</t>
+        </is>
+      </c>
+      <c r="B259" s="2">
+        <v>7.66</v>
+      </c>
+      <c r="C259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">driver:usefulLife</t>
+        </is>
+      </c>
+      <c r="B260" s="2">
+        <v>10</v>
+      </c>
+      <c r="C260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2026</t>
+        </is>
+      </c>
+      <c r="B261" s="2">
+        <v>7.67</v>
+      </c>
+      <c r="C261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2027</t>
+        </is>
+      </c>
+      <c r="B262" s="2">
+        <v>7.67</v>
+      </c>
+      <c r="C262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2028</t>
+        </is>
+      </c>
+      <c r="B263" s="2">
+        <v>7.66</v>
+      </c>
+      <c r="C263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2029</t>
+        </is>
+      </c>
+      <c r="B264" s="2">
+        <v>0</v>
+      </c>
+      <c r="C264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2030</t>
+        </is>
+      </c>
+      <c r="B265" s="2">
+        <v>0</v>
+      </c>
+      <c r="C265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future-capex:2031</t>
+        </is>
+      </c>
+      <c r="B266" s="2">
+        <v>0</v>
+      </c>
+      <c r="C266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
+        </is>
+      </c>
+      <c r="B267" s="2">
+        <v>7</v>
+      </c>
+      <c r="C267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
+        </is>
+      </c>
+      <c r="B268" s="2">
+        <v>2</v>
+      </c>
+      <c r="C268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B269" s="2">
+        <v>35</v>
+      </c>
+      <c r="C269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B270" s="2">
+        <v>15</v>
+      </c>
+      <c r="C270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
+        </is>
+      </c>
+      <c r="B271" s="2">
+        <v>252.69</v>
+      </c>
+      <c r="C271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B272" s="2">
+        <v>82.4</v>
+      </c>
+      <c r="C272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
+        </is>
+      </c>
+      <c r="B273" s="2">
+        <v>10</v>
+      </c>
+      <c r="C273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
+        </is>
+      </c>
+      <c r="B274" s="2">
+        <v>7</v>
+      </c>
+      <c r="C274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
+        </is>
+      </c>
+      <c r="B275" s="2">
+        <v>3.74</v>
+      </c>
+      <c r="C275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B276" s="2">
+        <v>2.85</v>
+      </c>
+      <c r="C276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+        </is>
+      </c>
+      <c r="B277" s="2">
+        <v>70</v>
+      </c>
+      <c r="C277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+        </is>
+      </c>
+      <c r="B278" s="2">
+        <v>15</v>
+      </c>
+      <c r="C278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+        </is>
+      </c>
+      <c r="B279" s="2">
+        <v>35</v>
+      </c>
+      <c r="C279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+        </is>
+      </c>
+      <c r="B280" s="2">
+        <v>21</v>
+      </c>
+      <c r="C280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:max</t>
+        </is>
+      </c>
+      <c r="B281" s="2">
+        <v>40</v>
+      </c>
+      <c r="C281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:localBenchmark:value</t>
+        </is>
+      </c>
+      <c r="B282" s="2">
+        <v>23</v>
+      </c>
+      <c r="C282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
+        </is>
+      </c>
+      <c r="B283" s="2">
+        <v>10</v>
+      </c>
+      <c r="C283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
+        </is>
+      </c>
+      <c r="B284" s="2">
+        <v>6</v>
+      </c>
+      <c r="C284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
+        </is>
+      </c>
+      <c r="B285" s="2">
+        <v>0</v>
+      </c>
+      <c r="C285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明示的な0</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
+        </is>
+      </c>
+      <c r="B286" s="2">
+        <v>35</v>
+      </c>
+      <c r="C286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
+        </is>
+      </c>
+      <c r="B287" s="2">
+        <v>22</v>
+      </c>
+      <c r="C287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+        </is>
+      </c>
+      <c r="B288" s="2">
+        <v>136.84</v>
+      </c>
+      <c r="C288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+        </is>
+      </c>
+      <c r="B289" s="2">
+        <v>74.8</v>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
+        </is>
+      </c>
+      <c r="B290" s="2">
+        <v>95</v>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
+        </is>
+      </c>
+      <c r="B291" s="2">
+        <v>60</v>
+      </c>
+      <c r="C291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+        </is>
+      </c>
+      <c r="B292" s="2">
+        <v>33.43</v>
+      </c>
+      <c r="C292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B293" s="2">
+        <v>18.78</v>
+      </c>
+      <c r="C293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B294" s="2">
+        <v>350</v>
+      </c>
+      <c r="C294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B259" s="2">
+      <c r="B295" s="2">
         <v>213</v>
       </c>
-      <c r="C259" s="0" t="inlineStr">
+      <c r="C295" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -10374,7 +11234,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Mi43NjQwMDAwMDAwMDAwMDJ9fSx7InllYXIiOjIwMjQsInJvbGUiOiJwcmV2aW91cyIsInByb2plY3QiOnsic2FsZXMiOjc2LCJjb2dzIjo1MS42OCwiZW1wbG95ZWVQYXkiOjUuNTksIm9mZmljZXJQYXkiOjAuMzgsImRlcHJlY2lhdGlvbiI6MS45LCJvdGhlclNnYSI6OS41LCJoZWFkY291bnQiOjk1LCJvZmZpY2VyQ291bnQiOjIsImVtcGxveWVlU2FsYXJ5Ijo1LjMxLCJlbXBsb3llZUJvbnVzIjowLjI4LCJvZmZpY2VyQ29tcGVuc2F0aW9uIjowLjM0LCJvZmZpY2VyQm9udXMiOjAuMDQsImNvZ3NEZXByZWNpYXRpb24iOjAuNDcsInNnYURlcHJlY2lhdGlvbiI6MS40MywicmVzZWFyY2hEZXZlbG9wbWVudCI6MC4zOH0sIm90aGVyIjp7InNhbGVzIjo2Ny4yLCJjb2dzIjo0NS43LCJlbXBsb3llZVBheSI6Ny41NCwib2ZmaWNlclBheSI6MC41OCwiZGVwcmVjaWF0aW9uIjoxLjQ0LCJvdGhlclNnYSI6Ny42OCwiaGVhZGNvdW50IjoxMjUsIm9mZmljZXJDb3VudCI6MywiZW1wbG95ZWVTYWxhcnkiOjcuMTYsImVtcGxveWVlQm9udXMiOjAuMzgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTIsIm9mZmljZXJCb251cyI6MC4wNiwiY29nc0RlcHJlY2lhdGlvbiI6MC4yOSwic2dhRGVwcmVjaWF0aW9uIjoxLjE1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI5LCJvcmRpbmFyeUluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsInByZVRheEluY29tZSI6My45Njk5OTk5OTk5OTk5OTcsIm5ldEluY29tZSI6Mi43ODE5OTk5OTk5OTk5OTgzfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjIuNzk5OTk5OTk5OTk5OTk3fX1dLCJiYWxhbmNlU2hlZXRzIjpbeyJ5ZWFyIjoyMDIzLCJhc3NldHMiOjEzMiwiY3VycmVudEFzc2V0cyI6NjcsImNhc2giOjI0LCJmaXhlZEFzc2V0cyI6NjUsInRhbmdpYmxlQXNzZXRzIjo1MywiYnVpbGRpbmdzIjoxOSwibWFjaGluZXJ5IjoyNCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjcsInNvZnR3YXJlIjo1LCJsaWFiaWxpdGllcyI6NzUsImN1cnJlbnRMaWFiaWxpdGllcyI6MzksInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozNiwibG9uZ1Rlcm1EZWJ0IjoyOSwibmV0QXNzZXRzIjo1Nywic2hhcmVob2xkZXJFcXVpdHkiOjU0LCJjYXBpdGFsIjoxMCwiY2FwZXgiOjV9LHsieWVhciI6MjAyNCwiYXNzZXRzIjoxNDMsImN1cnJlbnRBc3NldHMiOjcyLCJjYXNoIjoyNSwiZml4ZWRBc3NldHMiOjcxLCJ0YW5naWJsZUFzc2V0cyI6NTgsImJ1aWxkaW5ncyI6MjAsIm1hY2hpbmVyeSI6MjgsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo4LCJzb2Z0d2FyZSI6NiwibGlhYmlsaXRpZXMiOjc5LCJjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJzaG9ydFRlcm1EZWJ0IjoxMiwiZml4ZWRMaWFiaWxpdGllcyI6MzgsImxvbmdUZXJtRGVidCI6MzEsIm5ldEFzc2V0cyI6NjQsInNoYXJlaG9sZGVyRXF1aXR5Ijo2MSwiY2FwaXRhbCI6MTAsImNhcGV4Ijo4fSx7InllYXIiOjIwMjUsImFzc2V0cyI6MTU2LCJjdXJyZW50QXNzZXRzIjo3OCwiY2FzaCI6MjcsImZpeGVkQXNzZXRzIjo3OCwidGFuZ2libGVBc3NldHMiOjY0LCJidWlsZGluZ3MiOjIyLCJtYWNoaW5lcnkiOjMyLCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6OSwic29mdHdhcmUiOjcsImxpYWJpbGl0aWVzIjo4MywiY3VycmVudExpYWJpbGl0aWVzIjo0Mywic2hvcnRUZXJtRGVidCI6MTEsImZpeGVkTGlhYmlsaXRpZXMiOjQwLCJsb25nVGVybURlYnQiOjMyLCJuZXRBc3NldHMiOjczLCJzaGFyZWhvbGRlckVxdWl0eSI6NzAsImNhcGl0YWwiOjEwLCJjYXBleCI6MTB9XSwiZnV0dXJlQ2FwZXgiOlt7InllYXIiOjIwMjYsInZhbHVlIjo3LjY3fSx7InllYXIiOjIwMjcsInZhbHVlIjo3LjY3fSx7InllYXIiOjIwMjgsInZhbHVlIjo3LjY2fSx7InllYXIiOjIwMjksInZhbHVlIjowfSx7InllYXIiOjIwMzAsInZhbHVlIjowfSx7InllYXIiOjIwMzEsInZhbHVlIjowfV0sImRyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjIsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNTEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjo3MiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjIzLjA0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Ni43OCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjUuMTksImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC41MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjQ3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6Ny45MSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2Ijo3LjY3LCJmdXR1cmUtY2FwZXg6MjAyNyI6Ny42NywiZnV0dXJlLWNhcGV4OjIwMjgiOjcuNjYsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjplZmZlY3RpdmVUYXhSYXRlIjowLjMsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjAiOjAsImRyaXZlci1yYW5nZTplZmZlY3RpdmVUYXhSYXRlOjEiOjAuNiwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6NS41NTExMTUxMjMxMjU3ODNlLTE3LCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZToxIjoxLjY2NTMzNDUzNjkzNzczNDhlLTE2LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMjAwMzA2NjIzNDI1MTgwNDYsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MzI1MzMwNTAxODQ2OTI3LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZToxIjowLjAyMDczNTk5NDE4MzE4OTE2NiwiZHJpdmVyOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA1NzAxNzU0Mzg1OTY0OTE5LCJkcml2ZXI6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1NzI0NjM3NjgxMTU4NTQsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoVG9CYXNlOjAiOjAuMDQwNzYwODY5NTY1MjE3MTg0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZToxIjowLjA0NDM4NDA1Nzk3MTAxNDUyLCJkcml2ZXI6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MC4wMDAxMzQ1NzU1NjkzNTgxOTczNywiZHJpdmVyOm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MCI6MC4wMTkxMzk0NTcwMjM3MTc0NDMsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aFRvQmFzZToxIjowLjAyMDU1MzQ1OTkxNDc2MzA5NSwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjEiOjAuMDgsImRyaXZlcjpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA4MzMzMzMzMzMzMzMzOSwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlOjAiOjAuMDM5MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZToxIjowLjA0MjUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6b3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MCwiZHJpdmVyOnByb2plY3RTYWxlc0dyb3d0aCI6MC4yMiwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDowIjowLjE1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNhbGVzR3Jvd3RoOjEiOjAuMywiZHJpdmVyOm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjAiOjAuMDYwNzYwODY5NTY1MjE3MTksImRyaXZlci1yYW5nZTpvdGhlclNhbGVzR3Jvd3RoOjEiOjAuMDY0Mzg0MDU3OTcxMDE0NTMsImRyaXZlcjpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNSwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2U6MSI6MC4wMywiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjAiOjAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnQ6MSI6MC4wMDUxMzQ1NzU1NjkzNTgxOTc1LCJkcml2ZXI6cHJvamVjdFBheUdyb3d0aCI6MC4wNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MCI6MC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGg6MSI6MC4xLCJkcml2ZXI6b3RoZXJQYXlHcm93dGgiOjAuMDI0ODQ2NDU4NDY5MjQwMjcsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDowIjowLjAyNDEzOTQ1NzAyMzcxNzQ0NCwiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoOjEiOjAuMDI1NTUzNDU5OTE0NzYzMDk2LCJkcml2ZXI6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyUGF5R3Jvd3RoOjEiOjAuMDgsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aDoxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODMzMzMzMzMzMzMzMzg2LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGg6MCI6MC4wNDQxNjY2NjY2NjY2NjY2OCwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjEiOjAuMDQ3NTAwMDAwMDAwMDAwMDksImRyaXZlcjpwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMSwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FSYXRlRW5kOjAiOjAuMDg0OTk5OTk5OTk5OTk5OTksImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDoxIjowLjEzNSwiZHJpdmVyOm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyODU3MTQyODU3MTQyOCwiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDowIjowLjA4OTI4NTcxNDI4NTcxNDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJTZ2FSYXRlRW5kOjEiOjAuMTE5Mjg1NzE0Mjg1NzE0MjcsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM4MDExNjk1OTA2NDMyNSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoOjAiOjAuMDQyNjMxNTc4OTQ3MzY4MzYsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDoxIjowLjA2NTU1NTU1NTU1NTU1NTU4LCJkcml2ZXI6dXNlZnVsTGlmZSI6MTAsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjAiOjUsImRyaXZlci1yYW5nZTp1c2VmdWxMaWZlOjEiOjIwLCJkcml2ZXI6aW52ZXN0bWVudCI6MjMsImRyaXZlci1yYW5nZTppbnZlc3RtZW50OjAiOjE1LCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDoxIjoyMDAsImRyaXZlcjpzdWJzaWR5Ijo3LjY2LCJkcml2ZXItcmFuZ2U6c3Vic2lkeTowIjoxLCJkcml2ZXItcmFuZ2U6c3Vic2lkeToxIjo1MCwiZHJpdmVyOmxvY2FsQmVuY2htYXJrIjoyMywiZHJpdmVyLXJhbmdlOmxvY2FsQmVuY2htYXJrOjAiOjAsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazoxIjoxMDAsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOnZhbHVlIjoxNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOnZhbHVlIjo4Mi40LCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOnZhbHVlIjoyLCJ0YXJnZXQ6Y29tcGFueVBheVNjaGVkdWxlOm1heCI6NywidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOnZhbHVlIjo2MCwidGFyZ2V0OnByb2plY3RTYWxlc1NoYXJlOm1heCI6OTUsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOnZhbHVlIjoyMiwidGFyZ2V0OnByb2plY3RTYWxlc0NhZ3I6bWF4IjozNSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOnZhbHVlIjo3NC44LCJ0YXJnZXQ6bGFib3JQcm9kdWN0aXZpdHlDYWdyOnZhbHVlIjoyMSwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2FncjptYXgiOjM1LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOnZhbHVlIjoxOC43OCwidGFyZ2V0OmVtcGxveWVlUGF5Q2Fncjp2YWx1ZSI6NywidGFyZ2V0OmVtcGxveWVlUGF5Q2FncjptYXgiOjEwLCJ0YXJnZXQ6ZW1wbG95ZWVQYXlJbmNyZWFzZTp2YWx1ZSI6Mi44NSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOnZhbHVlIjoxNSwidGFyZ2V0OmludmVzdG1lbnRTYWxlc1JhdGlvOm1heCI6NzAsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOnZhbHVlIjoyMTMsInRhcmdldDp2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvOm1heCI6MzUwLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6dmFsdWUiOjIzLCJ0YXJnZXQ6bG9jYWxCZW5jaG1hcms6bWF4Ijo0MCwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOnZhbHVlIjo2LCJ0YXJnZXQ6b2ZmaWNlclBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0Om9mZmljZXJQYXlJbmNyZWFzZTp2YWx1ZSI6MCwidGFyZ2V0OmNvbXBhbnlTYWxlc0luY3JlYXNlOm1heCI6MjUyLjY5LCJ0YXJnZXQ6cHJvamVjdFNhbGVzSW5jcmVhc2U6bWF4IjoxMzYuODQsInRhcmdldDp2YWx1ZUFkZGVkSW5jcmVhc2U6bWF4IjozMy40MywidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6bWF4IjozLjc0fSwibWV0cmljR3JvdXBCYXNlcyI6eyJjb21wYW55U2FsZXMiOiJyYXRlIiwicHJvamVjdFNhbGVzIjoicmF0ZSIsImxhYm9yUHJvZHVjdGl2aXR5IjoicmF0ZSIsImVtcGxveWVlUGF5IjoicmF0ZSJ9LCJhcHBsaWNhdGlvbkNhdGVnb3J5IjoiZ2VuZXJhbCIsImFkanVzdGVkRHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MTA1OTU3NjAyMzM5MTYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjEuMTc0MTg2NDkxMDY0NDY2ZS0xNiwicHJvamVjdFBheUdyb3d0aFRvQmFzZSI6MC4wMTk5ODIxMzU1MTE4Nzk4NzMsInByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDU0MDYzOTAxMjQ5NzIyOTM0LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDEyMDQ1MTMzMzE1NzYzLCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjYwNTUxNjI3MzAwNTI3LCJvdGhlckNvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MCwib3RoZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDE5ODgxMzY3NTAwOTE3MTE3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDYwOTM1Mzk0MzcxNzg1NSwib3RoZXJTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdFNhbGVzR3Jvd3RoIjowLjIyMDIyNDg3MjE2OTQ2NjczLCJvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU2NTE3ODU5NDUyMTc5LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNDk5MDQ4MTM0MTI2NTU1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDg5MDA2MjI5OTc1MDgwMSwib3RoZXJQYXlHcm93dGgiOjAuMDI0ODg3NzYxNzEwMzMzMDMsIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsInByb2plY3RIZWFkY291bnRHcm93dGgiOjAuMDI5MDQ1NDgyMzk3MjA1MDU1LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU3ODQ4MTQ3MzIzMDg2NjUsInByb2plY3RTZ2FSYXRlRW5kIjowLjEwOTkzMTgwOTE2NDg0ODI0LCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5MjcyNTg5ODcyMTI4MjMsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1Mzc3ODA1NzYyODcxNjMyLCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM319</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjcuNjd9LHsieWVhciI6MjAyNywidmFsdWUiOjcuNjd9LHsieWVhciI6MjAyOCwidmFsdWUiOjcuNjZ9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjIsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNTEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjo3MiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjIzLjA0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Ni43OCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjUuMTksImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC41MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjQ3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6Ny45MSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2Ijo3LjY3LCJmdXR1cmUtY2FwZXg6MjAyNyI6Ny42NywiZnV0dXJlLWNhcGV4OjIwMjgiOjcuNjYsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA4NDk5OTk5OTk5OTk5OTk5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4xMzUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wODkyODU3MTQyODU3MTQyNywiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjExOTI4NTcxNDI4NTcxNDI3LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6MiwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQxMDU5NTc2MDIzMzkxNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAxOTk4MjEzNTUxMTg3OTg3MywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwNjM5MDEyNDk3MjI5MzQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MTIwNDUxMzMzMTU3NjMsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA1NTE2MjczMDA1MjcsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4ODEzNjc1MDA5MTcxMTcsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjA5MzUzOTQzNzE3ODU1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTY1MTc4NTk0NTIxNzksInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE0OTkwNDgxMzQxMjY1NTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODkwMDYyMjk5NzUwODAxLCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4ODc3NjE3MTAzMzMwMywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMjkwNDU0ODIzOTcyMDUwNTUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTc4NDgxNDczMjMwODY2NSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTA5OTMxODA5MTY0ODQ4MjQsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -5001,17 +5001,17 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.88 %</t>
+          <t xml:space="preserve">全社 0 %</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.65 %</t>
+          <t xml:space="preserve">全社 0 %</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.43 %</t>
+          <t xml:space="preserve">全社 0 %</t>
         </is>
       </c>
       <c r="J27" s="0" t="inlineStr">
@@ -5063,17 +5063,17 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.49 倍</t>
+          <t xml:space="preserve">全社 0 倍</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.47 倍</t>
+          <t xml:space="preserve">全社 0 倍</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.45 倍</t>
+          <t xml:space="preserve">全社 0 倍</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
@@ -5187,17 +5187,17 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.95 倍</t>
+          <t xml:space="preserve">全社 —</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1 倍</t>
+          <t xml:space="preserve">全社 —</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.05 倍</t>
+          <t xml:space="preserve">全社 —</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
@@ -6697,7 +6697,7 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">新規投資の耐用年数</t>
+          <t xml:space="preserve">新規投資の平均耐用年数（減価償却費の自動予測用・モデル内管理・第6次公式様式外）</t>
         </is>
       </c>
       <c r="B43" s="2">
@@ -6775,7 +6775,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C295"/>
+  <dimension ref="A1:C289"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -10690,11 +10690,11 @@
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2026</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>7.67</v>
+        <v>7</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
@@ -10705,11 +10705,11 @@
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2027</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>7.67</v>
+        <v>2</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10720,11 +10720,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2028</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>7.66</v>
+        <v>35</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10735,56 +10735,56 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2029</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2030</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B265" s="2">
-        <v>0</v>
+        <v>252.69</v>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">future-capex:2031</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>0</v>
+        <v>82.4</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B267" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
@@ -10795,11 +10795,11 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B268" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C268" s="0" t="inlineStr">
         <is>
@@ -10810,11 +10810,11 @@
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>35</v>
+        <v>3.74</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10825,11 +10825,11 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B270" s="2">
-        <v>15</v>
+        <v>2.85</v>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
@@ -10840,11 +10840,11 @@
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>252.69</v>
+        <v>70</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
@@ -10855,11 +10855,11 @@
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>82.4</v>
+        <v>15</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -10870,11 +10870,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -10885,11 +10885,11 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
@@ -10900,11 +10900,11 @@
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>3.74</v>
+        <v>40</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -10915,11 +10915,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>2.85</v>
+        <v>23</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -10930,11 +10930,11 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
@@ -10945,11 +10945,11 @@
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -10960,26 +10960,26 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B280" s="2">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C280" s="0" t="inlineStr">
         <is>
@@ -10990,11 +10990,11 @@
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -11005,11 +11005,11 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>23</v>
+        <v>136.84</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
@@ -11020,11 +11020,11 @@
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
         </is>
       </c>
       <c r="B283" s="2">
-        <v>10</v>
+        <v>74.8</v>
       </c>
       <c r="C283" s="0" t="inlineStr">
         <is>
@@ -11035,11 +11035,11 @@
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11050,26 +11050,26 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
         </is>
       </c>
       <c r="B285" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
         </is>
       </c>
       <c r="B286" s="2">
-        <v>35</v>
+        <v>33.43</v>
       </c>
       <c r="C286" s="0" t="inlineStr">
         <is>
@@ -11080,11 +11080,11 @@
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
         </is>
       </c>
       <c r="B287" s="2">
-        <v>22</v>
+        <v>18.78</v>
       </c>
       <c r="C287" s="0" t="inlineStr">
         <is>
@@ -11095,11 +11095,11 @@
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
         </is>
       </c>
       <c r="B288" s="2">
-        <v>136.84</v>
+        <v>350</v>
       </c>
       <c r="C288" s="0" t="inlineStr">
         <is>
@@ -11110,103 +11110,13 @@
     <row r="289">
       <c r="A289" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
       <c r="B289" s="2">
-        <v>74.8</v>
+        <v>213</v>
       </c>
       <c r="C289" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
-        </is>
-      </c>
-      <c r="B290" s="2">
-        <v>95</v>
-      </c>
-      <c r="C290" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
-        </is>
-      </c>
-      <c r="B291" s="2">
-        <v>60</v>
-      </c>
-      <c r="C291" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
-        </is>
-      </c>
-      <c r="B292" s="2">
-        <v>33.43</v>
-      </c>
-      <c r="C292" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
-        </is>
-      </c>
-      <c r="B293" s="2">
-        <v>18.78</v>
-      </c>
-      <c r="C293" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
-        </is>
-      </c>
-      <c r="B294" s="2">
-        <v>350</v>
-      </c>
-      <c r="C294" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
-        </is>
-      </c>
-      <c r="B295" s="2">
-        <v>213</v>
-      </c>
-      <c r="C295" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11234,7 +11144,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjcuNjd9LHsieWVhciI6MjAyNywidmFsdWUiOjcuNjd9LHsieWVhciI6MjAyOCwidmFsdWUiOjcuNjZ9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjIsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNTEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjo3MiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjIzLjA0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Ni43OCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjUuMTksImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC41MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjQ3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6Ny45MSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImZ1dHVyZS1jYXBleDoyMDI2Ijo3LjY3LCJmdXR1cmUtY2FwZXg6MjAyNyI6Ny42NywiZnV0dXJlLWNhcGV4OjIwMjgiOjcuNjYsImZ1dHVyZS1jYXBleDoyMDI5IjowLCJmdXR1cmUtY2FwZXg6MjAzMCI6MCwiZnV0dXJlLWNhcGV4OjIwMzEiOjAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA4NDk5OTk5OTk5OTk5OTk5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4xMzUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wODkyODU3MTQyODU3MTQyNywiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjExOTI4NTcxNDI4NTcxNDI3LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6MiwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQxMDU5NTc2MDIzMzkxNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAxOTk4MjEzNTUxMTg3OTg3MywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwNjM5MDEyNDk3MjI5MzQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MTIwNDUxMzMzMTU3NjMsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA1NTE2MjczMDA1MjcsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4ODEzNjc1MDA5MTcxMTcsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjA5MzUzOTQzNzE3ODU1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTY1MTc4NTk0NTIxNzksInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE0OTkwNDgxMzQxMjY1NTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODkwMDYyMjk5NzUwODAxLCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4ODc3NjE3MTAzMzMwMywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMjkwNDU0ODIzOTcyMDUwNTUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTc4NDgxNDczMjMwODY2NSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTA5OTMxODA5MTY0ODQ4MjQsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjIsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNTEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjo3MiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjIzLjA0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Ni43OCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjUuMTksImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC41MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjQ3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6Ny45MSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA4NDk5OTk5OTk5OTk5OTk5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4xMzUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wODkyODU3MTQyODU3MTQyNywiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjExOTI4NTcxNDI4NTcxNDI3LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6MiwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQxMDU5NTc2MDIzMzkxNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAxOTk4MjEzNTUxMTg3OTg3MywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwNjM5MDEyNDk3MjI5MzQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MTIwNDUxMzMzMTU3NjMsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA1NTE2MjczMDA1MjcsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4ODEzNjc1MDA5MTcxMTcsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjA5MzUzOTQzNzE3ODU1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTY1MTc4NTk0NTIxNzksInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE0OTkwNDgxMzQxMjY1NTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODkwMDYyMjk5NzUwODAxLCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4ODc3NjE3MTAzMzMwMywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMjkwNDU0ODIzOTcyMDUwNTUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTc4NDgxNDczMjMwODY2NSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTA5OTMxODA5MTY0ODQ4MjQsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -204,7 +204,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>15.464691482957393</v>
+        <v>15.474805389539558</v>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
@@ -234,7 +234,7 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>93.33000000000001</v>
+        <v>93.4</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
@@ -264,7 +264,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>2.0628917862888008</v>
+        <v>2.002890072409058</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -294,7 +294,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>63.91350052560445</v>
+        <v>63.919228315129686</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -324,7 +324,7 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>22.02271203454029</v>
+        <v>22.037045725736924</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -354,7 +354,7 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>76.54</v>
+        <v>76.60000000000001</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>23.487308177598077</v>
+        <v>24.447010059327056</v>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
@@ -414,7 +414,7 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>19.66</v>
+        <v>19.660000000000004</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>7.000299957045453</v>
+        <v>7.017971691139446</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>2.46</v>
+        <v>2.380000000000001</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>256.65796344647515</v>
+        <v>256.6579634464752</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
@@ -1268,13 +1268,13 @@
         <v>173.03</v>
       </c>
       <c r="H3" s="4">
-        <v>199.47</v>
+        <v>199.48</v>
       </c>
       <c r="I3" s="4">
-        <v>229.95999999999998</v>
+        <v>230.01</v>
       </c>
       <c r="J3" s="4">
-        <v>266.36</v>
+        <v>266.43</v>
       </c>
     </row>
     <row r="4">
@@ -1304,13 +1304,13 @@
         <v>4.879379318705279</v>
       </c>
       <c r="H4" s="2">
-        <v>15.28058718141363</v>
+        <v>15.286366526035945</v>
       </c>
       <c r="I4" s="2">
-        <v>15.285506592470032</v>
+        <v>15.304792460397042</v>
       </c>
       <c r="J4" s="2">
-        <v>15.828839798225802</v>
+        <v>15.834094169818712</v>
       </c>
     </row>
     <row r="5">
@@ -1335,16 +1335,16 @@
         <v>112.19</v>
       </c>
       <c r="G5" s="2">
-        <v>117.67</v>
+        <v>117.66</v>
       </c>
       <c r="H5" s="2">
-        <v>134.36</v>
+        <v>134.37</v>
       </c>
       <c r="I5" s="2">
-        <v>154.09</v>
+        <v>154.12</v>
       </c>
       <c r="J5" s="2">
-        <v>177.45999999999998</v>
+        <v>177.51</v>
       </c>
     </row>
     <row r="6">
@@ -1363,22 +1363,22 @@
         <v>0.8</v>
       </c>
       <c r="E6" s="2">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="F6" s="2">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G6" s="2">
-        <v>1.37</v>
+        <v>0.8</v>
       </c>
       <c r="H6" s="2">
-        <v>1.37</v>
+        <v>0.8</v>
       </c>
       <c r="I6" s="2">
-        <v>1.37</v>
+        <v>0.8</v>
       </c>
       <c r="J6" s="2">
-        <v>1.37</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -1403,16 +1403,16 @@
         <v>52.79000000000002</v>
       </c>
       <c r="G7" s="4">
-        <v>55.36</v>
+        <v>55.370000000000005</v>
       </c>
       <c r="H7" s="4">
         <v>65.10999999999999</v>
       </c>
       <c r="I7" s="4">
-        <v>75.86999999999998</v>
+        <v>75.88999999999999</v>
       </c>
       <c r="J7" s="4">
-        <v>88.90000000000003</v>
+        <v>88.92000000000002</v>
       </c>
     </row>
     <row r="8">
@@ -1437,16 +1437,16 @@
         <v>31.997817917323324</v>
       </c>
       <c r="G8" s="2">
-        <v>31.994451829162575</v>
+        <v>32.00023117378489</v>
       </c>
       <c r="H8" s="2">
-        <v>32.641499974933566</v>
+        <v>32.63986364547824</v>
       </c>
       <c r="I8" s="2">
-        <v>32.99269438163158</v>
+        <v>32.994217642711185</v>
       </c>
       <c r="J8" s="2">
-        <v>33.37588226460431</v>
+        <v>33.37461997522802</v>
       </c>
     </row>
     <row r="9">
@@ -1465,22 +1465,22 @@
         <v>36.4</v>
       </c>
       <c r="E9" s="2">
-        <v>38.85</v>
+        <v>38.26</v>
       </c>
       <c r="F9" s="2">
-        <v>41.44</v>
+        <v>40.26</v>
       </c>
       <c r="G9" s="2">
-        <v>44.15</v>
+        <v>42.400000000000006</v>
       </c>
       <c r="H9" s="2">
-        <v>47.900000000000006</v>
+        <v>46.18</v>
       </c>
       <c r="I9" s="2">
-        <v>52.56</v>
+        <v>50.78999999999999</v>
       </c>
       <c r="J9" s="2">
-        <v>57.769999999999996</v>
+        <v>55.97</v>
       </c>
     </row>
     <row r="10">
@@ -1601,22 +1601,22 @@
         <v>14</v>
       </c>
       <c r="E13" s="2">
-        <v>14.940000000000001</v>
+        <v>14.93</v>
       </c>
       <c r="F13" s="2">
-        <v>15.95</v>
+        <v>15.92</v>
       </c>
       <c r="G13" s="2">
-        <v>17.02</v>
+        <v>16.990000000000002</v>
       </c>
       <c r="H13" s="2">
         <v>18.15</v>
       </c>
       <c r="I13" s="2">
-        <v>19.84</v>
+        <v>19.79</v>
       </c>
       <c r="J13" s="2">
-        <v>21.689999999999998</v>
+        <v>21.58</v>
       </c>
     </row>
     <row r="14">
@@ -1635,22 +1635,22 @@
         <v>13.3</v>
       </c>
       <c r="E14" s="2">
-        <v>14.2</v>
+        <v>14.190000000000001</v>
       </c>
       <c r="F14" s="2">
-        <v>15.15</v>
+        <v>15.120000000000001</v>
       </c>
       <c r="G14" s="2">
-        <v>16.17</v>
+        <v>16.14</v>
       </c>
       <c r="H14" s="2">
-        <v>17.68</v>
+        <v>17.59</v>
       </c>
       <c r="I14" s="2">
-        <v>19.34</v>
+        <v>19.18</v>
       </c>
       <c r="J14" s="2">
-        <v>21.15</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="15">
@@ -1678,13 +1678,13 @@
         <v>0.85</v>
       </c>
       <c r="H15" s="2">
-        <v>0.9299999999999999</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="I15" s="2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="J15" s="2">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
@@ -1703,22 +1703,22 @@
         <v>2.7</v>
       </c>
       <c r="E16" s="2">
-        <v>3.2800000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="F16" s="2">
-        <v>3.8499999999999996</v>
+        <v>2.7</v>
       </c>
       <c r="G16" s="2">
-        <v>4.42</v>
+        <v>2.7</v>
       </c>
       <c r="H16" s="2">
-        <v>4.42</v>
+        <v>2.7</v>
       </c>
       <c r="I16" s="2">
-        <v>4.42</v>
+        <v>2.7</v>
       </c>
       <c r="J16" s="2">
-        <v>4.42</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -1771,22 +1771,22 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>11.490000000000006</v>
+        <v>12.080000000000005</v>
       </c>
       <c r="F18" s="4">
-        <v>11.350000000000016</v>
+        <v>12.530000000000012</v>
       </c>
       <c r="G18" s="4">
-        <v>11.21</v>
+        <v>12.969999999999999</v>
       </c>
       <c r="H18" s="4">
-        <v>17.209999999999987</v>
+        <v>18.929999999999986</v>
       </c>
       <c r="I18" s="4">
-        <v>23.309999999999974</v>
+        <v>25.099999999999987</v>
       </c>
       <c r="J18" s="4">
-        <v>31.130000000000045</v>
+        <v>32.950000000000024</v>
       </c>
     </row>
     <row r="19">
@@ -1805,22 +1805,22 @@
         <v>7.733333333333333</v>
       </c>
       <c r="E19" s="2">
-        <v>7.304049329349695</v>
+        <v>7.679104952005597</v>
       </c>
       <c r="F19" s="2">
-        <v>6.879621772336049</v>
+        <v>7.594859983028251</v>
       </c>
       <c r="G19" s="2">
-        <v>6.478645321620529</v>
+        <v>7.495809975148818</v>
       </c>
       <c r="H19" s="2">
-        <v>8.627863839173804</v>
+        <v>9.48967315019049</v>
       </c>
       <c r="I19" s="2">
-        <v>10.136545486171498</v>
+        <v>10.91256901873831</v>
       </c>
       <c r="J19" s="2">
-        <v>11.687190268809147</v>
+        <v>12.367225912997794</v>
       </c>
     </row>
     <row r="20">
@@ -1839,22 +1839,22 @@
         <v>11.3</v>
       </c>
       <c r="E20" s="4">
-        <v>11.129999999999999</v>
+        <v>11.719999999999999</v>
       </c>
       <c r="F20" s="4">
-        <v>10.97</v>
+        <v>12.149999999999999</v>
       </c>
       <c r="G20" s="4">
-        <v>10.81</v>
+        <v>12.57</v>
       </c>
       <c r="H20" s="4">
-        <v>15.5</v>
+        <v>17.31</v>
       </c>
       <c r="I20" s="4">
-        <v>21.46</v>
+        <v>23.36</v>
       </c>
       <c r="J20" s="4">
-        <v>29.130000000000003</v>
+        <v>31.07</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1873,22 @@
         <v>11.3</v>
       </c>
       <c r="E21" s="2">
-        <v>11.129999999999999</v>
+        <v>11.719999999999999</v>
       </c>
       <c r="F21" s="2">
-        <v>10.97</v>
+        <v>12.149999999999999</v>
       </c>
       <c r="G21" s="2">
-        <v>10.81</v>
+        <v>12.57</v>
       </c>
       <c r="H21" s="2">
-        <v>15.5</v>
+        <v>17.31</v>
       </c>
       <c r="I21" s="2">
-        <v>21.46</v>
+        <v>23.36</v>
       </c>
       <c r="J21" s="2">
-        <v>29.130000000000003</v>
+        <v>31.07</v>
       </c>
     </row>
     <row r="22">
@@ -1907,22 +1907,22 @@
         <v>7.91</v>
       </c>
       <c r="E22" s="2">
-        <v>7.79</v>
+        <v>8.2</v>
       </c>
       <c r="F22" s="2">
-        <v>7.68</v>
+        <v>8.51</v>
       </c>
       <c r="G22" s="2">
-        <v>7.57</v>
+        <v>8.8</v>
       </c>
       <c r="H22" s="2">
-        <v>10.85</v>
+        <v>12.120000000000001</v>
       </c>
       <c r="I22" s="2">
-        <v>15.030000000000001</v>
+        <v>16.36</v>
       </c>
       <c r="J22" s="2">
-        <v>20.39</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="23">
@@ -1941,22 +1941,22 @@
         <v>14</v>
       </c>
       <c r="E23" s="2">
-        <v>14.940000000000001</v>
+        <v>14.93</v>
       </c>
       <c r="F23" s="2">
-        <v>15.95</v>
+        <v>15.92</v>
       </c>
       <c r="G23" s="2">
-        <v>17.02</v>
+        <v>16.990000000000002</v>
       </c>
       <c r="H23" s="2">
         <v>18.15</v>
       </c>
       <c r="I23" s="2">
-        <v>19.84</v>
+        <v>19.79</v>
       </c>
       <c r="J23" s="2">
-        <v>21.689999999999998</v>
+        <v>21.58</v>
       </c>
     </row>
     <row r="24">
@@ -2009,22 +2009,22 @@
         <v>3.5</v>
       </c>
       <c r="E25" s="2">
-        <v>4.27</v>
+        <v>3.5</v>
       </c>
       <c r="F25" s="2">
-        <v>5.029999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="G25" s="2">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="H25" s="2">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="I25" s="2">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="J25" s="2">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="26">
@@ -2043,22 +2043,22 @@
         <v>30.1</v>
       </c>
       <c r="E26" s="4">
-        <v>31.740000000000006</v>
+        <v>31.550000000000004</v>
       </c>
       <c r="F26" s="4">
-        <v>33.420000000000016</v>
+        <v>33.040000000000006</v>
       </c>
       <c r="G26" s="4">
-        <v>35.17</v>
+        <v>34.6</v>
       </c>
       <c r="H26" s="4">
-        <v>42.36999999999998</v>
+        <v>41.789999999999985</v>
       </c>
       <c r="I26" s="4">
-        <v>50.20999999999997</v>
+        <v>49.649999999999984</v>
       </c>
       <c r="J26" s="4">
-        <v>59.94000000000004</v>
+        <v>59.35000000000002</v>
       </c>
     </row>
     <row r="27">
@@ -2079,22 +2079,22 @@
         <v>4.768534632788035</v>
       </c>
       <c r="E27" s="2">
-        <v>5.448504983388713</v>
+        <v>4.8172757475083205</v>
       </c>
       <c r="F27" s="2">
-        <v>5.293005671077533</v>
+        <v>4.722662440570535</v>
       </c>
       <c r="G27" s="2">
-        <v>5.236385397965249</v>
+        <v>4.721549636803868</v>
       </c>
       <c r="H27" s="2">
-        <v>20.47199317600221</v>
+        <v>20.780346820809203</v>
       </c>
       <c r="I27" s="2">
-        <v>18.5036582487609</v>
+        <v>18.808327351040923</v>
       </c>
       <c r="J27" s="2">
-        <v>19.378609838677697</v>
+        <v>19.536757301107844</v>
       </c>
     </row>
     <row r="28">
@@ -2113,22 +2113,22 @@
         <v>20.06666666666667</v>
       </c>
       <c r="E28" s="2">
-        <v>20.176721123895497</v>
+        <v>20.055940499650372</v>
       </c>
       <c r="F28" s="2">
-        <v>20.257000848587715</v>
+        <v>20.026669899381744</v>
       </c>
       <c r="G28" s="2">
-        <v>20.32595503669884</v>
+        <v>19.99653239322661</v>
       </c>
       <c r="H28" s="2">
-        <v>21.241289416954924</v>
+        <v>20.949468618407856</v>
       </c>
       <c r="I28" s="2">
-        <v>21.834232040354834</v>
+        <v>21.586017999217418</v>
       </c>
       <c r="J28" s="2">
-        <v>22.50337888571859</v>
+        <v>22.27601996772136</v>
       </c>
     </row>
     <row r="29">
@@ -2156,13 +2156,13 @@
         <v>263</v>
       </c>
       <c r="H29" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I29" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J29" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30">
@@ -2215,22 +2215,22 @@
         <v>0.06086956521739131</v>
       </c>
       <c r="E31" s="2">
-        <v>0.06225000000000001</v>
+        <v>0.06220833333333333</v>
       </c>
       <c r="F31" s="2">
-        <v>0.06329365079365079</v>
+        <v>0.06317460317460317</v>
       </c>
       <c r="G31" s="2">
-        <v>0.0647148288973384</v>
+        <v>0.06460076045627378</v>
       </c>
       <c r="H31" s="2">
-        <v>0.06648351648351648</v>
+        <v>0.06672794117647059</v>
       </c>
       <c r="I31" s="2">
-        <v>0.06985915492957746</v>
+        <v>0.070177304964539</v>
       </c>
       <c r="J31" s="2">
-        <v>0.07352542372881356</v>
+        <v>0.0736518771331058</v>
       </c>
     </row>
     <row r="32">
@@ -2251,22 +2251,22 @@
         <v>1.9901321235802572</v>
       </c>
       <c r="E32" s="2">
-        <v>2.267857142857155</v>
+        <v>2.199404761904744</v>
       </c>
       <c r="F32" s="2">
-        <v>1.6765474596799779</v>
+        <v>1.5532803878416823</v>
       </c>
       <c r="G32" s="2">
-        <v>2.2453723017509475</v>
+        <v>2.2574851443529553</v>
       </c>
       <c r="H32" s="2">
-        <v>2.733048385222303</v>
+        <v>3.2928106498632204</v>
       </c>
       <c r="I32" s="2">
-        <v>5.077406588290079</v>
+        <v>5.169294492311893</v>
       </c>
       <c r="J32" s="2">
-        <v>5.24808638600327</v>
+        <v>4.951133661120943</v>
       </c>
     </row>
     <row r="33">
@@ -2355,22 +2355,22 @@
         <v>0.12808510638297874</v>
       </c>
       <c r="E35" s="2">
-        <v>0.1295510204081633</v>
+        <v>0.12877551020408165</v>
       </c>
       <c r="F35" s="2">
-        <v>0.13003891050583663</v>
+        <v>0.1285603112840467</v>
       </c>
       <c r="G35" s="2">
-        <v>0.1312313432835821</v>
+        <v>0.1291044776119403</v>
       </c>
       <c r="H35" s="2">
-        <v>0.152410071942446</v>
+        <v>0.15086642599277972</v>
       </c>
       <c r="I35" s="2">
-        <v>0.17373702422145318</v>
+        <v>0.17299651567944246</v>
       </c>
       <c r="J35" s="2">
-        <v>0.19980000000000014</v>
+        <v>0.19916107382550344</v>
       </c>
     </row>
     <row r="36">
@@ -2389,22 +2389,22 @@
         <v>15.100000000000001</v>
       </c>
       <c r="E36" s="4">
-        <v>15.760000000000005</v>
+        <v>15.580000000000005</v>
       </c>
       <c r="F36" s="4">
-        <v>16.380000000000017</v>
+        <v>16.030000000000012</v>
       </c>
       <c r="G36" s="4">
-        <v>17.01</v>
+        <v>16.47</v>
       </c>
       <c r="H36" s="4">
-        <v>23.009999999999987</v>
+        <v>22.429999999999986</v>
       </c>
       <c r="I36" s="4">
-        <v>29.109999999999975</v>
+        <v>28.599999999999987</v>
       </c>
       <c r="J36" s="4">
-        <v>36.93000000000004</v>
+        <v>36.450000000000024</v>
       </c>
     </row>
     <row r="37">
@@ -2423,22 +2423,22 @@
         <v>10.066666666666668</v>
       </c>
       <c r="E37" s="2">
-        <v>10.018434937384784</v>
+        <v>9.904011188099933</v>
       </c>
       <c r="F37" s="2">
-        <v>9.928476178930788</v>
+        <v>9.716329252030555</v>
       </c>
       <c r="G37" s="2">
-        <v>9.83066520256603</v>
+        <v>9.518580592960756</v>
       </c>
       <c r="H37" s="2">
-        <v>11.535569258535112</v>
+        <v>11.244235011028668</v>
       </c>
       <c r="I37" s="2">
-        <v>12.658723256218462</v>
+        <v>12.434241989478712</v>
       </c>
       <c r="J37" s="2">
-        <v>13.864694398558358</v>
+        <v>13.680891791464934</v>
       </c>
     </row>
     <row r="38">
@@ -2459,22 +2459,22 @@
         <v>3.1420765027322606</v>
       </c>
       <c r="E38" s="2">
-        <v>4.370860927152331</v>
+        <v>3.1788079470199015</v>
       </c>
       <c r="F38" s="2">
-        <v>3.9340101522843396</v>
+        <v>2.888318356867825</v>
       </c>
       <c r="G38" s="2">
-        <v>3.8461538461537437</v>
+        <v>2.744853399875158</v>
       </c>
       <c r="H38" s="2">
-        <v>35.27336860670185</v>
+        <v>36.18700667880987</v>
       </c>
       <c r="I38" s="2">
-        <v>26.510212950890867</v>
+        <v>27.507802050824814</v>
       </c>
       <c r="J38" s="2">
-        <v>26.863620748883797</v>
+        <v>27.447552447552592</v>
       </c>
     </row>
   </sheetData>
@@ -2483,7 +2483,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="58" customWidth="1"/>
@@ -2636,13 +2636,13 @@
         <v>93.7</v>
       </c>
       <c r="H3" s="4">
-        <v>114.34</v>
+        <v>114.35</v>
       </c>
       <c r="I3" s="4">
-        <v>139.51</v>
+        <v>139.55</v>
       </c>
       <c r="J3" s="4">
-        <v>170.24</v>
+        <v>170.3</v>
       </c>
     </row>
     <row r="4">
@@ -2672,13 +2672,13 @@
         <v>5.41118236022049</v>
       </c>
       <c r="H4" s="2">
-        <v>22.027748132337255</v>
+        <v>22.03842049092848</v>
       </c>
       <c r="I4" s="2">
-        <v>22.01329368549938</v>
+        <v>22.03760384783562</v>
       </c>
       <c r="J4" s="2">
-        <v>22.027094831911697</v>
+        <v>22.035112862773197</v>
       </c>
     </row>
     <row r="5">
@@ -2706,13 +2706,13 @@
         <v>54.1524591111368</v>
       </c>
       <c r="H5" s="2">
-        <v>57.321903043064125</v>
+        <v>57.32404251052737</v>
       </c>
       <c r="I5" s="2">
-        <v>60.66707253435381</v>
+        <v>60.67127516194949</v>
       </c>
       <c r="J5" s="2">
-        <v>63.91350052560445</v>
+        <v>63.919228315129686</v>
       </c>
     </row>
     <row r="6">
@@ -2743,10 +2743,10 @@
         <v>37.16</v>
       </c>
       <c r="I6" s="4">
-        <v>46.02999999999999</v>
+        <v>46.040000000000006</v>
       </c>
       <c r="J6" s="4">
-        <v>57.02000000000001</v>
+        <v>57.040000000000006</v>
       </c>
     </row>
     <row r="7">
@@ -2774,13 +2774,13 @@
         <v>31.995731056563503</v>
       </c>
       <c r="H7" s="2">
-        <v>32.49956270771383</v>
+        <v>32.496720594665504</v>
       </c>
       <c r="I7" s="2">
-        <v>32.99405060569134</v>
+        <v>32.99175922608384</v>
       </c>
       <c r="J7" s="2">
-        <v>33.49389097744361</v>
+        <v>33.493834409864945</v>
       </c>
     </row>
     <row r="8">
@@ -2799,22 +2799,22 @@
         <v>7.300000000000004</v>
       </c>
       <c r="E8" s="4">
-        <v>7.079999999999991</v>
+        <v>7.669999999999991</v>
       </c>
       <c r="F8" s="4">
-        <v>6.859999999999996</v>
+        <v>8.039999999999996</v>
       </c>
       <c r="G8" s="4">
-        <v>6.650000000000006</v>
+        <v>8.410000000000004</v>
       </c>
       <c r="H8" s="4">
-        <v>11.249999999999998</v>
+        <v>12.969999999999997</v>
       </c>
       <c r="I8" s="4">
-        <v>16.69999999999998</v>
+        <v>18.480000000000004</v>
       </c>
       <c r="J8" s="4">
-        <v>23.77000000000001</v>
+        <v>25.61000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2833,22 +2833,22 @@
         <v>9.125000000000005</v>
       </c>
       <c r="E9" s="2">
-        <v>8.395588758448941</v>
+        <v>9.095221154986351</v>
       </c>
       <c r="F9" s="2">
-        <v>7.717403532455839</v>
+        <v>9.044886938913258</v>
       </c>
       <c r="G9" s="2">
-        <v>7.097118463180369</v>
+        <v>8.975453575240131</v>
       </c>
       <c r="H9" s="2">
-        <v>9.83907643869162</v>
+        <v>11.34236991692173</v>
       </c>
       <c r="I9" s="2">
-        <v>11.970468066805234</v>
+        <v>13.242565388749552</v>
       </c>
       <c r="J9" s="2">
-        <v>13.962640977443613</v>
+        <v>15.038167938931302</v>
       </c>
     </row>
     <row r="10">
@@ -2867,22 +2867,22 @@
         <v>6</v>
       </c>
       <c r="E10" s="2">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
       <c r="F10" s="2">
-        <v>6.94</v>
+        <v>6.91</v>
       </c>
       <c r="G10" s="2">
-        <v>7.46</v>
+        <v>7.42</v>
       </c>
       <c r="H10" s="2">
         <v>7.9</v>
       </c>
       <c r="I10" s="2">
-        <v>8.85</v>
+        <v>8.8</v>
       </c>
       <c r="J10" s="2">
-        <v>9.92</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="11">
@@ -2922,283 +2922,281 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-10 減価償却費（合計）（億円）</t>
+          <t xml:space="preserve">P2-4 売上原価に含まれる減価償却費（内部管理用）（億円）</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>1.8</v>
+        <v>0.45</v>
       </c>
       <c r="C12" s="2">
-        <v>1.9</v>
+        <v>0.47</v>
       </c>
       <c r="D12" s="2">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="2">
-        <v>2.77</v>
+        <v>0.5</v>
       </c>
       <c r="F12" s="2">
-        <v>3.53</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="2">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="2">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="I12" s="2">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J12" s="2">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7-11 付加価値（億円）</t>
-        </is>
-      </c>
-      <c r="B13" s="4">
-        <v>14.129999999999999</v>
-      </c>
-      <c r="C13" s="4">
-        <v>14.910000000000004</v>
-      </c>
-      <c r="D13" s="4">
-        <v>15.700000000000005</v>
-      </c>
-      <c r="E13" s="4">
-        <v>16.71999999999999</v>
-      </c>
-      <c r="F13" s="4">
-        <v>17.769999999999996</v>
-      </c>
-      <c r="G13" s="4">
-        <v>18.880000000000006</v>
-      </c>
-      <c r="H13" s="4">
-        <v>23.95</v>
-      </c>
-      <c r="I13" s="4">
-        <v>30.369999999999983</v>
-      </c>
-      <c r="J13" s="4">
-        <v>38.540000000000006</v>
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2-14 販管費に含まれる減価償却費（内部管理用）（億円）</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <v>1.35</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1.43</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-12 付加価値増加率（%）</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">7-10 減価償却費（合計）（億円）</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <v>1.8</v>
       </c>
       <c r="C14" s="2">
-        <v>5.520169851380086</v>
+        <v>1.9</v>
       </c>
       <c r="D14" s="2">
-        <v>5.2984574111334615</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2">
-        <v>6.496815286624114</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2">
-        <v>6.279904306220119</v>
+        <v>2</v>
       </c>
       <c r="G14" s="2">
-        <v>6.246482836240919</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2">
-        <v>26.853813559321992</v>
+        <v>2</v>
       </c>
       <c r="I14" s="2">
-        <v>26.805845511482197</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2">
-        <v>26.901547579848618</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7-13 常時使用する従業員数（就業時間換算）（人）</t>
-        </is>
-      </c>
-      <c r="B15" s="2">
-        <v>90</v>
-      </c>
-      <c r="C15" s="2">
-        <v>95</v>
-      </c>
-      <c r="D15" s="2">
-        <v>100</v>
-      </c>
-      <c r="E15" s="2">
-        <v>105</v>
-      </c>
-      <c r="F15" s="2">
-        <v>111</v>
-      </c>
-      <c r="G15" s="2">
-        <v>117</v>
-      </c>
-      <c r="H15" s="2">
-        <v>120</v>
-      </c>
-      <c r="I15" s="2">
-        <v>124</v>
-      </c>
-      <c r="J15" s="2">
-        <v>127</v>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7-11 付加価値（億円）</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <v>14.129999999999999</v>
+      </c>
+      <c r="C15" s="4">
+        <v>14.910000000000004</v>
+      </c>
+      <c r="D15" s="4">
+        <v>15.700000000000005</v>
+      </c>
+      <c r="E15" s="4">
+        <v>16.529999999999994</v>
+      </c>
+      <c r="F15" s="4">
+        <v>17.389999999999993</v>
+      </c>
+      <c r="G15" s="4">
+        <v>18.300000000000004</v>
+      </c>
+      <c r="H15" s="4">
+        <v>23.369999999999997</v>
+      </c>
+      <c r="I15" s="4">
+        <v>29.800000000000004</v>
+      </c>
+      <c r="J15" s="4">
+        <v>37.96000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-14 役員数（人）</t>
-        </is>
-      </c>
-      <c r="B16" s="2">
-        <v>2</v>
+          <t xml:space="preserve">7-12 付加価値増加率（%）</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>5.520169851380086</v>
       </c>
       <c r="D16" s="2">
-        <v>2</v>
+        <v>5.2984574111334615</v>
       </c>
       <c r="E16" s="2">
-        <v>2</v>
+        <v>5.286624203821577</v>
       </c>
       <c r="F16" s="2">
-        <v>2</v>
+        <v>5.202661826981236</v>
       </c>
       <c r="G16" s="2">
-        <v>2</v>
+        <v>5.23289246693508</v>
       </c>
       <c r="H16" s="2">
-        <v>2</v>
+        <v>27.70491803278685</v>
       </c>
       <c r="I16" s="2">
-        <v>2</v>
+        <v>27.513906718014592</v>
       </c>
       <c r="J16" s="2">
-        <v>2</v>
+        <v>27.38255033557049</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-15 従業員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">7-13 常時使用する従業員数（就業時間換算）（人）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0.05766666666666667</v>
+        <v>90</v>
       </c>
       <c r="C17" s="2">
-        <v>0.05884210526315789</v>
+        <v>95</v>
       </c>
       <c r="D17" s="2">
-        <v>0.06</v>
+        <v>100</v>
       </c>
       <c r="E17" s="2">
-        <v>0.06142857142857143</v>
+        <v>105</v>
       </c>
       <c r="F17" s="2">
-        <v>0.06252252252252252</v>
+        <v>111</v>
       </c>
       <c r="G17" s="2">
-        <v>0.06376068376068376</v>
+        <v>116</v>
       </c>
       <c r="H17" s="2">
-        <v>0.06583333333333334</v>
+        <v>119</v>
       </c>
       <c r="I17" s="2">
-        <v>0.07137096774193548</v>
+        <v>122</v>
       </c>
       <c r="J17" s="2">
-        <v>0.07811023622047245</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-16 従業員1人当たり給与支給総額の上昇率（%）</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">7-14 役員数（人）</t>
+        </is>
+      </c>
+      <c r="B18" s="2">
+        <v>2</v>
       </c>
       <c r="C18" s="2">
-        <v>2.0383328262853606</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>1.9677996422182487</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2">
-        <v>2.3809523809523947</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2">
-        <v>1.780850618059926</v>
+        <v>2</v>
       </c>
       <c r="G18" s="2">
-        <v>1.9803443434567525</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2">
-        <v>3.250670241286868</v>
+        <v>2</v>
       </c>
       <c r="I18" s="2">
-        <v>8.411596570028568</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2">
-        <v>9.442590862582879</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-17 役員1人当たり給与支給総額（億円/人）</t>
+          <t xml:space="preserve">7-15 従業員1人当たり給与支給総額（億円/人）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>0.18</v>
+        <v>0.05766666666666667</v>
       </c>
       <c r="C19" s="2">
-        <v>0.19</v>
+        <v>0.05884210526315789</v>
       </c>
       <c r="D19" s="2">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="E19" s="2">
-        <v>0.21</v>
+        <v>0.06133333333333334</v>
       </c>
       <c r="F19" s="2">
-        <v>0.22</v>
+        <v>0.062252252252252255</v>
       </c>
       <c r="G19" s="2">
-        <v>0.235</v>
+        <v>0.0639655172413793</v>
       </c>
       <c r="H19" s="2">
-        <v>0.25</v>
+        <v>0.06638655462184874</v>
       </c>
       <c r="I19" s="2">
-        <v>0.26</v>
+        <v>0.07213114754098361</v>
       </c>
       <c r="J19" s="2">
-        <v>0.275</v>
+        <v>0.07840000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-18 役員1人当たり給与支給総額の上昇率（%）</t>
+          <t xml:space="preserve">7-16 従業員1人当たり給与支給総額の上昇率（%）</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
@@ -3207,109 +3205,179 @@
         </is>
       </c>
       <c r="C20" s="2">
-        <v>5.555555555555558</v>
+        <v>2.0383328262853606</v>
       </c>
       <c r="D20" s="2">
-        <v>5.263157894736836</v>
+        <v>1.9677996422182487</v>
       </c>
       <c r="E20" s="2">
-        <v>4.999999999999982</v>
+        <v>2.2222222222222365</v>
       </c>
       <c r="F20" s="2">
-        <v>4.761904761904767</v>
+        <v>1.4982373678025906</v>
       </c>
       <c r="G20" s="2">
-        <v>6.818181818181812</v>
+        <v>2.7521333399870063</v>
       </c>
       <c r="H20" s="2">
-        <v>6.382978723404253</v>
+        <v>3.7849101904912974</v>
       </c>
       <c r="I20" s="2">
-        <v>4.0000000000000036</v>
+        <v>8.653247561734801</v>
       </c>
       <c r="J20" s="2">
-        <v>5.769230769230771</v>
+        <v>8.690909090909106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-19 労働生産性（億円/人）</t>
+          <t xml:space="preserve">7-17 役員1人当たり給与支給総額（億円/人）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>0.15358695652173912</v>
+        <v>0.18</v>
       </c>
       <c r="C21" s="2">
-        <v>0.1537113402061856</v>
+        <v>0.19</v>
       </c>
       <c r="D21" s="2">
-        <v>0.15392156862745102</v>
+        <v>0.2</v>
       </c>
       <c r="E21" s="2">
-        <v>0.15626168224299058</v>
+        <v>0.21</v>
       </c>
       <c r="F21" s="2">
-        <v>0.15725663716814156</v>
+        <v>0.22</v>
       </c>
       <c r="G21" s="2">
-        <v>0.158655462184874</v>
+        <v>0.235</v>
       </c>
       <c r="H21" s="2">
-        <v>0.19631147540983607</v>
+        <v>0.25</v>
       </c>
       <c r="I21" s="2">
-        <v>0.2410317460317459</v>
+        <v>0.26</v>
       </c>
       <c r="J21" s="2">
-        <v>0.29875968992248064</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">7-18 役員1人当たり給与支給総額の上昇率（%）</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C22" s="2">
+        <v>5.555555555555558</v>
+      </c>
+      <c r="D22" s="2">
+        <v>5.263157894736836</v>
+      </c>
+      <c r="E22" s="2">
+        <v>4.999999999999982</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4.761904761904767</v>
+      </c>
+      <c r="G22" s="2">
+        <v>6.818181818181812</v>
+      </c>
+      <c r="H22" s="2">
+        <v>6.382978723404253</v>
+      </c>
+      <c r="I22" s="2">
+        <v>4.0000000000000036</v>
+      </c>
+      <c r="J22" s="2">
+        <v>5.769230769230771</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7-19 労働生産性（億円/人）</t>
+        </is>
+      </c>
+      <c r="B23" s="2">
+        <v>0.15358695652173912</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.1537113402061856</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.15392156862745102</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.15448598130841115</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.15389380530973445</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.1550847457627119</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.19314049586776857</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0.24032258064516132</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0.2988976377952757</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">7-20 市場伸び率（年あたり）（%）</t>
         </is>
       </c>
-      <c r="B22" s="2">
+      <c r="B24" s="2">
         <v>5</v>
       </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3590,17 +3658,17 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.28 % / 補助 22.03 % / ベース 7.31 %</t>
+          <t xml:space="preserve">全社 15.29 % / 補助 22.04 % / ベース 7.31 %</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.29 % / 補助 22.01 % / ベース 6.25 %</t>
+          <t xml:space="preserve">全社 15.3 % / 補助 22.04 % / ベース 6.26 %</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 15.83 % / 補助 22.03 % / ベース 6.27 %</t>
+          <t xml:space="preserve">全社 15.83 % / 補助 22.04 % / ベース 6.27 %</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3715,7 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 68.01 % / 補助 68 % / ベース 68.01 %</t>
+          <t xml:space="preserve">全社 68 % / 補助 68 % / ベース 67.99 %</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
@@ -3657,12 +3725,12 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 67.01 % / 補助 67.01 % / ベース 67.01 %</t>
+          <t xml:space="preserve">全社 67.01 % / 補助 67.01 % / ベース 67 %</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 66.62 % / 補助 66.51 % / ベース 66.83 %</t>
+          <t xml:space="preserve">全社 66.63 % / 補助 66.51 % / ベース 66.84 %</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3777,7 @@
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 31.99 % / 補助 32 % / ベース 31.99 %</t>
+          <t xml:space="preserve">全社 32 % / 補助 32 % / ベース 32.01 %</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
@@ -3719,12 +3787,12 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 32.99 % / 補助 32.99 % / ベース 32.99 %</t>
+          <t xml:space="preserve">全社 32.99 % / 補助 32.99 % / ベース 33 %</t>
         </is>
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 33.38 % / 補助 33.49 % / ベース 33.17 %</t>
+          <t xml:space="preserve">全社 33.37 % / 補助 33.49 % / ベース 33.16 %</t>
         </is>
       </c>
     </row>
@@ -3761,32 +3829,32 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.7 % / 補助 23.61 % / ベース 25.95 %</t>
+          <t xml:space="preserve">全社 24.32 % / 補助 22.91 % / ベース 25.95 %</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.12 % / 補助 24.28 % / ベース 26.1 %</t>
+          <t xml:space="preserve">全社 24.4 % / 補助 22.95 % / ベース 26.1 %</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 25.52 % / 補助 24.9 % / ベース 26.24 %</t>
+          <t xml:space="preserve">全社 24.5 % / 補助 23.02 % / ベース 26.26 %</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 24.01 % / 補助 22.66 % / ベース 25.83 %</t>
+          <t xml:space="preserve">全社 23.15 % / 補助 21.15 % / ベース 25.83 %</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 22.86 % / 補助 21.02 % / ベース 25.68 %</t>
+          <t xml:space="preserve">全社 22.08 % / 補助 19.75 % / ベース 25.68 %</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 21.69 % / 補助 19.53 % / ベース 25.51 %</t>
+          <t xml:space="preserve">全社 21.01 % / 補助 18.46 % / ベース 25.53 %</t>
         </is>
       </c>
     </row>
@@ -3823,32 +3891,32 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 7.3 % / 補助 8.4 % / ベース 6.04 %</t>
+          <t xml:space="preserve">全社 7.68 % / 補助 9.1 % / ベース 6.04 %</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.88 % / 補助 7.72 % / ベース 5.9 %</t>
+          <t xml:space="preserve">全社 7.59 % / 補助 9.04 % / ベース 5.9 %</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.48 % / 補助 7.1 % / ベース 5.75 %</t>
+          <t xml:space="preserve">全社 7.5 % / 補助 8.98 % / ベース 5.75 %</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.63 % / 補助 9.84 % / ベース 7 %</t>
+          <t xml:space="preserve">全社 9.49 % / 補助 11.34 % / ベース 7 %</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.14 % / 補助 11.97 % / ベース 7.31 %</t>
+          <t xml:space="preserve">全社 10.91 % / 補助 13.24 % / ベース 7.32 %</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.69 % / 補助 13.96 % / ベース 7.66 %</t>
+          <t xml:space="preserve">全社 12.37 % / 補助 15.04 % / ベース 7.64 %</t>
         </is>
       </c>
     </row>
@@ -3885,32 +3953,32 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.02 % / 補助 11.68 % / ベース 8.1 %</t>
+          <t xml:space="preserve">全社 9.9 % / 補助 11.47 % / ベース 8.1 %</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.93 % / 補助 11.69 % / ベース 7.87 %</t>
+          <t xml:space="preserve">全社 9.72 % / 補助 11.29 % / ベース 7.87 %</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.83 % / 補助 11.69 % / ベース 7.64 %</t>
+          <t xml:space="preserve">全社 9.52 % / 補助 11.11 % / ベース 7.64 %</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.54 % / 補助 13.6 % / ベース 8.76 %</t>
+          <t xml:space="preserve">全社 11.24 % / 補助 13.09 % / ベース 8.76 %</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 12.66 % / 補助 15.05 % / ベース 8.97 %</t>
+          <t xml:space="preserve">全社 12.43 % / 補助 14.68 % / ベース 8.98 %</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 13.86 % / 補助 16.49 % / ベース 9.22 %</t>
+          <t xml:space="preserve">全社 13.68 % / 補助 16.21 % / ベース 9.2 %</t>
         </is>
       </c>
     </row>
@@ -3967,12 +4035,12 @@
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.3 % / 補助 11.5 % / ベース 10.99 %</t>
+          <t xml:space="preserve">全社 11.3 % / 補助 11.49 % / ベース 10.99 %</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.93 % / 補助 10.99 % / ベース 10.82 %</t>
+          <t xml:space="preserve">全社 10.94 % / 補助 11 % / ベース 10.83 %</t>
         </is>
       </c>
     </row>
@@ -4071,17 +4139,17 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.5 % / 補助 7.65 % / ベース 11.63 %</t>
+          <t xml:space="preserve">全社 9.49 % / 補助 7.64 % / ベース 11.63 %</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.67 % / 補助 7.81 % / ベース 11.84 %</t>
+          <t xml:space="preserve">全社 9.65 % / 補助 7.77 % / ベース 11.84 %</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.84 % / 補助 7.96 % / ベース 12.05 %</t>
+          <t xml:space="preserve">全社 9.82 % / 補助 7.92 % / ベース 12.06 %</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
@@ -4091,12 +4159,12 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.63 % / 補助 6.34 % / ベース 12.15 %</t>
+          <t xml:space="preserve">全社 8.6 % / 補助 6.31 % / ベース 12.15 %</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.14 % / 補助 5.83 % / ベース 12.25 %</t>
+          <t xml:space="preserve">全社 8.1 % / 補助 5.75 % / ベース 12.25 %</t>
         </is>
       </c>
     </row>
@@ -4195,17 +4263,17 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.16 % / 補助 8.15 % / ベース 12.48 %</t>
+          <t xml:space="preserve">全社 10.15 % / 補助 8.13 % / ベース 12.48 %</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.33 % / 補助 8.3 % / ベース 12.7 %</t>
+          <t xml:space="preserve">全社 10.31 % / 補助 8.27 % / ベース 12.7 %</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 10.5 % / 補助 8.46 % / ベース 12.9 %</t>
+          <t xml:space="preserve">全社 10.48 % / 補助 8.42 % / ベース 12.91 %</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
@@ -4215,12 +4283,12 @@
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 9.18 % / 補助 6.72 % / ベース 12.97 %</t>
+          <t xml:space="preserve">全社 9.15 % / 補助 6.68 % / ベース 12.97 %</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 8.64 % / 補助 6.15 % / ベース 13.05 %</t>
+          <t xml:space="preserve">全社 8.6 % / 補助 6.08 % / ベース 13.06 %</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4330,7 @@
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.063 億円/人 / ベース 0.064 億円/人</t>
+          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.062 億円/人 / ベース 0.064 億円/人</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
@@ -4272,12 +4340,12 @@
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.066 億円/人 / 補助 0.066 億円/人 / ベース 0.067 億円/人</t>
+          <t xml:space="preserve">全社 0.067 億円/人 / 補助 0.066 億円/人 / ベース 0.067 億円/人</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.071 億円/人 / ベース 0.069 億円/人</t>
+          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.072 億円/人 / ベース 0.069 億円/人</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
@@ -4381,32 +4449,32 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.27 % / 補助 2.38 % / ベース 2.19 %</t>
+          <t xml:space="preserve">全社 2.2 % / 補助 2.22 % / ベース 2.19 %</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 1.68 % / 補助 1.78 % / ベース 1.61 %</t>
+          <t xml:space="preserve">全社 1.55 % / 補助 1.5 % / ベース 1.61 %</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.25 % / 補助 1.98 % / ベース 2.47 %</t>
+          <t xml:space="preserve">全社 2.26 % / 補助 2.75 % / ベース 1.88 %</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.73 % / 補助 3.25 % / ベース 2.31 %</t>
+          <t xml:space="preserve">全社 3.29 % / 補助 3.78 % / ベース 2.91 %</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.08 % / 補助 8.41 % / ベース 2.53 %</t>
+          <t xml:space="preserve">全社 5.17 % / 補助 8.65 % / ベース 2.53 %</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.25 % / 補助 9.44 % / ベース 2 %</t>
+          <t xml:space="preserve">全社 4.95 % / 補助 8.69 % / ベース 2.08 %</t>
         </is>
       </c>
     </row>
@@ -4443,32 +4511,32 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.35 % / 補助 41.09 % / ベース 60.65 %</t>
+          <t xml:space="preserve">全社 50.62 % / 補助 41.5 % / ベース 60.65 %</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 50.99 % / 補助 41.53 % / ベース 61.73 %</t>
+          <t xml:space="preserve">全社 51.48 % / 補助 42.27 % / ベース 61.73 %</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 51.63 % / 補助 42 % / ベース 62.8 %</t>
+          <t xml:space="preserve">全社 52.4 % / 補助 43.11 % / ベース 62.82 %</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 45.69 % / 補助 35.07 % / ベース 59.5 %</t>
+          <t xml:space="preserve">全社 46.33 % / 補助 35.94 % / ベース 59.5 %</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 42.02 % / 補助 30.85 % / ベース 59.12 %</t>
+          <t xml:space="preserve">全社 42.4 % / 補助 31.28 % / ベース 59.09 %</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 38.39 % / 補助 27.17 % / ベース 58.6 %</t>
+          <t xml:space="preserve">全社 38.58 % / 補助 27.27 % / ベース 58.67 %</t>
         </is>
       </c>
     </row>
@@ -4577,22 +4645,22 @@
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.658 億円/人 / 補助 0.801 億円/人 / ベース 0.543 億円/人</t>
+          <t xml:space="preserve">全社 0.658 億円/人 / 補助 0.808 億円/人 / ベース 0.54 億円/人</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.731 億円/人 / 補助 0.953 億円/人 / ベース 0.556 億円/人</t>
+          <t xml:space="preserve">全社 0.733 億円/人 / 補助 0.961 億円/人 / ベース 0.556 億円/人</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.81 億円/人 / 補助 1.125 億円/人 / ベース 0.565 億円/人</t>
+          <t xml:space="preserve">全社 0.816 億円/人 / 補助 1.144 億円/人 / ベース 0.565 億円/人</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.903 億円/人 / 補助 1.34 億円/人 / ベース 0.572 億円/人</t>
+          <t xml:space="preserve">全社 0.909 億円/人 / 補助 1.362 億円/人 / ベース 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -4629,32 +4697,32 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.048 億円/人 / 補助 0.067 億円/人 / ベース 0.033 億円/人</t>
+          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.073 億円/人 / ベース 0.033 億円/人</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.045 億円/人 / 補助 0.062 億円/人 / ベース 0.032 億円/人</t>
+          <t xml:space="preserve">全社 0.05 億円/人 / 補助 0.072 億円/人 / ベース 0.032 億円/人</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.043 億円/人 / 補助 0.057 億円/人 / ベース 0.031 億円/人</t>
+          <t xml:space="preserve">全社 0.049 億円/人 / 補助 0.073 億円/人 / ベース 0.031 億円/人</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.063 億円/人 / 補助 0.094 億円/人 / ベース 0.039 億円/人</t>
+          <t xml:space="preserve">全社 0.07 億円/人 / 補助 0.109 億円/人 / ベース 0.039 億円/人</t>
         </is>
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.082 億円/人 / 補助 0.135 億円/人 / ベース 0.041 億円/人</t>
+          <t xml:space="preserve">全社 0.089 億円/人 / 補助 0.151 億円/人 / ベース 0.041 億円/人</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.106 億円/人 / 補助 0.187 億円/人 / ベース 0.044 億円/人</t>
+          <t xml:space="preserve">全社 0.112 億円/人 / 補助 0.205 億円/人 / ベース 0.044 億円/人</t>
         </is>
       </c>
     </row>
@@ -4691,32 +4759,32 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.156 億円/人 / ベース 0.109 億円/人</t>
+          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.154 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.13 億円/人 / 補助 0.157 億円/人 / ベース 0.109 億円/人</t>
+          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.154 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.131 億円/人 / 補助 0.159 億円/人 / ベース 0.109 億円/人</t>
+          <t xml:space="preserve">全社 0.129 億円/人 / 補助 0.155 億円/人 / ベース 0.109 億円/人</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.152 億円/人 / 補助 0.196 億円/人 / ベース 0.118 億円/人</t>
+          <t xml:space="preserve">全社 0.151 億円/人 / 補助 0.193 億円/人 / ベース 0.118 億円/人</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.174 億円/人 / 補助 0.241 億円/人 / ベース 0.122 億円/人</t>
+          <t xml:space="preserve">全社 0.173 億円/人 / 補助 0.24 億円/人 / ベース 0.122 億円/人</t>
         </is>
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.2 億円/人 / 補助 0.299 億円/人 / ベース 0.125 億円/人</t>
+          <t xml:space="preserve">全社 0.199 億円/人 / 補助 0.299 億円/人 / ベース 0.125 億円/人</t>
         </is>
       </c>
     </row>
@@ -4763,22 +4831,22 @@
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.37 % / 補助 5.41 % / ベース 3.55 %</t>
+          <t xml:space="preserve">全社 4.37 % / 補助 4.5 % / ベース 4.26 %</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.8 % / 補助 2.56 % / ベース 4.79 %</t>
+          <t xml:space="preserve">全社 3.42 % / 補助 2.59 % / ベース 4.08 %</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 4.03 % / 補助 3.33 % / ベース 4.58 %</t>
+          <t xml:space="preserve">全社 3.68 % / 補助 2.52 % / ベース 4.58 %</t>
         </is>
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.87 % / 補助 2.42 % / ベース 5 %</t>
+          <t xml:space="preserve">全社 3.9 % / 補助 2.46 % / ベース 5 %</t>
         </is>
       </c>
     </row>
@@ -4825,22 +4893,22 @@
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 0.51 pt / 補助 0.01 pt / ベース 0.71 pt</t>
+          <t xml:space="preserve">全社 0.51 pt / 補助 0.91 pt / ベース 0 pt</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.48 pt / 補助 19.46 pt / ベース 2.52 pt</t>
+          <t xml:space="preserve">全社 11.86 pt / 補助 19.45 pt / ベース 3.23 pt</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.26 pt / 補助 18.68 pt / ベース 1.67 pt</t>
+          <t xml:space="preserve">全社 11.63 pt / 補助 19.52 pt / ベース 1.69 pt</t>
         </is>
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 11.96 pt / 補助 19.61 pt / ベース 1.27 pt</t>
+          <t xml:space="preserve">全社 11.93 pt / 補助 19.58 pt / ベース 1.27 pt</t>
         </is>
       </c>
     </row>
@@ -4939,32 +5007,32 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.71 % / 補助 3.28 % / ベース 2.06 %</t>
+          <t xml:space="preserve">全社 2.22 % / 補助 2.37 % / ベース 2.06 %</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.05 % / 補助 3.97 % / ベース 1.97 %</t>
+          <t xml:space="preserve">全社 2.12 % / 補助 2.25 % / ベース 1.97 %</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.35 % / 補助 4.59 % / ベース 1.89 %</t>
+          <t xml:space="preserve">全社 2.02 % / 補助 2.13 % / ベース 1.89 %</t>
         </is>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.91 % / 補助 3.76 % / ベース 1.76 %</t>
+          <t xml:space="preserve">全社 1.75 % / 補助 1.75 % / ベース 1.76 %</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.52 % / 補助 3.08 % / ベース 1.66 %</t>
+          <t xml:space="preserve">全社 1.52 % / 補助 1.43 % / ベース 1.66 %</t>
         </is>
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.18 % / 補助 2.53 % / ベース 1.56 %</t>
+          <t xml:space="preserve">全社 1.31 % / 補助 1.17 % / ベース 1.56 %</t>
         </is>
       </c>
     </row>
@@ -5125,32 +5193,32 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.69 倍 / 補助 3.56 倍 / ベース 3.94 倍</t>
+          <t xml:space="preserve">全社 4.45 倍 / 補助 4.83 倍 / ベース 3.94 倍</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.26 倍 / 補助 2.94 倍 / ベース 3.99 倍</t>
+          <t xml:space="preserve">全社 4.58 倍 / 補助 5.02 倍 / ベース 3.99 倍</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 2.93 倍 / 補助 2.55 倍 / ベース 4.04 倍</t>
+          <t xml:space="preserve">全社 4.71 倍 / 補助 5.21 倍 / ベース 4.04 倍</t>
         </is>
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 3.97 倍 / 補助 3.62 倍 / ベース 4.97 倍</t>
+          <t xml:space="preserve">全社 6.41 倍 / 補助 7.48 倍 / ベース 4.97 倍</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 5.02 倍 / 補助 4.88 倍 / ベース 5.41 倍</t>
+          <t xml:space="preserve">全社 8.17 倍 / 補助 10.24 倍 / ベース 5.41 倍</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">全社 6.37 倍 / 補助 6.53 倍 / ベース 5.91 倍</t>
+          <t xml:space="preserve">全社 10.41 倍 / 補助 13.81 倍 / ベース 5.89 倍</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5404,7 @@
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">構成比 63.91 %</t>
+          <t xml:space="preserve">構成比 63.92 %</t>
         </is>
       </c>
     </row>
@@ -5388,17 +5456,17 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.03 % / ベース 7.31 %</t>
+          <t xml:space="preserve">補助 22.04 % / ベース 7.31 %</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.01 % / ベース 6.25 %</t>
+          <t xml:space="preserve">補助 22.04 % / ベース 6.26 %</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 22.03 % / ベース 6.27 %</t>
+          <t xml:space="preserve">補助 22.04 % / ベース 6.27 %</t>
         </is>
       </c>
     </row>
@@ -5445,17 +5513,17 @@
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0 pt</t>
+          <t xml:space="preserve">差 0.01 pt</t>
         </is>
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 0.33 pt</t>
+          <t xml:space="preserve">差 0.34 pt</t>
         </is>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 -0 pt</t>
+          <t xml:space="preserve">差 0.01 pt</t>
         </is>
       </c>
       <c r="L34" s="0" t="inlineStr">
@@ -5497,32 +5565,32 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.35 pt</t>
+          <t xml:space="preserve">差 3.05 pt</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.82 pt</t>
+          <t xml:space="preserve">差 3.14 pt</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 1.35 pt</t>
+          <t xml:space="preserve">差 3.23 pt</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 2.84 pt</t>
+          <t xml:space="preserve">差 4.34 pt</t>
         </is>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 4.66 pt</t>
+          <t xml:space="preserve">差 5.92 pt</t>
         </is>
       </c>
       <c r="L35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">差 6.31 pt</t>
+          <t xml:space="preserve">差 7.4 pt</t>
         </is>
       </c>
     </row>
@@ -5569,22 +5637,22 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.801 億円/人 / ベース 0.543 億円/人</t>
+          <t xml:space="preserve">補助 0.808 億円/人 / ベース 0.54 億円/人</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.953 億円/人 / ベース 0.556 億円/人</t>
+          <t xml:space="preserve">補助 0.961 億円/人 / ベース 0.556 億円/人</t>
         </is>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.125 億円/人 / ベース 0.565 億円/人</t>
+          <t xml:space="preserve">補助 1.144 億円/人 / ベース 0.565 億円/人</t>
         </is>
       </c>
       <c r="L36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 1.34 億円/人 / ベース 0.572 億円/人</t>
+          <t xml:space="preserve">補助 1.362 億円/人 / ベース 0.572 億円/人</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5694,7 @@
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.063 億円/人 / ベース 0.064 億円/人</t>
+          <t xml:space="preserve">補助 0.062 億円/人 / ベース 0.064 億円/人</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
@@ -5641,7 +5709,7 @@
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助 0.071 億円/人 / ベース 0.069 億円/人</t>
+          <t xml:space="preserve">補助 0.072 億円/人 / ベース 0.069 億円/人</t>
         </is>
       </c>
       <c r="L37" s="0" t="inlineStr">
@@ -5683,32 +5751,32 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 200 %</t>
+          <t xml:space="preserve">寄与率 77.08 %</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 157.14 %</t>
+          <t xml:space="preserve">寄与率 82.22 %</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 150 %</t>
+          <t xml:space="preserve">寄与率 84.09 %</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 76.67 %</t>
+          <t xml:space="preserve">寄与率 76.51 %</t>
         </is>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 89.34 %</t>
+          <t xml:space="preserve">寄与率 89.3 %</t>
         </is>
       </c>
       <c r="L38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">寄与率 90.41 %</t>
+          <t xml:space="preserve">寄与率 90.83 %</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5786,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="68" customWidth="1"/>
@@ -5960,11 +6028,11 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 減価償却費のうち売上原価に含める割合</t>
+          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>25</v>
+        <v>0.5</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
@@ -5985,11 +6053,11 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 減価償却費のうち売上原価に含める割合</t>
+          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>20</v>
+        <v>0.4</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
@@ -6010,11 +6078,11 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 研究開発費の売上高比率</t>
+          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
@@ -6035,11 +6103,11 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 研究開発費の売上高比率</t>
+          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
@@ -6060,7 +6128,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 営業外損益の売上高比率</t>
+          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -6085,11 +6153,11 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 営業外損益の売上高比率</t>
+          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
@@ -6110,11 +6178,11 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 特別損益の売上高比率</t>
+          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -6135,82 +6203,74 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 特別損益の売上高比率</t>
+          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D17" s="2">
+        <v>5.116959064327475</v>
+      </c>
+      <c r="E17" s="2">
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">実効税率（当期純利益割合＝100%－実効税率）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>5.551115123125783e-15</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.6653345369377348e-14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <v>5.409356725146197</v>
+        <v>2.0030662342518046</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
         </is>
       </c>
       <c r="D19" s="2">
-        <v>5.116959064327475</v>
+        <v>1.9325330501846927</v>
       </c>
       <c r="E19" s="2">
-        <v>5.701754385964919</v>
+        <v>2.0735994183189166</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>5.551115123125783e-15</v>
+        <v>5.409356725146197</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
@@ -6218,37 +6278,37 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <v>0</v>
+        <v>5.116959064327475</v>
       </c>
       <c r="E20" s="2">
-        <v>1.6653345369377348e-14</v>
+        <v>5.701754385964919</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>2.0030662342518046</v>
+        <v>0</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">基準年度額が最新決算期額以上（成長率0%以上）</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D21" s="2">
-        <v>1.9325330501846927</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2">
-        <v>2.0735994183189166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -6269,11 +6329,11 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>0</v>
+        <v>4.257246376811585</v>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
@@ -6281,20 +6341,20 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <v>0</v>
+        <v>4.076086956521719</v>
       </c>
       <c r="E23" s="2">
-        <v>0</v>
+        <v>4.438405797101453</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>5.409356725146197</v>
+        <v>0</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -6302,20 +6362,20 @@
         </is>
       </c>
       <c r="D24" s="2">
-        <v>5.116959064327475</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2">
-        <v>5.701754385964919</v>
+        <v>0.013457556935819737</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>4.257246376811585</v>
+        <v>1.984645846924027</v>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
@@ -6323,41 +6383,45 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <v>4.076086956521719</v>
+        <v>1.9139457023717443</v>
       </c>
       <c r="E25" s="2">
-        <v>4.438405797101453</v>
+        <v>2.0553459914763095</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D26" s="2">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0.013457556935819737</v>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>1.984645846924027</v>
+        <v>4.083333333333339</v>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
@@ -6365,45 +6429,41 @@
         </is>
       </c>
       <c r="D27" s="2">
-        <v>1.9139457023717443</v>
+        <v>3.9166666666666683</v>
       </c>
       <c r="E27" s="2">
-        <v>2.0553459914763095</v>
+        <v>4.250000000000009</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（設備導入期間）</t>
+          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>4.083333333333339</v>
+        <v>22</v>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
@@ -6411,20 +6471,20 @@
         </is>
       </c>
       <c r="D29" s="2">
-        <v>3.9166666666666683</v>
+        <v>15</v>
       </c>
       <c r="E29" s="2">
-        <v>4.250000000000009</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率改善ポイント（設備導入期間）</t>
+          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>0</v>
+        <v>6.257246376811586</v>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
@@ -6432,20 +6492,20 @@
         </is>
       </c>
       <c r="D30" s="2">
-        <v>0</v>
+        <v>6.076086956521719</v>
       </c>
       <c r="E30" s="2">
-        <v>0</v>
+        <v>6.438405797101453</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>22</v>
+        <v>1.5</v>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
@@ -6453,20 +6513,20 @@
         </is>
       </c>
       <c r="D31" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 売上成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>6.257246376811586</v>
+        <v>0.5</v>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
@@ -6474,20 +6534,20 @@
         </is>
       </c>
       <c r="D32" s="2">
-        <v>6.076086956521719</v>
+        <v>0.5</v>
       </c>
       <c r="E32" s="2">
-        <v>6.438405797101453</v>
+        <v>0.5134575569358197</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>1.5</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -6495,20 +6555,20 @@
         </is>
       </c>
       <c r="D33" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E33" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 原価率改善ポイント（基準年度後）</t>
+          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B34" s="2">
-        <v>0.5</v>
+        <v>2.484645846924027</v>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
@@ -6516,41 +6576,45 @@
         </is>
       </c>
       <c r="D34" s="2">
-        <v>0.5</v>
+        <v>2.4139457023717443</v>
       </c>
       <c r="E34" s="2">
-        <v>0.5134575569358197</v>
+        <v>2.5553459914763095</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>7.000000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D35" s="2">
-        <v>5</v>
-      </c>
-      <c r="E35" s="2">
-        <v>10</v>
+      <c r="D35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業1人当たり給与支給総額の年平均上昇率（基準年度後）</t>
+          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
         </is>
       </c>
       <c r="B36" s="2">
-        <v>2.484645846924027</v>
+        <v>4</v>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
@@ -6558,45 +6622,41 @@
         </is>
       </c>
       <c r="D36" s="2">
-        <v>2.4139457023717443</v>
+        <v>0</v>
       </c>
       <c r="E36" s="2">
-        <v>2.5553459914763095</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 役員1人当たり給与支給総額上昇率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>4.5</v>
+        <v>4.583333333333338</v>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="D37" s="2">
+        <v>4.416666666666668</v>
+      </c>
+      <c r="E37" s="2">
+        <v>4.750000000000009</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 常時使用する従業員数の成長率</t>
+          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
@@ -6604,20 +6664,20 @@
         </is>
       </c>
       <c r="D38" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="E38" s="2">
-        <v>8</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 常時使用する従業員数の成長率（基準年度後）</t>
+          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>4.583333333333338</v>
+        <v>10.928571428571427</v>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
@@ -6625,20 +6685,20 @@
         </is>
       </c>
       <c r="D39" s="2">
-        <v>4.416666666666668</v>
+        <v>8.928571428571427</v>
       </c>
       <c r="E39" s="2">
-        <v>4.750000000000009</v>
+        <v>11.928571428571427</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">補助事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>11</v>
+        <v>5.380116959064325</v>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
@@ -6646,124 +6706,57 @@
         </is>
       </c>
       <c r="D40" s="2">
-        <v>8.5</v>
+        <v>4.263157894736836</v>
       </c>
       <c r="E40" s="2">
-        <v>13.5</v>
+        <v>6.555555555555557</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ベース事業 その他販管費率（事業化報告3年目）</t>
+          <t xml:space="preserve">補助事業投資額</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>10.928571428571427</v>
+        <v>23</v>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D41" s="2">
-        <v>8.928571428571427</v>
-      </c>
-      <c r="E41" s="2">
-        <v>11.928571428571427</v>
+          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">役員1人当たり給与支給総額の年平均上昇率</t>
+          <t xml:space="preserve">申請補助金額</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>5.380116959064325</v>
+        <v>7.66</v>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D42" s="2">
-        <v>4.263157894736836</v>
-      </c>
-      <c r="E42" s="2">
-        <v>6.555555555555557</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">新規投資の平均耐用年数（減価償却費の自動予測用・モデル内管理・第6次公式様式外）</t>
-        </is>
-      </c>
-      <c r="B43" s="2">
-        <v>10</v>
-      </c>
-      <c r="C43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">補助事業投資額</t>
-        </is>
-      </c>
-      <c r="B44" s="2">
-        <v>23</v>
-      </c>
-      <c r="C44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20億円以上（専門家経費・外注費を除く補助対象経費）</t>
-        </is>
-      </c>
-      <c r="D44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E44" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">申請補助金額</t>
-        </is>
-      </c>
-      <c r="B45" s="2">
-        <v>7.66</v>
-      </c>
-      <c r="C45" s="0" t="inlineStr">
-        <is>
           <t xml:space="preserve">50億円以下、かつ投資額の1/3以下（現在上限7.66億円）</t>
         </is>
       </c>
-      <c r="D45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E45" s="0" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6775,7 +6768,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C289"/>
+  <dimension ref="A1:C292"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -7510,11 +7503,11 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-10</t>
+          <t xml:space="preserve">actual:project:2023:7-13</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <v>1.8</v>
+        <v>90</v>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
@@ -7525,11 +7518,11 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-13</t>
+          <t xml:space="preserve">actual:project:2023:7-14</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
@@ -7540,11 +7533,11 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-14</t>
+          <t xml:space="preserve">actual:project:2023:7-4</t>
         </is>
       </c>
       <c r="B51" s="2">
-        <v>2</v>
+        <v>23.04</v>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
@@ -7555,11 +7548,11 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-4</t>
+          <t xml:space="preserve">actual:project:2023:7-6</t>
         </is>
       </c>
       <c r="B52" s="2">
-        <v>23.04</v>
+        <v>6.78</v>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
@@ -7570,11 +7563,11 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-6</t>
+          <t xml:space="preserve">actual:project:2023:7-8</t>
         </is>
       </c>
       <c r="B53" s="2">
-        <v>6.78</v>
+        <v>5.19</v>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
@@ -7585,11 +7578,11 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-8</t>
+          <t xml:space="preserve">actual:project:2023:7-9</t>
         </is>
       </c>
       <c r="B54" s="2">
-        <v>5.19</v>
+        <v>0.36</v>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
@@ -7600,11 +7593,11 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2023:7-9</t>
+          <t xml:space="preserve">actual:project:2023:P2-14</t>
         </is>
       </c>
       <c r="B55" s="2">
-        <v>0.36</v>
+        <v>1.35</v>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
@@ -7615,11 +7608,11 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-1</t>
+          <t xml:space="preserve">actual:project:2023:P2-4</t>
         </is>
       </c>
       <c r="B56" s="2">
-        <v>76</v>
+        <v>0.45</v>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
@@ -7630,11 +7623,11 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2024:7-10</t>
+          <t xml:space="preserve">actual:project:2024:7-1</t>
         </is>
       </c>
       <c r="B57" s="2">
-        <v>1.9</v>
+        <v>76</v>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
@@ -7735,11 +7728,11 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-1</t>
+          <t xml:space="preserve">actual:project:2024:P2-14</t>
         </is>
       </c>
       <c r="B64" s="2">
-        <v>80</v>
+        <v>1.43</v>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
@@ -7750,11 +7743,11 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-10</t>
+          <t xml:space="preserve">actual:project:2024:P2-4</t>
         </is>
       </c>
       <c r="B65" s="2">
-        <v>2</v>
+        <v>0.47</v>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
@@ -7765,11 +7758,11 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-13</t>
+          <t xml:space="preserve">actual:project:2025:7-1</t>
         </is>
       </c>
       <c r="B66" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
@@ -7780,11 +7773,11 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-14</t>
+          <t xml:space="preserve">actual:project:2025:7-13</t>
         </is>
       </c>
       <c r="B67" s="2">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
@@ -7795,11 +7788,11 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-4</t>
+          <t xml:space="preserve">actual:project:2025:7-14</t>
         </is>
       </c>
       <c r="B68" s="2">
-        <v>25.6</v>
+        <v>2</v>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
@@ -7810,11 +7803,11 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-6</t>
+          <t xml:space="preserve">actual:project:2025:7-4</t>
         </is>
       </c>
       <c r="B69" s="2">
-        <v>7.3</v>
+        <v>25.6</v>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
@@ -7825,11 +7818,11 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-8</t>
+          <t xml:space="preserve">actual:project:2025:7-6</t>
         </is>
       </c>
       <c r="B70" s="2">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
@@ -7840,11 +7833,11 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">actual:project:2025:7-9</t>
+          <t xml:space="preserve">actual:project:2025:7-8</t>
         </is>
       </c>
       <c r="B71" s="2">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
@@ -7855,11 +7848,11 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:assets</t>
+          <t xml:space="preserve">actual:project:2025:7-9</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>132</v>
+        <v>0.4</v>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
@@ -7870,11 +7863,11 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:buildings</t>
+          <t xml:space="preserve">actual:project:2025:P2-14</t>
         </is>
       </c>
       <c r="B73" s="2">
-        <v>19</v>
+        <v>1.5</v>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
@@ -7885,11 +7878,11 @@
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capex</t>
+          <t xml:space="preserve">actual:project:2025:P2-4</t>
         </is>
       </c>
       <c r="B74" s="2">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
@@ -7900,11 +7893,11 @@
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:capital</t>
+          <t xml:space="preserve">balance-sheet:2023:assets</t>
         </is>
       </c>
       <c r="B75" s="2">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
@@ -7915,11 +7908,11 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:cash</t>
+          <t xml:space="preserve">balance-sheet:2023:buildings</t>
         </is>
       </c>
       <c r="B76" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
@@ -7930,11 +7923,11 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:capex</t>
         </is>
       </c>
       <c r="B77" s="2">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
@@ -7945,11 +7938,11 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:capital</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
@@ -7960,11 +7953,11 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:cash</t>
         </is>
       </c>
       <c r="B79" s="2">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
@@ -7975,11 +7968,11 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:currentAssets</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
@@ -7990,11 +7983,11 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:currentLiabilities</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
@@ -8005,11 +7998,11 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:land</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedAssets</t>
         </is>
       </c>
       <c r="B82" s="2">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
@@ -8020,11 +8013,11 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2023:fixedLiabilities</t>
         </is>
       </c>
       <c r="B83" s="2">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
@@ -8035,11 +8028,11 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:intangibleAssets</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
@@ -8050,11 +8043,11 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:machinery</t>
+          <t xml:space="preserve">balance-sheet:2023:land</t>
         </is>
       </c>
       <c r="B85" s="2">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
@@ -8065,11 +8058,11 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:liabilities</t>
         </is>
       </c>
       <c r="B86" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
@@ -8080,11 +8073,11 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2023:longTermDebt</t>
         </is>
       </c>
       <c r="B87" s="2">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
@@ -8095,11 +8088,11 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2023:machinery</t>
         </is>
       </c>
       <c r="B88" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
@@ -8110,11 +8103,11 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:software</t>
+          <t xml:space="preserve">balance-sheet:2023:netAssets</t>
         </is>
       </c>
       <c r="B89" s="2">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
@@ -8125,11 +8118,11 @@
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2023:shareholderEquity</t>
         </is>
       </c>
       <c r="B90" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
@@ -8140,11 +8133,11 @@
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:assets</t>
+          <t xml:space="preserve">balance-sheet:2023:shortTermDebt</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
@@ -8155,11 +8148,11 @@
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:buildings</t>
+          <t xml:space="preserve">balance-sheet:2023:software</t>
         </is>
       </c>
       <c r="B92" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
@@ -8170,11 +8163,11 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capex</t>
+          <t xml:space="preserve">balance-sheet:2023:tangibleAssets</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
@@ -8185,11 +8178,11 @@
     <row r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:capital</t>
+          <t xml:space="preserve">balance-sheet:2024:assets</t>
         </is>
       </c>
       <c r="B94" s="2">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
@@ -8200,11 +8193,11 @@
     <row r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:cash</t>
+          <t xml:space="preserve">balance-sheet:2024:buildings</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
@@ -8215,11 +8208,11 @@
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:capex</t>
         </is>
       </c>
       <c r="B96" s="2">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
@@ -8230,11 +8223,11 @@
     <row r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:capital</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
@@ -8245,11 +8238,11 @@
     <row r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:cash</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
@@ -8260,11 +8253,11 @@
     <row r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:currentAssets</t>
         </is>
       </c>
       <c r="B99" s="2">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
@@ -8275,11 +8268,11 @@
     <row r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:currentLiabilities</t>
         </is>
       </c>
       <c r="B100" s="2">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
@@ -8290,11 +8283,11 @@
     <row r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:land</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedAssets</t>
         </is>
       </c>
       <c r="B101" s="2">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
@@ -8305,11 +8298,11 @@
     <row r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2024:fixedLiabilities</t>
         </is>
       </c>
       <c r="B102" s="2">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
@@ -8320,11 +8313,11 @@
     <row r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:intangibleAssets</t>
         </is>
       </c>
       <c r="B103" s="2">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
@@ -8335,11 +8328,11 @@
     <row r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:machinery</t>
+          <t xml:space="preserve">balance-sheet:2024:land</t>
         </is>
       </c>
       <c r="B104" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
@@ -8350,11 +8343,11 @@
     <row r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:liabilities</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
@@ -8365,11 +8358,11 @@
     <row r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2024:longTermDebt</t>
         </is>
       </c>
       <c r="B106" s="2">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
@@ -8380,11 +8373,11 @@
     <row r="107">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2024:machinery</t>
         </is>
       </c>
       <c r="B107" s="2">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
@@ -8395,11 +8388,11 @@
     <row r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:software</t>
+          <t xml:space="preserve">balance-sheet:2024:netAssets</t>
         </is>
       </c>
       <c r="B108" s="2">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
@@ -8410,11 +8403,11 @@
     <row r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2024:shareholderEquity</t>
         </is>
       </c>
       <c r="B109" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
@@ -8425,11 +8418,11 @@
     <row r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:assets</t>
+          <t xml:space="preserve">balance-sheet:2024:shortTermDebt</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
@@ -8440,11 +8433,11 @@
     <row r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:buildings</t>
+          <t xml:space="preserve">balance-sheet:2024:software</t>
         </is>
       </c>
       <c r="B111" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
@@ -8455,11 +8448,11 @@
     <row r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capex</t>
+          <t xml:space="preserve">balance-sheet:2024:tangibleAssets</t>
         </is>
       </c>
       <c r="B112" s="2">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
@@ -8470,11 +8463,11 @@
     <row r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:capital</t>
+          <t xml:space="preserve">balance-sheet:2025:assets</t>
         </is>
       </c>
       <c r="B113" s="2">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
@@ -8485,11 +8478,11 @@
     <row r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:cash</t>
+          <t xml:space="preserve">balance-sheet:2025:buildings</t>
         </is>
       </c>
       <c r="B114" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
@@ -8500,11 +8493,11 @@
     <row r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:capex</t>
         </is>
       </c>
       <c r="B115" s="2">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
@@ -8515,11 +8508,11 @@
     <row r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2025:capital</t>
         </is>
       </c>
       <c r="B116" s="2">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
@@ -8530,11 +8523,11 @@
     <row r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:cash</t>
         </is>
       </c>
       <c r="B117" s="2">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
@@ -8545,11 +8538,11 @@
     <row r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
+          <t xml:space="preserve">balance-sheet:2025:currentAssets</t>
         </is>
       </c>
       <c r="B118" s="2">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
@@ -8560,11 +8553,11 @@
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:currentLiabilities</t>
         </is>
       </c>
       <c r="B119" s="2">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
@@ -8575,11 +8568,11 @@
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:land</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedAssets</t>
         </is>
       </c>
       <c r="B120" s="2">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
@@ -8590,11 +8583,11 @@
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
+          <t xml:space="preserve">balance-sheet:2025:fixedLiabilities</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
@@ -8605,11 +8598,11 @@
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:intangibleAssets</t>
         </is>
       </c>
       <c r="B122" s="2">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
@@ -8620,11 +8613,11 @@
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:machinery</t>
+          <t xml:space="preserve">balance-sheet:2025:land</t>
         </is>
       </c>
       <c r="B123" s="2">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
@@ -8635,11 +8628,11 @@
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:liabilities</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
@@ -8650,11 +8643,11 @@
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
+          <t xml:space="preserve">balance-sheet:2025:longTermDebt</t>
         </is>
       </c>
       <c r="B125" s="2">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
@@ -8665,11 +8658,11 @@
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
+          <t xml:space="preserve">balance-sheet:2025:machinery</t>
         </is>
       </c>
       <c r="B126" s="2">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
@@ -8680,11 +8673,11 @@
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:software</t>
+          <t xml:space="preserve">balance-sheet:2025:netAssets</t>
         </is>
       </c>
       <c r="B127" s="2">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
@@ -8695,11 +8688,11 @@
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
+          <t xml:space="preserve">balance-sheet:2025:shareholderEquity</t>
         </is>
       </c>
       <c r="B128" s="2">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
@@ -8710,26 +8703,26 @@
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:effectiveTaxRate:0</t>
+          <t xml:space="preserve">balance-sheet:2025:shortTermDebt</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:effectiveTaxRate:1</t>
+          <t xml:space="preserve">balance-sheet:2025:software</t>
         </is>
       </c>
       <c r="B130" s="2">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
@@ -8740,11 +8733,11 @@
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:0</t>
+          <t xml:space="preserve">balance-sheet:2025:tangibleAssets</t>
         </is>
       </c>
       <c r="B131" s="2">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
@@ -8755,41 +8748,41 @@
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:investment:1</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:0</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:0</t>
+          <t xml:space="preserve">driver-range:effectiveTaxRate:1</t>
         </is>
       </c>
       <c r="B133" s="2">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:localBenchmark:1</t>
+          <t xml:space="preserve">driver-range:investment:0</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
@@ -8800,41 +8793,41 @@
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:0</t>
+          <t xml:space="preserve">driver-range:investment:1</t>
         </is>
       </c>
       <c r="B135" s="2">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:1</t>
+          <t xml:space="preserve">driver-range:localBenchmark:0</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
+          <t xml:space="preserve">driver-range:localBenchmark:1</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0.005</v>
+        <v>100</v>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
@@ -8845,41 +8838,41 @@
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0.0051345755693581975</v>
+        <v>0</v>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:0</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0.00013457556935819737</v>
+        <v>0.005</v>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
@@ -8890,71 +8883,71 @@
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovement:1</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>0</v>
+        <v>0.0051345755693581975</v>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:otherCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0</v>
+        <v>0.00013457556935819737</v>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:otherCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>-0.5</v>
+        <v>0.99</v>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
@@ -8965,26 +8958,26 @@
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0.04416666666666668</v>
+        <v>1</v>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
@@ -8995,11 +8988,11 @@
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0.04750000000000009</v>
+        <v>-0.5</v>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
@@ -9010,11 +9003,11 @@
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>0.03916666666666668</v>
+        <v>0.5</v>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
@@ -9025,11 +9018,11 @@
     <row r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B150" s="2">
-        <v>0.04250000000000009</v>
+        <v>0.04416666666666668</v>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
@@ -9040,11 +9033,11 @@
     <row r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B151" s="2">
-        <v>-0.5</v>
+        <v>0.04750000000000009</v>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
@@ -9055,11 +9048,11 @@
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>0.5</v>
+        <v>0.03916666666666668</v>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
@@ -9070,26 +9063,26 @@
     <row r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
+          <t xml:space="preserve">driver-range:otherHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B153" s="2">
-        <v>0</v>
+        <v>0.04250000000000009</v>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B154" s="2">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
@@ -9100,71 +9093,71 @@
     <row r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0.024139457023717444</v>
+        <v>0.08</v>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
@@ -9175,26 +9168,26 @@
     <row r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0.025553459914763096</v>
+        <v>0</v>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>0.019139457023717443</v>
+        <v>0.08</v>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
@@ -9205,11 +9198,11 @@
     <row r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:0</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>0.020553459914763095</v>
+        <v>0.024139457023717444</v>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
@@ -9220,26 +9213,26 @@
     <row r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowth:1</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0</v>
+        <v>0.025553459914763096</v>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B164" s="2">
-        <v>0.3</v>
+        <v>0.019139457023717443</v>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
@@ -9250,11 +9243,11 @@
     <row r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:otherPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>0.06076086956521719</v>
+        <v>0.020553459914763095</v>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
@@ -9265,26 +9258,26 @@
     <row r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B166" s="2">
-        <v>0.06438405797101453</v>
+        <v>0</v>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:otherResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B167" s="2">
-        <v>0.040760869565217184</v>
+        <v>0.3</v>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
@@ -9295,11 +9288,11 @@
     <row r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:0</t>
         </is>
       </c>
       <c r="B168" s="2">
-        <v>0.04438405797101452</v>
+        <v>0.06076086956521719</v>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
@@ -9310,41 +9303,41 @@
     <row r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowth:1</t>
         </is>
       </c>
       <c r="B169" s="2">
-        <v>0</v>
+        <v>0.06438405797101453</v>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>0</v>
+        <v>0.040760869565217184</v>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:otherSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0.08928571428571427</v>
+        <v>0.04438405797101452</v>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
@@ -9355,22 +9348,22 @@
     <row r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>0.11928571428571427</v>
+        <v>0</v>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
+          <t xml:space="preserve">driver-range:otherSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B173" s="2">
@@ -9385,11 +9378,11 @@
     <row r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B174" s="2">
-        <v>1</v>
+        <v>0.08928571428571427</v>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
@@ -9400,131 +9393,131 @@
     <row r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
+          <t xml:space="preserve">driver-range:otherSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0</v>
+        <v>0.11928571428571427</v>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:0</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectCogsDepreciationShare:1</t>
         </is>
       </c>
       <c r="B177" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:0</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>1.6653345369377348e-16</v>
+        <v>0</v>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementAfterBase:1</t>
         </is>
       </c>
       <c r="B179" s="2">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:0</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
+          <t xml:space="preserve">driver-range:projectCogsImprovementToBase:1</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>0</v>
+        <v>1.6653345369377348e-16</v>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:0</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
+          <t xml:space="preserve">driver-range:projectCogsRateWhenSalesZero:1</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>-0.5</v>
+        <v>0.99</v>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
@@ -9535,41 +9528,41 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:0</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectEmployeeSalaryShare:1</t>
         </is>
       </c>
       <c r="B185" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:0</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>0.08</v>
+        <v>-0.5</v>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
@@ -9580,11 +9573,11 @@
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectExtraordinaryRate:1</t>
         </is>
       </c>
       <c r="B187" s="2">
-        <v>0.051169590643274754</v>
+        <v>0.5</v>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
@@ -9595,26 +9588,26 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:0</t>
         </is>
       </c>
       <c r="B188" s="2">
-        <v>0.05701754385964919</v>
+        <v>0</v>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowth:1</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>-0.05</v>
+        <v>0.08</v>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
@@ -9625,11 +9618,11 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:0</t>
         </is>
       </c>
       <c r="B190" s="2">
-        <v>0.3</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
@@ -9640,11 +9633,11 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
+          <t xml:space="preserve">driver-range:projectHeadcountGrowthToBase:1</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>-0.5</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
@@ -9655,11 +9648,11 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:0</t>
         </is>
       </c>
       <c r="B192" s="2">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
@@ -9670,26 +9663,26 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
+          <t xml:space="preserve">driver-range:projectMarketGrowth:1</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:0</t>
         </is>
       </c>
       <c r="B194" s="2">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
@@ -9700,11 +9693,11 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectNonOperatingRate:1</t>
         </is>
       </c>
       <c r="B195" s="2">
-        <v>0.04263157894736836</v>
+        <v>0.5</v>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
@@ -9715,26 +9708,26 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:0</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>0.06555555555555558</v>
+        <v>0</v>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerCompensationShare:1</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>0.051169590643274754</v>
+        <v>1</v>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
@@ -9745,11 +9738,11 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:0</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.04263157894736836</v>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
@@ -9760,11 +9753,11 @@
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowth:1</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0.05</v>
+        <v>0.06555555555555558</v>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
@@ -9775,11 +9768,11 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0.1</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
@@ -9790,11 +9783,11 @@
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectOfficerPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B201" s="2">
-        <v>0.019325330501846927</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
@@ -9805,11 +9798,11 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:0</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0.020735994183189166</v>
+        <v>0.05</v>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
@@ -9820,26 +9813,26 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowth:1</t>
         </is>
       </c>
       <c r="B203" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:0</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>0.3</v>
+        <v>0.019325330501846927</v>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
@@ -9850,11 +9843,11 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
+          <t xml:space="preserve">driver-range:projectPayGrowthToBase:1</t>
         </is>
       </c>
       <c r="B205" s="2">
-        <v>0.15</v>
+        <v>0.020735994183189166</v>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
@@ -9865,26 +9858,26 @@
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:0</t>
         </is>
       </c>
       <c r="B206" s="2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
+          <t xml:space="preserve">driver-range:projectResearchDevelopmentRate:1</t>
         </is>
       </c>
       <c r="B207" s="2">
-        <v>0.051169590643274754</v>
+        <v>0.3</v>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
@@ -9895,11 +9888,11 @@
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:0</t>
         </is>
       </c>
       <c r="B208" s="2">
-        <v>0.05701754385964919</v>
+        <v>0.15</v>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
@@ -9910,41 +9903,41 @@
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowth:1</t>
         </is>
       </c>
       <c r="B209" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:0</t>
         </is>
       </c>
       <c r="B210" s="2">
-        <v>0</v>
+        <v>0.051169590643274754</v>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
+          <t xml:space="preserve">driver-range:projectSalesGrowthToBase:1</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0.08499999999999999</v>
+        <v>0.05701754385964919</v>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
@@ -9955,41 +9948,41 @@
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:0</t>
         </is>
       </c>
       <c r="B212" s="2">
-        <v>0.135</v>
+        <v>0</v>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:0</t>
+          <t xml:space="preserve">driver-range:projectSgaImprovementToBase:1</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:subsidy:1</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:0</t>
         </is>
       </c>
       <c r="B214" s="2">
-        <v>50</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
@@ -10000,11 +9993,11 @@
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver-range:projectSgaRateEnd:1</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>5</v>
+        <v>0.135</v>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
@@ -10015,11 +10008,11 @@
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver-range:subsidy:0</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
@@ -10030,11 +10023,11 @@
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver-range:subsidy:1</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>0.3</v>
+        <v>50</v>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
@@ -10045,11 +10038,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver-range:usefulLife:0</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -10060,11 +10053,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver-range:usefulLife:1</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -10075,11 +10068,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -10090,11 +10083,11 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>0.005</v>
+        <v>23</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -10105,26 +10098,26 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>0.68</v>
+        <v>0.2</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
@@ -10135,11 +10128,11 @@
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>0.95</v>
+        <v>0.005</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -10150,7 +10143,7 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B225" s="2">
@@ -10165,11 +10158,11 @@
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>0.045833333333333386</v>
+        <v>0.68</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
@@ -10180,11 +10173,11 @@
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>0.04083333333333339</v>
+        <v>0.95</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -10195,26 +10188,26 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherNonOperatingRate</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>0.9</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
@@ -10225,11 +10218,11 @@
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0.045</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
@@ -10240,11 +10233,11 @@
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>0.04</v>
+        <v>-0.005</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -10255,11 +10248,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>0.02484645846924027</v>
+        <v>0.9</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -10270,11 +10263,11 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>0.01984645846924027</v>
+        <v>0.045</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
@@ -10285,11 +10278,11 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>0.004</v>
+        <v>0.04</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
@@ -10300,11 +10293,11 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>0.06257246376811586</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -10315,11 +10308,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>0.042572463768115854</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -10330,26 +10323,26 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>0.10928571428571428</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
@@ -10360,11 +10353,11 @@
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>0.25</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10375,26 +10368,26 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>5.551115123125783e-17</v>
+        <v>0.10928571428571428</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -10405,11 +10398,11 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>0.68</v>
+        <v>0.25</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -10420,11 +10413,11 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>0.95</v>
+        <v>0.015</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10435,26 +10428,26 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>0.04</v>
+        <v>0.68</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
@@ -10465,11 +10458,11 @@
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.95</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10480,41 +10473,41 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectNonOperatingRate</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B249" s="2">
-        <v>0.9</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
@@ -10525,11 +10518,11 @@
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>0.05380116959064325</v>
+        <v>0.05</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
@@ -10540,26 +10533,26 @@
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>0.05409356725146197</v>
+        <v>0</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>0.07</v>
+        <v>0.9</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10570,11 +10563,11 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>0.020030662342518046</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
@@ -10585,11 +10578,11 @@
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>0.005</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
@@ -10600,11 +10593,11 @@
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B255" s="2">
-        <v>0.22</v>
+        <v>0.07</v>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
@@ -10615,11 +10608,11 @@
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B256" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
@@ -10630,26 +10623,26 @@
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B257" s="2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B258" s="2">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
@@ -10660,11 +10653,11 @@
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B259" s="2">
-        <v>7.66</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
@@ -10675,26 +10668,26 @@
     <row r="260">
       <c r="A260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B260" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>7</v>
+        <v>0.11</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
@@ -10705,11 +10698,11 @@
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>2</v>
+        <v>7.66</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10720,11 +10713,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">driver:usefulLife</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10735,11 +10728,11 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
@@ -10750,11 +10743,11 @@
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B265" s="2">
-        <v>252.69</v>
+        <v>2</v>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
@@ -10765,11 +10758,11 @@
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>82.4</v>
+        <v>35</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
@@ -10780,11 +10773,11 @@
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B267" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
@@ -10795,11 +10788,11 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B268" s="2">
-        <v>7</v>
+        <v>252.69</v>
       </c>
       <c r="C268" s="0" t="inlineStr">
         <is>
@@ -10810,11 +10803,11 @@
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>3.74</v>
+        <v>82.4</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10825,11 +10818,11 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B270" s="2">
-        <v>2.85</v>
+        <v>10</v>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
@@ -10840,11 +10833,11 @@
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
@@ -10855,11 +10848,11 @@
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>15</v>
+        <v>3.74</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -10870,11 +10863,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>35</v>
+        <v>2.85</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -10885,11 +10878,11 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
@@ -10900,11 +10893,11 @@
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -10915,11 +10908,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -10930,11 +10923,11 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
@@ -10945,11 +10938,11 @@
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -10960,26 +10953,26 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B280" s="2">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C280" s="0" t="inlineStr">
         <is>
@@ -10990,11 +10983,11 @@
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -11005,26 +10998,26 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>136.84</v>
+        <v>0</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B283" s="2">
-        <v>74.8</v>
+        <v>35</v>
       </c>
       <c r="C283" s="0" t="inlineStr">
         <is>
@@ -11035,11 +11028,11 @@
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11050,11 +11043,11 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
         </is>
       </c>
       <c r="B285" s="2">
-        <v>60</v>
+        <v>136.84</v>
       </c>
       <c r="C285" s="0" t="inlineStr">
         <is>
@@ -11065,11 +11058,11 @@
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
         </is>
       </c>
       <c r="B286" s="2">
-        <v>33.43</v>
+        <v>74.8</v>
       </c>
       <c r="C286" s="0" t="inlineStr">
         <is>
@@ -11080,11 +11073,11 @@
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
         </is>
       </c>
       <c r="B287" s="2">
-        <v>18.78</v>
+        <v>95</v>
       </c>
       <c r="C287" s="0" t="inlineStr">
         <is>
@@ -11095,11 +11088,11 @@
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
         </is>
       </c>
       <c r="B288" s="2">
-        <v>350</v>
+        <v>60</v>
       </c>
       <c r="C288" s="0" t="inlineStr">
         <is>
@@ -11110,13 +11103,58 @@
     <row r="289">
       <c r="A289" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+        </is>
+      </c>
+      <c r="B289" s="2">
+        <v>33.43</v>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
+        </is>
+      </c>
+      <c r="B290" s="2">
+        <v>18.78</v>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
+        </is>
+      </c>
+      <c r="B291" s="2">
+        <v>350</v>
+      </c>
+      <c r="C291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
-      <c r="B289" s="2">
+      <c r="B292" s="2">
         <v>213</v>
       </c>
-      <c r="C289" s="0" t="inlineStr">
+      <c r="C292" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11144,7 +11182,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjIsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNTEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjo3MiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjIzLjA0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Ni43OCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjUuMTksImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctMTAiOjEuOCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTEzIjo5MCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMSI6MTQzLjIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0zIjo5Ny4zOCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTQiOjAuNzYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi03IjozNC41MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTkiOjAuODYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xMCI6MC4xLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTIiOjEyLjQ3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTMiOjAuNjYsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNCI6Mi41OCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE1IjowLjY3LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTgiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTkiOjExLjAxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjAiOjcuNzEsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0yNyI6MjIwLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny0xIjo3NiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTQiOjI0LjMyLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctNiI6Ny4wNCwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTgiOjUuNTksImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny05IjowLjM4LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTAiOjEuOSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTEzIjo5NSwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTE0IjoyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMSI6MTUwLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMyI6MTAyLCJhY3R1YWw6Y29tcGFueToyMDI1OjItNCI6MC44LCJhY3R1YWw6Y29tcGFueToyMDI1OjItNyI6MzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTkiOjAuOSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEwIjowLjEsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xMiI6MTMuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEzIjowLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNCI6Mi43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTUiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE4IjoxMS4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTkiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yMCI6Ny45MSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI3IjoyMzAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0yOCI6NSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEiOjgwLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNCI6MjUuNiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTYiOjcuMywiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTgiOjYsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny05IjowLjQsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xMCI6MiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA4NDk5OTk5OTk5OTk5OTk5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4xMzUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wODkyODU3MTQyODU3MTQyNywiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjExOTI4NTcxNDI4NTcxNDI3LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6MiwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQxMDU5NTc2MDIzMzkxNiwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAxOTk4MjEzNTUxMTg3OTg3MywicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTQwNjM5MDEyNDk3MjI5MzQsInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwicHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDU0MTIwNDUxMzMzMTU3NjMsIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNjA1NTE2MjczMDA1MjcsIm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4ODEzNjc1MDA5MTcxMTcsIm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNCwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwNjA5MzUzOTQzNzE3ODU1LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIwMjI0ODcyMTY5NDY2NzMsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTY1MTc4NTk0NTIxNzksInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE0OTkwNDgxMzQxMjY1NTUsIm90aGVyQ29nc0ltcHJvdmVtZW50IjowLjAwNSwicHJvamVjdFBheUdyb3d0aCI6MC4wODkwMDYyMjk5NzUwODAxLCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4ODc3NjE3MTAzMzMwMywib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMjkwNDU0ODIzOTcyMDUwNTUsIm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTc4NDgxNDczMjMwODY2NSwicHJvamVjdFNnYVJhdGVFbmQiOjAuMTA5OTMxODA5MTY0ODQ4MjQsIm90aGVyU2dhUmF0ZUVuZCI6MC4xMDkyNzI1ODk4NzIxMjgyMywicHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzNzc4MDU3NjI4NzE2MzIsInVzZWZ1bExpZmUiOjEwLCJpbnZlc3RtZW50IjoyMywic3Vic2lkeSI6Ny42NiwibG9jYWxCZW5jaG1hcmsiOjIzfX0=</t>
+          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjIsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNTEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjo3MiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjIzLjA0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Ni43OCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjUuMTksImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTQiOjAuNDUsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjEuMzUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjo3LjcxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjU5LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MC4zOCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi00IjowLjQ3LCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjoxLjQzLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo3LjkxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi00IjowLjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItMTQiOjEuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZTowIjowLCJkcml2ZXItcmFuZ2U6ZWZmZWN0aXZlVGF4UmF0ZToxIjowLjYsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2UiOjAuMDU0MDkzNTY3MjUxNDYxOTcsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MCI6MC4wNTExNjk1OTA2NDMyNzQ3NTQsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjUuNTUxMTE1MTIzMTI1NzgzZS0xNywiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MSI6MS42NjUzMzQ1MzY5Mzc3MzQ4ZS0xNiwiZHJpdmVyOnByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJkcml2ZXItcmFuZ2U6cHJvamVjdFBheUdyb3d0aFRvQmFzZTowIjowLjAxOTMyNTMzMDUwMTg0NjkyNywiZHJpdmVyLXJhbmdlOnByb2plY3RQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA3MzU5OTQxODMxODkxNjYsImRyaXZlcjpwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJkcml2ZXItcmFuZ2U6cHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjA1MTE2OTU5MDY0MzI3NDc1NCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZTowIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQwOTM1NjcyNTE0NjE5NywiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDUxMTY5NTkwNjQzMjc0NzU0LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wNTcwMTc1NDM4NTk2NDkxOSwiZHJpdmVyOm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOjAuMDQyNTcyNDYzNzY4MTE1ODU0LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aFRvQmFzZTowIjowLjA0MDc2MDg2OTU2NTIxNzE4NCwiZHJpdmVyLXJhbmdlOm90aGVyU2FsZXNHcm93dGhUb0Jhc2U6MSI6MC4wNDQzODQwNTc5NzEwMTQ1MiwiZHJpdmVyOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50VG9CYXNlOjEiOjAuMDAwMTM0NTc1NTY5MzU4MTk3MzcsImRyaXZlcjpvdGhlclBheUdyb3d0aFRvQmFzZSI6MC4wMTk4NDY0NTg0NjkyNDAyNywiZHJpdmVyLXJhbmdlOm90aGVyUGF5R3Jvd3RoVG9CYXNlOjAiOjAuMDE5MTM5NDU3MDIzNzE3NDQzLCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGhUb0Jhc2U6MSI6MC4wMjA1NTM0NTk5MTQ3NjMwOTUsImRyaXZlcjpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2U6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aFRvQmFzZToxIjowLjA4LCJkcml2ZXI6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOjAuMDQwODMzMzMzMzMzMzMzMzksImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZTowIjowLjAzOTE2NjY2NjY2NjY2NjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2U6MSI6MC4wNDI1MDAwMDAwMDAwMDAwOSwiZHJpdmVyOm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlOjEiOjAsImRyaXZlcjpwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsImRyaXZlci1yYW5nZTpwcm9qZWN0U2FsZXNHcm93dGg6MCI6MC4xNSwiZHJpdmVyLXJhbmdlOnByb2plY3RTYWxlc0dyb3d0aDoxIjowLjMsImRyaXZlcjpvdGhlclNhbGVzR3Jvd3RoIjowLjA2MjU3MjQ2Mzc2ODExNTg2LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDowIjowLjA2MDc2MDg2OTU2NTIxNzE5LCJkcml2ZXItcmFuZ2U6b3RoZXJTYWxlc0dyb3d0aDoxIjowLjA2NDM4NDA1Nzk3MTAxNDUzLCJkcml2ZXI6cHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6MC4wMTUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlOjEiOjAuMDMsImRyaXZlcjpvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsImRyaXZlci1yYW5nZTpvdGhlckNvZ3NJbXByb3ZlbWVudDowIjowLjAwNSwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0ltcHJvdmVtZW50OjEiOjAuMDA1MTM0NTc1NTY5MzU4MTk3NSwiZHJpdmVyOnByb2plY3RQYXlHcm93dGgiOjAuMDcsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjAiOjAuMDUsImRyaXZlci1yYW5nZTpwcm9qZWN0UGF5R3Jvd3RoOjEiOjAuMSwiZHJpdmVyOm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJkcml2ZXItcmFuZ2U6b3RoZXJQYXlHcm93dGg6MCI6MC4wMjQxMzk0NTcwMjM3MTc0NDQsImRyaXZlci1yYW5nZTpvdGhlclBheUdyb3d0aDoxIjowLjAyNTU1MzQ1OTkxNDc2MzA5NiwiZHJpdmVyOm90aGVyT2ZmaWNlclBheUdyb3d0aCI6MC4wNDUsImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJQYXlHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyT2ZmaWNlclBheUdyb3d0aDoxIjowLjA4LCJkcml2ZXI6cHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wNCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RIZWFkY291bnRHcm93dGg6MSI6MC4wOCwiZHJpdmVyOm90aGVySGVhZGNvdW50R3Jvd3RoIjowLjA0NTgzMzMzMzMzMzMzMzM4NiwiZHJpdmVyLXJhbmdlOm90aGVySGVhZGNvdW50R3Jvd3RoOjAiOjAuMDQ0MTY2NjY2NjY2NjY2NjgsImRyaXZlci1yYW5nZTpvdGhlckhlYWRjb3VudEdyb3d0aDoxIjowLjA0NzUwMDAwMDAwMDAwMDA5LCJkcml2ZXI6cHJvamVjdFNnYVJhdGVFbmQiOjAuMTEsImRyaXZlci1yYW5nZTpwcm9qZWN0U2dhUmF0ZUVuZDowIjowLjA4NDk5OTk5OTk5OTk5OTk5LCJkcml2ZXItcmFuZ2U6cHJvamVjdFNnYVJhdGVFbmQ6MSI6MC4xMzUsImRyaXZlcjpvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsImRyaXZlci1yYW5nZTpvdGhlclNnYVJhdGVFbmQ6MCI6MC4wODkyODU3MTQyODU3MTQyNywiZHJpdmVyLXJhbmdlOm90aGVyU2dhUmF0ZUVuZDoxIjowLjExOTI4NTcxNDI4NTcxNDI3LCJkcml2ZXI6cHJvamVjdE9mZmljZXJQYXlHcm93dGgiOjAuMDUzODAxMTY5NTkwNjQzMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0T2ZmaWNlclBheUdyb3d0aDowIjowLjA0MjYzMTU3ODk0NzM2ODM2LCJkcml2ZXItcmFuZ2U6cHJvamVjdE9mZmljZXJQYXlHcm93dGg6MSI6MC4wNjU1NTU1NTU1NTU1NTU1OCwiZHJpdmVyOnVzZWZ1bExpZmUiOjEwLCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZTowIjo1LCJkcml2ZXItcmFuZ2U6dXNlZnVsTGlmZToxIjoyMCwiZHJpdmVyOmludmVzdG1lbnQiOjIzLCJkcml2ZXItcmFuZ2U6aW52ZXN0bWVudDowIjoxNSwiZHJpdmVyLXJhbmdlOmludmVzdG1lbnQ6MSI6MjAwLCJkcml2ZXI6c3Vic2lkeSI6Ny42NiwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MCI6MSwiZHJpdmVyLXJhbmdlOnN1YnNpZHk6MSI6NTAsImRyaXZlcjpsb2NhbEJlbmNobWFyayI6MjMsImRyaXZlci1yYW5nZTpsb2NhbEJlbmNobWFyazowIjowLCJkcml2ZXItcmFuZ2U6bG9jYWxCZW5jaG1hcms6MSI6MTAwLCJ0YXJnZXQ6Y29tcGFueVNhbGVzQ2Fncjp2YWx1ZSI6MTUsInRhcmdldDpjb21wYW55U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTp2YWx1ZSI6ODIuNCwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTp2YWx1ZSI6MiwidGFyZ2V0OmNvbXBhbnlQYXlTY2hlZHVsZTptYXgiOjcsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTp2YWx1ZSI6NjAsInRhcmdldDpwcm9qZWN0U2FsZXNTaGFyZTptYXgiOjk1LCJ0YXJnZXQ6cHJvamVjdFNhbGVzQ2Fncjp2YWx1ZSI6MjIsInRhcmdldDpwcm9qZWN0U2FsZXNDYWdyOm1heCI6MzUsInRhcmdldDpwcm9qZWN0U2FsZXNJbmNyZWFzZTp2YWx1ZSI6NzQuOCwidGFyZ2V0OmxhYm9yUHJvZHVjdGl2aXR5Q2Fncjp2YWx1ZSI6MjEsInRhcmdldDpsYWJvclByb2R1Y3Rpdml0eUNhZ3I6bWF4IjozNSwidGFyZ2V0OnZhbHVlQWRkZWRJbmNyZWFzZTp2YWx1ZSI6MTguNzgsInRhcmdldDplbXBsb3llZVBheUNhZ3I6dmFsdWUiOjcsInRhcmdldDplbXBsb3llZVBheUNhZ3I6bWF4IjoxMCwidGFyZ2V0OmVtcGxveWVlUGF5SW5jcmVhc2U6dmFsdWUiOjIuODUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzp2YWx1ZSI6MTUsInRhcmdldDppbnZlc3RtZW50U2FsZXNSYXRpbzptYXgiOjcwLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzp2YWx1ZSI6MjEzLCJ0YXJnZXQ6dmFsdWVBZGRlZFN1YnNpZHlSYXRpbzptYXgiOjM1MCwidGFyZ2V0OmxvY2FsQmVuY2htYXJrOnZhbHVlIjoyMywidGFyZ2V0OmxvY2FsQmVuY2htYXJrOm1heCI6NDAsInRhcmdldDpvZmZpY2VyUGF5Q2Fncjp2YWx1ZSI6NiwidGFyZ2V0Om9mZmljZXJQYXlDYWdyOm1heCI6MTAsInRhcmdldDpvZmZpY2VyUGF5SW5jcmVhc2U6dmFsdWUiOjAsInRhcmdldDpjb21wYW55U2FsZXNJbmNyZWFzZTptYXgiOjI1Mi42OSwidGFyZ2V0OnByb2plY3RTYWxlc0luY3JlYXNlOm1heCI6MTM2Ljg0LCJ0YXJnZXQ6dmFsdWVBZGRlZEluY3JlYXNlOm1heCI6MzMuNDMsInRhcmdldDplbXBsb3llZVBheUluY3JlYXNlOm1heCI6My43NH0sIm1ldHJpY0dyb3VwQmFzZXMiOnsiY29tcGFueVNhbGVzIjoicmF0ZSIsInByb2plY3RTYWxlcyI6InJhdGUiLCJsYWJvclByb2R1Y3Rpdml0eSI6InJhdGUiLCJlbXBsb3llZVBheSI6InJhdGUifSwiYXBwbGljYXRpb25DYXRlZ29yeSI6ImdlbmVyYWwiLCJhZGp1c3RlZERyaXZlcnMiOnsicHJvamVjdE1hcmtldEdyb3d0aCI6MC4wNSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwib3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm8iOjAuNjgsInByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsInByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwicHJvamVjdENvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yNSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMiwicHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNSwib3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOi0wLjAwNSwicHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJvdGhlckV4dHJhb3JkaW5hcnlSYXRlIjowLCJlZmZlY3RpdmVUYXhSYXRlIjowLjMsInByb2plY3RTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNTQxMTgyMzgzMDQwOTM1NSwicHJvamVjdENvZ3NJbXByb3ZlbWVudFRvQmFzZSI6MS4xNzQxODY0OTEwNjQ0NjZlLTE2LCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjowLjAyMDAzODU2MjA1OTEzMzU2MiwicHJvamVjdEhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNTIxNTg4ODg3MTgzOTQ1NSwicHJvamVjdFNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aFRvQmFzZSI6MC4wNTQxMzg0NDUwMzUzNjE4Nywib3RoZXJTYWxlc0dyb3d0aFRvQmFzZSI6MC4wNDI1Njk3MDU2MzE2MTMxOCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTgxOTg4OTExNDM0OTkxNSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aFRvQmFzZSI6MC4wNDA3OTQ0MTE0MTQ5ODIyMjUsIm90aGVyU2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RTYWxlc0dyb3d0aCI6MC4yMjAzNzA4MTgxMTU0MTI2OCwib3RoZXJTYWxlc0dyb3d0aCI6MC4wNjI2MjE3MzU2ODE4MzE4LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50QWZ0ZXJCYXNlIjowLjAxNDk1MjgwNjkyMjY2MDg5NSwib3RoZXJDb2dzSW1wcm92ZW1lbnQiOjAuMDA1LCJwcm9qZWN0UGF5R3Jvd3RoIjowLjA4NDgxMjgzMzc0ODY2NTAxLCJvdGhlclBheUdyb3d0aCI6MC4wMjQ4NjM3OTU1NTk2MzczNCwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoIjowLjA0NSwicHJvamVjdEhlYWRjb3VudEdyb3d0aCI6MC4wMjY1MzQwMDY5ODczNjg5OSwib3RoZXJIZWFkY291bnRHcm93dGgiOjAuMDQ1ODY4Mzk2ODIxODYwOTA0LCJwcm9qZWN0U2dhUmF0ZUVuZCI6MC4xMDk5Nzc1ODM4MTI3MzU1Niwib3RoZXJTZ2FSYXRlRW5kIjowLjEwOTMyMTYzMDk2ODAxODY1LCJwcm9qZWN0T2ZmaWNlclBheUdyb3d0aCI6MC4wNTM3NjI5Njg0Mjg5MjM1OSwidXNlZnVsTGlmZSI6MTAsImludmVzdG1lbnQiOjIzLCJzdWJzaWR5Ijo3LjY2LCJsb2NhbEJlbmNobWFyayI6MjN9fQ==</t>
         </is>
       </c>
     </row>

--- a/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
+++ b/補助金/大規模成長投資補助金/planning_model/examples/成長投資計画_提案計画サンプル.xlsx
@@ -6768,7 +6768,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C292"/>
+  <dimension ref="A1:C289"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
@@ -10038,11 +10038,11 @@
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:0</t>
+          <t xml:space="preserve">driver:effectiveTaxRate</t>
         </is>
       </c>
       <c r="B218" s="2">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
@@ -10053,11 +10053,11 @@
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver-range:usefulLife:1</t>
+          <t xml:space="preserve">driver:investment</t>
         </is>
       </c>
       <c r="B219" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
@@ -10068,11 +10068,11 @@
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:effectiveTaxRate</t>
+          <t xml:space="preserve">driver:localBenchmark</t>
         </is>
       </c>
       <c r="B220" s="2">
-        <v>0.3</v>
+        <v>23</v>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
@@ -10083,11 +10083,11 @@
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:investment</t>
+          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>23</v>
+        <v>0.2</v>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
@@ -10098,11 +10098,11 @@
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:localBenchmark</t>
+          <t xml:space="preserve">driver:otherCogsImprovement</t>
         </is>
       </c>
       <c r="B222" s="2">
-        <v>23</v>
+        <v>0.005</v>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
@@ -10113,26 +10113,26 @@
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B223" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovement</t>
+          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B224" s="2">
-        <v>0.005</v>
+        <v>0.68</v>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
@@ -10143,41 +10143,41 @@
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B225" s="2">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
         </is>
       </c>
       <c r="B226" s="2">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
         </is>
       </c>
       <c r="B227" s="2">
-        <v>0.95</v>
+        <v>0.045833333333333386</v>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
@@ -10188,26 +10188,26 @@
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherExtraordinaryRate</t>
+          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B228" s="2">
-        <v>0</v>
+        <v>0.04083333333333339</v>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowth</t>
+          <t xml:space="preserve">driver:otherNonOperatingRate</t>
         </is>
       </c>
       <c r="B229" s="2">
-        <v>0.045833333333333386</v>
+        <v>-0.005</v>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
@@ -10218,11 +10218,11 @@
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B230" s="2">
-        <v>0.04083333333333339</v>
+        <v>0.9</v>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
@@ -10233,11 +10233,11 @@
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherNonOperatingRate</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B231" s="2">
-        <v>-0.005</v>
+        <v>0.045</v>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
@@ -10248,11 +10248,11 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B232" s="2">
-        <v>0.9</v>
+        <v>0.04</v>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
@@ -10263,11 +10263,11 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:otherPayGrowth</t>
         </is>
       </c>
       <c r="B233" s="2">
-        <v>0.045</v>
+        <v>0.02484645846924027</v>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
@@ -10278,11 +10278,11 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
         </is>
       </c>
       <c r="B234" s="2">
-        <v>0.04</v>
+        <v>0.01984645846924027</v>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
@@ -10293,11 +10293,11 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowth</t>
+          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B235" s="2">
-        <v>0.02484645846924027</v>
+        <v>0.004</v>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
@@ -10308,11 +10308,11 @@
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherPayGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSalesGrowth</t>
         </is>
       </c>
       <c r="B236" s="2">
-        <v>0.01984645846924027</v>
+        <v>0.06257246376811586</v>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
@@ -10323,11 +10323,11 @@
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B237" s="2">
-        <v>0.004</v>
+        <v>0.042572463768115854</v>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
@@ -10338,26 +10338,26 @@
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowth</t>
+          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B238" s="2">
-        <v>0.06257246376811586</v>
+        <v>0</v>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:otherSgaRateEnd</t>
         </is>
       </c>
       <c r="B239" s="2">
-        <v>0.042572463768115854</v>
+        <v>0.10928571428571428</v>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
@@ -10368,26 +10368,26 @@
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
         </is>
       </c>
       <c r="B240" s="2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:otherSgaRateEnd</t>
+          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
         </is>
       </c>
       <c r="B241" s="2">
-        <v>0.10928571428571428</v>
+        <v>0.015</v>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
@@ -10398,11 +10398,11 @@
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsDepreciationShare</t>
+          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
         </is>
       </c>
       <c r="B242" s="2">
-        <v>0.25</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
@@ -10413,11 +10413,11 @@
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementAfterBase</t>
+          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
         </is>
       </c>
       <c r="B243" s="2">
-        <v>0.015</v>
+        <v>0.68</v>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
@@ -10428,11 +10428,11 @@
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsImprovementToBase</t>
+          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
         </is>
       </c>
       <c r="B244" s="2">
-        <v>5.551115123125783e-17</v>
+        <v>0.95</v>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
@@ -10443,26 +10443,26 @@
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectCogsRateWhenSalesZero</t>
+          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
         </is>
       </c>
       <c r="B245" s="2">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectEmployeeSalaryShare</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
         </is>
       </c>
       <c r="B246" s="2">
-        <v>0.95</v>
+        <v>0.04</v>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
@@ -10473,26 +10473,26 @@
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectExtraordinaryRate</t>
+          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
         </is>
       </c>
       <c r="B247" s="2">
-        <v>0</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowth</t>
+          <t xml:space="preserve">driver:projectMarketGrowth</t>
         </is>
       </c>
       <c r="B248" s="2">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
@@ -10503,26 +10503,26 @@
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectHeadcountGrowthToBase</t>
+          <t xml:space="preserve">driver:projectNonOperatingRate</t>
         </is>
       </c>
       <c r="B249" s="2">
-        <v>0.05409356725146197</v>
+        <v>0</v>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectMarketGrowth</t>
+          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
         </is>
       </c>
       <c r="B250" s="2">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
@@ -10533,26 +10533,26 @@
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectNonOperatingRate</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
         </is>
       </c>
       <c r="B251" s="2">
-        <v>0</v>
+        <v>0.05380116959064325</v>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerCompensationShare</t>
+          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
         </is>
       </c>
       <c r="B252" s="2">
-        <v>0.9</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
@@ -10563,11 +10563,11 @@
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowth</t>
+          <t xml:space="preserve">driver:projectPayGrowth</t>
         </is>
       </c>
       <c r="B253" s="2">
-        <v>0.05380116959064325</v>
+        <v>0.07</v>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
@@ -10578,11 +10578,11 @@
     <row r="254">
       <c r="A254" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectOfficerPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
         </is>
       </c>
       <c r="B254" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.020030662342518046</v>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
@@ -10593,11 +10593,11 @@
     <row r="255">
       <c r="A255" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowth</t>
+          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
         </is>
       </c>
       <c r="B255" s="2">
-        <v>0.07</v>
+        <v>0.005</v>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
@@ -10608,11 +10608,11 @@
     <row r="256">
       <c r="A256" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectPayGrowthToBase</t>
+          <t xml:space="preserve">driver:projectSalesGrowth</t>
         </is>
       </c>
       <c r="B256" s="2">
-        <v>0.020030662342518046</v>
+        <v>0.22</v>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
@@ -10623,11 +10623,11 @@
     <row r="257">
       <c r="A257" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectResearchDevelopmentRate</t>
+          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
         </is>
       </c>
       <c r="B257" s="2">
-        <v>0.005</v>
+        <v>0.05409356725146197</v>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
@@ -10638,26 +10638,26 @@
     <row r="258">
       <c r="A258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowth</t>
+          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
         </is>
       </c>
       <c r="B258" s="2">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSalesGrowthToBase</t>
+          <t xml:space="preserve">driver:projectSgaRateEnd</t>
         </is>
       </c>
       <c r="B259" s="2">
-        <v>0.05409356725146197</v>
+        <v>0.11</v>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
@@ -10668,26 +10668,26 @@
     <row r="260">
       <c r="A260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaImprovementToBase</t>
+          <t xml:space="preserve">driver:subsidy</t>
         </is>
       </c>
       <c r="B260" s="2">
-        <v>0</v>
+        <v>7.66</v>
       </c>
       <c r="C260" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:projectSgaRateEnd</t>
+          <t xml:space="preserve">target:companyPaySchedule:max</t>
         </is>
       </c>
       <c r="B261" s="2">
-        <v>0.11</v>
+        <v>7</v>
       </c>
       <c r="C261" s="0" t="inlineStr">
         <is>
@@ -10698,11 +10698,11 @@
     <row r="262">
       <c r="A262" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:subsidy</t>
+          <t xml:space="preserve">target:companyPaySchedule:value</t>
         </is>
       </c>
       <c r="B262" s="2">
-        <v>7.66</v>
+        <v>2</v>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
@@ -10713,11 +10713,11 @@
     <row r="263">
       <c r="A263" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">driver:usefulLife</t>
+          <t xml:space="preserve">target:companySalesCagr:max</t>
         </is>
       </c>
       <c r="B263" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C263" s="0" t="inlineStr">
         <is>
@@ -10728,11 +10728,11 @@
     <row r="264">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:max</t>
+          <t xml:space="preserve">target:companySalesCagr:value</t>
         </is>
       </c>
       <c r="B264" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
@@ -10743,11 +10743,11 @@
     <row r="265">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companyPaySchedule:value</t>
+          <t xml:space="preserve">target:companySalesIncrease:max</t>
         </is>
       </c>
       <c r="B265" s="2">
-        <v>2</v>
+        <v>252.69</v>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
@@ -10758,11 +10758,11 @@
     <row r="266">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:max</t>
+          <t xml:space="preserve">target:companySalesIncrease:value</t>
         </is>
       </c>
       <c r="B266" s="2">
-        <v>35</v>
+        <v>82.4</v>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
@@ -10773,11 +10773,11 @@
     <row r="267">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesCagr:value</t>
+          <t xml:space="preserve">target:employeePayCagr:max</t>
         </is>
       </c>
       <c r="B267" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
@@ -10788,11 +10788,11 @@
     <row r="268">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:max</t>
+          <t xml:space="preserve">target:employeePayCagr:value</t>
         </is>
       </c>
       <c r="B268" s="2">
-        <v>252.69</v>
+        <v>7</v>
       </c>
       <c r="C268" s="0" t="inlineStr">
         <is>
@@ -10803,11 +10803,11 @@
     <row r="269">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:companySalesIncrease:value</t>
+          <t xml:space="preserve">target:employeePayIncrease:max</t>
         </is>
       </c>
       <c r="B269" s="2">
-        <v>82.4</v>
+        <v>3.74</v>
       </c>
       <c r="C269" s="0" t="inlineStr">
         <is>
@@ -10818,11 +10818,11 @@
     <row r="270">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:max</t>
+          <t xml:space="preserve">target:employeePayIncrease:value</t>
         </is>
       </c>
       <c r="B270" s="2">
-        <v>10</v>
+        <v>2.85</v>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
@@ -10833,11 +10833,11 @@
     <row r="271">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayCagr:value</t>
+          <t xml:space="preserve">target:investmentSalesRatio:max</t>
         </is>
       </c>
       <c r="B271" s="2">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
@@ -10848,11 +10848,11 @@
     <row r="272">
       <c r="A272" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:max</t>
+          <t xml:space="preserve">target:investmentSalesRatio:value</t>
         </is>
       </c>
       <c r="B272" s="2">
-        <v>3.74</v>
+        <v>15</v>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
@@ -10863,11 +10863,11 @@
     <row r="273">
       <c r="A273" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:employeePayIncrease:value</t>
+          <t xml:space="preserve">target:laborProductivityCagr:max</t>
         </is>
       </c>
       <c r="B273" s="2">
-        <v>2.85</v>
+        <v>35</v>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
@@ -10878,11 +10878,11 @@
     <row r="274">
       <c r="A274" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:max</t>
+          <t xml:space="preserve">target:laborProductivityCagr:value</t>
         </is>
       </c>
       <c r="B274" s="2">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
@@ -10893,11 +10893,11 @@
     <row r="275">
       <c r="A275" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:investmentSalesRatio:value</t>
+          <t xml:space="preserve">target:localBenchmark:max</t>
         </is>
       </c>
       <c r="B275" s="2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
@@ -10908,11 +10908,11 @@
     <row r="276">
       <c r="A276" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:max</t>
+          <t xml:space="preserve">target:localBenchmark:value</t>
         </is>
       </c>
       <c r="B276" s="2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
@@ -10923,11 +10923,11 @@
     <row r="277">
       <c r="A277" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:laborProductivityCagr:value</t>
+          <t xml:space="preserve">target:officerPayCagr:max</t>
         </is>
       </c>
       <c r="B277" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
@@ -10938,11 +10938,11 @@
     <row r="278">
       <c r="A278" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:max</t>
+          <t xml:space="preserve">target:officerPayCagr:value</t>
         </is>
       </c>
       <c r="B278" s="2">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
@@ -10953,26 +10953,26 @@
     <row r="279">
       <c r="A279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:localBenchmark:value</t>
+          <t xml:space="preserve">target:officerPayIncrease:value</t>
         </is>
       </c>
       <c r="B279" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力済み</t>
+          <t xml:space="preserve">明示的な0</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:max</t>
+          <t xml:space="preserve">target:projectSalesCagr:max</t>
         </is>
       </c>
       <c r="B280" s="2">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C280" s="0" t="inlineStr">
         <is>
@@ -10983,11 +10983,11 @@
     <row r="281">
       <c r="A281" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayCagr:value</t>
+          <t xml:space="preserve">target:projectSalesCagr:value</t>
         </is>
       </c>
       <c r="B281" s="2">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
@@ -10998,26 +10998,26 @@
     <row r="282">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:officerPayIncrease:value</t>
+          <t xml:space="preserve">target:projectSalesIncrease:max</t>
         </is>
       </c>
       <c r="B282" s="2">
-        <v>0</v>
+        <v>136.84</v>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">明示的な0</t>
+          <t xml:space="preserve">入力済み</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:max</t>
+          <t xml:space="preserve">target:projectSalesIncrease:value</t>
         </is>
       </c>
       <c r="B283" s="2">
-        <v>35</v>
+        <v>74.8</v>
       </c>
       <c r="C283" s="0" t="inlineStr">
         <is>
@@ -11028,11 +11028,11 @@
     <row r="284">
       <c r="A284" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesCagr:value</t>
+          <t xml:space="preserve">target:projectSalesShare:max</t>
         </is>
       </c>
       <c r="B284" s="2">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
@@ -11043,11 +11043,11 @@
     <row r="285">
       <c r="A285" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:max</t>
+          <t xml:space="preserve">target:projectSalesShare:value</t>
         </is>
       </c>
       <c r="B285" s="2">
-        <v>136.84</v>
+        <v>60</v>
       </c>
       <c r="C285" s="0" t="inlineStr">
         <is>
@@ -11058,11 +11058,11 @@
     <row r="286">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesIncrease:value</t>
+          <t xml:space="preserve">target:valueAddedIncrease:max</t>
         </is>
       </c>
       <c r="B286" s="2">
-        <v>74.8</v>
+        <v>33.43</v>
       </c>
       <c r="C286" s="0" t="inlineStr">
         <is>
@@ -11073,11 +11073,11 @@
     <row r="287">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:max</t>
+          <t xml:space="preserve">target:valueAddedIncrease:value</t>
         </is>
       </c>
       <c r="B287" s="2">
-        <v>95</v>
+        <v>18.78</v>
       </c>
       <c r="C287" s="0" t="inlineStr">
         <is>
@@ -11088,11 +11088,11 @@
     <row r="288">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:projectSalesShare:value</t>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
         </is>
       </c>
       <c r="B288" s="2">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="C288" s="0" t="inlineStr">
         <is>
@@ -11103,58 +11103,13 @@
     <row r="289">
       <c r="A289" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">target:valueAddedIncrease:max</t>
+          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
         </is>
       </c>
       <c r="B289" s="2">
-        <v>33.43</v>
+        <v>213</v>
       </c>
       <c r="C289" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedIncrease:value</t>
-        </is>
-      </c>
-      <c r="B290" s="2">
-        <v>18.78</v>
-      </c>
-      <c r="C290" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:max</t>
-        </is>
-      </c>
-      <c r="B291" s="2">
-        <v>350</v>
-      </c>
-      <c r="C291" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入力済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target:valueAddedSubsidyRatio:value</t>
-        </is>
-      </c>
-      <c r="B292" s="2">
-        <v>213</v>
-      </c>
-      <c r="C292" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">入力済み</t>
         </is>
@@ -11182,7 +11137,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eyJmb3JtYXQiOiJncm93dGgtaW52ZXN0bWVudC1wcm9wb3NhbC92MSIsInRpdGxlIjoi5oiQ6ZW35oqV6LOH6KiI55S7IOaPkOahiOioiOeUu+OCteODs+ODl+ODqyIsImV4cG9ydGVkQXQiOiIyMDI2LTA3LTIyVDAwOjAwOjAwLjAwMFoiLCJ0aW1lbGluZSI6eyJsYXRlc3RZZWFyIjoyMDI1LCJiYXNlWWVhciI6MjAyOH0sImhpc3RvcmljYWxQbGFuIjpbeyJ5ZWFyIjoyMDIzLCJyb2xlIjoicHJlUHJldmlvdXMiLCJwcm9qZWN0Ijp7InNhbGVzIjo3MiwiY29ncyI6NDguOTYsImVtcGxveWVlUGF5Ijo1LjE5LCJvZmZpY2VyUGF5IjowLjM2LCJkZXByZWNpYXRpb24iOjEuOCwib3RoZXJTZ2EiOjksImhlYWRjb3VudCI6OTAsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjQuOTMsImVtcGxveWVlQm9udXMiOjAuMjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzIsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40NSwic2dhRGVwcmVjaWF0aW9uIjoxLjM1LCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM2fSwib3RoZXIiOnsic2FsZXMiOjY0LjQsImNvZ3MiOjQzLjc5LCJlbXBsb3llZVBheSI6Ny4xLCJvZmZpY2VyUGF5IjowLjU1LCJkZXByZWNpYXRpb24iOjEuMzgsIm90aGVyU2dhIjo3LjM2LCJoZWFkY291bnQiOjEyMCwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ni43NCwiZW1wbG95ZWVCb251cyI6MC4zNiwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41LCJvZmZpY2VyQm9udXMiOjAuMDUsImNvZ3NEZXByZWNpYXRpb24iOjAuMjgsInNnYURlcHJlY2lhdGlvbiI6MS4xLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjI4LCJvcmRpbmFyeUluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsInByZVRheEluY29tZSI6My45NTAwMDAwMDAwMDAwMDMsIm5ldEluY29tZSI6Ny41MX19LHsieWVhciI6MjAyNCwicm9sZSI6InByZXZpb3VzIiwicHJvamVjdCI6eyJzYWxlcyI6NzYsImNvZ3MiOjUxLjY4LCJlbXBsb3llZVBheSI6NS41OSwib2ZmaWNlclBheSI6MC4zOCwiZGVwcmVjaWF0aW9uIjoxLjksIm90aGVyU2dhIjo5LjUsImhlYWRjb3VudCI6OTUsIm9mZmljZXJDb3VudCI6MiwiZW1wbG95ZWVTYWxhcnkiOjUuMzEsImVtcGxveWVlQm9udXMiOjAuMjgsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuMzQsIm9mZmljZXJCb251cyI6MC4wNCwiY29nc0RlcHJlY2lhdGlvbiI6MC40Nywic2dhRGVwcmVjaWF0aW9uIjoxLjQzLCJyZXNlYXJjaERldmVsb3BtZW50IjowLjM4fSwib3RoZXIiOnsic2FsZXMiOjY3LjIsImNvZ3MiOjQ1LjcsImVtcGxveWVlUGF5Ijo3LjU0LCJvZmZpY2VyUGF5IjowLjU4LCJkZXByZWNpYXRpb24iOjEuNDQsIm90aGVyU2dhIjo3LjY4LCJoZWFkY291bnQiOjEyNSwib2ZmaWNlckNvdW50IjozLCJlbXBsb3llZVNhbGFyeSI6Ny4xNiwiZW1wbG95ZWVCb251cyI6MC4zOCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC41Miwib2ZmaWNlckJvbnVzIjowLjA2LCJjb2dzRGVwcmVjaWF0aW9uIjowLjI5LCJzZ2FEZXByZWNpYXRpb24iOjEuMTUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMjksIm9yZGluYXJ5SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywicHJlVGF4SW5jb21lIjozLjk2OTk5OTk5OTk5OTk5NywibmV0SW5jb21lIjo3LjcxfX0seyJ5ZWFyIjoyMDI1LCJyb2xlIjoibGF0ZXN0IiwicHJvamVjdCI6eyJzYWxlcyI6ODAsImNvZ3MiOjU0LjQsImVtcGxveWVlUGF5Ijo2LCJlbXBsb3llZVNhbGFyeSI6NS43LCJlbXBsb3llZUJvbnVzIjowLjMsIm9mZmljZXJQYXkiOjAuNCwib2ZmaWNlckNvbXBlbnNhdGlvbiI6MC4zNiwib2ZmaWNlckJvbnVzIjowLjA0LCJkZXByZWNpYXRpb24iOjIsImNvZ3NEZXByZWNpYXRpb24iOjAuNSwic2dhRGVwcmVjaWF0aW9uIjoxLjUsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuNCwib3RoZXJTZ2EiOjEwLCJoZWFkY291bnQiOjEwMCwib2ZmaWNlckNvdW50IjoyfSwib3RoZXIiOnsic2FsZXMiOjcwLCJjb2dzIjo0Ny42LCJlbXBsb3llZVBheSI6OCwiZW1wbG95ZWVTYWxhcnkiOjcuNiwiZW1wbG95ZWVCb251cyI6MC40LCJvZmZpY2VyUGF5IjowLjYsIm9mZmljZXJDb21wZW5zYXRpb24iOjAuNTQsIm9mZmljZXJCb251cyI6MC4wNiwiZGVwcmVjaWF0aW9uIjoxLjUsImNvZ3NEZXByZWNpYXRpb24iOjAuMywic2dhRGVwcmVjaWF0aW9uIjoxLjIsInJlc2VhcmNoRGV2ZWxvcG1lbnQiOjAuMywib3RoZXJTZ2EiOjgsImhlYWRjb3VudCI6MTMwLCJvZmZpY2VyQ291bnQiOjMsIm9yZGluYXJ5SW5jb21lIjozLjk5OTk5OTk5OTk5OTk5NjQsInByZVRheEluY29tZSI6My45OTk5OTk5OTk5OTk5OTY0LCJuZXRJbmNvbWUiOjcuOTF9fV0sImJhbGFuY2VTaGVldHMiOlt7InllYXIiOjIwMjMsImFzc2V0cyI6MTMyLCJjdXJyZW50QXNzZXRzIjo2NywiY2FzaCI6MjQsImZpeGVkQXNzZXRzIjo2NSwidGFuZ2libGVBc3NldHMiOjUzLCJidWlsZGluZ3MiOjE5LCJtYWNoaW5lcnkiOjI0LCJsYW5kIjoxMCwiaW50YW5naWJsZUFzc2V0cyI6Nywic29mdHdhcmUiOjUsImxpYWJpbGl0aWVzIjo3NSwiY3VycmVudExpYWJpbGl0aWVzIjozOSwic2hvcnRUZXJtRGVidCI6MTIsImZpeGVkTGlhYmlsaXRpZXMiOjM2LCJsb25nVGVybURlYnQiOjI5LCJuZXRBc3NldHMiOjU3LCJzaGFyZWhvbGRlckVxdWl0eSI6NTQsImNhcGl0YWwiOjEwLCJjYXBleCI6NX0seyJ5ZWFyIjoyMDI0LCJhc3NldHMiOjE0MywiY3VycmVudEFzc2V0cyI6NzIsImNhc2giOjI1LCJmaXhlZEFzc2V0cyI6NzEsInRhbmdpYmxlQXNzZXRzIjo1OCwiYnVpbGRpbmdzIjoyMCwibWFjaGluZXJ5IjoyOCwibGFuZCI6MTAsImludGFuZ2libGVBc3NldHMiOjgsInNvZnR3YXJlIjo2LCJsaWFiaWxpdGllcyI6NzksImN1cnJlbnRMaWFiaWxpdGllcyI6NDEsInNob3J0VGVybURlYnQiOjEyLCJmaXhlZExpYWJpbGl0aWVzIjozOCwibG9uZ1Rlcm1EZWJ0IjozMSwibmV0QXNzZXRzIjo2NCwic2hhcmVob2xkZXJFcXVpdHkiOjYxLCJjYXBpdGFsIjoxMCwiY2FwZXgiOjh9LHsieWVhciI6MjAyNSwiYXNzZXRzIjoxNTYsImN1cnJlbnRBc3NldHMiOjc4LCJjYXNoIjoyNywiZml4ZWRBc3NldHMiOjc4LCJ0YW5naWJsZUFzc2V0cyI6NjQsImJ1aWxkaW5ncyI6MjIsIm1hY2hpbmVyeSI6MzIsImxhbmQiOjEwLCJpbnRhbmdpYmxlQXNzZXRzIjo5LCJzb2Z0d2FyZSI6NywibGlhYmlsaXRpZXMiOjgzLCJjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJzaG9ydFRlcm1EZWJ0IjoxMSwiZml4ZWRMaWFiaWxpdGllcyI6NDAsImxvbmdUZXJtRGVidCI6MzIsIm5ldEFzc2V0cyI6NzMsInNoYXJlaG9sZGVyRXF1aXR5Ijo3MCwiY2FwaXRhbCI6MTAsImNhcGV4IjoxMH1dLCJmdXR1cmVDYXBleCI6W3sieWVhciI6MjAyNiwidmFsdWUiOjB9LHsieWVhciI6MjAyNywidmFsdWUiOjB9LHsieWVhciI6MjAyOCwidmFsdWUiOjB9LHsieWVhciI6MjAyOSwidmFsdWUiOjB9LHsieWVhciI6MjAzMCwidmFsdWUiOjB9LHsieWVhciI6MjAzMSwidmFsdWUiOjB9XSwiZHJpdmVycyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJwcm9qZWN0Q29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJvdGhlckNvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOjAuOTUsIm90aGVyRW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwicHJvamVjdE9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZSI6MC45LCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjowLjI1LCJvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlIjowLjAwNCwicHJvamVjdE5vbk9wZXJhdGluZ1JhdGUiOjAsIm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGUiOjAsIm90aGVyRXh0cmFvcmRpbmFyeVJhdGUiOjAsImVmZmVjdGl2ZVRheFJhdGUiOjAuMywicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0Q29nc0ltcHJvdmVtZW50VG9CYXNlIjo1LjU1MTExNTEyMzEyNTc4M2UtMTcsInByb2plY3RQYXlHcm93dGhUb0Jhc2UiOjAuMDIwMDMwNjYyMzQyNTE4MDQ2LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJwcm9qZWN0U2dhSW1wcm92ZW1lbnRUb0Jhc2UiOjAsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjowLjA1NDA5MzU2NzI1MTQ2MTk3LCJvdGhlclNhbGVzR3Jvd3RoVG9CYXNlIjowLjA0MjU3MjQ2Mzc2ODExNTg1NCwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOjAsIm90aGVyUGF5R3Jvd3RoVG9CYXNlIjowLjAxOTg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGhUb0Jhc2UiOjAuMDQsIm90aGVySGVhZGNvdW50R3Jvd3RoVG9CYXNlIjowLjA0MDgzMzMzMzMzMzMzMzM5LCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjowLCJwcm9qZWN0U2FsZXNHcm93dGgiOjAuMjIsIm90aGVyU2FsZXNHcm93dGgiOjAuMDYyNTcyNDYzNzY4MTE1ODYsInByb2plY3RDb2dzSW1wcm92ZW1lbnRBZnRlckJhc2UiOjAuMDE1LCJvdGhlckNvZ3NJbXByb3ZlbWVudCI6MC4wMDUsInByb2plY3RQYXlHcm93dGgiOjAuMDcsIm90aGVyUGF5R3Jvd3RoIjowLjAyNDg0NjQ1ODQ2OTI0MDI3LCJvdGhlck9mZmljZXJQYXlHcm93dGgiOjAuMDQ1LCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoIjowLjA0LCJvdGhlckhlYWRjb3VudEdyb3d0aCI6MC4wNDU4MzMzMzMzMzMzMzMzODYsInByb2plY3RTZ2FSYXRlRW5kIjowLjExLCJvdGhlclNnYVJhdGVFbmQiOjAuMTA5Mjg1NzE0Mjg1NzE0MjgsInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjowLjA1MzgwMTE2OTU5MDY0MzI1LCJ1c2VmdWxMaWZlIjoxMCwiaW52ZXN0bWVudCI6MjMsInN1YnNpZHkiOjcuNjYsImxvY2FsQmVuY2htYXJrIjoyM30sImRyaXZlclJhbmdlcyI6eyJwcm9qZWN0TWFya2V0R3Jvd3RoIjpbLTAuMDUsMC4zXSwicHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6WzAsMC45OV0sIm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjpbMCwwLjk5XSwicHJvamVjdEVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmUiOlswLDFdLCJwcm9qZWN0T2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlIjpbMCwxXSwib3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOlswLDFdLCJwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sIm90aGVyUmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOlswLDAuM10sInByb2plY3ROb25PcGVyYXRpbmdSYXRlIjpbLTAuNSwwLjVdLCJvdGhlck5vbk9wZXJhdGluZ1JhdGUiOlstMC41LDAuNV0sInByb2plY3RFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwib3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6Wy0wLjUsMC41XSwiZWZmZWN0aXZlVGF4UmF0ZSI6WzAsMC42XSwicHJvamVjdFNhbGVzR3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDEuNjY1MzM0NTM2OTM3NzM0OGUtMTZdLCJwcm9qZWN0UGF5R3Jvd3RoVG9CYXNlIjpbMC4wMTkzMjUzMzA1MDE4NDY5MjcsMC4wMjA3MzU5OTQxODMxODkxNjZdLCJwcm9qZWN0SGVhZGNvdW50R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sInByb2plY3RTZ2FJbXByb3ZlbWVudFRvQmFzZSI6WzAsMF0sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMC4wNTExNjk1OTA2NDMyNzQ3NTQsMC4wNTcwMTc1NDM4NTk2NDkxOV0sIm90aGVyU2FsZXNHcm93dGhUb0Jhc2UiOlswLjA0MDc2MDg2OTU2NTIxNzE4NCwwLjA0NDM4NDA1Nzk3MTAxNDUyXSwib3RoZXJDb2dzSW1wcm92ZW1lbnRUb0Jhc2UiOlswLDAuMDAwMTM0NTc1NTY5MzU4MTk3MzddLCJvdGhlclBheUdyb3d0aFRvQmFzZSI6WzAuMDE5MTM5NDU3MDIzNzE3NDQzLDAuMDIwNTUzNDU5OTE0NzYzMDk1XSwib3RoZXJPZmZpY2VyUGF5R3Jvd3RoVG9CYXNlIjpbMCwwLjA4XSwib3RoZXJIZWFkY291bnRHcm93dGhUb0Jhc2UiOlswLjAzOTE2NjY2NjY2NjY2NjY4LDAuMDQyNTAwMDAwMDAwMDAwMDldLCJvdGhlclNnYUltcHJvdmVtZW50VG9CYXNlIjpbMCwwXSwicHJvamVjdFNhbGVzR3Jvd3RoIjpbMC4xNSwwLjNdLCJvdGhlclNhbGVzR3Jvd3RoIjpbMC4wNjA3NjA4Njk1NjUyMTcxOSwwLjA2NDM4NDA1Nzk3MTAxNDUzXSwicHJvamVjdENvZ3NJbXByb3ZlbWVudEFmdGVyQmFzZSI6WzAsMC4wM10sIm90aGVyQ29nc0ltcHJvdmVtZW50IjpbMC4wMDUsMC4wMDUxMzQ1NzU1NjkzNTgxOTc1XSwicHJvamVjdFBheUdyb3d0aCI6WzAuMDUsMC4xXSwib3RoZXJQYXlHcm93dGgiOlswLjAyNDEzOTQ1NzAyMzcxNzQ0NCwwLjAyNTU1MzQ1OTkxNDc2MzA5Nl0sIm90aGVyT2ZmaWNlclBheUdyb3d0aCI6WzAsMC4wOF0sInByb2plY3RIZWFkY291bnRHcm93dGgiOlswLDAuMDhdLCJvdGhlckhlYWRjb3VudEdyb3d0aCI6WzAuMDQ0MTY2NjY2NjY2NjY2NjgsMC4wNDc1MDAwMDAwMDAwMDAwOV0sInByb2plY3RTZ2FSYXRlRW5kIjpbMC4wODQ5OTk5OTk5OTk5OTk5OSwwLjEzNV0sIm90aGVyU2dhUmF0ZUVuZCI6WzAuMDg5Mjg1NzE0Mjg1NzE0MjcsMC4xMTkyODU3MTQyODU3MTQyN10sInByb2plY3RPZmZpY2VyUGF5R3Jvd3RoIjpbMC4wNDI2MzE1Nzg5NDczNjgzNiwwLjA2NTU1NTU1NTU1NTU1NTU4XSwidXNlZnVsTGlmZSI6WzUsMjBdLCJpbnZlc3RtZW50IjpbMTUsMjAwXSwic3Vic2lkeSI6WzEsNTBdLCJsb2NhbEJlbmNobWFyayI6WzAsMTAwXX0sInRhcmdldHMiOnsiY29tcGFueVNhbGVzQ2FnciI6eyJ2YWx1ZSI6MTUsIm1heCI6MzUsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55U2FsZXNJbmNyZWFzZSI6eyJ2YWx1ZSI6ODIuNCwibWF4IjoyNTIuNjksInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJjb21wYW55UGF5U2NoZWR1bGUiOnsidmFsdWUiOjIsIm1heCI6NywicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc1NoYXJlIjp7InZhbHVlIjo2MCwibWF4Ijo5NSwicG9saWN5IjoibW9uaXRvciIsIndlaWdodCI6MX0sInByb2plY3RTYWxlc0NhZ3IiOnsidmFsdWUiOjIyLCJtYXgiOjM1LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwicHJvamVjdFNhbGVzSW5jcmVhc2UiOnsidmFsdWUiOjc0LjgsIm1heCI6MTM2Ljg0LCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibGFib3JQcm9kdWN0aXZpdHlDYWdyIjp7InZhbHVlIjoyMSwibWF4IjozNSwicG9saWN5Ijoic29mdCIsIndlaWdodCI6MX0sInZhbHVlQWRkZWRJbmNyZWFzZSI6eyJ2YWx1ZSI6MTguNzgsIm1heCI6MzMuNDMsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUNhZ3IiOnsidmFsdWUiOjcsIm1heCI6MTAsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJlbXBsb3llZVBheUluY3JlYXNlIjp7InZhbHVlIjoyLjg1LCJtYXgiOjMuNzQsInBvbGljeSI6InNvZnQiLCJ3ZWlnaHQiOjF9LCJpbnZlc3RtZW50U2FsZXNSYXRpbyI6eyJ2YWx1ZSI6MTUsIm1heCI6NzAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJ2YWx1ZUFkZGVkU3Vic2lkeVJhdGlvIjp7InZhbHVlIjoyMTMsIm1heCI6MzUwLCJwb2xpY3kiOiJzb2Z0Iiwid2VpZ2h0IjoxfSwibG9jYWxCZW5jaG1hcmsiOnsidmFsdWUiOjIzLCJtYXgiOjQwLCJwb2xpY3kiOiJtb25pdG9yIiwid2VpZ2h0IjoxfSwib2ZmaWNlclBheUNhZ3IiOnsidmFsdWUiOjYsIm1heCI6MTAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9LCJvZmZpY2VyUGF5SW5jcmVhc2UiOnsidmFsdWUiOjAsInBvbGljeSI6Im1vbml0b3IiLCJ3ZWlnaHQiOjF9fSwiZm9yZWNhc3RPdmVycmlkZXMiOnsiMjAyOTpvdGhlcjpzYWxlcyI6ODUuMTMsIjIwMjk6cHJvamVjdDo3LTgiOjcuOX0sImZ1dHVyZUlucHV0QmFzaXMiOiJvdGhlciIsImlucHV0VmFsdWVzIjp7ImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xIjoxMzYuNCwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTMiOjkyLjc1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItNCI6MC43MywiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTciOjMyLjY1LCJhY3R1YWw6Y29tcGFueToyMDIzOjItOSI6MC44MiwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTEwIjowLjA5LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTIiOjExLjY3LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTMiOjAuNjIsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0xNCI6Mi40NSwiYWN0dWFsOmNvbXBhbnk6MjAyMzoyLTE1IjowLjY0LCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTgiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMTkiOjEwLjczLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjAiOjcuNTEsImFjdHVhbDpjb21wYW55OjIwMjM6Mi0yNyI6MjEwLCJhY3R1YWw6Y29tcGFueToyMDIzOjItMjgiOjUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xIjo3MiwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTQiOjIzLjA0LCJhY3R1YWw6cHJvamVjdDoyMDIzOjctNiI6Ni43OCwiYWN0dWFsOnByb2plY3Q6MjAyMzo3LTgiOjUuMTksImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny05IjowLjM2LCJhY3R1YWw6cHJvamVjdDoyMDIzOlAyLTQiOjAuNDUsImFjdHVhbDpwcm9qZWN0OjIwMjM6UDItMTQiOjEuMzUsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xMyI6OTAsImFjdHVhbDpwcm9qZWN0OjIwMjM6Ny0xNCI6MiwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEiOjE0My4yLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMyI6OTcuMzgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi00IjowLjc2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItNyI6MzQuNTIsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi05IjowLjg2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEyIjoxMi40NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTEzIjowLjY2LCJhY3R1YWw6Y29tcGFueToyMDI0OjItMTQiOjIuNTgsImFjdHVhbDpjb21wYW55OjIwMjQ6Mi0xNSI6MC42NywiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE4IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTE5IjoxMS4wMSwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTIwIjo3LjcxLCJhY3R1YWw6Y29tcGFueToyMDI0OjItMjciOjIyMCwiYWN0dWFsOmNvbXBhbnk6MjAyNDoyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMSI6NzYsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny00IjoyNC4zMiwiYWN0dWFsOnByb2plY3Q6MjAyNDo3LTYiOjcuMDQsImFjdHVhbDpwcm9qZWN0OjIwMjQ6Ny04Ijo1LjU5LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctOSI6MC4zOCwiYWN0dWFsOnByb2plY3Q6MjAyNDpQMi00IjowLjQ3LCJhY3R1YWw6cHJvamVjdDoyMDI0OlAyLTE0IjoxLjQzLCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTMiOjk1LCJhY3R1YWw6cHJvamVjdDoyMDI0OjctMTQiOjIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xIjoxNTAsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0zIjoxMDIsImFjdHVhbDpjb21wYW55OjIwMjU6Mi00IjowLjgsImFjdHVhbDpjb21wYW55OjIwMjU6Mi03IjozNi40LCJhY3R1YWw6Y29tcGFueToyMDI1OjItOSI6MC45LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTAiOjAuMSwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTEyIjoxMy4zLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTMiOjAuNywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTE0IjoyLjcsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xNSI6MC43LCJhY3R1YWw6Y29tcGFueToyMDI1OjItMTgiOjExLjMsImFjdHVhbDpjb21wYW55OjIwMjU6Mi0xOSI6MTEuMywiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTIwIjo3LjkxLCJhY3R1YWw6Y29tcGFueToyMDI1OjItMjciOjIzMCwiYWN0dWFsOmNvbXBhbnk6MjAyNToyLTI4Ijo1LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctMSI6ODAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny00IjoyNS42LCJhY3R1YWw6cHJvamVjdDoyMDI1OjctNiI6Ny4zLCJhY3R1YWw6cHJvamVjdDoyMDI1OjctOCI6NiwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTkiOjAuNCwiYWN0dWFsOnByb2plY3Q6MjAyNTpQMi00IjowLjUsImFjdHVhbDpwcm9qZWN0OjIwMjU6UDItMTQiOjEuNSwiYWN0dWFsOnByb2plY3Q6MjAyNTo3LTEzIjoxMDAsImFjdHVhbDpwcm9qZWN0OjIwMjU6Ny0xNCI6MiwiYmFsYW5jZS1zaGVldDoyMDIzOmFzc2V0cyI6MTMyLCJiYWxhbmNlLXNoZWV0OjIwMjM6Y3VycmVudEFzc2V0cyI6NjcsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXNoIjoyNCwiYmFsYW5jZS1zaGVldDoyMDIzOmZpeGVkQXNzZXRzIjo2NSwiYmFsYW5jZS1zaGVldDoyMDIzOnRhbmdpYmxlQXNzZXRzIjo1MywiYmFsYW5jZS1zaGVldDoyMDIzOmJ1aWxkaW5ncyI6MTksImJhbGFuY2Utc2hlZXQ6MjAyMzptYWNoaW5lcnkiOjI0LCJiYWxhbmNlLXNoZWV0OjIwMjM6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzppbnRhbmdpYmxlQXNzZXRzIjo3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c29mdHdhcmUiOjUsImJhbGFuY2Utc2hlZXQ6MjAyMzpsaWFiaWxpdGllcyI6NzUsImJhbGFuY2Utc2hlZXQ6MjAyMzpjdXJyZW50TGlhYmlsaXRpZXMiOjM5LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyMzpmaXhlZExpYWJpbGl0aWVzIjozNiwiYmFsYW5jZS1zaGVldDoyMDIzOmxvbmdUZXJtRGVidCI6MjksImJhbGFuY2Utc2hlZXQ6MjAyMzpuZXRBc3NldHMiOjU3LCJiYWxhbmNlLXNoZWV0OjIwMjM6c2hhcmVob2xkZXJFcXVpdHkiOjU0LCJiYWxhbmNlLXNoZWV0OjIwMjM6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyMzpjYXBleCI6NSwiYmFsYW5jZS1zaGVldDoyMDI0OmFzc2V0cyI6MTQzLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y3VycmVudEFzc2V0cyI6NzIsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXNoIjoyNSwiYmFsYW5jZS1zaGVldDoyMDI0OmZpeGVkQXNzZXRzIjo3MSwiYmFsYW5jZS1zaGVldDoyMDI0OnRhbmdpYmxlQXNzZXRzIjo1OCwiYmFsYW5jZS1zaGVldDoyMDI0OmJ1aWxkaW5ncyI6MjAsImJhbGFuY2Utc2hlZXQ6MjAyNDptYWNoaW5lcnkiOjI4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDppbnRhbmdpYmxlQXNzZXRzIjo4LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c29mdHdhcmUiOjYsImJhbGFuY2Utc2hlZXQ6MjAyNDpsaWFiaWxpdGllcyI6NzksImJhbGFuY2Utc2hlZXQ6MjAyNDpjdXJyZW50TGlhYmlsaXRpZXMiOjQxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hvcnRUZXJtRGVidCI6MTIsImJhbGFuY2Utc2hlZXQ6MjAyNDpmaXhlZExpYWJpbGl0aWVzIjozOCwiYmFsYW5jZS1zaGVldDoyMDI0OmxvbmdUZXJtRGVidCI6MzEsImJhbGFuY2Utc2hlZXQ6MjAyNDpuZXRBc3NldHMiOjY0LCJiYWxhbmNlLXNoZWV0OjIwMjQ6c2hhcmVob2xkZXJFcXVpdHkiOjYxLCJiYWxhbmNlLXNoZWV0OjIwMjQ6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNDpjYXBleCI6OCwiYmFsYW5jZS1zaGVldDoyMDI1OmFzc2V0cyI6MTU2LCJiYWxhbmNlLXNoZWV0OjIwMjU6Y3VycmVudEFzc2V0cyI6NzgsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXNoIjoyNywiYmFsYW5jZS1zaGVldDoyMDI1OmZpeGVkQXNzZXRzIjo3OCwiYmFsYW5jZS1zaGVldDoyMDI1OnRhbmdpYmxlQXNzZXRzIjo2NCwiYmFsYW5jZS1zaGVldDoyMDI1OmJ1aWxkaW5ncyI6MjIsImJhbGFuY2Utc2hlZXQ6MjAyNTptYWNoaW5lcnkiOjMyLCJiYWxhbmNlLXNoZWV0OjIwMjU6bGFuZCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTppbnRhbmdpYmxlQXNzZXRzIjo5LCJiYWxhbmNlLXNoZWV0OjIwMjU6c29mdHdhcmUiOjcsImJhbGFuY2Utc2hlZXQ6MjAyNTpsaWFiaWxpdGllcyI6ODMsImJhbGFuY2Utc2hlZXQ6MjAyNTpjdXJyZW50TGlhYmlsaXRpZXMiOjQzLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hvcnRUZXJtRGVidCI6MTEsImJhbGFuY2Utc2hlZXQ6MjAyNTpmaXhlZExpYWJpbGl0aWVzIjo0MCwiYmFsYW5jZS1zaGVldDoyMDI1OmxvbmdUZXJtRGVidCI6MzIsImJhbGFuY2Utc2hlZXQ6MjAyNTpuZXRBc3NldHMiOjczLCJiYWxhbmNlLXNoZWV0OjIwMjU6c2hhcmVob2xkZXJFcXVpdHkiOjcwLCJiYWxhbmNlLXNoZWV0OjIwMjU6Y2FwaXRhbCI6MTAsImJhbGFuY2Utc2hlZXQ6MjAyNTpjYXBleCI6MTAsImRyaXZlcjpwcm9qZWN0TWFya2V0R3Jvd3RoIjowLjA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdE1hcmtldEdyb3d0aDowIjotMC4wNSwiZHJpdmVyLXJhbmdlOnByb2plY3RNYXJrZXRHcm93dGg6MSI6MC4zLCJkcml2ZXI6cHJvamVjdENvZ3NSYXRlV2hlblNhbGVzWmVybyI6MC42OCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RDb2dzUmF0ZVdoZW5TYWxlc1plcm86MSI6MC45OSwiZHJpdmVyOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvIjowLjY4LCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzUmF0ZVdoZW5TYWxlc1plcm86MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc1JhdGVXaGVuU2FsZXNaZXJvOjEiOjAuOTksImRyaXZlcjpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZSI6MC45NSwiZHJpdmVyLXJhbmdlOnByb2plY3RFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0RW1wbG95ZWVTYWxhcnlTaGFyZToxIjoxLCJkcml2ZXI6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlIjowLjk1LCJkcml2ZXItcmFuZ2U6b3RoZXJFbXBsb3llZVNhbGFyeVNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlckVtcGxveWVlU2FsYXJ5U2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmUiOjAuOSwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOnByb2plY3RPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOm90aGVyT2ZmaWNlckNvbXBlbnNhdGlvblNoYXJlIjowLjksImRyaXZlci1yYW5nZTpvdGhlck9mZmljZXJDb21wZW5zYXRpb25TaGFyZTowIjowLCJkcml2ZXItcmFuZ2U6b3RoZXJPZmZpY2VyQ29tcGVuc2F0aW9uU2hhcmU6MSI6MSwiZHJpdmVyOnByb2plY3RDb2dzRGVwcmVjaWF0aW9uU2hhcmUiOjAuMjUsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0Q29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpvdGhlckNvZ3NEZXByZWNpYXRpb25TaGFyZSI6MC4yLCJkcml2ZXItcmFuZ2U6b3RoZXJDb2dzRGVwcmVjaWF0aW9uU2hhcmU6MCI6MCwiZHJpdmVyLXJhbmdlOm90aGVyQ29nc0RlcHJlY2lhdGlvblNoYXJlOjEiOjEsImRyaXZlcjpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGUiOjAuMDA1LCJkcml2ZXItcmFuZ2U6cHJvamVjdFJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpwcm9qZWN0UmVzZWFyY2hEZXZlbG9wbWVudFJhdGU6MSI6MC4zLCJkcml2ZXI6b3RoZXJSZXNlYXJjaERldmVsb3BtZW50UmF0ZSI6MC4wMDQsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjAiOjAsImRyaXZlci1yYW5nZTpvdGhlclJlc2VhcmNoRGV2ZWxvcG1lbnRSYXRlOjEiOjAuMywiZHJpdmVyOnByb2plY3ROb25PcGVyYXRpbmdSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdE5vbk9wZXJhdGluZ1JhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOnByb2plY3ROb25PcGVyYXRpbmdSYXRlOjEiOjAuNSwiZHJpdmVyOm90aGVyTm9uT3BlcmF0aW5nUmF0ZSI6LTAuMDA1LCJkcml2ZXItcmFuZ2U6b3RoZXJOb25PcGVyYXRpbmdSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpvdGhlck5vbk9wZXJhdGluZ1JhdGU6MSI6MC41LCJkcml2ZXI6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlIjowLCJkcml2ZXItcmFuZ2U6cHJvamVjdEV4dHJhb3JkaW5hcnlSYXRlOjAiOi0wLjUsImRyaXZlci1yYW5nZTpwcm9qZWN0RXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6b3RoZXJFeHRyYW9yZGluYXJ5UmF0ZSI6MCwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MCI6LTAuNSwiZHJpdmVyLXJhbmdlOm90aGVyRXh0cmFvcmRpbmFyeVJhdGU6MSI6MC41LCJkcml2ZXI6ZWZmZWN0aXZlVGF4UmF0ZSI6MC4zLCJkcml2ZXItcmFuZ2U6Z